--- a/Results/Phase 2/Ammonia/ammonia acidification results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia acidification results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004391607079443107</v>
+        <v>0.004391607079443093</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003817758413578878</v>
+        <v>0.003817758413578879</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004328983070835576</v>
+        <v>0.004328983070835566</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004261665380936314</v>
+        <v>0.004261665380936307</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00427189443694961</v>
+        <v>0.0042718944369496</v>
       </c>
       <c r="G2" t="n">
-        <v>0.004483170412482494</v>
+        <v>0.004483170412482487</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004284777811167432</v>
+        <v>0.00428477781116742</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004343903144453759</v>
+        <v>0.00434390314445376</v>
       </c>
       <c r="J2" t="n">
         <v>0.004387487349788448</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004429344019466958</v>
+        <v>0.004429344019466951</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004529332524502835</v>
+        <v>0.004529332524502838</v>
       </c>
       <c r="M2" t="n">
         <v>0.004566518047425531</v>
       </c>
       <c r="N2" t="n">
-        <v>0.004347888305800266</v>
+        <v>0.00434788830580026</v>
       </c>
       <c r="O2" t="n">
-        <v>0.00632116500269313</v>
+        <v>0.006321165002693125</v>
       </c>
       <c r="P2" t="n">
-        <v>0.004363648592234841</v>
+        <v>0.004363648592234835</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.004260613584596762</v>
+        <v>0.004260613584596751</v>
       </c>
       <c r="R2" t="n">
-        <v>0.004258289630751357</v>
+        <v>0.004258289630751345</v>
       </c>
       <c r="S2" t="n">
-        <v>0.004389043216454781</v>
+        <v>0.00438904321645477</v>
       </c>
       <c r="T2" t="n">
-        <v>0.004349277569147204</v>
+        <v>0.004349277569147199</v>
       </c>
       <c r="U2" t="n">
-        <v>0.004569524901442988</v>
+        <v>0.004569524901442994</v>
       </c>
       <c r="V2" t="n">
-        <v>0.004239589808022171</v>
+        <v>0.004239589808022167</v>
       </c>
       <c r="W2" t="n">
-        <v>0.00438684981371568</v>
+        <v>0.004386849813715688</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004322412777297827</v>
+        <v>0.004322412777297829</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.004380180051790823</v>
+        <v>0.004380180051790813</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.005382217050810934</v>
+        <v>0.00538221705081093</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.004380835959910188</v>
+        <v>0.004380835959910193</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.004648172247065749</v>
+        <v>0.004648172247065748</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005505825127271275</v>
+        <v>0.005505825127271284</v>
       </c>
       <c r="C3" t="n">
         <v>0.003511853972299631</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005069462781791013</v>
+        <v>0.005069462781791015</v>
       </c>
       <c r="E3" t="n">
-        <v>0.004583443421235253</v>
+        <v>0.004583443421235257</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004662039210097947</v>
+        <v>0.00466203921009795</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006160106129368032</v>
+        <v>0.00616010612936803</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004755470764412017</v>
+        <v>0.004755470764412031</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005177228661488801</v>
+        <v>0.005177228661488805</v>
       </c>
       <c r="J3" t="n">
-        <v>0.005481457501273485</v>
+        <v>0.005481457501273489</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005786953426973665</v>
+        <v>0.005786953426973655</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00649494321508932</v>
+        <v>0.006494943215089317</v>
       </c>
       <c r="M3" t="n">
-        <v>0.006765988943800492</v>
+        <v>0.006765988943800488</v>
       </c>
       <c r="N3" t="n">
-        <v>0.005202371793799051</v>
+        <v>0.005202371793799044</v>
       </c>
       <c r="O3" t="n">
         <v>0.00857448678154976</v>
       </c>
       <c r="P3" t="n">
-        <v>0.005308280957866633</v>
+        <v>0.005308280957866631</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.004579058232816325</v>
+        <v>0.004579058232816326</v>
       </c>
       <c r="R3" t="n">
-        <v>0.004564542278836812</v>
+        <v>0.004564542278836817</v>
       </c>
       <c r="S3" t="n">
-        <v>0.005490314378875901</v>
+        <v>0.005490314378875899</v>
       </c>
       <c r="T3" t="n">
-        <v>0.005215079107630201</v>
+        <v>0.005215079107630199</v>
       </c>
       <c r="U3" t="n">
         <v>0.006489667482195008</v>
       </c>
       <c r="V3" t="n">
-        <v>0.004425581133996605</v>
+        <v>0.004425581133996619</v>
       </c>
       <c r="W3" t="n">
         <v>0.005403709112101868</v>
       </c>
       <c r="X3" t="n">
-        <v>0.005021488509952069</v>
+        <v>0.005021488509952065</v>
       </c>
       <c r="Y3" t="n">
         <v>0.005431502357568885</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006703440019232663</v>
+        <v>0.00670344001923266</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.005436719880551142</v>
+        <v>0.005436719880551138</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.007343850550428903</v>
+        <v>0.007343850550428897</v>
       </c>
     </row>
     <row r="4">
@@ -765,22 +765,22 @@
         <v>0.01057922498495065</v>
       </c>
       <c r="C4" t="n">
-        <v>0.008407145210441275</v>
+        <v>0.008407145210441273</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009871857999261305</v>
+        <v>0.009871857999261303</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009111473724181857</v>
+        <v>0.009111473724181855</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009227015617450204</v>
+        <v>0.009227015617450205</v>
       </c>
       <c r="G4" t="n">
         <v>0.0116134749528447</v>
       </c>
       <c r="H4" t="n">
-        <v>0.009372539255885527</v>
+        <v>0.009372539255885525</v>
       </c>
       <c r="I4" t="n">
         <v>0.01004038709435169</v>
@@ -792,7 +792,7 @@
         <v>0.01100548108237016</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01213489724373528</v>
+        <v>0.01213489724373527</v>
       </c>
       <c r="M4" t="n">
         <v>0.01254378360919656</v>
@@ -807,13 +807,13 @@
         <v>0.01026342101039378</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.009099593200676296</v>
+        <v>0.009099593200676295</v>
       </c>
       <c r="R4" t="n">
         <v>0.009073343072920865</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01055026497306222</v>
+        <v>0.01055026497306221</v>
       </c>
       <c r="T4" t="n">
         <v>0.01010109369362163</v>
@@ -828,13 +828,13 @@
         <v>0.0103704836556645</v>
       </c>
       <c r="X4" t="n">
-        <v>0.009797643511268214</v>
+        <v>0.00979764351126821</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.01041359168895358</v>
+        <v>0.01041359168895357</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.009670395352647293</v>
+        <v>0.009670395352647286</v>
       </c>
       <c r="AA4" t="n">
         <v>0.01045756023486664</v>
@@ -850,25 +850,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0594322269569774</v>
+        <v>0.05943222695697745</v>
       </c>
       <c r="C5" t="n">
         <v>0.02017587652762347</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05148054578874676</v>
+        <v>0.05148054578874679</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03285772109074126</v>
+        <v>0.03285772109074125</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03850720200791591</v>
+        <v>0.03850720200791583</v>
       </c>
       <c r="G5" t="n">
-        <v>0.08072869676011513</v>
+        <v>0.08072869676011507</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04231872197073494</v>
+        <v>0.04231872197073493</v>
       </c>
       <c r="I5" t="n">
         <v>0.05563546596524061</v>
@@ -877,58 +877,58 @@
         <v>0.06148378269833901</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0750281729656683</v>
+        <v>0.07502817296566838</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09442411994233935</v>
+        <v>0.09442411994233939</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1096145088787171</v>
+        <v>0.1096145088787172</v>
       </c>
       <c r="N5" t="n">
-        <v>0.08804433079195338</v>
+        <v>0.08804433079195326</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05395259327934611</v>
+        <v>0.05395259327934612</v>
       </c>
       <c r="P5" t="n">
-        <v>0.05425949940561927</v>
+        <v>0.05425949940561923</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03447375601992615</v>
+        <v>0.03447375601992612</v>
       </c>
       <c r="R5" t="n">
-        <v>0.03517556984416991</v>
+        <v>0.03517556984416989</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06050588520617564</v>
+        <v>0.0605058852061755</v>
       </c>
       <c r="T5" t="n">
-        <v>0.05655657701532821</v>
+        <v>0.05655657701532817</v>
       </c>
       <c r="U5" t="n">
-        <v>0.08995188373592472</v>
+        <v>0.08995188373592461</v>
       </c>
       <c r="V5" t="n">
         <v>0.02762661927586626</v>
       </c>
       <c r="W5" t="n">
-        <v>0.05946359159340565</v>
+        <v>0.0594635915934056</v>
       </c>
       <c r="X5" t="n">
-        <v>0.04934308229550463</v>
+        <v>0.0493430822955046</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0611315956952454</v>
+        <v>0.06113159569524531</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.04342653869740346</v>
+        <v>0.04342653869740336</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.06159952698547085</v>
+        <v>0.06159952698547083</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1328484431906183</v>
+        <v>0.1328484431906181</v>
       </c>
     </row>
     <row r="6">
@@ -938,82 +938,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01093550891421795</v>
+        <v>0.0119911352975019</v>
       </c>
       <c r="C6" t="n">
         <v>0.00981905552299254</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01022814192852862</v>
+        <v>0.0102281419285286</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01052338403673312</v>
+        <v>0.009467757653449144</v>
       </c>
       <c r="F6" t="n">
-        <v>0.009583299546717518</v>
+        <v>0.01063892593000147</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01196975888211201</v>
+        <v>0.01302538526539597</v>
       </c>
       <c r="H6" t="n">
         <v>0.01078444956843679</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01145229740690296</v>
+        <v>0.01039667102361897</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01088502571291157</v>
+        <v>0.01194065209619554</v>
       </c>
       <c r="K6" t="n">
         <v>0.01136176501163745</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01354680755628654</v>
+        <v>0.01249118117300257</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01290006753846386</v>
+        <v>0.01290006753846385</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01044664206167215</v>
+        <v>0.01044664206167219</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01175818808380583</v>
+        <v>0.01175818808380584</v>
       </c>
       <c r="P6" t="n">
         <v>0.01167965711469463</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.009455877129943606</v>
+        <v>0.009455877129943583</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01048525338547213</v>
+        <v>0.009429627002188154</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01196217528561348</v>
+        <v>0.01196217528561347</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01045737762288894</v>
+        <v>0.01045737762288891</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01234923819826391</v>
+        <v>0.01234923819826389</v>
       </c>
       <c r="V6" t="n">
         <v>0.01024733108197831</v>
       </c>
       <c r="W6" t="n">
-        <v>0.01076404435500339</v>
+        <v>0.01178671966707292</v>
       </c>
       <c r="X6" t="n">
         <v>0.01120955382381947</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0108308192596445</v>
+        <v>0.01083081925964454</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0100266792819146</v>
+        <v>0.01002667928191458</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0118694705474179</v>
+        <v>0.01081384416413393</v>
       </c>
       <c r="AB6" t="n">
         <v>0.0138249509946607</v>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01142114152199847</v>
+        <v>0.01142114152199846</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0092490617474891</v>
+        <v>0.009249061747489098</v>
       </c>
       <c r="D7" t="n">
         <v>0.01071377453630913</v>
@@ -1071,19 +1071,19 @@
         <v>0.0111053099725692</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.009941509737724116</v>
+        <v>0.009941509737724117</v>
       </c>
       <c r="R7" t="n">
-        <v>0.009915259609968686</v>
+        <v>0.009915259609968684</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01139218151011004</v>
+        <v>0.01139218151011003</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01094301023066945</v>
+        <v>0.01094301023066944</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01283385089095072</v>
+        <v>0.01283385089095073</v>
       </c>
       <c r="V7" t="n">
         <v>0.009677337306474873</v>
@@ -1104,7 +1104,7 @@
         <v>0.01129947677191446</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01428299511138279</v>
+        <v>0.01428299511138278</v>
       </c>
     </row>
     <row r="8">
@@ -1114,40 +1114,40 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01299383581141073</v>
+        <v>0.01299383581141072</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01250309083858721</v>
+        <v>0.01250309083858722</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01396780362740725</v>
+        <v>0.01396780362740726</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01320741935232779</v>
+        <v>0.01231215816672619</v>
       </c>
       <c r="F8" t="n">
         <v>0.01190355875582718</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01570942058099064</v>
+        <v>0.01605805630499009</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01346848488403147</v>
+        <v>0.01346848488403149</v>
       </c>
       <c r="I8" t="n">
         <v>0.01413633272249763</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01462468741179022</v>
+        <v>0.01462468741179023</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01510142671051611</v>
+        <v>0.01510142671051612</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01623084287188122</v>
+        <v>0.01623084287188123</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0166397292373425</v>
+        <v>0.01663972923734238</v>
       </c>
       <c r="N8" t="n">
         <v>0.01287803120065466</v>
@@ -1162,37 +1162,37 @@
         <v>0.01118378336404161</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01316928870106681</v>
+        <v>0.01316928870106682</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01464621060120815</v>
+        <v>0.01464621060120816</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01419703932176756</v>
+        <v>0.01419703932176757</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01505357188711487</v>
+        <v>0.01526749378159184</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01293136639757299</v>
+        <v>0.01247098401689845</v>
       </c>
       <c r="W8" t="n">
         <v>0.01446675971417251</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01203593135000737</v>
+        <v>0.01203593135000738</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01621649440018977</v>
+        <v>0.01621649440018978</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01376634098079323</v>
+        <v>0.01205377452197816</v>
       </c>
       <c r="AA8" t="n">
         <v>0.01455350586301259</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01929331899367227</v>
+        <v>0.01929331899367226</v>
       </c>
     </row>
     <row r="9">
@@ -1202,25 +1202,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0140268820704704</v>
+        <v>0.01402688207047042</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01287230340009267</v>
+        <v>0.01287230340009266</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01433701618891268</v>
+        <v>0.01433701618891269</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01357663191383325</v>
+        <v>0.01334179683753518</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0136921738071016</v>
+        <v>0.01134655601178581</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0160786331424961</v>
+        <v>0.01607863317918869</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01383769744553692</v>
+        <v>0.01383769744553691</v>
       </c>
       <c r="I9" t="n">
         <v>0.01450554528400308</v>
@@ -1232,7 +1232,7 @@
         <v>0.01547063927202155</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01660005543338667</v>
+        <v>0.01660005543338666</v>
       </c>
       <c r="M9" t="n">
         <v>0.01700894179884794</v>
@@ -1241,7 +1241,7 @@
         <v>0.01455055951467663</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01514430915039636</v>
+        <v>0.01514430915039635</v>
       </c>
       <c r="P9" t="n">
         <v>0.01513911268085407</v>
@@ -1250,7 +1250,7 @@
         <v>0.01356475142702029</v>
       </c>
       <c r="R9" t="n">
-        <v>0.01353850126257225</v>
+        <v>0.01353850126257226</v>
       </c>
       <c r="S9" t="n">
         <v>0.0150154231627136</v>
@@ -1259,10 +1259,10 @@
         <v>0.01456625188327301</v>
       </c>
       <c r="U9" t="n">
-        <v>0.016458112458648</v>
+        <v>0.01645811245864799</v>
       </c>
       <c r="V9" t="n">
-        <v>0.01330057895907844</v>
+        <v>0.0144747520382415</v>
       </c>
       <c r="W9" t="n">
         <v>0.01483564184531589</v>
@@ -1274,13 +1274,13 @@
         <v>0.01491530964057703</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.01413555354229867</v>
+        <v>0.01352209087080598</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.01492271842451803</v>
+        <v>0.01492271842451802</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.01790623676398635</v>
+        <v>0.01790623676398634</v>
       </c>
     </row>
   </sheetData>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003713420773599502</v>
+        <v>0.003713420773599496</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003298393310672763</v>
+        <v>0.003298393310672761</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003719737692913644</v>
+        <v>0.00371973769291364</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003719689162554142</v>
+        <v>0.003719689162554137</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003723524963300832</v>
+        <v>0.003723524963300827</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003730133553932613</v>
+        <v>0.003730133553932607</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003721679599376591</v>
+        <v>0.003721679599376586</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003722730234166609</v>
+        <v>0.003722730234166605</v>
       </c>
       <c r="J2" t="n">
         <v>0.003735179872189336</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003732100584313305</v>
+        <v>0.003732100584313301</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003736124611386517</v>
+        <v>0.003736124611386513</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003721615464065396</v>
+        <v>0.003721615464065394</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003724275073632436</v>
+        <v>0.003724275073632431</v>
       </c>
       <c r="O2" t="n">
-        <v>0.005406754705151457</v>
+        <v>0.00540675470515146</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003728044859943883</v>
+        <v>0.003728044859943878</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003718835840116516</v>
+        <v>0.00371883584011651</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003737456002634775</v>
+        <v>0.00373745600263477</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003731970895124057</v>
+        <v>0.003731970895124054</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003722706359580102</v>
+        <v>0.003722706359580097</v>
       </c>
       <c r="U2" t="n">
         <v>0.003593286217671968</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003731272603195406</v>
+        <v>0.003731272603195401</v>
       </c>
       <c r="W2" t="n">
-        <v>0.003565222865256896</v>
+        <v>0.003565222865256889</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004135590945049441</v>
+        <v>0.00413559094504944</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003961537823240252</v>
+        <v>0.003961537823240249</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.004724616486176464</v>
+        <v>0.00472461648617646</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003764487350899711</v>
+        <v>0.003764487350899706</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.003714872630915944</v>
+        <v>0.003714872630915942</v>
       </c>
     </row>
     <row r="3">
@@ -1534,46 +1534,46 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003501493555079834</v>
+        <v>0.003501493555079836</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002834061618692766</v>
+        <v>0.002834061618692768</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003546966705219043</v>
+        <v>0.003546966705219042</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003544761105244298</v>
+        <v>0.003544761105244294</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003574106176940844</v>
+        <v>0.003574106176940842</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003620118977130854</v>
+        <v>0.003620118977130851</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003561228197813701</v>
+        <v>0.003561228197813699</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003568460765436039</v>
+        <v>0.003568460765436038</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003656512344118938</v>
+        <v>0.003656512344118931</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003634667953625596</v>
+        <v>0.003634667953625595</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003662944060899612</v>
+        <v>0.003662944060899614</v>
       </c>
       <c r="M3" t="n">
-        <v>0.003565447177186036</v>
+        <v>0.003565447177186034</v>
       </c>
       <c r="N3" t="n">
         <v>0.003579283220797366</v>
       </c>
       <c r="O3" t="n">
-        <v>0.006373998615432724</v>
+        <v>0.006373998615432726</v>
       </c>
       <c r="P3" t="n">
         <v>0.00360523472180605</v>
@@ -1582,37 +1582,37 @@
         <v>0.003540293053343459</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003674077239661175</v>
+        <v>0.003674077239661177</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003633191611233588</v>
+        <v>0.003633191611233592</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003568268645872682</v>
+        <v>0.003568268645872677</v>
       </c>
       <c r="U3" t="n">
-        <v>0.003472357971296796</v>
+        <v>0.003472357971296795</v>
       </c>
       <c r="V3" t="n">
         <v>0.003628282925322868</v>
       </c>
       <c r="W3" t="n">
-        <v>0.003395583478053737</v>
+        <v>0.003395583478053736</v>
       </c>
       <c r="X3" t="n">
-        <v>0.006510647988657268</v>
+        <v>0.006510647988657262</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.005274108278873397</v>
+        <v>0.005274108278873396</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.005264410807348635</v>
+        <v>0.005264410807348637</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.00386633776345701</v>
+        <v>0.003866337763457011</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.003516981533663204</v>
+        <v>0.003516981533663207</v>
       </c>
     </row>
     <row r="4">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.007230781795339931</v>
+        <v>0.007230781795339934</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007267632173020867</v>
+        <v>0.007267632173020865</v>
       </c>
       <c r="D4" t="n">
-        <v>0.007302134304919602</v>
+        <v>0.007302134304919604</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00730158613218398</v>
+        <v>0.007301586132183987</v>
       </c>
       <c r="F4" t="n">
-        <v>0.007344913266173377</v>
+        <v>0.007344913266173378</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007419560337461161</v>
+        <v>0.007419560337461167</v>
       </c>
       <c r="H4" t="n">
-        <v>0.007324069031739655</v>
+        <v>0.007324069031739658</v>
       </c>
       <c r="I4" t="n">
-        <v>0.007335936435008849</v>
+        <v>0.007335936435008852</v>
       </c>
       <c r="J4" t="n">
         <v>0.007473542407354657</v>
       </c>
       <c r="K4" t="n">
-        <v>0.007441778850489801</v>
+        <v>0.007441778850489805</v>
       </c>
       <c r="L4" t="n">
-        <v>0.007487232087425626</v>
+        <v>0.007487232087425629</v>
       </c>
       <c r="M4" t="n">
-        <v>0.007332415121802077</v>
+        <v>0.007332415121802082</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01158961008737806</v>
+        <v>0.01158961008737803</v>
       </c>
       <c r="O4" t="n">
-        <v>0.007391239562488076</v>
+        <v>0.00739123956248808</v>
       </c>
       <c r="P4" t="n">
-        <v>0.007395967578011819</v>
+        <v>0.007395967578011821</v>
       </c>
       <c r="Q4" t="n">
         <v>0.007291947462703255</v>
       </c>
       <c r="R4" t="n">
-        <v>0.007502270764044927</v>
+        <v>0.007502270764044931</v>
       </c>
       <c r="S4" t="n">
-        <v>0.007440313951437259</v>
+        <v>0.007440313951437261</v>
       </c>
       <c r="T4" t="n">
-        <v>0.00733566676057137</v>
+        <v>0.007335666760571371</v>
       </c>
       <c r="U4" t="n">
         <v>0.007567447708847467</v>
       </c>
       <c r="V4" t="n">
-        <v>0.007412004799961933</v>
+        <v>0.007412004799961937</v>
       </c>
       <c r="W4" t="n">
-        <v>0.007516141163222323</v>
+        <v>0.007516141163222327</v>
       </c>
       <c r="X4" t="n">
         <v>0.01199938808974082</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.01001953275154995</v>
+        <v>0.01001953275154996</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.007425740013333518</v>
+        <v>0.007425740013333521</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.007807602277731988</v>
+        <v>0.007807602277731991</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.007255488739521762</v>
+        <v>0.007255488739521767</v>
       </c>
     </row>
     <row r="5">
@@ -1719,22 +1719,22 @@
         <v>0.01071785678747123</v>
       </c>
       <c r="E5" t="n">
-        <v>0.009744659274076535</v>
+        <v>0.009744659274076542</v>
       </c>
       <c r="F5" t="n">
         <v>0.01153123661579586</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01225395915531029</v>
+        <v>0.01225395915531031</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01131413979796105</v>
+        <v>0.01131413979796106</v>
       </c>
       <c r="I5" t="n">
         <v>0.01138625647386159</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01345473998675167</v>
+        <v>0.01345473998675165</v>
       </c>
       <c r="K5" t="n">
         <v>0.01291131943906625</v>
@@ -1746,49 +1746,49 @@
         <v>0.01133142929594206</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01158961008737806</v>
+        <v>0.01158961008737803</v>
       </c>
       <c r="O5" t="n">
         <v>0.01178689718900643</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01184852774842605</v>
+        <v>0.01184852774842604</v>
       </c>
       <c r="Q5" t="n">
         <v>0.01041482315109271</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01459655795360035</v>
+        <v>0.01459655795360036</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01260000105516281</v>
+        <v>0.0126000010551628</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0113702281724972</v>
+        <v>0.01137022817249721</v>
       </c>
       <c r="U5" t="n">
-        <v>0.01487165450401677</v>
+        <v>0.01487165450401676</v>
       </c>
       <c r="V5" t="n">
-        <v>0.01247897258859761</v>
+        <v>0.01247897258859763</v>
       </c>
       <c r="W5" t="n">
-        <v>0.01436071279910378</v>
+        <v>0.01436071279910377</v>
       </c>
       <c r="X5" t="n">
-        <v>0.09157641048637431</v>
+        <v>0.09157641048637413</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.05975095408509207</v>
+        <v>0.05975095408509202</v>
       </c>
       <c r="Z5" t="n">
         <v>0.01221511381055931</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0196529783411981</v>
+        <v>0.01965297834119811</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0100086042520721</v>
+        <v>0.01000860425207211</v>
       </c>
     </row>
     <row r="6">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.008120270639152516</v>
+        <v>0.007467185762395059</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008157121016833451</v>
+        <v>0.007504036140075992</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008191623148732185</v>
+        <v>0.008191623148732194</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008191074975996568</v>
+        <v>0.00753799009923911</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00823440210998596</v>
+        <v>0.007581317233228503</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007655964304516288</v>
+        <v>0.00830904918127375</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007560472998794783</v>
+        <v>0.008213557875552243</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007572340402063971</v>
+        <v>0.008225425278821438</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00770994637440978</v>
+        <v>0.008363031251167243</v>
       </c>
       <c r="K6" t="n">
-        <v>0.008331267694302383</v>
+        <v>0.007678182817544927</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007723636054480753</v>
+        <v>0.008376720931238216</v>
       </c>
       <c r="M6" t="n">
-        <v>0.007568819088857204</v>
+        <v>0.008221903965614671</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01158961008737806</v>
+        <v>0.01158961008737803</v>
       </c>
       <c r="O6" t="n">
-        <v>0.008291237360358427</v>
+        <v>0.008291237360358431</v>
       </c>
       <c r="P6" t="n">
-        <v>0.007617257777930834</v>
+        <v>0.008290209905718538</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.008181436306515842</v>
+        <v>0.008181436306515844</v>
       </c>
       <c r="R6" t="n">
-        <v>0.007738674731100055</v>
+        <v>0.00839175960785752</v>
       </c>
       <c r="S6" t="n">
-        <v>0.007676717918492386</v>
+        <v>0.008329802795249849</v>
       </c>
       <c r="T6" t="n">
-        <v>0.008225155604383952</v>
+        <v>0.007572070727626494</v>
       </c>
       <c r="U6" t="n">
-        <v>0.007817696934866754</v>
+        <v>0.008470781811624218</v>
       </c>
       <c r="V6" t="n">
-        <v>0.007648408767017058</v>
+        <v>0.008301493643774523</v>
       </c>
       <c r="W6" t="n">
-        <v>0.007773399610189625</v>
+        <v>0.007773399610189626</v>
       </c>
       <c r="X6" t="n">
         <v>0.01223579205679596</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01029170359901404</v>
+        <v>0.01029170359901406</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.008315228857146103</v>
+        <v>0.007662143980388644</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.00804400624478711</v>
+        <v>0.008044006244787112</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.007491694594443665</v>
+        <v>0.007491694594443667</v>
       </c>
     </row>
     <row r="7">
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007771520560952806</v>
+        <v>0.007771520560952809</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007808370938633746</v>
+        <v>0.007808370938633743</v>
       </c>
       <c r="D7" t="n">
         <v>0.007842873070532478</v>
@@ -1898,49 +1898,49 @@
         <v>0.007842324897796859</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007885652031786252</v>
+        <v>0.007885652031786254</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007960299103074041</v>
+        <v>0.007960299103074045</v>
       </c>
       <c r="H7" t="n">
         <v>0.007864807797352534</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007876675200621724</v>
+        <v>0.007876675200621722</v>
       </c>
       <c r="J7" t="n">
         <v>0.008014281172967531</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007982517616102679</v>
+        <v>0.007982517616102681</v>
       </c>
       <c r="L7" t="n">
-        <v>0.008027970853038503</v>
+        <v>0.008027970853038505</v>
       </c>
       <c r="M7" t="n">
         <v>0.007873153887414955</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01158961008737806</v>
+        <v>0.01158961008737803</v>
       </c>
       <c r="O7" t="n">
         <v>0.007931956929167426</v>
       </c>
       <c r="P7" t="n">
-        <v>0.007936684944691165</v>
+        <v>0.007936684944691168</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.00783268622831613</v>
+        <v>0.007832686228316128</v>
       </c>
       <c r="R7" t="n">
         <v>0.008043009529657802</v>
       </c>
       <c r="S7" t="n">
-        <v>0.007981052717050137</v>
+        <v>0.007981052717050135</v>
       </c>
       <c r="T7" t="n">
-        <v>0.007876405526184245</v>
+        <v>0.007876405526184243</v>
       </c>
       <c r="U7" t="n">
         <v>0.00812069575906061</v>
@@ -1949,22 +1949,22 @@
         <v>0.007952743565574811</v>
       </c>
       <c r="W7" t="n">
-        <v>0.008056879928835199</v>
+        <v>0.008056879928835201</v>
       </c>
       <c r="X7" t="n">
         <v>0.01254012685535369</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01057411677612699</v>
+        <v>0.010574116776127</v>
       </c>
       <c r="Z7" t="n">
         <v>0.007966478778946391</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.008348341043344859</v>
+        <v>0.008348341043344863</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.007796227505134638</v>
+        <v>0.007796227505134643</v>
       </c>
     </row>
     <row r="8">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.008966591875286692</v>
+        <v>0.008966591875286704</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0101896426818664</v>
+        <v>0.01018964268186641</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01022414481376512</v>
+        <v>0.01022414481376514</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01022359664102952</v>
+        <v>0.009591979903369173</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009265519509523651</v>
+        <v>0.009265519509523652</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01034157084630669</v>
+        <v>0.01058753723261362</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01024607954058518</v>
+        <v>0.01024607954058519</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01025794694385438</v>
+        <v>0.01025794694385439</v>
       </c>
       <c r="J8" t="n">
         <v>0.01039555291620019</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01036378935933533</v>
+        <v>0.01036378935933534</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01040924259627115</v>
+        <v>0.01040924259627116</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01025442563064761</v>
+        <v>0.01025442563064744</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01158961008737806</v>
+        <v>0.01158961008737803</v>
       </c>
       <c r="O8" t="n">
-        <v>0.009646433914413928</v>
+        <v>0.009646433914413931</v>
       </c>
       <c r="P8" t="n">
-        <v>0.00958922208787694</v>
+        <v>0.009589222087876947</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.008794642084674929</v>
+        <v>0.008794642084674936</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01042428127289046</v>
+        <v>0.01042428127289047</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01036232446028279</v>
+        <v>0.0103623244602828</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01025767726941689</v>
+        <v>0.01025767726941691</v>
       </c>
       <c r="U8" t="n">
-        <v>0.009772420891444433</v>
+        <v>0.009923316115652005</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01033401530880746</v>
+        <v>0.01000868517930753</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01043838479442102</v>
+        <v>0.01043838479442103</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01361080033802521</v>
+        <v>0.01361080033802522</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0141330577978753</v>
+        <v>0.01413305779787531</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01034775052217905</v>
+        <v>0.009139515811320019</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01072961278657752</v>
+        <v>0.01072961278657753</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01141658478479814</v>
+        <v>0.01141658478479816</v>
       </c>
     </row>
     <row r="9">
@@ -2062,49 +2062,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008626918653870497</v>
+        <v>0.008626918653870495</v>
       </c>
       <c r="C9" t="n">
         <v>0.009086128438443284</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00912063057034202</v>
+        <v>0.009120630570342021</v>
       </c>
       <c r="E9" t="n">
-        <v>0.009120082397606404</v>
+        <v>0.009022603719737328</v>
       </c>
       <c r="F9" t="n">
-        <v>0.009163409531595801</v>
+        <v>0.008189755570558548</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00923805660288358</v>
+        <v>0.009238056798499985</v>
       </c>
       <c r="H9" t="n">
         <v>0.009142565297162076</v>
       </c>
       <c r="I9" t="n">
-        <v>0.009154432700431269</v>
+        <v>0.009154432700431267</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009292038672777078</v>
+        <v>0.009292038672777076</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009260275115912221</v>
+        <v>0.009260275115912219</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009305728352848045</v>
+        <v>0.009305728352848047</v>
       </c>
       <c r="M9" t="n">
         <v>0.009150911387224498</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01158961008737806</v>
+        <v>0.01158961008737803</v>
       </c>
       <c r="O9" t="n">
-        <v>0.009349705442765442</v>
+        <v>0.009349705442765446</v>
       </c>
       <c r="P9" t="n">
-        <v>0.009384874405502754</v>
+        <v>0.009384874405502753</v>
       </c>
       <c r="Q9" t="n">
         <v>0.009110443923742086</v>
@@ -2113,16 +2113,16 @@
         <v>0.009320767029467346</v>
       </c>
       <c r="S9" t="n">
-        <v>0.009258810216859679</v>
+        <v>0.009258810216859677</v>
       </c>
       <c r="T9" t="n">
         <v>0.00915416302599379</v>
       </c>
       <c r="U9" t="n">
-        <v>0.009399789233234049</v>
+        <v>0.009399789233234045</v>
       </c>
       <c r="V9" t="n">
-        <v>0.009230501065384355</v>
+        <v>0.009717894905815051</v>
       </c>
       <c r="W9" t="n">
         <v>0.009334637428644739</v>
@@ -2134,10 +2134,10 @@
         <v>0.01185187427593654</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.009244236278755933</v>
+        <v>0.008989591191741109</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.00962609854315441</v>
+        <v>0.009626098543154406</v>
       </c>
       <c r="AB9" t="n">
         <v>0.009073985004944178</v>
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004302273140983153</v>
+        <v>0.004302273140983157</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003788018389257375</v>
+        <v>0.003788018389257376</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004285389134520556</v>
+        <v>0.004285389134520562</v>
       </c>
       <c r="E2" t="n">
         <v>0.004159607524156993</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004192109656813371</v>
+        <v>0.004192109656813377</v>
       </c>
       <c r="G2" t="n">
-        <v>0.004391746411352346</v>
+        <v>0.004391746411352353</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004146175938589163</v>
+        <v>0.004146175938589169</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00420998866813796</v>
+        <v>0.004209988668137966</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00429392607927942</v>
+        <v>0.004293926079279423</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004350333314198482</v>
+        <v>0.004350333314198479</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004393894628605893</v>
+        <v>0.004393894628605897</v>
       </c>
       <c r="M2" t="n">
-        <v>0.004247049138802043</v>
+        <v>0.004247049138802044</v>
       </c>
       <c r="N2" t="n">
-        <v>0.004232407368283381</v>
+        <v>0.004232407368283385</v>
       </c>
       <c r="O2" t="n">
-        <v>0.006216667025544141</v>
+        <v>0.00621666702554414</v>
       </c>
       <c r="P2" t="n">
-        <v>0.004367504259715287</v>
+        <v>0.004367504259715293</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.004185214709555174</v>
+        <v>0.004185214709555182</v>
       </c>
       <c r="R2" t="n">
-        <v>0.004154390524084806</v>
+        <v>0.004154390524084811</v>
       </c>
       <c r="S2" t="n">
-        <v>0.00433653434065212</v>
+        <v>0.004336534340652126</v>
       </c>
       <c r="T2" t="n">
-        <v>0.004263283448728446</v>
+        <v>0.004263283448728453</v>
       </c>
       <c r="U2" t="n">
-        <v>0.004480498811119223</v>
+        <v>0.004480498811119222</v>
       </c>
       <c r="V2" t="n">
-        <v>0.004157161594058746</v>
+        <v>0.004157161594058754</v>
       </c>
       <c r="W2" t="n">
-        <v>0.004316928088636357</v>
+        <v>0.004316928088636355</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004323128723509859</v>
+        <v>0.004323128723509864</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.004312334281948803</v>
+        <v>0.004312334281948814</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.005261624549574828</v>
+        <v>0.005261624549574843</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.004291779374205689</v>
+        <v>0.004291779374205699</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.004302772432069168</v>
+        <v>0.004302772432069157</v>
       </c>
     </row>
     <row r="3">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00517429813684862</v>
+        <v>0.005174298136848635</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003456129897723568</v>
+        <v>0.003456129897723569</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00506365363326555</v>
+        <v>0.005063653633265562</v>
       </c>
       <c r="E3" t="n">
-        <v>0.004160364983340488</v>
+        <v>0.004160364983340498</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004396111403389511</v>
+        <v>0.004396111403389515</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00581271707322007</v>
+        <v>0.005812717073220079</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004067860783236276</v>
+        <v>0.004067860783236285</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004524413132104912</v>
+        <v>0.004524413132104924</v>
       </c>
       <c r="J3" t="n">
-        <v>0.005118262241342432</v>
+        <v>0.005118262241342438</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005521395207126798</v>
+        <v>0.005521395207126815</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005833708429436855</v>
+        <v>0.005833708429436865</v>
       </c>
       <c r="M3" t="n">
-        <v>0.004799127001538847</v>
+        <v>0.004799127001538849</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004682788495073603</v>
+        <v>0.004682788495073616</v>
       </c>
       <c r="O3" t="n">
-        <v>0.008300800640740142</v>
+        <v>0.008300800640740144</v>
       </c>
       <c r="P3" t="n">
-        <v>0.005639718409118344</v>
+        <v>0.005639718409118363</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.004345675206112612</v>
+        <v>0.004345675206112616</v>
       </c>
       <c r="R3" t="n">
-        <v>0.004126421196474135</v>
+        <v>0.004126421196474143</v>
       </c>
       <c r="S3" t="n">
-        <v>0.005420124489210822</v>
+        <v>0.005420124489210828</v>
       </c>
       <c r="T3" t="n">
-        <v>0.004905343748026365</v>
+        <v>0.004905343748026377</v>
       </c>
       <c r="U3" t="n">
-        <v>0.006225521837719075</v>
+        <v>0.006225521837719072</v>
       </c>
       <c r="V3" t="n">
-        <v>0.00414302502590437</v>
+        <v>0.004143025025904384</v>
       </c>
       <c r="W3" t="n">
-        <v>0.005226463715967344</v>
+        <v>0.005226463715967349</v>
       </c>
       <c r="X3" t="n">
-        <v>0.005332183961237596</v>
+        <v>0.005332183961237602</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.005251679361733286</v>
+        <v>0.005251679361733292</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006359584248456917</v>
+        <v>0.006359584248456922</v>
       </c>
       <c r="AA3" t="n">
         <v>0.005105615413653617</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.005194436376638232</v>
+        <v>0.005194436376638233</v>
       </c>
     </row>
     <row r="4">
@@ -2482,31 +2482,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009947384417457733</v>
+        <v>0.009947384417457735</v>
       </c>
       <c r="C4" t="n">
-        <v>0.008143542860131017</v>
+        <v>0.008143542860131019</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009756671797435947</v>
+        <v>0.009756671797435952</v>
       </c>
       <c r="E4" t="n">
         <v>0.008335910645980089</v>
       </c>
       <c r="F4" t="n">
-        <v>0.008703037186053513</v>
+        <v>0.008703037186053511</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0109580261660156</v>
+        <v>0.01095802616601559</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00818419470815674</v>
+        <v>0.008184194708156742</v>
       </c>
       <c r="I4" t="n">
-        <v>0.008904988843716344</v>
+        <v>0.008904988843716346</v>
       </c>
       <c r="J4" t="n">
-        <v>0.009848612586012041</v>
+        <v>0.009848612586012044</v>
       </c>
       <c r="K4" t="n">
         <v>0.01049024618269678</v>
@@ -2515,31 +2515,31 @@
         <v>0.01098229126812322</v>
       </c>
       <c r="M4" t="n">
-        <v>0.009340824550151615</v>
+        <v>0.00934082455015162</v>
       </c>
       <c r="N4" t="n">
-        <v>0.009158218374970431</v>
+        <v>0.009158218374970429</v>
       </c>
       <c r="O4" t="n">
-        <v>0.009881432594946078</v>
+        <v>0.009881432594946081</v>
       </c>
       <c r="P4" t="n">
         <v>0.01068419991133433</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.008625155584939819</v>
+        <v>0.008625155584939821</v>
       </c>
       <c r="R4" t="n">
-        <v>0.008276982230226089</v>
+        <v>0.008276982230226092</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0103343804286492</v>
+        <v>0.01033438042864921</v>
       </c>
       <c r="T4" t="n">
         <v>0.009506977907296215</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01146937197002781</v>
+        <v>0.01146937197002782</v>
       </c>
       <c r="V4" t="n">
         <v>0.008277957822975667</v>
@@ -2554,13 +2554,13 @@
         <v>0.01002997526565449</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.009120356384072085</v>
+        <v>0.009120356384072086</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.009828852494335178</v>
+        <v>0.009828852494335179</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.009957631672156861</v>
+        <v>0.009957631672156859</v>
       </c>
     </row>
     <row r="5">
@@ -2573,10 +2573,10 @@
         <v>0.04732379549423119</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01677652688413818</v>
+        <v>0.01677652688413817</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04920008599366247</v>
+        <v>0.04920008599366237</v>
       </c>
       <c r="E5" t="n">
         <v>0.01923368177488292</v>
@@ -2585,70 +2585,70 @@
         <v>0.0282759063195393</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06634601177937134</v>
+        <v>0.06634601177937142</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01823244132600952</v>
+        <v>0.01823244132600953</v>
       </c>
       <c r="I5" t="n">
         <v>0.0324827687751388</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04750398513870995</v>
+        <v>0.04750398513871003</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0598624017921438</v>
+        <v>0.05986240179214375</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06995231462758028</v>
+        <v>0.06995231462758034</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04119908726291237</v>
+        <v>0.04119908726291243</v>
       </c>
       <c r="N5" t="n">
-        <v>0.07582332776271718</v>
+        <v>0.07582332776271709</v>
       </c>
       <c r="O5" t="n">
         <v>0.04523069613759211</v>
       </c>
       <c r="P5" t="n">
-        <v>0.06117897600555764</v>
+        <v>0.06117897600555774</v>
       </c>
       <c r="Q5" t="n">
         <v>0.02612114376597994</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01994932257229474</v>
+        <v>0.01994932257229476</v>
       </c>
       <c r="S5" t="n">
-        <v>0.05536544647992381</v>
+        <v>0.055365446479924</v>
       </c>
       <c r="T5" t="n">
-        <v>0.04417829539686322</v>
+        <v>0.04417829539686315</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0781655357251383</v>
+        <v>0.07816553572513822</v>
       </c>
       <c r="V5" t="n">
-        <v>0.01874591163249572</v>
+        <v>0.01874591163249567</v>
       </c>
       <c r="W5" t="n">
-        <v>0.05167431636538315</v>
+        <v>0.05167431636538316</v>
       </c>
       <c r="X5" t="n">
-        <v>0.05680477261309191</v>
+        <v>0.05680477261309209</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.05257278138041033</v>
+        <v>0.05257278138041042</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0335775403254652</v>
+        <v>0.03357754032546514</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.04853731923792332</v>
+        <v>0.04853731923792333</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.05534339586243275</v>
+        <v>0.05534339586243267</v>
       </c>
     </row>
     <row r="6">
@@ -2658,34 +2658,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01133096711697732</v>
+        <v>0.01037973942137702</v>
       </c>
       <c r="C6" t="n">
-        <v>0.009527125559650601</v>
+        <v>0.009527125559650605</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01018902680135523</v>
+        <v>0.01114025449695554</v>
       </c>
       <c r="E6" t="n">
         <v>0.008768265649899369</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0100866198855731</v>
+        <v>0.009135392189972799</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01234160886553518</v>
+        <v>0.01139038116993488</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008616549712076024</v>
+        <v>0.009567777407676323</v>
       </c>
       <c r="I6" t="n">
-        <v>0.009337343847635623</v>
+        <v>0.009337343847635625</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01123219528553163</v>
+        <v>0.01123219528553162</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01092260118661607</v>
+        <v>0.01187382888221637</v>
       </c>
       <c r="L6" t="n">
         <v>0.0114146462720425</v>
@@ -2694,46 +2694,46 @@
         <v>0.009773179554070902</v>
       </c>
       <c r="N6" t="n">
-        <v>0.009596093138066409</v>
+        <v>0.009596093138066418</v>
       </c>
       <c r="O6" t="n">
         <v>0.01126807809332104</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0120708381066582</v>
+        <v>0.01207083810665821</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.009057510588859105</v>
+        <v>0.0100087382844594</v>
       </c>
       <c r="R6" t="n">
-        <v>0.008709337234145373</v>
+        <v>0.009660564929745671</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01076673543256848</v>
+        <v>0.01171796312816879</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0108905606068158</v>
+        <v>0.009939332911215491</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01288400903691119</v>
+        <v>0.0119327813413109</v>
       </c>
       <c r="V6" t="n">
-        <v>0.009661540522495253</v>
+        <v>0.009661540522495255</v>
       </c>
       <c r="W6" t="n">
         <v>0.01137863560076826</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01061531282005806</v>
+        <v>0.01156654051565837</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01052224019606418</v>
+        <v>0.01052224019606419</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.00955271138799137</v>
+        <v>0.01050393908359167</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.01121243519385476</v>
+        <v>0.01026120749825446</v>
       </c>
       <c r="AB6" t="n">
         <v>0.01039970133216694</v>
@@ -2749,25 +2749,25 @@
         <v>0.01066071660100212</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008856875043675402</v>
+        <v>0.0088568750436754</v>
       </c>
       <c r="D7" t="n">
         <v>0.01047000398098033</v>
       </c>
       <c r="E7" t="n">
-        <v>0.009049242829524469</v>
+        <v>0.009049242829524467</v>
       </c>
       <c r="F7" t="n">
-        <v>0.009416369369597897</v>
+        <v>0.009416369369597898</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01167135834955998</v>
+        <v>0.01167135834955997</v>
       </c>
       <c r="H7" t="n">
-        <v>0.008897526891701124</v>
+        <v>0.008897526891701125</v>
       </c>
       <c r="I7" t="n">
-        <v>0.009618321027260728</v>
+        <v>0.009618321027260729</v>
       </c>
       <c r="J7" t="n">
         <v>0.01056194476955643</v>
@@ -2782,13 +2782,13 @@
         <v>0.010054156733696</v>
       </c>
       <c r="N7" t="n">
-        <v>0.009871550558514816</v>
+        <v>0.009871550558514817</v>
       </c>
       <c r="O7" t="n">
         <v>0.01059473918452504</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01139750650091328</v>
+        <v>0.01139750650091329</v>
       </c>
       <c r="Q7" t="n">
         <v>0.009338487768484203</v>
@@ -2797,7 +2797,7 @@
         <v>0.008990314413770475</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01104771261219359</v>
+        <v>0.0110477126121936</v>
       </c>
       <c r="T7" t="n">
         <v>0.0102203100908406</v>
@@ -2812,10 +2812,10 @@
         <v>0.01070532945932445</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01089628999968317</v>
+        <v>0.01089628999968316</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01077436181656268</v>
+        <v>0.01077436181656267</v>
       </c>
       <c r="Z7" t="n">
         <v>0.009833688567616471</v>
@@ -2843,13 +2843,13 @@
         <v>0.01342274526736322</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01200198411590736</v>
+        <v>0.01119614725721185</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01109148702839937</v>
+        <v>0.01109148702839938</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01462409963594286</v>
+        <v>0.01493791142760152</v>
       </c>
       <c r="H8" t="n">
         <v>0.01185026817808401</v>
@@ -2867,52 +2867,52 @@
         <v>0.01464836473805049</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01300689802007889</v>
+        <v>0.01300689802007871</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01165115947996403</v>
+        <v>0.01165115947996402</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01269676065991274</v>
+        <v>0.01269676065991275</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0134205031424555</v>
+        <v>0.01342050314245551</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01048042039894056</v>
+        <v>0.01048042039894057</v>
       </c>
       <c r="R8" t="n">
         <v>0.01194305570015336</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01400045389857647</v>
+        <v>0.01400045389857648</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01317305137722349</v>
+        <v>0.01317305137722348</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01423454124042479</v>
+        <v>0.01442709230279679</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01194403129290294</v>
+        <v>0.01152958119333358</v>
       </c>
       <c r="W8" t="n">
         <v>0.01365836817059902</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01217692805895816</v>
+        <v>0.01217692805895817</v>
       </c>
       <c r="Y8" t="n">
         <v>0.01523056746586462</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01278642985399935</v>
+        <v>0.01124492532138406</v>
       </c>
       <c r="AA8" t="n">
         <v>0.01349492596426245</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01520457014576872</v>
+        <v>0.01520457014576871</v>
       </c>
     </row>
     <row r="9">
@@ -2925,34 +2925,34 @@
         <v>0.01266146236171374</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01167158675640936</v>
+        <v>0.01167158675640937</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0132847156937143</v>
+        <v>0.01328471569371431</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01186395454225843</v>
+        <v>0.01167609505403282</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01223108108233186</v>
+        <v>0.01035466650541079</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01448607006229394</v>
+        <v>0.01448607075573084</v>
       </c>
       <c r="H9" t="n">
         <v>0.01171223860443509</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01243303273999468</v>
+        <v>0.01243303273999469</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01337665648229039</v>
+        <v>0.0133766564822904</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01401829007897513</v>
+        <v>0.01401829007897514</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01451033516440156</v>
+        <v>0.01451033516440157</v>
       </c>
       <c r="M9" t="n">
         <v>0.01286886844642997</v>
@@ -2964,7 +2964,7 @@
         <v>0.01367922466516817</v>
       </c>
       <c r="P9" t="n">
-        <v>0.01454065743047929</v>
+        <v>0.01454065743047931</v>
       </c>
       <c r="Q9" t="n">
         <v>0.01215320017465506</v>
@@ -2973,28 +2973,28 @@
         <v>0.01180502612650444</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01386242432492755</v>
+        <v>0.01386242432492756</v>
       </c>
       <c r="T9" t="n">
         <v>0.01303502180357456</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01502847023366996</v>
+        <v>0.01502847023366998</v>
       </c>
       <c r="V9" t="n">
-        <v>0.01180600171925402</v>
+        <v>0.0127453012493229</v>
       </c>
       <c r="W9" t="n">
         <v>0.01352004117205842</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01371100171241713</v>
+        <v>0.01371100171241714</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.01358907352929663</v>
+        <v>0.01358907352929664</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.01264840028035043</v>
+        <v>0.01215765146731363</v>
       </c>
       <c r="AA9" t="n">
         <v>0.01335689639061353</v>
@@ -3169,82 +3169,82 @@
         <v>0.004415065367693025</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004003415423593323</v>
+        <v>0.004003415423593327</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004470187714911664</v>
+        <v>0.004470187714911665</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004348930064478861</v>
+        <v>0.00434893006447886</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004359131415316872</v>
+        <v>0.004359131415316873</v>
       </c>
       <c r="G2" t="n">
         <v>0.004525603678828764</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004271732178310048</v>
+        <v>0.00427173217831005</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004411544266561278</v>
+        <v>0.004411544266561277</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004433943456133704</v>
+        <v>0.0044339434561337</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004473100949035379</v>
+        <v>0.004473100949035378</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004494335834809566</v>
+        <v>0.004494335834809565</v>
       </c>
       <c r="M2" t="n">
-        <v>0.004366279363027862</v>
+        <v>0.004366279363027865</v>
       </c>
       <c r="N2" t="n">
-        <v>0.004347336192422675</v>
+        <v>0.004347336192422674</v>
       </c>
       <c r="O2" t="n">
-        <v>0.006365710050447095</v>
+        <v>0.006365710050447092</v>
       </c>
       <c r="P2" t="n">
-        <v>0.004514450182457479</v>
+        <v>0.004514450182457483</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.004326106019106953</v>
+        <v>0.00432610601910695</v>
       </c>
       <c r="R2" t="n">
-        <v>0.004281705035253209</v>
+        <v>0.004281705035253211</v>
       </c>
       <c r="S2" t="n">
-        <v>0.004461549177406342</v>
+        <v>0.004461549177406344</v>
       </c>
       <c r="T2" t="n">
         <v>0.004403573169186957</v>
       </c>
       <c r="U2" t="n">
-        <v>0.004686775475786234</v>
+        <v>0.004686775475786237</v>
       </c>
       <c r="V2" t="n">
-        <v>0.004321344125383369</v>
+        <v>0.004321344125383367</v>
       </c>
       <c r="W2" t="n">
-        <v>0.004505503735370779</v>
+        <v>0.00450550373537078</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004756973589622611</v>
+        <v>0.004756973589622615</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.00469763353290365</v>
+        <v>0.004697633532903654</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.005374908637512193</v>
+        <v>0.00537490863751219</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.004455774106202257</v>
+        <v>0.004455774106202255</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.004399772191544987</v>
+        <v>0.004399772191544986</v>
       </c>
     </row>
     <row r="3">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005071393288354366</v>
+        <v>0.005071393288354365</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003683920832798927</v>
+        <v>0.003683920832798929</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005472559568051197</v>
+        <v>0.005472559568051202</v>
       </c>
       <c r="E3" t="n">
         <v>0.00460161974536795</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004677986732100782</v>
+        <v>0.004677986732100783</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005856922834951407</v>
+        <v>0.00585692283495141</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004053086068079549</v>
+        <v>0.004053086068079554</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005054088761955038</v>
+        <v>0.005054088761955042</v>
       </c>
       <c r="J3" t="n">
-        <v>0.005207125533844533</v>
+        <v>0.005207125533844537</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005484344206684976</v>
+        <v>0.005484344206684978</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005640221180799242</v>
+        <v>0.00564022118079924</v>
       </c>
       <c r="M3" t="n">
-        <v>0.004742460726629359</v>
+        <v>0.00474246072662936</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004592820590007522</v>
+        <v>0.004592820590007523</v>
       </c>
       <c r="O3" t="n">
-        <v>0.008292878452378161</v>
+        <v>0.00829287845237817</v>
       </c>
       <c r="P3" t="n">
-        <v>0.005777465914130671</v>
+        <v>0.005777465914130682</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.004440655892618803</v>
+        <v>0.004440655892618804</v>
       </c>
       <c r="R3" t="n">
-        <v>0.004124385427746248</v>
+        <v>0.004124385427746242</v>
       </c>
       <c r="S3" t="n">
-        <v>0.00540227038942023</v>
+        <v>0.005402270389420242</v>
       </c>
       <c r="T3" t="n">
-        <v>0.004996563540060017</v>
+        <v>0.004996563540060019</v>
       </c>
       <c r="U3" t="n">
-        <v>0.006316664543535289</v>
+        <v>0.006316664543535297</v>
       </c>
       <c r="V3" t="n">
         <v>0.0044040205035437</v>
       </c>
       <c r="W3" t="n">
-        <v>0.005118112858482765</v>
+        <v>0.005118112858482764</v>
       </c>
       <c r="X3" t="n">
-        <v>0.007521547598336966</v>
+        <v>0.007521547598336969</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.007091503139868145</v>
+        <v>0.007091503139868149</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006462975034969765</v>
+        <v>0.00646297503496977</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.005366309192609429</v>
+        <v>0.005366309192609426</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.004980083711083457</v>
+        <v>0.004980083711083459</v>
       </c>
     </row>
     <row r="4">
@@ -3351,43 +3351,43 @@
         <v>0.01022302889329951</v>
       </c>
       <c r="E4" t="n">
-        <v>0.008853367950385868</v>
+        <v>0.008853367950385872</v>
       </c>
       <c r="F4" t="n">
-        <v>0.008968596900954461</v>
+        <v>0.008968596900954463</v>
       </c>
       <c r="G4" t="n">
         <v>0.01084897769834599</v>
       </c>
       <c r="H4" t="n">
-        <v>0.007981382313326952</v>
+        <v>0.00798138231332695</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009560624166862777</v>
+        <v>0.009560624166862781</v>
       </c>
       <c r="J4" t="n">
-        <v>0.009809430594326853</v>
+        <v>0.009809430594326858</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01025593521288066</v>
+        <v>0.01025593521288067</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01049579301623025</v>
+        <v>0.01049579301623026</v>
       </c>
       <c r="M4" t="n">
-        <v>0.009072096155819349</v>
+        <v>0.00907209615581935</v>
       </c>
       <c r="N4" t="n">
-        <v>0.008835364432293788</v>
+        <v>0.008835364432293786</v>
       </c>
       <c r="O4" t="n">
-        <v>0.009609516455006998</v>
+        <v>0.00960951645500701</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01072299382597052</v>
+        <v>0.01072299382597054</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.008595559858330515</v>
+        <v>0.008595559858330517</v>
       </c>
       <c r="R4" t="n">
         <v>0.008094030320240793</v>
@@ -3396,7 +3396,7 @@
         <v>0.01012545263825333</v>
       </c>
       <c r="T4" t="n">
-        <v>0.009470586955133871</v>
+        <v>0.009470586955133876</v>
       </c>
       <c r="U4" t="n">
         <v>0.01121525799640028</v>
@@ -3405,13 +3405,13 @@
         <v>0.008513363443148118</v>
       </c>
       <c r="W4" t="n">
-        <v>0.009380677059049988</v>
+        <v>0.009380677059049986</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01346240727617996</v>
+        <v>0.01346240727617998</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.01276577532786746</v>
+        <v>0.01276577532786747</v>
       </c>
       <c r="Z4" t="n">
         <v>0.009205897186131049</v>
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03844846838582188</v>
+        <v>0.03844846838582193</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01465372142704872</v>
+        <v>0.01465372142704873</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0534797558814173</v>
+        <v>0.05347975588141737</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02639551624471172</v>
+        <v>0.02639551624471174</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03027811859797566</v>
+        <v>0.03027811859797563</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05877599653004893</v>
+        <v>0.05877599653004886</v>
       </c>
       <c r="H5" t="n">
         <v>0.01223306677186347</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0418005225437543</v>
+        <v>0.04180052254375435</v>
       </c>
       <c r="J5" t="n">
         <v>0.04273309732656815</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04939397478847921</v>
+        <v>0.04939397478847922</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0558763005307103</v>
+        <v>0.05587630053071033</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03267500361170077</v>
+        <v>0.0326750036117008</v>
       </c>
       <c r="N5" t="n">
-        <v>0.06484267164585653</v>
+        <v>0.06484267164585669</v>
       </c>
       <c r="O5" t="n">
-        <v>0.03713768721141861</v>
+        <v>0.03713768721141866</v>
       </c>
       <c r="P5" t="n">
-        <v>0.05662349659226009</v>
+        <v>0.05662349659226042</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.02283722229989289</v>
+        <v>0.02283722229989293</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01428895793304688</v>
+        <v>0.01428895793304689</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0472788265816896</v>
+        <v>0.04727882658168974</v>
       </c>
       <c r="T5" t="n">
-        <v>0.03987894006173285</v>
+        <v>0.03987894006173294</v>
       </c>
       <c r="U5" t="n">
-        <v>0.06724892391986008</v>
+        <v>0.06724892391986029</v>
       </c>
       <c r="V5" t="n">
-        <v>0.02048444335311374</v>
+        <v>0.02048444335311349</v>
       </c>
       <c r="W5" t="n">
-        <v>0.03671581100201099</v>
+        <v>0.03671581100201095</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1119047642795585</v>
+        <v>0.1119047642795586</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.09666508353066371</v>
+        <v>0.09666508353066379</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.03084857271931557</v>
+        <v>0.0308485727193156</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.04884876142977891</v>
+        <v>0.04884876142977888</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.04089980574989653</v>
+        <v>0.0408998057498965</v>
       </c>
     </row>
     <row r="6">
@@ -3518,82 +3518,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01127151382740951</v>
+        <v>0.01030378232539556</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008836465145471128</v>
+        <v>0.008836465145471135</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01189414609677662</v>
+        <v>0.01189414609677663</v>
       </c>
       <c r="E6" t="n">
-        <v>0.009556753651849022</v>
+        <v>0.009556753651849027</v>
       </c>
       <c r="F6" t="n">
-        <v>0.009671982602417617</v>
+        <v>0.01063971410443158</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01252009490182311</v>
+        <v>0.01155236339980915</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008684768014790104</v>
+        <v>0.008684768014790109</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01123174137033989</v>
+        <v>0.01026400986832593</v>
       </c>
       <c r="J6" t="n">
         <v>0.01148054779780397</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01095932091434382</v>
+        <v>0.01192705241635778</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01216691021970737</v>
+        <v>0.01119917871769341</v>
       </c>
       <c r="M6" t="n">
         <v>0.01074321335929646</v>
       </c>
       <c r="N6" t="n">
-        <v>0.009542147545114536</v>
+        <v>0.009542147545114532</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0112856923586429</v>
+        <v>0.01031629956782776</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01239914413896593</v>
+        <v>0.01239914413896595</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01026667706180763</v>
+        <v>0.01026667706180764</v>
       </c>
       <c r="R6" t="n">
         <v>0.009765147523717908</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01082883833971648</v>
+        <v>0.01082883833971649</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01017397265659703</v>
+        <v>0.01017397265659704</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01291273390977452</v>
+        <v>0.01194500240776056</v>
       </c>
       <c r="V6" t="n">
         <v>0.01018448064662523</v>
       </c>
       <c r="W6" t="n">
-        <v>0.01105684959422551</v>
+        <v>0.01013658628074778</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01416579297764312</v>
+        <v>0.01416579297764314</v>
       </c>
       <c r="Y6" t="n">
         <v>0.01353723334133833</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.01087701438960816</v>
+        <v>0.009909282887594203</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0107636062538023</v>
+        <v>0.01173133775581626</v>
       </c>
       <c r="AB6" t="n">
         <v>0.01014856821204261</v>
@@ -3612,19 +3612,19 @@
         <v>0.008739727421100725</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01082967687039226</v>
+        <v>0.01082967687039227</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00946001592747862</v>
+        <v>0.009460015927478622</v>
       </c>
       <c r="F7" t="n">
-        <v>0.009575244878047211</v>
+        <v>0.009575244878047213</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01145562567543874</v>
+        <v>0.01145562567543875</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0085880302904197</v>
+        <v>0.008588030290419702</v>
       </c>
       <c r="I7" t="n">
         <v>0.01016727214395553</v>
@@ -3633,40 +3633,40 @@
         <v>0.01041607857141961</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01086258318997342</v>
+        <v>0.01086258318997343</v>
       </c>
       <c r="L7" t="n">
         <v>0.011102440993323</v>
       </c>
       <c r="M7" t="n">
-        <v>0.009678744132912101</v>
+        <v>0.009678744132912103</v>
       </c>
       <c r="N7" t="n">
-        <v>0.009442012409386538</v>
+        <v>0.009442012409386542</v>
       </c>
       <c r="O7" t="n">
         <v>0.01021613997164719</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01132961734261069</v>
+        <v>0.01132961734261071</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.009202207835423266</v>
+        <v>0.009202207835423271</v>
       </c>
       <c r="R7" t="n">
-        <v>0.008700678297333541</v>
+        <v>0.008700678297333543</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01073210061534608</v>
+        <v>0.01073210061534609</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01007723493222662</v>
+        <v>0.01007723493222663</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01184689356738437</v>
+        <v>0.01184689356738439</v>
       </c>
       <c r="V7" t="n">
-        <v>0.009120011420240869</v>
+        <v>0.009120011420240865</v>
       </c>
       <c r="W7" t="n">
         <v>0.009987325036142743</v>
@@ -3675,10 +3675,10 @@
         <v>0.01406905525327273</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01339878201485733</v>
+        <v>0.01339878201485734</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.009812545163223794</v>
+        <v>0.009812545163223798</v>
       </c>
       <c r="AA7" t="n">
         <v>0.0106668685294319</v>
@@ -3703,76 +3703,76 @@
         <v>0.01368066004469194</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01231099910177829</v>
+        <v>0.01153736079801796</v>
       </c>
       <c r="F8" t="n">
         <v>0.01119965400646279</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01430660884973842</v>
+        <v>0.01460788176816982</v>
       </c>
       <c r="H8" t="n">
         <v>0.01143901346471937</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01301825531825519</v>
+        <v>0.0130182553182552</v>
       </c>
       <c r="J8" t="n">
         <v>0.01326706174571927</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01371356636427308</v>
+        <v>0.01371356636427309</v>
       </c>
       <c r="L8" t="n">
         <v>0.01395342416762267</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01252972730721177</v>
+        <v>0.01252972730721162</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01116673767787247</v>
+        <v>0.01116673767787248</v>
       </c>
       <c r="O8" t="n">
         <v>0.0122503951521807</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01328800525826375</v>
+        <v>0.01328800525826376</v>
       </c>
       <c r="Q8" t="n">
         <v>0.01031473623206977</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0115516614716332</v>
+        <v>0.01155166147163321</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01358308378964572</v>
+        <v>0.01358308378964574</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01292821810652629</v>
+        <v>0.0129282181065263</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01380421513283574</v>
+        <v>0.01398905221550552</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01197099459454053</v>
+        <v>0.01157273791536184</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01283859375120748</v>
+        <v>0.01283859375120749</v>
       </c>
       <c r="X8" t="n">
         <v>0.01531474687211113</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01769258749277147</v>
+        <v>0.01769258749277148</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01266352833752346</v>
+        <v>0.01118361718803065</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01351785170373156</v>
+        <v>0.01351785170373157</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01441714826565104</v>
+        <v>0.01441714826565105</v>
       </c>
     </row>
     <row r="9">
@@ -3788,22 +3788,22 @@
         <v>0.01119545931467686</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01328540876396839</v>
+        <v>0.0132854087639684</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01191574782105475</v>
+        <v>0.01174853151552194</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01203097677162334</v>
+        <v>0.01036075312848894</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01391135756901488</v>
+        <v>0.01391135833171526</v>
       </c>
       <c r="H9" t="n">
         <v>0.01104376218399584</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01262300403753166</v>
+        <v>0.01262300403753167</v>
       </c>
       <c r="J9" t="n">
         <v>0.01287181046499574</v>
@@ -3824,7 +3824,7 @@
         <v>0.01291200322717842</v>
       </c>
       <c r="P9" t="n">
-        <v>0.01407769956380381</v>
+        <v>0.01407769956380382</v>
       </c>
       <c r="Q9" t="n">
         <v>0.01165794049169979</v>
@@ -3833,19 +3833,19 @@
         <v>0.01115641019090968</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01318783250892221</v>
+        <v>0.01318783250892223</v>
       </c>
       <c r="T9" t="n">
         <v>0.01253296682580275</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01430399657696628</v>
+        <v>0.01430399657696629</v>
       </c>
       <c r="V9" t="n">
-        <v>0.011575743313817</v>
+        <v>0.01241182749964322</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01244305692971887</v>
+        <v>0.01244305692971888</v>
       </c>
       <c r="X9" t="n">
         <v>0.01652478714684885</v>
@@ -3854,7 +3854,7 @@
         <v>0.01585451390843349</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.01226827705679993</v>
+        <v>0.01183145457689935</v>
       </c>
       <c r="AA9" t="n">
         <v>0.01312260042300804</v>
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004166456991908829</v>
+        <v>0.004166456991908827</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003654459516349171</v>
+        <v>0.003654459516349168</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004181966274925441</v>
+        <v>0.004181966274925444</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004099020519234392</v>
+        <v>0.004099020519234397</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004151931497932112</v>
+        <v>0.004151931497932118</v>
       </c>
       <c r="G2" t="n">
-        <v>0.004269907591629523</v>
+        <v>0.004269907591629528</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004049124587820167</v>
+        <v>0.004049124587820165</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004188942057528038</v>
+        <v>0.004188942057528043</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004193507562392809</v>
+        <v>0.004193507562392806</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004290119537013496</v>
+        <v>0.004290119537013493</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004223377782921596</v>
+        <v>0.0042233777829216</v>
       </c>
       <c r="M2" t="n">
         <v>0.004126687049752296</v>
       </c>
       <c r="N2" t="n">
-        <v>0.004090593282381863</v>
+        <v>0.004090593282381866</v>
       </c>
       <c r="O2" t="n">
-        <v>0.005960444331515838</v>
+        <v>0.005960444331515828</v>
       </c>
       <c r="P2" t="n">
-        <v>0.004259934836562337</v>
+        <v>0.00425993483656234</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.004106424984343772</v>
+        <v>0.004106424984343776</v>
       </c>
       <c r="R2" t="n">
-        <v>0.004082575360882908</v>
+        <v>0.004082575360882912</v>
       </c>
       <c r="S2" t="n">
-        <v>0.004226513492466693</v>
+        <v>0.004226513492466696</v>
       </c>
       <c r="T2" t="n">
-        <v>0.004181735044758273</v>
+        <v>0.004181735044758279</v>
       </c>
       <c r="U2" t="n">
-        <v>0.004293641261479717</v>
+        <v>0.004293641261479725</v>
       </c>
       <c r="V2" t="n">
-        <v>0.004138352839961956</v>
+        <v>0.004138352839961962</v>
       </c>
       <c r="W2" t="n">
-        <v>0.004034545802303915</v>
+        <v>0.004034545802303917</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004646133772721244</v>
+        <v>0.004646133772721247</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.004676378821027548</v>
+        <v>0.004676378821027553</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.005184603233043006</v>
+        <v>0.00518460323304301</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.004247032686219913</v>
+        <v>0.004247032686219918</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.00416277191301822</v>
+        <v>0.004162771913018217</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004660627386928741</v>
+        <v>0.004660627386928749</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003262266503615204</v>
+        <v>0.003262266503615203</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004776378827801556</v>
+        <v>0.004776378827801562</v>
       </c>
       <c r="E3" t="n">
-        <v>0.004181162408797284</v>
+        <v>0.004181162408797282</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004563318468968558</v>
+        <v>0.004563318468968561</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005394541648189114</v>
+        <v>0.00539454164818911</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003828564419986449</v>
+        <v>0.003828564419986445</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00482856462847747</v>
+        <v>0.004828564628477471</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004854565293080615</v>
+        <v>0.004854565293080617</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005541723454940558</v>
+        <v>0.005541723454940562</v>
       </c>
       <c r="L3" t="n">
         <v>0.005068222905167005</v>
       </c>
       <c r="M3" t="n">
-        <v>0.004393551458136427</v>
+        <v>0.004393551458136424</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004124433380747148</v>
+        <v>0.004124433380747146</v>
       </c>
       <c r="O3" t="n">
-        <v>0.007438541060675861</v>
+        <v>0.007438541060675863</v>
       </c>
       <c r="P3" t="n">
-        <v>0.005323532338572363</v>
+        <v>0.005323532338572369</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.004236447375150136</v>
+        <v>0.004236447375150137</v>
       </c>
       <c r="R3" t="n">
-        <v>0.004068196267538554</v>
+        <v>0.004068196267538556</v>
       </c>
       <c r="S3" t="n">
-        <v>0.00508851298134769</v>
+        <v>0.005088512981347694</v>
       </c>
       <c r="T3" t="n">
-        <v>0.004777647005206446</v>
+        <v>0.00477764700520645</v>
       </c>
       <c r="U3" t="n">
-        <v>0.005961557115340506</v>
+        <v>0.00596155711534051</v>
       </c>
       <c r="V3" t="n">
-        <v>0.004460256866850873</v>
+        <v>0.00446025686685087</v>
       </c>
       <c r="W3" t="n">
-        <v>0.00422766380587428</v>
+        <v>0.004227663805874277</v>
       </c>
       <c r="X3" t="n">
-        <v>0.008088606168304696</v>
+        <v>0.008088606168304707</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.008308789030032565</v>
+        <v>0.008308789030032571</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006223268526085683</v>
+        <v>0.006223268526085681</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.005241286204723558</v>
+        <v>0.005241286204723563</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.004650318700041595</v>
+        <v>0.004650318700041592</v>
       </c>
     </row>
     <row r="4">
@@ -4202,16 +4202,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009116342615031371</v>
+        <v>0.009116342615031369</v>
       </c>
       <c r="C4" t="n">
         <v>0.007966772763896153</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009291527101326743</v>
+        <v>0.009291527101326745</v>
       </c>
       <c r="E4" t="n">
-        <v>0.008354616633863646</v>
+        <v>0.008354616633863648</v>
       </c>
       <c r="F4" t="n">
         <v>0.008952270478507164</v>
@@ -4220,28 +4220,28 @@
         <v>0.01028486472850378</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00779101913527743</v>
+        <v>0.007791019135277429</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009370321774841699</v>
+        <v>0.0093703217748417</v>
       </c>
       <c r="J4" t="n">
         <v>0.009418296483961306</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01051316794956999</v>
+        <v>0.01051316794957</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009759289134378244</v>
+        <v>0.009759289134378245</v>
       </c>
       <c r="M4" t="n">
-        <v>0.008687332706640053</v>
+        <v>0.008687332706640051</v>
       </c>
       <c r="N4" t="n">
-        <v>0.008259427116893816</v>
+        <v>0.008259427116893812</v>
       </c>
       <c r="O4" t="n">
-        <v>0.008737418076438836</v>
+        <v>0.00873741807643884</v>
       </c>
       <c r="P4" t="n">
         <v>0.01017221787232593</v>
@@ -4253,10 +4253,10 @@
         <v>0.008168861005136989</v>
       </c>
       <c r="S4" t="n">
-        <v>0.009794708416187788</v>
+        <v>0.009794708416187795</v>
       </c>
       <c r="T4" t="n">
-        <v>0.009288915250217508</v>
+        <v>0.00928891525021751</v>
       </c>
       <c r="U4" t="n">
         <v>0.01135280079579315</v>
@@ -4265,19 +4265,19 @@
         <v>0.008774582510577522</v>
       </c>
       <c r="W4" t="n">
-        <v>0.008663277450526488</v>
+        <v>0.008663277450526486</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01453451251652878</v>
+        <v>0.01453451251652879</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.01485754433475376</v>
+        <v>0.01485754433475378</v>
       </c>
       <c r="Z4" t="n">
         <v>0.008877062271187643</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01002648214892584</v>
+        <v>0.01002648214892585</v>
       </c>
       <c r="AB4" t="n">
         <v>0.009086737447572591</v>
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03252457912627837</v>
+        <v>0.03252457912627839</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01468346379443616</v>
+        <v>0.01468346379443617</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03824569679368391</v>
+        <v>0.038245696793684</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02000183932017068</v>
+        <v>0.02000183932017073</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03291873461864758</v>
+        <v>0.03291873461864759</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05090239437773294</v>
+        <v>0.05090239437773299</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01185356881435596</v>
+        <v>0.01185356881435598</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04088268319139628</v>
+        <v>0.04088268319139636</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03837941065912016</v>
+        <v>0.03837941065912018</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05645775054134997</v>
+        <v>0.05645775054135007</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04459523185270236</v>
+        <v>0.04459523185270241</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02793408510184547</v>
+        <v>0.02793408510184548</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0670344919470562</v>
+        <v>0.06703449194705631</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02616378043955451</v>
+        <v>0.02616378043955455</v>
       </c>
       <c r="P5" t="n">
-        <v>0.04899645786492331</v>
+        <v>0.04899645786492345</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.02274500841984295</v>
+        <v>0.02274500841984299</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01899858872229366</v>
+        <v>0.0189985887222937</v>
       </c>
       <c r="S5" t="n">
-        <v>0.04413877771526854</v>
+        <v>0.04413877771526859</v>
       </c>
       <c r="T5" t="n">
-        <v>0.03971192954763211</v>
+        <v>0.0397119295476322</v>
       </c>
       <c r="U5" t="n">
-        <v>0.07014646554175996</v>
+        <v>0.07014646554175985</v>
       </c>
       <c r="V5" t="n">
         <v>0.02699459098793026</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02701969997836058</v>
+        <v>0.02701969997836057</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1306867382070005</v>
+        <v>0.1306867382070007</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1389690564089064</v>
+        <v>0.1389690564089067</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.027373319550465</v>
+        <v>0.02737331955046499</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0515167382907619</v>
+        <v>0.05151673829076204</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.03690413164916714</v>
+        <v>0.03690413164916716</v>
       </c>
     </row>
     <row r="6">
@@ -4378,73 +4378,73 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.009451615302259722</v>
+        <v>0.01028575381592654</v>
       </c>
       <c r="C6" t="n">
         <v>0.008302045451124505</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009626799788555095</v>
+        <v>0.009626799788555098</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008689889321091993</v>
+        <v>0.009524027834758813</v>
       </c>
       <c r="F6" t="n">
         <v>0.009287543165735514</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01062013741573213</v>
+        <v>0.01145427592939895</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008960430336172597</v>
+        <v>0.008126291822505778</v>
       </c>
       <c r="I6" t="n">
-        <v>0.009705594462070049</v>
+        <v>0.00970559446207005</v>
       </c>
       <c r="J6" t="n">
-        <v>0.009753569171189651</v>
+        <v>0.01058770768485647</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01168257915046515</v>
+        <v>0.01168257915046516</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0100945618216066</v>
+        <v>0.01092870033527342</v>
       </c>
       <c r="M6" t="n">
-        <v>0.009022605393868404</v>
+        <v>0.009022605393868401</v>
       </c>
       <c r="N6" t="n">
-        <v>0.008601825014165648</v>
+        <v>0.008601825014165636</v>
       </c>
       <c r="O6" t="n">
-        <v>0.009079815973710671</v>
+        <v>0.009910167364208243</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01134494471446369</v>
+        <v>0.01048455207031501</v>
       </c>
       <c r="Q6" t="n">
         <v>0.009607664674391394</v>
       </c>
       <c r="R6" t="n">
-        <v>0.009338272206032157</v>
+        <v>0.009338272206032158</v>
       </c>
       <c r="S6" t="n">
         <v>0.01096411961708296</v>
       </c>
       <c r="T6" t="n">
-        <v>0.009624187937445855</v>
+        <v>0.01045832645111268</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01254081191249267</v>
+        <v>0.01170667339882585</v>
       </c>
       <c r="V6" t="n">
-        <v>0.00994399371147269</v>
+        <v>0.009109855197805869</v>
       </c>
       <c r="W6" t="n">
         <v>0.009836025895301586</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01486978520375713</v>
+        <v>0.01486978520375714</v>
       </c>
       <c r="Y6" t="n">
         <v>0.01523882210624927</v>
@@ -4453,10 +4453,10 @@
         <v>0.01004647347208281</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.01119589334982101</v>
+        <v>0.01119589334982102</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.009426149763699217</v>
+        <v>0.009426149763699215</v>
       </c>
     </row>
     <row r="7">
@@ -4484,31 +4484,31 @@
         <v>0.01092785763214904</v>
       </c>
       <c r="H7" t="n">
-        <v>0.008434012038922696</v>
+        <v>0.008434012038922694</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01001331467848696</v>
+        <v>0.01001331467848697</v>
       </c>
       <c r="J7" t="n">
         <v>0.01006128938760657</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01115616085321525</v>
+        <v>0.01115616085321526</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01040228203802351</v>
+        <v>0.01040228203802352</v>
       </c>
       <c r="M7" t="n">
         <v>0.009330325610285317</v>
       </c>
       <c r="N7" t="n">
-        <v>0.008902420020539075</v>
+        <v>0.008902420020539073</v>
       </c>
       <c r="O7" t="n">
         <v>0.009380387183483238</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01081518697937033</v>
+        <v>0.01081518697937034</v>
       </c>
       <c r="Q7" t="n">
         <v>0.009081246377141488</v>
@@ -4517,7 +4517,7 @@
         <v>0.008811853908782252</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01043770131983305</v>
+        <v>0.01043770131983306</v>
       </c>
       <c r="T7" t="n">
         <v>0.009931908153862773</v>
@@ -4526,19 +4526,19 @@
         <v>0.01201290123593426</v>
       </c>
       <c r="V7" t="n">
-        <v>0.009417575414222785</v>
+        <v>0.009417575414222784</v>
       </c>
       <c r="W7" t="n">
-        <v>0.009306270354171755</v>
+        <v>0.009306270354171753</v>
       </c>
       <c r="X7" t="n">
         <v>0.01517750542017403</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01551913715420337</v>
+        <v>0.01551913715420339</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.009520055174832906</v>
+        <v>0.009520055174832903</v>
       </c>
       <c r="AA7" t="n">
         <v>0.01066947505257111</v>
@@ -4554,31 +4554,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01106339215927876</v>
+        <v>0.01106339215927875</v>
       </c>
       <c r="C8" t="n">
         <v>0.01127304712683278</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01259780146426337</v>
+        <v>0.01259780146426336</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01166089099680027</v>
+        <v>0.01093714387548823</v>
       </c>
       <c r="F8" t="n">
         <v>0.01111107136390203</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01359113909144041</v>
+        <v>0.01387298321211569</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01109729349821406</v>
+        <v>0.01109729349821405</v>
       </c>
       <c r="I8" t="n">
         <v>0.01267659613777833</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01272457084689793</v>
+        <v>0.01272457084689792</v>
       </c>
       <c r="K8" t="n">
         <v>0.01381944231250662</v>
@@ -4587,16 +4587,16 @@
         <v>0.01306556349731487</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01199360706957668</v>
+        <v>0.01199360706957655</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01051207485196857</v>
+        <v>0.01051207485196856</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0112796115572987</v>
+        <v>0.01127961155729869</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01264343669449151</v>
+        <v>0.0126434366944915</v>
       </c>
       <c r="Q8" t="n">
         <v>0.01011818431810092</v>
@@ -4611,22 +4611,22 @@
         <v>0.01259518961315413</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01384021021919648</v>
+        <v>0.01401311746630994</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01208085687351415</v>
+        <v>0.0117081049277517</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01196981894001038</v>
+        <v>0.01196981894001037</v>
       </c>
       <c r="X8" t="n">
         <v>0.01633901901654006</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01953191792816644</v>
+        <v>0.01953191792816646</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01218333663412428</v>
+        <v>0.01079886351660841</v>
       </c>
       <c r="AA8" t="n">
         <v>0.01333275651186247</v>
@@ -4651,16 +4651,16 @@
         <v>0.01209777294421262</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01116086247674952</v>
+        <v>0.01101094301334375</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01175851632139304</v>
+        <v>0.01026106124632791</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01309111057138966</v>
+        <v>0.01309111117070366</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01059726497816331</v>
+        <v>0.0105972649781633</v>
       </c>
       <c r="I9" t="n">
         <v>0.01217656761772757</v>
@@ -4669,7 +4669,7 @@
         <v>0.01222454232684718</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01331941379245586</v>
+        <v>0.01331941379245587</v>
       </c>
       <c r="L9" t="n">
         <v>0.01256553497726412</v>
@@ -4690,19 +4690,19 @@
         <v>0.01124449991569611</v>
       </c>
       <c r="R9" t="n">
-        <v>0.01097510684802287</v>
+        <v>0.01097510684802286</v>
       </c>
       <c r="S9" t="n">
         <v>0.01260095425907366</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01209516109310338</v>
+        <v>0.01209516109310339</v>
       </c>
       <c r="U9" t="n">
         <v>0.01417764655448337</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0115808283534634</v>
+        <v>0.01233042771657539</v>
       </c>
       <c r="W9" t="n">
         <v>0.01146952329341236</v>
@@ -4711,10 +4711,10 @@
         <v>0.01734075835941463</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.01768239009344398</v>
+        <v>0.01768239009344399</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.01168330811407352</v>
+        <v>0.0112916706550234</v>
       </c>
       <c r="AA9" t="n">
         <v>0.01283272799181173</v>
@@ -4886,7 +4886,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003881658471006679</v>
+        <v>0.003881658471006691</v>
       </c>
       <c r="C2" t="n">
         <v>0.003499259087885846</v>
@@ -4895,19 +4895,19 @@
         <v>0.003928365579078565</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003882535624564613</v>
+        <v>0.003882535624564618</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003870380710197178</v>
+        <v>0.003870380710197176</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003931505629238635</v>
+        <v>0.003931505629238636</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003883924668451437</v>
+        <v>0.00388392466845144</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003899143045175842</v>
+        <v>0.003899143045175846</v>
       </c>
       <c r="J2" t="n">
         <v>0.003913734509460385</v>
@@ -4916,55 +4916,55 @@
         <v>0.003953106861082458</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003942777130248605</v>
+        <v>0.003942777130248606</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003903336493579154</v>
+        <v>0.003903336493579151</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003923339218874477</v>
+        <v>0.003923339218874476</v>
       </c>
       <c r="O2" t="n">
-        <v>0.005618453274500378</v>
+        <v>0.00561845327450038</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003930226790258164</v>
+        <v>0.003930226790258163</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.00389002247594882</v>
+        <v>0.003890022475948827</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003882177311272367</v>
+        <v>0.003882177311272368</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003899417459862579</v>
+        <v>0.00389941745986258</v>
       </c>
       <c r="T2" t="n">
         <v>0.003885884589932644</v>
       </c>
       <c r="U2" t="n">
-        <v>0.003983763111971469</v>
+        <v>0.003983763111971479</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003871941291022007</v>
+        <v>0.003871941291022009</v>
       </c>
       <c r="W2" t="n">
-        <v>0.003901811916171415</v>
+        <v>0.003901811916171427</v>
       </c>
       <c r="X2" t="n">
-        <v>0.003938104113064199</v>
+        <v>0.003938104113064211</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.00389682734620944</v>
+        <v>0.003896827346209441</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.004895242431779244</v>
+        <v>0.00489524243177924</v>
       </c>
       <c r="AA2" t="n">
         <v>0.003946782848892006</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.004292114978774204</v>
+        <v>0.004292114978774202</v>
       </c>
     </row>
     <row r="3">
@@ -4977,82 +4977,82 @@
         <v>0.003801718855312581</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003030825266089502</v>
+        <v>0.003030825266089499</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004137273073521149</v>
+        <v>0.004137273073521151</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003807332804790463</v>
+        <v>0.003807332804790462</v>
       </c>
       <c r="F3" t="n">
         <v>0.003722662476694246</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004154430508024475</v>
+        <v>0.004154430508024483</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003820172820599447</v>
+        <v>0.003820172820599441</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003928570949368198</v>
+        <v>0.003928570949368195</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004029866118009713</v>
+        <v>0.004029866118009723</v>
       </c>
       <c r="K3" t="n">
-        <v>0.004310854827787212</v>
+        <v>0.004310854827787225</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004235122594015207</v>
+        <v>0.00423512259401521</v>
       </c>
       <c r="M3" t="n">
-        <v>0.003962837320244075</v>
+        <v>0.003962837320244076</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004099988708790296</v>
+        <v>0.004099988708790298</v>
       </c>
       <c r="O3" t="n">
-        <v>0.006673241396617207</v>
+        <v>0.006673241396617205</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004147141136226854</v>
+        <v>0.00414714113622686</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003862204333339802</v>
+        <v>0.003862204333339799</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003807409135836012</v>
+        <v>0.003807409135836014</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003926640641581824</v>
+        <v>0.003926640641581829</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003833152772446975</v>
+        <v>0.00383315277244698</v>
       </c>
       <c r="U3" t="n">
-        <v>0.004537202623962098</v>
+        <v>0.004537202623962103</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003732812642087225</v>
+        <v>0.003732812642087241</v>
       </c>
       <c r="W3" t="n">
-        <v>0.004144499030065352</v>
+        <v>0.00414449903006537</v>
       </c>
       <c r="X3" t="n">
-        <v>0.004206442777863056</v>
+        <v>0.004206442777863059</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.003910878435814197</v>
+        <v>0.003910878435814205</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.005568623174113253</v>
+        <v>0.005568623174113261</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.004267546191620427</v>
+        <v>0.004267546191620428</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.006712641572959449</v>
+        <v>0.006712641572959446</v>
       </c>
     </row>
     <row r="4">
@@ -5071,7 +5071,7 @@
         <v>0.008216891662988878</v>
       </c>
       <c r="E4" t="n">
-        <v>0.007699221243933108</v>
+        <v>0.007699221243933106</v>
       </c>
       <c r="F4" t="n">
         <v>0.007561925894616051</v>
@@ -5089,10 +5089,10 @@
         <v>0.008047970290629331</v>
       </c>
       <c r="K4" t="n">
-        <v>0.008496355824774914</v>
+        <v>0.00849635582477491</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008379676763095593</v>
+        <v>0.008379676763095591</v>
       </c>
       <c r="M4" t="n">
         <v>0.00794455152424842</v>
@@ -5107,31 +5107,31 @@
         <v>0.008237914899461901</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.007783788674439603</v>
+        <v>0.007783788674439602</v>
       </c>
       <c r="R4" t="n">
-        <v>0.007695173930464959</v>
+        <v>0.007695173930464956</v>
       </c>
       <c r="S4" t="n">
-        <v>0.007889909339651538</v>
+        <v>0.007889909339651537</v>
       </c>
       <c r="T4" t="n">
-        <v>0.007737049348365196</v>
+        <v>0.007737049348365195</v>
       </c>
       <c r="U4" t="n">
-        <v>0.008847064397553357</v>
+        <v>0.008847064397553358</v>
       </c>
       <c r="V4" t="n">
-        <v>0.007554850382002326</v>
+        <v>0.007554850382002324</v>
       </c>
       <c r="W4" t="n">
-        <v>0.008324357600469224</v>
+        <v>0.008324357600469222</v>
       </c>
       <c r="X4" t="n">
         <v>0.008326892884303619</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.00784785325731136</v>
+        <v>0.007847853257311358</v>
       </c>
       <c r="Z4" t="n">
         <v>0.007884362782362086</v>
@@ -5150,10 +5150,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01427436157035501</v>
+        <v>0.01427436157035502</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00946873830174438</v>
+        <v>0.009468738301744375</v>
       </c>
       <c r="D5" t="n">
         <v>0.02547510886656053</v>
@@ -5162,10 +5162,10 @@
         <v>0.0141022353102078</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01266300996474852</v>
+        <v>0.01266300996474857</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02322412791180388</v>
+        <v>0.02322412791180391</v>
       </c>
       <c r="H5" t="n">
         <v>0.01602638901706481</v>
@@ -5177,22 +5177,22 @@
         <v>0.0206869284110916</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02909184120729449</v>
+        <v>0.02909184120729445</v>
       </c>
       <c r="L5" t="n">
         <v>0.025768691865521</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01952552941733622</v>
+        <v>0.01952552941733621</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03478789430679163</v>
+        <v>0.03478789430679164</v>
       </c>
       <c r="O5" t="n">
         <v>0.01434576685133382</v>
       </c>
       <c r="P5" t="n">
-        <v>0.02397307938600793</v>
+        <v>0.02397307938600794</v>
       </c>
       <c r="Q5" t="n">
         <v>0.01650069539632577</v>
@@ -5204,31 +5204,31 @@
         <v>0.01705223135358884</v>
       </c>
       <c r="T5" t="n">
-        <v>0.015884316140244</v>
+        <v>0.01588431614024399</v>
       </c>
       <c r="U5" t="n">
         <v>0.03548764164921811</v>
       </c>
       <c r="V5" t="n">
-        <v>0.01242225083290519</v>
+        <v>0.01242225083290513</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02687299129334454</v>
+        <v>0.02687299129334453</v>
       </c>
       <c r="X5" t="n">
-        <v>0.02736885829800336</v>
+        <v>0.02736885829800335</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.01801376829639026</v>
+        <v>0.01801376829639027</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01743963743831876</v>
+        <v>0.01743963743831874</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.02875681963489287</v>
+        <v>0.02875681963489288</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1071480050506687</v>
+        <v>0.1071480050506686</v>
       </c>
     </row>
     <row r="6">
@@ -5238,82 +5238,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.008064947245576194</v>
+        <v>0.008064947245576187</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008590893131389523</v>
+        <v>0.008590893131389521</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009407907663056264</v>
+        <v>0.00859252551757933</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008890237244000499</v>
+        <v>0.008074855098523558</v>
       </c>
       <c r="F6" t="n">
-        <v>0.008752941894683439</v>
+        <v>0.00875294189468344</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008627993828631808</v>
+        <v>0.009443375974108733</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008090544988217005</v>
+        <v>0.008090544988216998</v>
       </c>
       <c r="I6" t="n">
-        <v>0.009077825699595329</v>
+        <v>0.008262443554118391</v>
       </c>
       <c r="J6" t="n">
-        <v>0.008423604145219792</v>
+        <v>0.008423604145219785</v>
       </c>
       <c r="K6" t="n">
-        <v>0.009687371824842304</v>
+        <v>0.008871989679365365</v>
       </c>
       <c r="L6" t="n">
-        <v>0.009570692763162985</v>
+        <v>0.008755310617686043</v>
       </c>
       <c r="M6" t="n">
-        <v>0.008320185378838876</v>
+        <v>0.00913556752431581</v>
       </c>
       <c r="N6" t="n">
         <v>0.008537021502963194</v>
       </c>
       <c r="O6" t="n">
-        <v>0.008892558029736097</v>
+        <v>0.008892558029736101</v>
       </c>
       <c r="P6" t="n">
-        <v>0.009431195926987775</v>
+        <v>0.008582742975031603</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.00897480467450699</v>
+        <v>0.008974804674506988</v>
       </c>
       <c r="R6" t="n">
-        <v>0.008886189930532345</v>
+        <v>0.008070807785055411</v>
       </c>
       <c r="S6" t="n">
-        <v>0.009080925339718923</v>
+        <v>0.008265543194241986</v>
       </c>
       <c r="T6" t="n">
-        <v>0.008112683202955653</v>
+        <v>0.008928065348432587</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01005087995473764</v>
+        <v>0.009235497809260701</v>
       </c>
       <c r="V6" t="n">
-        <v>0.007930484236592787</v>
+        <v>0.008745866382069714</v>
       </c>
       <c r="W6" t="n">
-        <v>0.008731944749363165</v>
+        <v>0.008731944749363169</v>
       </c>
       <c r="X6" t="n">
-        <v>0.00870252673889408</v>
+        <v>0.00870252673889407</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.00826035978809775</v>
+        <v>0.008260359788097747</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.008259996636952541</v>
+        <v>0.009075378782429477</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.008800557052484843</v>
+        <v>0.009615939197961774</v>
       </c>
       <c r="AB6" t="n">
         <v>0.01267367951230727</v>
@@ -5329,19 +5329,19 @@
         <v>0.008291352807723085</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008001916548059481</v>
+        <v>0.008001916548059483</v>
       </c>
       <c r="D7" t="n">
-        <v>0.008818931079726228</v>
+        <v>0.008818931079726231</v>
       </c>
       <c r="E7" t="n">
-        <v>0.008301260660670459</v>
+        <v>0.008301260660670457</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008163965311353404</v>
+        <v>0.008163965311353402</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0088543993907787</v>
+        <v>0.008854399390778698</v>
       </c>
       <c r="H7" t="n">
         <v>0.008316950550363899</v>
@@ -5353,7 +5353,7 @@
         <v>0.008650009707366681</v>
       </c>
       <c r="K7" t="n">
-        <v>0.009098395241512264</v>
+        <v>0.009098395241512262</v>
       </c>
       <c r="L7" t="n">
         <v>0.008981716179832944</v>
@@ -5365,46 +5365,46 @@
         <v>0.008762156028981094</v>
       </c>
       <c r="O7" t="n">
-        <v>0.008301282981088271</v>
+        <v>0.00830128298108827</v>
       </c>
       <c r="P7" t="n">
-        <v>0.008839930524326219</v>
+        <v>0.008839930524326222</v>
       </c>
       <c r="Q7" t="n">
         <v>0.008385828091176955</v>
       </c>
       <c r="R7" t="n">
-        <v>0.008297213347202306</v>
+        <v>0.008297213347202305</v>
       </c>
       <c r="S7" t="n">
-        <v>0.008491948756388888</v>
+        <v>0.008491948756388886</v>
       </c>
       <c r="T7" t="n">
-        <v>0.008339088765102547</v>
+        <v>0.008339088765102549</v>
       </c>
       <c r="U7" t="n">
         <v>0.009460819028066152</v>
       </c>
       <c r="V7" t="n">
-        <v>0.008156889798739677</v>
+        <v>0.008156889798739676</v>
       </c>
       <c r="W7" t="n">
-        <v>0.008926397017206574</v>
+        <v>0.008926397017206576</v>
       </c>
       <c r="X7" t="n">
         <v>0.008928932301040972</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0084626922311656</v>
+        <v>0.008462692231165603</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.008486402199099435</v>
+        <v>0.008486402199099437</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.009026962614631736</v>
+        <v>0.009026962614631737</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01287287782993044</v>
+        <v>0.01287287782993043</v>
       </c>
     </row>
     <row r="8">
@@ -5423,13 +5423,13 @@
         <v>0.01151964814749354</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01100197772843777</v>
+        <v>0.01028047508201856</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009720767430993477</v>
+        <v>0.00972076743099348</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01155511645854601</v>
+        <v>0.01183608652800272</v>
       </c>
       <c r="H8" t="n">
         <v>0.01101766761813121</v>
@@ -5441,13 +5441,13 @@
         <v>0.011350726775134</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01179911230927958</v>
+        <v>0.01179911230927957</v>
       </c>
       <c r="L8" t="n">
         <v>0.01168243324760025</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01124730800875308</v>
+        <v>0.01124730800875283</v>
       </c>
       <c r="N8" t="n">
         <v>0.01041251396170889</v>
@@ -5459,7 +5459,7 @@
         <v>0.01070820550629227</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.009465245235385897</v>
+        <v>0.009465245235385894</v>
       </c>
       <c r="R8" t="n">
         <v>0.01099793041496962</v>
@@ -5471,28 +5471,28 @@
         <v>0.01103980583286986</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0113280463250456</v>
+        <v>0.01150043643282469</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01085760686650699</v>
+        <v>0.01048635577616949</v>
       </c>
       <c r="W8" t="n">
         <v>0.01162738038313921</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01013253876831626</v>
+        <v>0.01013253876831625</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01250925847689741</v>
+        <v>0.0125092584768974</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01118711926686674</v>
+        <v>0.009806939658875469</v>
       </c>
       <c r="AA8" t="n">
         <v>0.01172767968239905</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01698901573815473</v>
+        <v>0.01698901573815472</v>
       </c>
     </row>
     <row r="9">
@@ -5502,7 +5502,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.009687554656318357</v>
+        <v>0.009687554656318358</v>
       </c>
       <c r="C9" t="n">
         <v>0.01000185540712718</v>
@@ -5511,13 +5511,13 @@
         <v>0.01081886993879393</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01030119951973816</v>
+        <v>0.01016185965087295</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01016390417042111</v>
+        <v>0.008772125296404394</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0108543382498464</v>
+        <v>0.01085433847157354</v>
       </c>
       <c r="H9" t="n">
         <v>0.0103168894094316</v>
@@ -5532,16 +5532,16 @@
         <v>0.01109833410057997</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01098165503890064</v>
+        <v>0.01098165503890065</v>
       </c>
       <c r="M9" t="n">
         <v>0.01054652980005347</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01076209488804879</v>
+        <v>0.0107620948880488</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01050132358198063</v>
+        <v>0.01050132358198064</v>
       </c>
       <c r="P9" t="n">
         <v>0.0110834845983517</v>
@@ -5562,7 +5562,7 @@
         <v>0.0114618422304753</v>
       </c>
       <c r="V9" t="n">
-        <v>0.01015682865780738</v>
+        <v>0.01085352815406552</v>
       </c>
       <c r="W9" t="n">
         <v>0.01092633587627428</v>
@@ -5574,13 +5574,13 @@
         <v>0.0104626310902333</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.01048634105816714</v>
+        <v>0.01012234141528731</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.01102690147369943</v>
+        <v>0.01102690147369944</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.01487281668899814</v>
+        <v>0.01487281668899815</v>
       </c>
     </row>
   </sheetData>
@@ -5746,82 +5746,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003881123028789565</v>
+        <v>0.003881123028789562</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003572163244156303</v>
+        <v>0.003572163244156304</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003896482115266019</v>
+        <v>0.003896482115266013</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003892896733464525</v>
+        <v>0.00389289673346452</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003889867977195539</v>
+        <v>0.003889867977195536</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00388861432552818</v>
+        <v>0.003888614325528174</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003890695893106888</v>
+        <v>0.003890695893106883</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003891398062849113</v>
+        <v>0.003891398062849114</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003894490657562974</v>
+        <v>0.003894490657562979</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003888570071506581</v>
+        <v>0.003888570071506579</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003892277177157343</v>
+        <v>0.003892277177157333</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003882137981284841</v>
+        <v>0.003882137981284845</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003891905964811793</v>
+        <v>0.003891905964811791</v>
       </c>
       <c r="O2" t="n">
-        <v>0.005634702035572607</v>
+        <v>0.005634702035572605</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003892595777159376</v>
+        <v>0.00389259577715937</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.00388041727395463</v>
+        <v>0.003880417273954626</v>
       </c>
       <c r="R2" t="n">
-        <v>0.00390515069401999</v>
+        <v>0.003905150694019985</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003895346875284532</v>
+        <v>0.003895346875284529</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003882358704641254</v>
+        <v>0.003882358704641249</v>
       </c>
       <c r="U2" t="n">
-        <v>0.003919929744865178</v>
+        <v>0.003919929744865181</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003893039085238876</v>
+        <v>0.003893039085238872</v>
       </c>
       <c r="W2" t="n">
-        <v>0.003924609538348826</v>
+        <v>0.003924609538348818</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004051597018974306</v>
+        <v>0.004051597018974302</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003992532193839391</v>
+        <v>0.003992532193839389</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.004863720228724175</v>
+        <v>0.004863720228724169</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003913595053049381</v>
+        <v>0.003913595053049378</v>
       </c>
       <c r="AB2" t="n">
         <v>0.003875238378919063</v>
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003705980642734149</v>
+        <v>0.003705980642734144</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003212456478895373</v>
+        <v>0.003212456478895372</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003816024224121555</v>
+        <v>0.00381602422412155</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003788736962029457</v>
+        <v>0.003788736962029447</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003769038439540232</v>
+        <v>0.003769038439540231</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003759055731266567</v>
+        <v>0.003759055731266565</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003775477584489055</v>
+        <v>0.003775477584489053</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003780063706575781</v>
+        <v>0.003780063706575772</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003801183504421967</v>
+        <v>0.003801183504421968</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003759436594749286</v>
+        <v>0.003759436594749284</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003784974529906787</v>
+        <v>0.003784974529906779</v>
       </c>
       <c r="M3" t="n">
-        <v>0.003720125917510446</v>
+        <v>0.00372012591751045</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003783129360073819</v>
+        <v>0.003783129360073817</v>
       </c>
       <c r="O3" t="n">
-        <v>0.006670362932193984</v>
+        <v>0.00667036293219398</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003787431723905107</v>
+        <v>0.00378743172390511</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003701193627099289</v>
+        <v>0.003701193627099285</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003878652221465693</v>
+        <v>0.003878652221465688</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003806537550792129</v>
+        <v>0.003806537550792126</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003715402729727278</v>
+        <v>0.003715402729727272</v>
       </c>
       <c r="U3" t="n">
-        <v>0.003778018012624021</v>
+        <v>0.003778018012624017</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003790547816962866</v>
+        <v>0.003790547816962856</v>
       </c>
       <c r="W3" t="n">
-        <v>0.003948169684959041</v>
+        <v>0.003948169684959034</v>
       </c>
       <c r="X3" t="n">
-        <v>0.004920724755106532</v>
+        <v>0.004920724755106529</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.004501619615262999</v>
+        <v>0.004501619615262996</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.005422133970853377</v>
+        <v>0.005422133970853373</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003938083691790758</v>
+        <v>0.003938083691790753</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.00367035163107332</v>
+        <v>0.003670351631073315</v>
       </c>
     </row>
     <row r="4">
@@ -5922,85 +5922,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.007418141749756668</v>
+        <v>0.00741814174975667</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007452165079104757</v>
+        <v>0.007452165079104754</v>
       </c>
       <c r="D4" t="n">
-        <v>0.007591629697037046</v>
+        <v>0.007591629697037044</v>
       </c>
       <c r="E4" t="n">
-        <v>0.007551131160232131</v>
+        <v>0.007551131160232128</v>
       </c>
       <c r="F4" t="n">
-        <v>0.007516919964877198</v>
+        <v>0.007516919964877204</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007502759392586102</v>
+        <v>0.0075027593925861</v>
       </c>
       <c r="H4" t="n">
-        <v>0.007526271655956003</v>
+        <v>0.007526271655956</v>
       </c>
       <c r="I4" t="n">
-        <v>0.007534202986208487</v>
+        <v>0.007534202986208486</v>
       </c>
       <c r="J4" t="n">
-        <v>0.007565937466530146</v>
+        <v>0.007565937466530147</v>
       </c>
       <c r="K4" t="n">
-        <v>0.007502259523054321</v>
+        <v>0.007502259523054316</v>
       </c>
       <c r="L4" t="n">
-        <v>0.007544132986732499</v>
+        <v>0.007544132986732498</v>
       </c>
       <c r="M4" t="n">
-        <v>0.007441105621522622</v>
+        <v>0.00744110562152262</v>
       </c>
       <c r="N4" t="n">
-        <v>0.007539939972523418</v>
+        <v>0.00753993997252342</v>
       </c>
       <c r="O4" t="n">
-        <v>0.007563049724431866</v>
+        <v>0.00756304972443187</v>
       </c>
       <c r="P4" t="n">
         <v>0.007547731720318715</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.007410169924232839</v>
+        <v>0.00741016992423284</v>
       </c>
       <c r="R4" t="n">
-        <v>0.007689545281806476</v>
+        <v>0.007689545281806475</v>
       </c>
       <c r="S4" t="n">
-        <v>0.007578806639209975</v>
+        <v>0.00757880663920997</v>
       </c>
       <c r="T4" t="n">
         <v>0.00743209927694051</v>
       </c>
       <c r="U4" t="n">
-        <v>0.007428262994256356</v>
+        <v>0.007428262994256357</v>
       </c>
       <c r="V4" t="n">
-        <v>0.00753112164399431</v>
+        <v>0.007531121643994314</v>
       </c>
       <c r="W4" t="n">
-        <v>0.007769747548865221</v>
+        <v>0.007769747548865218</v>
       </c>
       <c r="X4" t="n">
-        <v>0.009343723890803296</v>
+        <v>0.009343723890803301</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.008670648067945088</v>
+        <v>0.00867064806794509</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.007613918421487689</v>
+        <v>0.007613918421487684</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.007784928201640518</v>
+        <v>0.007784928201640512</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.007362030881444673</v>
+        <v>0.007362030881444678</v>
       </c>
     </row>
     <row r="5">
@@ -6016,25 +6016,25 @@
         <v>0.01120786222310443</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01362761630392678</v>
+        <v>0.01362761630392676</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01203127674146092</v>
+        <v>0.01203127674146093</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01242007871173036</v>
+        <v>0.01242007871173035</v>
       </c>
       <c r="G5" t="n">
         <v>0.01163309008508489</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0128602766682827</v>
+        <v>0.01286027666828269</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0127801552217171</v>
+        <v>0.01278015522171711</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01290133641091182</v>
+        <v>0.01290133641091181</v>
       </c>
       <c r="K5" t="n">
         <v>0.01198529964219891</v>
@@ -6049,7 +6049,7 @@
         <v>0.01080650192197832</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01258847278272581</v>
+        <v>0.0125884727827258</v>
       </c>
       <c r="P5" t="n">
         <v>0.01240786102450918</v>
@@ -6058,37 +6058,37 @@
         <v>0.01032749917908182</v>
       </c>
       <c r="R5" t="n">
-        <v>0.015753223582063</v>
+        <v>0.01575322358206302</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01268338446482556</v>
+        <v>0.01268338446482555</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0108982970700072</v>
+        <v>0.01089829707000719</v>
       </c>
       <c r="U5" t="n">
         <v>0.01070073639550863</v>
       </c>
       <c r="V5" t="n">
-        <v>0.01245002627448668</v>
+        <v>0.01245002627448674</v>
       </c>
       <c r="W5" t="n">
         <v>0.0163641774381362</v>
       </c>
       <c r="X5" t="n">
-        <v>0.04339210692173692</v>
+        <v>0.04339210692173694</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0328584662333094</v>
+        <v>0.03285846623330944</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01333788419787345</v>
+        <v>0.01333788419787346</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01700681534984784</v>
+        <v>0.01700681534984783</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.009730946736692352</v>
+        <v>0.009730946736692348</v>
       </c>
     </row>
     <row r="6">
@@ -6098,85 +6098,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.007926860105606465</v>
+        <v>0.007926860105606469</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008705370063662647</v>
+        <v>0.007960883434954552</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008100348052886843</v>
+        <v>0.008100348052886839</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008804336144790023</v>
+        <v>0.008804336144790021</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00877012494943509</v>
+        <v>0.008770124949435092</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008755964377143991</v>
+        <v>0.008011477748435896</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008779476640513895</v>
+        <v>0.0080349900118058</v>
       </c>
       <c r="I6" t="n">
         <v>0.008042921342058286</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00881914245108804</v>
+        <v>0.008074655822379944</v>
       </c>
       <c r="K6" t="n">
-        <v>0.008010977878904106</v>
+        <v>0.00801097787890411</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008797337971290387</v>
+        <v>0.008797337971290389</v>
       </c>
       <c r="M6" t="n">
-        <v>0.007949823977372412</v>
+        <v>0.008694310606080509</v>
       </c>
       <c r="N6" t="n">
-        <v>0.008048945948591945</v>
+        <v>0.00804894594859195</v>
       </c>
       <c r="O6" t="n">
-        <v>0.008072055700500395</v>
+        <v>0.008072055700500397</v>
       </c>
       <c r="P6" t="n">
-        <v>0.008803347840039341</v>
+        <v>0.00801603031846774</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.008663374908790733</v>
+        <v>0.007918888280082635</v>
       </c>
       <c r="R6" t="n">
-        <v>0.008942750266364371</v>
+        <v>0.008942750266364364</v>
       </c>
       <c r="S6" t="n">
-        <v>0.008832011623767864</v>
+        <v>0.008087524995059768</v>
       </c>
       <c r="T6" t="n">
-        <v>0.008685304261498404</v>
+        <v>0.008685304261498402</v>
       </c>
       <c r="U6" t="n">
         <v>0.007942892801903526</v>
       </c>
       <c r="V6" t="n">
-        <v>0.008039839999844112</v>
+        <v>0.008784326628552205</v>
       </c>
       <c r="W6" t="n">
-        <v>0.008315536929256132</v>
+        <v>0.008315536929256125</v>
       </c>
       <c r="X6" t="n">
-        <v>0.009852442246653093</v>
+        <v>0.009852442246653095</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.009216344008992967</v>
+        <v>0.009216344008992973</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.008867123406045577</v>
+        <v>0.008867123406045578</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.008293646557490314</v>
+        <v>0.009038133186198406</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.007869779337010574</v>
+        <v>0.007869779337010573</v>
       </c>
     </row>
     <row r="7">
@@ -6186,85 +6186,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007920584064431795</v>
+        <v>0.007920584064431791</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007954607393779876</v>
+        <v>0.007954607393779877</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00809407201171217</v>
+        <v>0.008094072011712168</v>
       </c>
       <c r="E7" t="n">
         <v>0.008053573474907254</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008019362279552324</v>
+        <v>0.008019362279552326</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008005201707261224</v>
+        <v>0.008005201707261222</v>
       </c>
       <c r="H7" t="n">
-        <v>0.008028713970631126</v>
+        <v>0.008028713970631127</v>
       </c>
       <c r="I7" t="n">
         <v>0.00803664530088361</v>
       </c>
       <c r="J7" t="n">
-        <v>0.008068379781205271</v>
+        <v>0.008068379781205269</v>
       </c>
       <c r="K7" t="n">
         <v>0.008004701837729439</v>
       </c>
       <c r="L7" t="n">
-        <v>0.008046575301407623</v>
+        <v>0.008046575301407621</v>
       </c>
       <c r="M7" t="n">
         <v>0.00794354793619774</v>
       </c>
       <c r="N7" t="n">
-        <v>0.008042382287198545</v>
+        <v>0.008042382287198543</v>
       </c>
       <c r="O7" t="n">
-        <v>0.008065469740007018</v>
+        <v>0.008065469740007014</v>
       </c>
       <c r="P7" t="n">
-        <v>0.00805015173589386</v>
+        <v>0.008050151735893855</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.007912612238907966</v>
+        <v>0.007912612238907964</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0081919875964816</v>
+        <v>0.008191987596481598</v>
       </c>
       <c r="S7" t="n">
-        <v>0.008081248953885099</v>
+        <v>0.008081248953885097</v>
       </c>
       <c r="T7" t="n">
         <v>0.007934541591615631</v>
       </c>
       <c r="U7" t="n">
-        <v>0.00793538591433538</v>
+        <v>0.007935385914335374</v>
       </c>
       <c r="V7" t="n">
-        <v>0.008033563958669438</v>
+        <v>0.008033563958669434</v>
       </c>
       <c r="W7" t="n">
-        <v>0.008272189863540344</v>
+        <v>0.008272189863540341</v>
       </c>
       <c r="X7" t="n">
-        <v>0.009846166205478415</v>
+        <v>0.009846166205478421</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.009179001834417586</v>
+        <v>0.00917900183441759</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.008116360736162807</v>
+        <v>0.008116360736162806</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.008287370516315642</v>
+        <v>0.00828737051631564</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0078644731961198</v>
+        <v>0.007864473196119801</v>
       </c>
     </row>
     <row r="8">
@@ -6274,7 +6274,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00917841509383689</v>
+        <v>0.009178415093836895</v>
       </c>
       <c r="C8" t="n">
         <v>0.01045849866913974</v>
@@ -6283,43 +6283,43 @@
         <v>0.01059796328707203</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01055746475026712</v>
+        <v>0.009893974425779165</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009471314932259705</v>
+        <v>0.009471314932259707</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01050909298262108</v>
+        <v>0.01076747169194465</v>
       </c>
       <c r="H8" t="n">
-        <v>0.010532605245991</v>
+        <v>0.01053260524599099</v>
       </c>
       <c r="I8" t="n">
         <v>0.01054053657624347</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01057227105656512</v>
+        <v>0.01057227105656513</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0105085931130893</v>
+        <v>0.01050859311308929</v>
       </c>
       <c r="L8" t="n">
         <v>0.01055046657676748</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0104474392115576</v>
+        <v>0.01044743921155728</v>
       </c>
       <c r="N8" t="n">
-        <v>0.009580368410597576</v>
+        <v>0.00958036841059757</v>
       </c>
       <c r="O8" t="n">
-        <v>0.009868917285065965</v>
+        <v>0.00986891728506597</v>
       </c>
       <c r="P8" t="n">
-        <v>0.009788533738106203</v>
+        <v>0.009788533738106201</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.008925563990053261</v>
+        <v>0.008925563990053263</v>
       </c>
       <c r="R8" t="n">
         <v>0.01069587887184146</v>
@@ -6331,22 +6331,22 @@
         <v>0.0104384328669755</v>
       </c>
       <c r="U8" t="n">
-        <v>0.009672867991927585</v>
+        <v>0.009831386066516614</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01053745523402929</v>
+        <v>0.01019585514417276</v>
       </c>
       <c r="W8" t="n">
         <v>0.01077632602541421</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01097332185410776</v>
+        <v>0.01097332185410777</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01292022020949294</v>
+        <v>0.01292022020949295</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01062025201152267</v>
+        <v>0.00935104555677289</v>
       </c>
       <c r="AA8" t="n">
         <v>0.0107912617916755</v>
@@ -6362,70 +6362,70 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.009013769937203911</v>
+        <v>0.00901376993720391</v>
       </c>
       <c r="C9" t="n">
-        <v>0.009544611707495739</v>
+        <v>0.009544611707495735</v>
       </c>
       <c r="D9" t="n">
-        <v>0.009684076325428028</v>
+        <v>0.009684076325428025</v>
       </c>
       <c r="E9" t="n">
-        <v>0.009643577788623115</v>
+        <v>0.009528914318747682</v>
       </c>
       <c r="F9" t="n">
-        <v>0.009609366593268186</v>
+        <v>0.008464064153217255</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009595206020977081</v>
+        <v>0.009595206280737654</v>
       </c>
       <c r="H9" t="n">
-        <v>0.009618718284346987</v>
+        <v>0.009618718284346984</v>
       </c>
       <c r="I9" t="n">
-        <v>0.009626649614599476</v>
+        <v>0.009626649614599471</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009658384094921131</v>
+        <v>0.009658384094921129</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009594706151445304</v>
+        <v>0.009594706151445295</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009636579615123486</v>
+        <v>0.009636579615123481</v>
       </c>
       <c r="M9" t="n">
-        <v>0.009533552249913599</v>
+        <v>0.009533552249913597</v>
       </c>
       <c r="N9" t="n">
-        <v>0.009632386600914403</v>
+        <v>0.0096323866009144</v>
       </c>
       <c r="O9" t="n">
-        <v>0.009820141679468271</v>
+        <v>0.009820141679468267</v>
       </c>
       <c r="P9" t="n">
-        <v>0.009840631152568936</v>
+        <v>0.009840631152568932</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.009502616812384401</v>
+        <v>0.009502616812384396</v>
       </c>
       <c r="R9" t="n">
-        <v>0.009781991910197456</v>
+        <v>0.009781991910197454</v>
       </c>
       <c r="S9" t="n">
-        <v>0.009671253267600956</v>
+        <v>0.009671253267600951</v>
       </c>
       <c r="T9" t="n">
         <v>0.009524545905331486</v>
       </c>
       <c r="U9" t="n">
-        <v>0.009526621074444718</v>
+        <v>0.009526621074444713</v>
       </c>
       <c r="V9" t="n">
-        <v>0.009623568272385296</v>
+        <v>0.01019688631364706</v>
       </c>
       <c r="W9" t="n">
-        <v>0.009862194177256202</v>
+        <v>0.009862194177256199</v>
       </c>
       <c r="X9" t="n">
         <v>0.01143617051919428</v>
@@ -6434,13 +6434,13 @@
         <v>0.01076900614813345</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.009706365049878669</v>
+        <v>0.009406827811957126</v>
       </c>
       <c r="AA9" t="n">
         <v>0.009877374830031494</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.009454477509835666</v>
+        <v>0.009454477509835659</v>
       </c>
     </row>
   </sheetData>
@@ -6606,82 +6606,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003753891341813413</v>
+        <v>0.003753891341813414</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003345933605001262</v>
+        <v>0.003345933605001261</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003758703228328575</v>
+        <v>0.003758703228328576</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003764942324250907</v>
+        <v>0.003764942324250911</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003755361878445195</v>
+        <v>0.003755361878445198</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003751769339052945</v>
+        <v>0.003751769339052948</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003753118869359134</v>
+        <v>0.003753118869359136</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003753137081410382</v>
+        <v>0.003753137081410384</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003759494875103356</v>
+        <v>0.003759494875103357</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00375224213643627</v>
+        <v>0.003752242136436274</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003759811607370261</v>
+        <v>0.003759811607370264</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003749504958223866</v>
+        <v>0.003749504958223863</v>
       </c>
       <c r="N2" t="n">
-        <v>0.00375287951871874</v>
+        <v>0.003752879518718742</v>
       </c>
       <c r="O2" t="n">
-        <v>0.005454953568144243</v>
+        <v>0.005454953568144245</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003760442184812253</v>
+        <v>0.003760442184812256</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003747778013822977</v>
+        <v>0.003747778013822979</v>
       </c>
       <c r="R2" t="n">
-        <v>0.00377059230863991</v>
+        <v>0.003770592308639911</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003759238749154382</v>
+        <v>0.003759238749154385</v>
       </c>
       <c r="T2" t="n">
-        <v>0.00374822485280432</v>
+        <v>0.003748224852804322</v>
       </c>
       <c r="U2" t="n">
-        <v>0.003627059494511488</v>
+        <v>0.003627059494511486</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003763912173406909</v>
+        <v>0.003763912173406911</v>
       </c>
       <c r="W2" t="n">
-        <v>0.003626907601488849</v>
+        <v>0.003626907601488845</v>
       </c>
       <c r="X2" t="n">
-        <v>0.003970883051158398</v>
+        <v>0.003970883051158397</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003846361357404327</v>
+        <v>0.003846361357404329</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.004752296538290246</v>
+        <v>0.004752296538290251</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003781631827935259</v>
+        <v>0.00378163182793526</v>
       </c>
       <c r="AB2" t="n">
         <v>0.003747490051483502</v>
@@ -6697,82 +6697,82 @@
         <v>0.003606220252701861</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002918078713698463</v>
+        <v>0.002918078713698462</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003641290702336831</v>
+        <v>0.003641290702336829</v>
       </c>
       <c r="E3" t="n">
         <v>0.003683579457580593</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00361763936028671</v>
+        <v>0.003617639360286709</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003591175469697647</v>
+        <v>0.003591175469697648</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003601866937410856</v>
+        <v>0.003601866937410855</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003601720290061975</v>
+        <v>0.003601720290061974</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003646380695039545</v>
+        <v>0.003646380695039543</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003595090665911982</v>
+        <v>0.00359509066591198</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003648255264470275</v>
+        <v>0.003648255264470276</v>
       </c>
       <c r="M3" t="n">
         <v>0.003581025954266781</v>
       </c>
       <c r="N3" t="n">
-        <v>0.00359952066499449</v>
+        <v>0.003599520664994491</v>
       </c>
       <c r="O3" t="n">
-        <v>0.006456131310080487</v>
+        <v>0.006456131310080486</v>
       </c>
       <c r="P3" t="n">
         <v>0.003652586810641031</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003563098137250031</v>
+        <v>0.003563098137250032</v>
       </c>
       <c r="R3" t="n">
         <v>0.003726836493633805</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003644128800739628</v>
+        <v>0.003644128800739627</v>
       </c>
       <c r="T3" t="n">
-        <v>0.00356654998979368</v>
+        <v>0.003566549989793678</v>
       </c>
       <c r="U3" t="n">
-        <v>0.003382107221934304</v>
+        <v>0.003382107221934301</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003677390642202202</v>
+        <v>0.003677390642202208</v>
       </c>
       <c r="W3" t="n">
-        <v>0.003480969805342703</v>
+        <v>0.003480969805342704</v>
       </c>
       <c r="X3" t="n">
-        <v>0.005151137751040707</v>
+        <v>0.005151137751040705</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.004267361096558298</v>
+        <v>0.004267361096558297</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.005284954737600895</v>
+        <v>0.0052849547376009</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003804779707650775</v>
+        <v>0.003804779707650774</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.003565899112956047</v>
+        <v>0.003565899112956046</v>
       </c>
     </row>
     <row r="4">
@@ -6782,85 +6782,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00738162401891755</v>
+        <v>0.007381624018917553</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007351193177459065</v>
+        <v>0.007351193177459068</v>
       </c>
       <c r="D4" t="n">
-        <v>0.007435976490683449</v>
+        <v>0.007435976490683452</v>
       </c>
       <c r="E4" t="n">
-        <v>0.007506449949252159</v>
+        <v>0.007506449949252161</v>
       </c>
       <c r="F4" t="n">
-        <v>0.007398234406653798</v>
+        <v>0.007398234406653801</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007357655021568577</v>
+        <v>0.007357655021568586</v>
       </c>
       <c r="H4" t="n">
-        <v>0.007372898587191601</v>
+        <v>0.007372898587191604</v>
       </c>
       <c r="I4" t="n">
-        <v>0.007373104300688433</v>
+        <v>0.007373104300688435</v>
       </c>
       <c r="J4" t="n">
-        <v>0.007441949994016816</v>
+        <v>0.007441949994016818</v>
       </c>
       <c r="K4" t="n">
         <v>0.007362995485510769</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00744849614183886</v>
+        <v>0.007448496141838862</v>
       </c>
       <c r="M4" t="n">
-        <v>0.007341723079660518</v>
+        <v>0.007341723079660521</v>
       </c>
       <c r="N4" t="n">
-        <v>0.007370195011601602</v>
+        <v>0.007370195011601605</v>
       </c>
       <c r="O4" t="n">
-        <v>0.007468935620690681</v>
+        <v>0.007468935620690684</v>
       </c>
       <c r="P4" t="n">
-        <v>0.007455618804126108</v>
+        <v>0.007455618804126109</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.007312571166995737</v>
+        <v>0.007312571166995741</v>
       </c>
       <c r="R4" t="n">
-        <v>0.007570269122047141</v>
+        <v>0.007570269122047144</v>
       </c>
       <c r="S4" t="n">
-        <v>0.007442025444762687</v>
+        <v>0.00744202544476269</v>
       </c>
       <c r="T4" t="n">
-        <v>0.007317618418846108</v>
+        <v>0.007317618418846109</v>
       </c>
       <c r="U4" t="n">
-        <v>0.007347466053688581</v>
+        <v>0.007347466053688582</v>
       </c>
       <c r="V4" t="n">
-        <v>0.007474730342286805</v>
+        <v>0.007474730342286809</v>
       </c>
       <c r="W4" t="n">
-        <v>0.007554942185041709</v>
+        <v>0.00755494218504171</v>
       </c>
       <c r="X4" t="n">
         <v>0.00983264519708707</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.008422970436182923</v>
+        <v>0.008422970436182927</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.007445850651280355</v>
+        <v>0.007445850651280359</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.007694965570917865</v>
+        <v>0.007694965570917867</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.007317351542833668</v>
+        <v>0.007317351542833672</v>
       </c>
     </row>
     <row r="5">
@@ -6876,25 +6876,25 @@
         <v>0.01099186955764026</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01251094368648399</v>
+        <v>0.01251094368648398</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01259656842342125</v>
+        <v>0.01259656842342126</v>
       </c>
       <c r="F5" t="n">
         <v>0.01194500471232285</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01080039967855074</v>
+        <v>0.01080039967855075</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01161922317285668</v>
+        <v>0.01161922317285667</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01147950627209851</v>
+        <v>0.0114795062720985</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01237590819755122</v>
+        <v>0.01237590819755123</v>
       </c>
       <c r="K5" t="n">
         <v>0.01117511968441958</v>
@@ -6906,19 +6906,19 @@
         <v>0.01091817278235978</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01078167360205666</v>
+        <v>0.01078167360205665</v>
       </c>
       <c r="O5" t="n">
         <v>0.01250319101361132</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01228057611658608</v>
+        <v>0.01228057611658607</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01021494773079119</v>
+        <v>0.0102149477307912</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01524517333077739</v>
+        <v>0.0152451733307774</v>
       </c>
       <c r="S5" t="n">
         <v>0.01210802720969082</v>
@@ -6927,25 +6927,25 @@
         <v>0.01044037529761296</v>
       </c>
       <c r="U5" t="n">
-        <v>0.01076208959128642</v>
+        <v>0.01076208959128643</v>
       </c>
       <c r="V5" t="n">
-        <v>0.01297359677143801</v>
+        <v>0.01297359677143802</v>
       </c>
       <c r="W5" t="n">
-        <v>0.01432928395698762</v>
+        <v>0.0143292839569876</v>
       </c>
       <c r="X5" t="n">
-        <v>0.05257267671875712</v>
+        <v>0.05257267671875709</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03025636272345641</v>
+        <v>0.03025636272345644</v>
       </c>
       <c r="Z5" t="n">
         <v>0.01204317182330283</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01701201792292641</v>
+        <v>0.01701201792292639</v>
       </c>
       <c r="AB5" t="n">
         <v>0.01055428899847168</v>
@@ -6958,58 +6958,58 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.008324948407266787</v>
+        <v>0.008324948407266788</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008294517565808304</v>
+        <v>0.008294517565808303</v>
       </c>
       <c r="D6" t="n">
         <v>0.008379300879032686</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008449774337601397</v>
+        <v>0.008449774337601398</v>
       </c>
       <c r="F6" t="n">
-        <v>0.007669202815371247</v>
+        <v>0.008341558795003036</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007628623430286027</v>
+        <v>0.008300979409917824</v>
       </c>
       <c r="H6" t="n">
         <v>0.007643866995909053</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008316428689037675</v>
+        <v>0.007644072709405886</v>
       </c>
       <c r="J6" t="n">
-        <v>0.008385274382366057</v>
+        <v>0.007712918402734268</v>
       </c>
       <c r="K6" t="n">
-        <v>0.007633963894228219</v>
+        <v>0.008306319873860008</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008391820530188098</v>
+        <v>0.008391820530188096</v>
       </c>
       <c r="M6" t="n">
-        <v>0.008285047468009756</v>
+        <v>0.00828504746800976</v>
       </c>
       <c r="N6" t="n">
-        <v>0.007641173311303631</v>
+        <v>0.00764117331130363</v>
       </c>
       <c r="O6" t="n">
-        <v>0.007739913920392705</v>
+        <v>0.008409444380760538</v>
       </c>
       <c r="P6" t="n">
         <v>0.008396115047900544</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.008255895555344979</v>
+        <v>0.008255895555344974</v>
       </c>
       <c r="R6" t="n">
-        <v>0.008513593510396378</v>
+        <v>0.007841237530764588</v>
       </c>
       <c r="S6" t="n">
-        <v>0.007712993853480135</v>
+        <v>0.007712993853480134</v>
       </c>
       <c r="T6" t="n">
         <v>0.008260942807195342</v>
@@ -7021,22 +7021,22 @@
         <v>0.007745698751004258</v>
       </c>
       <c r="W6" t="n">
-        <v>0.008495461913881624</v>
+        <v>0.008495461913881626</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01077596958543632</v>
+        <v>0.01010361360580452</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.008715354822071621</v>
+        <v>0.008715354822071622</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.008389175039629593</v>
+        <v>0.007716819059997809</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.008638289959267109</v>
+        <v>0.007965933979635317</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0075873464700018</v>
+        <v>0.007587346470001801</v>
       </c>
     </row>
     <row r="7">
@@ -7052,7 +7052,7 @@
         <v>0.007877844815312536</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00796262812853692</v>
+        <v>0.007962628128536917</v>
       </c>
       <c r="E7" t="n">
         <v>0.008033101587105629</v>
@@ -7061,31 +7061,31 @@
         <v>0.007924886044507268</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007884306659422047</v>
+        <v>0.007884306659422056</v>
       </c>
       <c r="H7" t="n">
         <v>0.007899550225045071</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007899755938541905</v>
+        <v>0.007899755938541904</v>
       </c>
       <c r="J7" t="n">
-        <v>0.007968601631870286</v>
+        <v>0.007968601631870284</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007889647123364244</v>
+        <v>0.007889647123364242</v>
       </c>
       <c r="L7" t="n">
         <v>0.00797514777969233</v>
       </c>
       <c r="M7" t="n">
-        <v>0.007868374717513992</v>
+        <v>0.00786837471751399</v>
       </c>
       <c r="N7" t="n">
-        <v>0.007896846649455074</v>
+        <v>0.007896846649455072</v>
       </c>
       <c r="O7" t="n">
-        <v>0.007995565117330648</v>
+        <v>0.007995565117330647</v>
       </c>
       <c r="P7" t="n">
         <v>0.007982248300766074</v>
@@ -7097,19 +7097,19 @@
         <v>0.008096920759900608</v>
       </c>
       <c r="S7" t="n">
-        <v>0.007968677082616161</v>
+        <v>0.007968677082616159</v>
       </c>
       <c r="T7" t="n">
-        <v>0.007844270056699578</v>
+        <v>0.007844270056699576</v>
       </c>
       <c r="U7" t="n">
         <v>0.007876206057496905</v>
       </c>
       <c r="V7" t="n">
-        <v>0.008001381980140275</v>
+        <v>0.008001381980140276</v>
       </c>
       <c r="W7" t="n">
-        <v>0.008081593822895181</v>
+        <v>0.008081593822895177</v>
       </c>
       <c r="X7" t="n">
         <v>0.01035929683494054</v>
@@ -7118,13 +7118,13 @@
         <v>0.008952767021179191</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.007972502289133824</v>
+        <v>0.007972502289133822</v>
       </c>
       <c r="AA7" t="n">
         <v>0.008221617208771338</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.007844003180687141</v>
+        <v>0.007844003180687139</v>
       </c>
     </row>
     <row r="8">
@@ -7134,7 +7134,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.009113369414750241</v>
+        <v>0.009113369414750239</v>
       </c>
       <c r="C8" t="n">
         <v>0.01027651233991045</v>
@@ -7143,43 +7143,43 @@
         <v>0.01036129565313483</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01043176911170355</v>
+        <v>0.009796226289200516</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009315924645735472</v>
+        <v>0.009315924645735467</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01028297418401996</v>
+        <v>0.0105304694799385</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01029821774964299</v>
+        <v>0.01029821774964298</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01029842346313982</v>
+        <v>0.01029842346313981</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0103672691564682</v>
+        <v>0.01036726915646819</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01028831464796216</v>
+        <v>0.01028831464796215</v>
       </c>
       <c r="L8" t="n">
         <v>0.01037381530429024</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0102670422421119</v>
+        <v>0.01026704224211159</v>
       </c>
       <c r="N8" t="n">
-        <v>0.009370294824384491</v>
+        <v>0.009370294824384486</v>
       </c>
       <c r="O8" t="n">
-        <v>0.009723293744314254</v>
+        <v>0.00972329374431425</v>
       </c>
       <c r="P8" t="n">
-        <v>0.009647652072019629</v>
+        <v>0.009647652072019621</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.008809752075693903</v>
+        <v>0.008809752075693901</v>
       </c>
       <c r="R8" t="n">
         <v>0.01049558828449852</v>
@@ -7191,28 +7191,28 @@
         <v>0.01024293758129749</v>
       </c>
       <c r="U8" t="n">
-        <v>0.009540714261928479</v>
+        <v>0.009692561072666478</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01040004950473819</v>
+        <v>0.01007294358373288</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01048049591894837</v>
+        <v>0.01048049591894836</v>
       </c>
       <c r="X8" t="n">
         <v>0.01143921951316914</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01253680635785633</v>
+        <v>0.01253680635785632</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01037116981373174</v>
+        <v>0.009155424801615518</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01062028473336925</v>
+        <v>0.01062028473336924</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01148945830954269</v>
+        <v>0.01148945830954268</v>
       </c>
     </row>
     <row r="9">
@@ -7222,70 +7222,70 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008898105157733279</v>
+        <v>0.008898105157733281</v>
       </c>
       <c r="C9" t="n">
         <v>0.00932764892822701</v>
       </c>
       <c r="D9" t="n">
-        <v>0.009412432241451394</v>
+        <v>0.00941243224145139</v>
       </c>
       <c r="E9" t="n">
-        <v>0.009482905700020104</v>
+        <v>0.009376745584029001</v>
       </c>
       <c r="F9" t="n">
-        <v>0.009374690157421737</v>
+        <v>0.008314322886330367</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009334110772336521</v>
+        <v>0.009334110965061988</v>
       </c>
       <c r="H9" t="n">
         <v>0.009349354337959543</v>
       </c>
       <c r="I9" t="n">
-        <v>0.009349560051456377</v>
+        <v>0.009349560051456381</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009418405744784759</v>
+        <v>0.009418405744784756</v>
       </c>
       <c r="K9" t="n">
         <v>0.00933945123627871</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0094249518926068</v>
+        <v>0.009424951892606802</v>
       </c>
       <c r="M9" t="n">
-        <v>0.009318178830428459</v>
+        <v>0.00931817883042846</v>
       </c>
       <c r="N9" t="n">
-        <v>0.009346650762369549</v>
+        <v>0.009346650762369547</v>
       </c>
       <c r="O9" t="n">
-        <v>0.009597826612168672</v>
+        <v>0.00959782661216867</v>
       </c>
       <c r="P9" t="n">
         <v>0.009617661803195759</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.009289027110489153</v>
+        <v>0.009289027110489156</v>
       </c>
       <c r="R9" t="n">
-        <v>0.009546724872815084</v>
+        <v>0.00954672487281508</v>
       </c>
       <c r="S9" t="n">
-        <v>0.009418481195530628</v>
+        <v>0.009418481195530624</v>
       </c>
       <c r="T9" t="n">
-        <v>0.009294074169614051</v>
+        <v>0.00929407416961405</v>
       </c>
       <c r="U9" t="n">
-        <v>0.009327066751599325</v>
+        <v>0.009327066751599323</v>
       </c>
       <c r="V9" t="n">
-        <v>0.009451186093054748</v>
+        <v>0.009981987077119931</v>
       </c>
       <c r="W9" t="n">
-        <v>0.009531397935809646</v>
+        <v>0.009531397935809647</v>
       </c>
       <c r="X9" t="n">
         <v>0.01180910094785502</v>
@@ -7294,13 +7294,13 @@
         <v>0.01040257113409366</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.009422306402048299</v>
+        <v>0.00914498269010865</v>
       </c>
       <c r="AA9" t="n">
         <v>0.009671421321685815</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.009293807293601609</v>
+        <v>0.009293807293601613</v>
       </c>
     </row>
   </sheetData>
@@ -7466,37 +7466,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004161764072521626</v>
+        <v>0.00416176407252162</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003711652095807794</v>
+        <v>0.003711652095807796</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004171631867455727</v>
+        <v>0.004171631867455728</v>
       </c>
       <c r="E2" t="n">
         <v>0.004087953920326843</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00409979185401804</v>
+        <v>0.004099791854018041</v>
       </c>
       <c r="G2" t="n">
         <v>0.004320263855006889</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004086045530175885</v>
+        <v>0.004086045530175887</v>
       </c>
       <c r="I2" t="n">
         <v>0.004149143452654195</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004210778926235955</v>
+        <v>0.004210778926235952</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004205213629546968</v>
+        <v>0.004205213629546969</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004299083786771625</v>
+        <v>0.00429908378677162</v>
       </c>
       <c r="M2" t="n">
         <v>0.004186358278763709</v>
@@ -7505,7 +7505,7 @@
         <v>0.00418891994706299</v>
       </c>
       <c r="O2" t="n">
-        <v>0.005981250467427237</v>
+        <v>0.005981250467427236</v>
       </c>
       <c r="P2" t="n">
         <v>0.004242576811662825</v>
@@ -7517,34 +7517,34 @@
         <v>0.00410151838910781</v>
       </c>
       <c r="S2" t="n">
-        <v>0.004183522056539221</v>
+        <v>0.004183522056539219</v>
       </c>
       <c r="T2" t="n">
         <v>0.004148034514299804</v>
       </c>
       <c r="U2" t="n">
-        <v>0.00435222274980217</v>
+        <v>0.004352222749802174</v>
       </c>
       <c r="V2" t="n">
-        <v>0.00408845590573058</v>
+        <v>0.004088455905730583</v>
       </c>
       <c r="W2" t="n">
-        <v>0.004166368362259254</v>
+        <v>0.004166368362259253</v>
       </c>
       <c r="X2" t="n">
         <v>0.004368798056780007</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.004266591798016339</v>
+        <v>0.004266591798016342</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.005159852585956764</v>
+        <v>0.005159852585956761</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.004211694479398788</v>
+        <v>0.004211694479398789</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.004218443773948944</v>
+        <v>0.004218443773948943</v>
       </c>
     </row>
     <row r="3">
@@ -7554,85 +7554,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004545749281182111</v>
+        <v>0.004545749281182105</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00329234448673807</v>
+        <v>0.003292344486738072</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004622539387709497</v>
+        <v>0.00462253938770949</v>
       </c>
       <c r="E3" t="n">
-        <v>0.004020986673423003</v>
+        <v>0.004020986673423004</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004108236301547205</v>
+        <v>0.004108236301547202</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005670620278199946</v>
+        <v>0.00567062027819995</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004010593994230015</v>
+        <v>0.004010593994230018</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004461631347956493</v>
+        <v>0.004461631347956491</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004895213682503707</v>
+        <v>0.004895213682503705</v>
       </c>
       <c r="K3" t="n">
         <v>0.004856474131060814</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005525732002931351</v>
+        <v>0.005525732002931357</v>
       </c>
       <c r="M3" t="n">
-        <v>0.004731023789940487</v>
+        <v>0.00473102378994049</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004744473456768861</v>
+        <v>0.004744473456768857</v>
       </c>
       <c r="O3" t="n">
-        <v>0.007460234555254969</v>
+        <v>0.007460234555254967</v>
       </c>
       <c r="P3" t="n">
-        <v>0.005121536117509275</v>
+        <v>0.005121536117509271</v>
       </c>
       <c r="Q3" t="n">
         <v>0.00411599563719063</v>
       </c>
       <c r="R3" t="n">
-        <v>0.004121219967155002</v>
+        <v>0.004121219967154999</v>
       </c>
       <c r="S3" t="n">
-        <v>0.004699051663838984</v>
+        <v>0.004699051663838982</v>
       </c>
       <c r="T3" t="n">
-        <v>0.004453552060828796</v>
+        <v>0.004453552060828792</v>
       </c>
       <c r="U3" t="n">
         <v>0.00577788792554578</v>
       </c>
       <c r="V3" t="n">
-        <v>0.004024998074629392</v>
+        <v>0.004024998074629393</v>
       </c>
       <c r="W3" t="n">
-        <v>0.004638383738370098</v>
+        <v>0.004638383738370099</v>
       </c>
       <c r="X3" t="n">
         <v>0.00603141644012022</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.005296890758373694</v>
+        <v>0.005296890758373693</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006095269175545406</v>
+        <v>0.006095269175545405</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.004905911766745541</v>
+        <v>0.004905911766745539</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.004962437933401567</v>
+        <v>0.004962437933401569</v>
       </c>
     </row>
     <row r="4">
@@ -7642,85 +7642,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.008929483491384274</v>
+        <v>0.008929483491384288</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007869812571557167</v>
+        <v>0.007869812571557175</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009040944774574919</v>
+        <v>0.009040944774574922</v>
       </c>
       <c r="E4" t="n">
-        <v>0.008095763867996725</v>
+        <v>0.008095763867996738</v>
       </c>
       <c r="F4" t="n">
-        <v>0.008229478774757291</v>
+        <v>0.008229478774757298</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01071981144805761</v>
+        <v>0.01071981144805762</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008074207723338812</v>
+        <v>0.008074207723338821</v>
       </c>
       <c r="I4" t="n">
-        <v>0.008786927784209706</v>
+        <v>0.008786927784209713</v>
       </c>
       <c r="J4" t="n">
-        <v>0.009478721102865181</v>
+        <v>0.009478721102865191</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009420266225769296</v>
+        <v>0.009420266225769308</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01048057283402754</v>
+        <v>0.01048057283402755</v>
       </c>
       <c r="M4" t="n">
-        <v>0.009219373994985144</v>
+        <v>0.009219373994985151</v>
       </c>
       <c r="N4" t="n">
-        <v>0.009236221586648491</v>
+        <v>0.009236221586648495</v>
       </c>
       <c r="O4" t="n">
-        <v>0.008746982143584804</v>
+        <v>0.008746982143584809</v>
       </c>
       <c r="P4" t="n">
         <v>0.009842300555680908</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.008243263443576896</v>
+        <v>0.008243263443576905</v>
       </c>
       <c r="R4" t="n">
-        <v>0.008248980782841643</v>
+        <v>0.008248980782841659</v>
       </c>
       <c r="S4" t="n">
-        <v>0.009175249930030153</v>
+        <v>0.009175249930030173</v>
       </c>
       <c r="T4" t="n">
-        <v>0.00877440181536002</v>
+        <v>0.008774401815360032</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01078894827415497</v>
+        <v>0.01078894827415498</v>
       </c>
       <c r="V4" t="n">
         <v>0.008071645167229151</v>
       </c>
       <c r="W4" t="n">
-        <v>0.009096604513504672</v>
+        <v>0.009096604513504679</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01126802758392088</v>
+        <v>0.01126802758392089</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.01008398151205763</v>
+        <v>0.01008398151205764</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.008725863992830367</v>
+        <v>0.008725863992830379</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.009493470406183851</v>
+        <v>0.009493470406183861</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.009572863854877918</v>
+        <v>0.009572863854877928</v>
       </c>
     </row>
     <row r="5">
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03094128600490548</v>
+        <v>0.0309412860049055</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01313863743382651</v>
+        <v>0.01313863743382652</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03658767226405682</v>
+        <v>0.03658767226405676</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0163031183453457</v>
+        <v>0.01630311834534573</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02036731561374604</v>
+        <v>0.02036731561374602</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06126115149941679</v>
+        <v>0.06126115149941677</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01769057185495118</v>
+        <v>0.01769057185495119</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03155833244910257</v>
+        <v>0.0315583324491026</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04120657525034031</v>
+        <v>0.04120657525034035</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04056755057376236</v>
+        <v>0.04056755057376231</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06022746574244087</v>
+        <v>0.06022746574244089</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03818939307325234</v>
+        <v>0.03818939307325232</v>
       </c>
       <c r="N5" t="n">
-        <v>0.06517488426045222</v>
+        <v>0.06517488426045225</v>
       </c>
       <c r="O5" t="n">
         <v>0.02734230082729382</v>
       </c>
       <c r="P5" t="n">
-        <v>0.04765698738261823</v>
+        <v>0.04765698738261825</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.020099318892671</v>
+        <v>0.02009931889267101</v>
       </c>
       <c r="R5" t="n">
-        <v>0.02110384042631985</v>
+        <v>0.02110384042631987</v>
       </c>
       <c r="S5" t="n">
-        <v>0.03448401079305684</v>
+        <v>0.03448401079305683</v>
       </c>
       <c r="T5" t="n">
-        <v>0.03122987276628151</v>
+        <v>0.03122987276628153</v>
       </c>
       <c r="U5" t="n">
-        <v>0.06675719030988425</v>
+        <v>0.06675719030988435</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0166189662694728</v>
+        <v>0.01661896626947279</v>
       </c>
       <c r="W5" t="n">
-        <v>0.03624858660627488</v>
+        <v>0.0362485866062749</v>
       </c>
       <c r="X5" t="n">
-        <v>0.079638223307857</v>
+        <v>0.07963822330785704</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.05498747251652849</v>
+        <v>0.05498747251652848</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0275879068758985</v>
+        <v>0.02758790687589851</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.04372219180651581</v>
+        <v>0.04372219180651579</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.04891666252729751</v>
+        <v>0.04891666252729748</v>
       </c>
     </row>
     <row r="6">
@@ -7818,85 +7818,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01026149703975971</v>
+        <v>0.01026149703975972</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008273133134581471</v>
+        <v>0.008273133134581485</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01037295832295035</v>
+        <v>0.01037295832295036</v>
       </c>
       <c r="E6" t="n">
-        <v>0.009427777416372166</v>
+        <v>0.009427777416372176</v>
       </c>
       <c r="F6" t="n">
-        <v>0.009561492323132734</v>
+        <v>0.009561492323132735</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01112313201108191</v>
+        <v>0.01112313201108192</v>
       </c>
       <c r="H6" t="n">
-        <v>0.009406221271714249</v>
+        <v>0.009406221271714256</v>
       </c>
       <c r="I6" t="n">
-        <v>0.009190248347234014</v>
+        <v>0.009190248347234021</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01081073465124062</v>
+        <v>0.009882041665889501</v>
       </c>
       <c r="K6" t="n">
-        <v>0.009823586788793604</v>
+        <v>0.009823586788793616</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01088389339705185</v>
+        <v>0.01181258638240299</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01055138754336058</v>
+        <v>0.01055138754336059</v>
       </c>
       <c r="N6" t="n">
-        <v>0.009644360772964751</v>
+        <v>0.009644360772964773</v>
       </c>
       <c r="O6" t="n">
-        <v>0.009155121329901057</v>
+        <v>0.009155121329901086</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01118010309553991</v>
+        <v>0.01118010309553992</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.008646584006601203</v>
+        <v>0.009575276991952342</v>
       </c>
       <c r="R6" t="n">
-        <v>0.009580994331217084</v>
+        <v>0.009580994331217094</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01050726347840559</v>
+        <v>0.01050726347840561</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01010641536373546</v>
+        <v>0.009177722378384339</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01215054118445603</v>
+        <v>0.01215054118445604</v>
       </c>
       <c r="V6" t="n">
-        <v>0.008474965730253458</v>
+        <v>0.009403658715604587</v>
       </c>
       <c r="W6" t="n">
-        <v>0.009537206902491387</v>
+        <v>0.009537206902491381</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01260004113229632</v>
+        <v>0.0116713481469452</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01054370545236893</v>
+        <v>0.01054370545236898</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.009129184555854677</v>
+        <v>0.009129184555854689</v>
       </c>
       <c r="AA6" t="n">
         <v>0.0108254839545593</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.009985041045931139</v>
+        <v>0.009985041045931144</v>
       </c>
     </row>
     <row r="7">
@@ -7906,28 +7906,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00961472629128517</v>
+        <v>0.009614726291285175</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008555055371458058</v>
+        <v>0.008555055371458065</v>
       </c>
       <c r="D7" t="n">
-        <v>0.009726187574475818</v>
+        <v>0.009726187574475817</v>
       </c>
       <c r="E7" t="n">
-        <v>0.008781006667897624</v>
+        <v>0.00878100666789763</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008914721574658184</v>
+        <v>0.008914721574658186</v>
       </c>
       <c r="G7" t="n">
         <v>0.01140505424795851</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0087594505232397</v>
+        <v>0.00875945052323971</v>
       </c>
       <c r="I7" t="n">
-        <v>0.009472170584110609</v>
+        <v>0.009472170584110606</v>
       </c>
       <c r="J7" t="n">
         <v>0.01016396390276609</v>
@@ -7936,55 +7936,55 @@
         <v>0.01010550902567019</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01116581563392843</v>
+        <v>0.01116581563392845</v>
       </c>
       <c r="M7" t="n">
         <v>0.00990461679488604</v>
       </c>
       <c r="N7" t="n">
-        <v>0.009921464386549388</v>
+        <v>0.009921464386549391</v>
       </c>
       <c r="O7" t="n">
-        <v>0.009432199819232939</v>
+        <v>0.009432199819232948</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01052751823132903</v>
+        <v>0.01052751823132904</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.008928506243477791</v>
+        <v>0.008928506243477793</v>
       </c>
       <c r="R7" t="n">
-        <v>0.008934223582742542</v>
+        <v>0.008934223582742548</v>
       </c>
       <c r="S7" t="n">
-        <v>0.009860492729931052</v>
+        <v>0.009860492729931057</v>
       </c>
       <c r="T7" t="n">
         <v>0.009459644615260922</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01150265261259123</v>
+        <v>0.01150265261259125</v>
       </c>
       <c r="V7" t="n">
         <v>0.008756887967130041</v>
       </c>
       <c r="W7" t="n">
-        <v>0.00978184731340556</v>
+        <v>0.009781847313405569</v>
       </c>
       <c r="X7" t="n">
         <v>0.01195327038382177</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01079880367388416</v>
+        <v>0.01079880367388417</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.009411106792731267</v>
+        <v>0.009411106792731272</v>
       </c>
       <c r="AA7" t="n">
         <v>0.01017871320608475</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01025810665477881</v>
+        <v>0.01025810665477882</v>
       </c>
     </row>
     <row r="8">
@@ -7994,85 +7994,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01103010252691</v>
+        <v>0.01103010252691001</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01144446349363393</v>
+        <v>0.01144446349363395</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01261559569665169</v>
+        <v>0.0126155956966517</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01167041479007349</v>
+        <v>0.01088553629172429</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01055973475082293</v>
+        <v>0.01055973475082295</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01429446237013438</v>
+        <v>0.01460011248422789</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01164885864541558</v>
+        <v>0.01164885864541559</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01236157870628648</v>
+        <v>0.01236157870628649</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01305337202494196</v>
+        <v>0.01305337202494197</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01299491714784606</v>
+        <v>0.01299491714784608</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01405522375610431</v>
+        <v>0.01405522375610432</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01279402491706191</v>
+        <v>0.01279402491706169</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01166825119646248</v>
+        <v>0.01166825119646249</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01149301401117765</v>
+        <v>0.01149301401117766</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01251136288253858</v>
+        <v>0.0125113628825386</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01005420157028567</v>
+        <v>0.01005420157028568</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01182363170491842</v>
+        <v>0.01182363170491843</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01274990085210692</v>
+        <v>0.01274990085210693</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01234905273743679</v>
+        <v>0.0123490527374368</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01348534093800968</v>
+        <v>0.01367287645295338</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01164629608930592</v>
+        <v>0.01124248693677714</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01267154512499215</v>
+        <v>0.01267154512499216</v>
       </c>
       <c r="X8" t="n">
         <v>0.01321406366192169</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01515235949559541</v>
+        <v>0.01515235949559542</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01230051491490714</v>
+        <v>0.01079910212930307</v>
       </c>
       <c r="AA8" t="n">
         <v>0.01306812132826063</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01468726433891221</v>
+        <v>0.01468726433891222</v>
       </c>
     </row>
     <row r="9">
@@ -8082,85 +8082,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0115244060661351</v>
+        <v>0.01152440606613511</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01124301438581023</v>
+        <v>0.01124301438581024</v>
       </c>
       <c r="D9" t="n">
         <v>0.01241414658882799</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01146896568224979</v>
+        <v>0.01128934242050225</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01160268058901036</v>
+        <v>0.009808533829955755</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01409301326231067</v>
+        <v>0.01409301379817156</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01144740953759188</v>
+        <v>0.01144740953759189</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01216012959846277</v>
+        <v>0.01216012959846278</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01285192291711825</v>
+        <v>0.01285192291711826</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01279346804002236</v>
+        <v>0.01279346804002237</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0138537746482806</v>
+        <v>0.01385377464828062</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0125925758092382</v>
+        <v>0.01259257580923821</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01260942340090156</v>
+        <v>0.01260942340090157</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01237810539218369</v>
+        <v>0.01237810539218371</v>
       </c>
       <c r="P9" t="n">
         <v>0.01352951717452289</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.01161646579369083</v>
+        <v>0.01161646579369084</v>
       </c>
       <c r="R9" t="n">
         <v>0.01162218259709472</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01254845174428322</v>
+        <v>0.01254845174428323</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01214760362961309</v>
+        <v>0.0121476036296131</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01419172945033367</v>
+        <v>0.01419172945033368</v>
       </c>
       <c r="V9" t="n">
-        <v>0.01144484698148221</v>
+        <v>0.01234296465760827</v>
       </c>
       <c r="W9" t="n">
         <v>0.01246980632775774</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01464122939817394</v>
+        <v>0.01464122939817395</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.01348676268823634</v>
+        <v>0.01348676268823635</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.01209906580708344</v>
+        <v>0.01162983284573826</v>
       </c>
       <c r="AA9" t="n">
         <v>0.01286667222043692</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.01294606566913099</v>
+        <v>0.012946065669131</v>
       </c>
     </row>
   </sheetData>
@@ -8326,85 +8326,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004124613077914794</v>
+        <v>0.004124613077914797</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003840004689084398</v>
+        <v>0.003840004689084397</v>
       </c>
       <c r="D2" t="n">
         <v>0.004146193782629318</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004141250237547774</v>
+        <v>0.004141250237547776</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004132982402317517</v>
+        <v>0.004132982402317519</v>
       </c>
       <c r="G2" t="n">
-        <v>0.004332546037331234</v>
+        <v>0.004332546037331233</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004132370218054701</v>
+        <v>0.004132370218054699</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004139474595460052</v>
+        <v>0.004139474595460053</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004230322753276426</v>
+        <v>0.004230322753276424</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004154057790590922</v>
+        <v>0.004154057790590924</v>
       </c>
       <c r="L2" t="n">
         <v>0.004216996617806276</v>
       </c>
       <c r="M2" t="n">
-        <v>0.004141397038354175</v>
+        <v>0.004141397038354177</v>
       </c>
       <c r="N2" t="n">
         <v>0.004144500618129082</v>
       </c>
       <c r="O2" t="n">
-        <v>0.005954992644810375</v>
+        <v>0.005954992644810373</v>
       </c>
       <c r="P2" t="n">
-        <v>0.004228834276731777</v>
+        <v>0.004228834276731775</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.00414178285614623</v>
+        <v>0.004141782856146232</v>
       </c>
       <c r="R2" t="n">
-        <v>0.00415518010540347</v>
+        <v>0.004155180105403472</v>
       </c>
       <c r="S2" t="n">
         <v>0.004154225754375656</v>
       </c>
       <c r="T2" t="n">
-        <v>0.004135933030939063</v>
+        <v>0.004135933030939061</v>
       </c>
       <c r="U2" t="n">
-        <v>0.004245491173623372</v>
+        <v>0.004245491173623371</v>
       </c>
       <c r="V2" t="n">
-        <v>0.004136152331425481</v>
+        <v>0.004136152331425484</v>
       </c>
       <c r="W2" t="n">
-        <v>0.004231063879309249</v>
+        <v>0.004231063879309247</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004506185292285069</v>
+        <v>0.004506185292285067</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.004570752304794942</v>
+        <v>0.004570752304794943</v>
       </c>
       <c r="Z2" t="n">
         <v>0.00508535105578739</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.004165164455528024</v>
+        <v>0.004165164455528027</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.006931667323015658</v>
+        <v>0.006931667323015631</v>
       </c>
     </row>
     <row r="3">
@@ -8414,13 +8414,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003899083188792777</v>
+        <v>0.003899083188792775</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003450396583895511</v>
+        <v>0.00345039658389551</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004053740952519918</v>
+        <v>0.004053740952519917</v>
       </c>
       <c r="E3" t="n">
         <v>0.00401642177398137</v>
@@ -8429,70 +8429,70 @@
         <v>0.003959435450241162</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005372434697017398</v>
+        <v>0.00537243469701739</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003955404227722398</v>
+        <v>0.003955404227722397</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004005959236841481</v>
+        <v>0.004005959236841482</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004650880723558673</v>
+        <v>0.004650880723558669</v>
       </c>
       <c r="K3" t="n">
-        <v>0.004108925546511432</v>
+        <v>0.004108925546511431</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004555259750869105</v>
+        <v>0.004555259750869109</v>
       </c>
       <c r="M3" t="n">
-        <v>0.004028357712546739</v>
+        <v>0.004028357712546736</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004041481688368213</v>
+        <v>0.004041481688368211</v>
       </c>
       <c r="O3" t="n">
-        <v>0.007029923652647952</v>
+        <v>0.00702992365264795</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004639442749885931</v>
+        <v>0.004639442749885927</v>
       </c>
       <c r="Q3" t="n">
         <v>0.00402149182550534</v>
       </c>
       <c r="R3" t="n">
-        <v>0.004118684285316176</v>
+        <v>0.004118684285316175</v>
       </c>
       <c r="S3" t="n">
         <v>0.004109162645536985</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003980509990175689</v>
+        <v>0.003980509990175684</v>
       </c>
       <c r="U3" t="n">
-        <v>0.004348843994831876</v>
+        <v>0.004348843994831875</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003981165997435893</v>
+        <v>0.003981165997435891</v>
       </c>
       <c r="W3" t="n">
-        <v>0.004338650635624371</v>
+        <v>0.004338650635624376</v>
       </c>
       <c r="X3" t="n">
-        <v>0.006622846399418933</v>
+        <v>0.006622846399418934</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.007082230945616365</v>
+        <v>0.007082230945616364</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.005593257034456293</v>
+        <v>0.005593257034456289</v>
       </c>
       <c r="AA3" t="n">
         <v>0.004188786221362329</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.02377740883373666</v>
+        <v>0.02377740883373661</v>
       </c>
     </row>
     <row r="4">
@@ -8502,82 +8502,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.007730443743713951</v>
+        <v>0.007730443743713953</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007773393635946755</v>
+        <v>0.007773393635946746</v>
       </c>
       <c r="D4" t="n">
-        <v>0.007974207731079161</v>
+        <v>0.007974207731079156</v>
       </c>
       <c r="E4" t="n">
-        <v>0.007918368115240037</v>
+        <v>0.00791836811524003</v>
       </c>
       <c r="F4" t="n">
-        <v>0.007824979112922166</v>
+        <v>0.007824979112922159</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01007914217420977</v>
+        <v>0.01007914217420974</v>
       </c>
       <c r="H4" t="n">
-        <v>0.007818064210054976</v>
+        <v>0.007818064210054973</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00789831142102344</v>
+        <v>0.007898311421023443</v>
       </c>
       <c r="J4" t="n">
         <v>0.008920452652056508</v>
       </c>
       <c r="K4" t="n">
-        <v>0.008063035318627888</v>
+        <v>0.008063035318627877</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008773958325316255</v>
+        <v>0.008773958325316239</v>
       </c>
       <c r="M4" t="n">
-        <v>0.007936532565587068</v>
+        <v>0.007936532565587059</v>
       </c>
       <c r="N4" t="n">
-        <v>0.007955082659154861</v>
+        <v>0.007955082659154865</v>
       </c>
       <c r="O4" t="n">
-        <v>0.007957495216461812</v>
+        <v>0.0079574952164618</v>
       </c>
       <c r="P4" t="n">
-        <v>0.008907670128471941</v>
+        <v>0.008907670128471953</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.007924384287326242</v>
+        <v>0.007924384287326234</v>
       </c>
       <c r="R4" t="n">
-        <v>0.00807571238072595</v>
+        <v>0.008075712380725946</v>
       </c>
       <c r="S4" t="n">
-        <v>0.008064932546843566</v>
+        <v>0.008064932546843569</v>
       </c>
       <c r="T4" t="n">
         <v>0.007858307820558767</v>
       </c>
       <c r="U4" t="n">
-        <v>0.008223131248611281</v>
+        <v>0.008223131248611279</v>
       </c>
       <c r="V4" t="n">
-        <v>0.007833540338164932</v>
+        <v>0.007833540338164927</v>
       </c>
       <c r="W4" t="n">
-        <v>0.008273119627959381</v>
+        <v>0.008273119627959383</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01204047743691706</v>
+        <v>0.01204047743691705</v>
       </c>
       <c r="Y4" t="n">
         <v>0.01274476474000445</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.007955223766674327</v>
+        <v>0.00795522376667432</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.008188490208410766</v>
+        <v>0.008188490208410767</v>
       </c>
       <c r="AB4" t="n">
         <v>0.03900445614188339</v>
@@ -8590,13 +8590,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01008996199019155</v>
+        <v>0.01008996199019154</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01111756174804413</v>
+        <v>0.01111756174804411</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01473050580391236</v>
+        <v>0.01473050580391235</v>
       </c>
       <c r="E5" t="n">
         <v>0.01268734368142881</v>
@@ -8605,49 +8605,49 @@
         <v>0.01208326283198328</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04609780114430218</v>
+        <v>0.04609780114430194</v>
       </c>
       <c r="H5" t="n">
         <v>0.01213610424729272</v>
       </c>
       <c r="I5" t="n">
-        <v>0.013478044596636</v>
+        <v>0.01347804459663599</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02982720923761143</v>
+        <v>0.02982720923761134</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01581380334992396</v>
+        <v>0.01581380334992399</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02690379478224871</v>
+        <v>0.02690379478224867</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01400361773346503</v>
+        <v>0.01400361773346501</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01829454560036653</v>
+        <v>0.01829454560036652</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0136817032767466</v>
+        <v>0.01368170327674665</v>
       </c>
       <c r="P5" t="n">
-        <v>0.02911170582988504</v>
+        <v>0.02911170582988506</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0134512347529394</v>
+        <v>0.01345123475293939</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01694424902682606</v>
+        <v>0.01694424902682603</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01534899945276274</v>
+        <v>0.01534899945276271</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01268090136195344</v>
+        <v>0.0126809013619534</v>
       </c>
       <c r="U5" t="n">
-        <v>0.01858762099532774</v>
+        <v>0.01858762099532775</v>
       </c>
       <c r="V5" t="n">
         <v>0.01222632377362828</v>
@@ -8656,19 +8656,19 @@
         <v>0.01982564757248575</v>
       </c>
       <c r="X5" t="n">
-        <v>0.08656011063882149</v>
+        <v>0.08656011063882142</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.09871638967579324</v>
+        <v>0.09871638967579326</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01361007554752627</v>
+        <v>0.01361007554752626</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01833939318510285</v>
+        <v>0.01833939318510286</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.6044076400564865</v>
+        <v>0.6044076400564856</v>
       </c>
     </row>
     <row r="6">
@@ -8678,85 +8678,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.009419159867859725</v>
+        <v>0.008342280492284084</v>
       </c>
       <c r="C6" t="n">
-        <v>0.009462109760092517</v>
+        <v>0.009462109760092508</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008586044479649306</v>
+        <v>0.008586044479649287</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008530204863810172</v>
+        <v>0.009607084239385786</v>
       </c>
       <c r="F6" t="n">
-        <v>0.008436815861492281</v>
+        <v>0.009513695237067918</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01176785829835552</v>
+        <v>0.01069097892277987</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008429900958625107</v>
+        <v>0.009506780334200736</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008510148169593577</v>
+        <v>0.009587027545169208</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01060916877620229</v>
+        <v>0.009532289400626641</v>
       </c>
       <c r="K6" t="n">
-        <v>0.008674872067197994</v>
+        <v>0.009751751442773638</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01046267444946202</v>
+        <v>0.00938579507388637</v>
       </c>
       <c r="M6" t="n">
-        <v>0.008548369314157202</v>
+        <v>0.009625248689732819</v>
       </c>
       <c r="N6" t="n">
-        <v>0.008568945788980983</v>
+        <v>0.008568945788980886</v>
       </c>
       <c r="O6" t="n">
-        <v>0.009646174165853973</v>
+        <v>0.008571358346287894</v>
       </c>
       <c r="P6" t="n">
-        <v>0.009471661471633129</v>
+        <v>0.009471661471633154</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.008536221035896381</v>
+        <v>0.009613100411471997</v>
       </c>
       <c r="R6" t="n">
-        <v>0.009764428504871726</v>
+        <v>0.009764428504871707</v>
       </c>
       <c r="S6" t="n">
-        <v>0.008676769295413705</v>
+        <v>0.008676769295413696</v>
       </c>
       <c r="T6" t="n">
-        <v>0.00847014456912891</v>
+        <v>0.008470144569128894</v>
       </c>
       <c r="U6" t="n">
-        <v>0.00993687417826186</v>
+        <v>0.008859994802686223</v>
       </c>
       <c r="V6" t="n">
-        <v>0.009522256462310693</v>
+        <v>0.009522256462310683</v>
       </c>
       <c r="W6" t="n">
-        <v>0.008930852465082875</v>
+        <v>0.008930852465082883</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01372919356106283</v>
+        <v>0.01265231418548717</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01341788285383919</v>
+        <v>0.01341788285383917</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.008567060515244463</v>
+        <v>0.008567060515244449</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.009877206332556541</v>
+        <v>0.009877206332556529</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.03978818974847476</v>
+        <v>0.03978818974847478</v>
       </c>
     </row>
     <row r="7">
@@ -8766,85 +8766,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.008279307979750471</v>
+        <v>0.00827930797975047</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008322257871983265</v>
+        <v>0.008322257871983261</v>
       </c>
       <c r="D7" t="n">
-        <v>0.008523071967115676</v>
+        <v>0.008523071967115672</v>
       </c>
       <c r="E7" t="n">
-        <v>0.008467232351276549</v>
+        <v>0.008467232351276544</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00837384334895868</v>
+        <v>0.00837384334895867</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01062800641024628</v>
+        <v>0.01062800641024625</v>
       </c>
       <c r="H7" t="n">
-        <v>0.008366928446091488</v>
+        <v>0.008366928446091489</v>
       </c>
       <c r="I7" t="n">
-        <v>0.008447175657059956</v>
+        <v>0.008447175657059958</v>
       </c>
       <c r="J7" t="n">
-        <v>0.009469316888093033</v>
+        <v>0.009469316888093021</v>
       </c>
       <c r="K7" t="n">
         <v>0.008611899554664395</v>
       </c>
       <c r="L7" t="n">
-        <v>0.009322822561352766</v>
+        <v>0.009322822561352757</v>
       </c>
       <c r="M7" t="n">
-        <v>0.008485396801623576</v>
+        <v>0.008485396801623571</v>
       </c>
       <c r="N7" t="n">
-        <v>0.008503946895191379</v>
+        <v>0.008503946895191378</v>
       </c>
       <c r="O7" t="n">
-        <v>0.008506336542684468</v>
+        <v>0.008506336542684465</v>
       </c>
       <c r="P7" t="n">
         <v>0.00945651145469462</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.008473248523362767</v>
+        <v>0.00847324852336275</v>
       </c>
       <c r="R7" t="n">
-        <v>0.008624576616762466</v>
+        <v>0.008624576616762462</v>
       </c>
       <c r="S7" t="n">
-        <v>0.008613796782880077</v>
+        <v>0.008613796782880082</v>
       </c>
       <c r="T7" t="n">
-        <v>0.00840717205659528</v>
+        <v>0.008407172056595283</v>
       </c>
       <c r="U7" t="n">
         <v>0.00879536944664659</v>
       </c>
       <c r="V7" t="n">
-        <v>0.008382404574201443</v>
+        <v>0.008382404574201445</v>
       </c>
       <c r="W7" t="n">
-        <v>0.008821983863995905</v>
+        <v>0.008821983863995898</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01258934167295358</v>
+        <v>0.01258934167295355</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01331865578154579</v>
+        <v>0.01331865578154578</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.008504088002710837</v>
+        <v>0.008504088002710835</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.008737354444447268</v>
+        <v>0.008737354444447279</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.03955332037791993</v>
+        <v>0.03955332037791989</v>
       </c>
     </row>
     <row r="8">
@@ -8854,40 +8854,40 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.009640811908631289</v>
+        <v>0.009640811908631291</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01106098009033127</v>
+        <v>0.01106098009033126</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01126179418546369</v>
+        <v>0.01126179418546368</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01120595456962457</v>
+        <v>0.01047262645590016</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009949901791437132</v>
+        <v>0.00994990179143712</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01336672862859426</v>
+        <v>0.01365230381265035</v>
       </c>
       <c r="H8" t="n">
         <v>0.01110565066443949</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01118589787540797</v>
+        <v>0.01118589787540795</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01220803910644104</v>
+        <v>0.01220803910644103</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0113506217730124</v>
+        <v>0.01135062177301239</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01206154477970077</v>
+        <v>0.01206154477970076</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01122411901997159</v>
+        <v>0.01122411901997132</v>
       </c>
       <c r="N8" t="n">
         <v>0.01017509453557695</v>
@@ -8896,43 +8896,43 @@
         <v>0.01047088585645553</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01134914654449424</v>
+        <v>0.01134914654449422</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.00956409762491566</v>
+        <v>0.009564097624915658</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01136329883511048</v>
+        <v>0.01136329883511046</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0113525190012281</v>
+        <v>0.01135251900122808</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01114589427494329</v>
+        <v>0.01114589427494328</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01068708999451217</v>
+        <v>0.01086227948428273</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01112112679254944</v>
+        <v>0.01074331904107698</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01156097674510519</v>
+        <v>0.01156097674510518</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01380641556725263</v>
+        <v>0.01380641556725262</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01742455390071684</v>
+        <v>0.01742455390071685</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01124281022105886</v>
+        <v>0.009840009394807954</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01147607666279529</v>
+        <v>0.01147607666279528</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.04373066226064865</v>
+        <v>0.04373066226064862</v>
       </c>
     </row>
     <row r="9">
@@ -8942,85 +8942,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.009748222439034313</v>
+        <v>0.00974822243903431</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01042031657848138</v>
+        <v>0.01042031657848136</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01062113067361379</v>
+        <v>0.01062113067361378</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01056529105777467</v>
+        <v>0.01042008700859144</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01047190205545678</v>
+        <v>0.0090215530648616</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01272606511674438</v>
+        <v>0.01272606495663237</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0104649871525896</v>
+        <v>0.01046498715258959</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01054523436355808</v>
+        <v>0.01054523436355806</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01156737559459114</v>
+        <v>0.01156737559459113</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0107099582611625</v>
+        <v>0.01070995826116249</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01142088126785088</v>
+        <v>0.01142088126785086</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0105834555081217</v>
+        <v>0.01058345550812168</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0106020056016895</v>
+        <v>0.01060200560168948</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01081291552555626</v>
+        <v>0.01081291552555625</v>
       </c>
       <c r="P9" t="n">
-        <v>0.01180843507240241</v>
+        <v>0.0118084350724024</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.01057130706974888</v>
+        <v>0.01057130706974887</v>
       </c>
       <c r="R9" t="n">
-        <v>0.01072263532326059</v>
+        <v>0.01072263532326057</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0107118554893782</v>
+        <v>0.01071185548937819</v>
       </c>
       <c r="T9" t="n">
         <v>0.01050523076309339</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01089508099665073</v>
+        <v>0.01089508099665071</v>
       </c>
       <c r="V9" t="n">
-        <v>0.01048046328069955</v>
+        <v>0.01120648126014712</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01092004257049402</v>
+        <v>0.010920042570494</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01468740037945168</v>
+        <v>0.01468740037945167</v>
       </c>
       <c r="Y9" t="n">
         <v>0.01541671448804389</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.01060214670920895</v>
+        <v>0.01022282861024934</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.0108354131509454</v>
+        <v>0.01083541315094538</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.04165137908441804</v>
+        <v>0.04165137908441798</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia acidification results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia acidification results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004391607079443093</v>
+        <v>0.004116316214163042</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003817758413578879</v>
+        <v>0.003592553314559209</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004328983070835566</v>
+        <v>0.004126324691716738</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004261665380936307</v>
+        <v>0.004013536159650488</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0042718944369496</v>
+        <v>0.004050125238621357</v>
       </c>
       <c r="G2" t="n">
-        <v>0.004483170412482487</v>
+        <v>0.004053526052125667</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00428477781116742</v>
+        <v>0.004064498810041619</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00434390314445376</v>
+        <v>0.004125614415330573</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004387487349788448</v>
+        <v>0.004101922240287673</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004429344019466951</v>
+        <v>0.004213500959104579</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004529332524502838</v>
+        <v>0.004172241513833184</v>
       </c>
       <c r="M2" t="n">
-        <v>0.004566518047425531</v>
+        <v>0.004519596152194601</v>
       </c>
       <c r="N2" t="n">
-        <v>0.00434788830580026</v>
+        <v>0.004137162154417322</v>
       </c>
       <c r="O2" t="n">
-        <v>0.006321165002693125</v>
+        <v>0.005896372691256779</v>
       </c>
       <c r="P2" t="n">
-        <v>0.004363648592234835</v>
+        <v>0.00403402015700444</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.004260613584596751</v>
+        <v>0.004039105312079051</v>
       </c>
       <c r="R2" t="n">
-        <v>0.004258289630751345</v>
+        <v>0.004041655597622013</v>
       </c>
       <c r="S2" t="n">
-        <v>0.00438904321645477</v>
+        <v>0.004095122440217853</v>
       </c>
       <c r="T2" t="n">
-        <v>0.004349277569147199</v>
+        <v>0.00412415682923042</v>
       </c>
       <c r="U2" t="n">
-        <v>0.004569524901442994</v>
+        <v>0.004359513622554973</v>
       </c>
       <c r="V2" t="n">
-        <v>0.004239589808022167</v>
+        <v>0.004016337980127826</v>
       </c>
       <c r="W2" t="n">
-        <v>0.004386849813715688</v>
+        <v>0.00416948784082571</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004322412777297829</v>
+        <v>0.004182283750630091</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.004380180051790813</v>
+        <v>0.004263574551906475</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.00538221705081093</v>
+        <v>0.005068054346676956</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.004380835959910193</v>
+        <v>0.004168258678017678</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.004648172247065748</v>
+        <v>0.004470950558842213</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005505825127271284</v>
+        <v>0.004873172513615616</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003511853972299631</v>
+        <v>0.003263481022465203</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005069462781791015</v>
+        <v>0.004953383440213432</v>
       </c>
       <c r="E3" t="n">
-        <v>0.004583443421235257</v>
+        <v>0.00414281042244523</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00466203921009795</v>
+        <v>0.004408996562734898</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00616010612936803</v>
+        <v>0.004427888049957835</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004755470764412031</v>
+        <v>0.004513004398341486</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005177228661488805</v>
+        <v>0.004949201192657067</v>
       </c>
       <c r="J3" t="n">
-        <v>0.005481457501273489</v>
+        <v>0.004775480951717598</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005786953426973655</v>
+        <v>0.005576519605993596</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006494943215089317</v>
+        <v>0.005276783998050813</v>
       </c>
       <c r="M3" t="n">
-        <v>0.006765988943800488</v>
+        <v>0.007746253868559221</v>
       </c>
       <c r="N3" t="n">
-        <v>0.005202371793799044</v>
+        <v>0.005028578229170426</v>
       </c>
       <c r="O3" t="n">
-        <v>0.00857448678154976</v>
+        <v>0.007554716489297571</v>
       </c>
       <c r="P3" t="n">
-        <v>0.005308280957866631</v>
+        <v>0.004288607589854999</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.004579058232816326</v>
+        <v>0.004328161446954817</v>
       </c>
       <c r="R3" t="n">
-        <v>0.004564542278836817</v>
+        <v>0.004348314360750659</v>
       </c>
       <c r="S3" t="n">
-        <v>0.005490314378875899</v>
+        <v>0.004724232994817289</v>
       </c>
       <c r="T3" t="n">
-        <v>0.005215079107630199</v>
+        <v>0.004938168739891872</v>
       </c>
       <c r="U3" t="n">
-        <v>0.006489667482195008</v>
+        <v>0.006367645191028866</v>
       </c>
       <c r="V3" t="n">
-        <v>0.004425581133996619</v>
+        <v>0.004162775103058753</v>
       </c>
       <c r="W3" t="n">
-        <v>0.005403709112101868</v>
+        <v>0.005233924444343134</v>
       </c>
       <c r="X3" t="n">
-        <v>0.005021488509952065</v>
+        <v>0.005352639995896313</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.005431502357568885</v>
+        <v>0.005929633346559138</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.00670344001923266</v>
+        <v>0.005996326383121189</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.005436719880551138</v>
+        <v>0.005249729461995022</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.007343850550428897</v>
+        <v>0.007398526987485315</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01057922498495065</v>
+        <v>0.008793826964907492</v>
       </c>
       <c r="C4" t="n">
-        <v>0.008407145210441273</v>
+        <v>0.007248466510527391</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009871857999261303</v>
+        <v>0.008906877323003572</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009111473724181855</v>
+        <v>0.0076328789680271</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009227015617450205</v>
+        <v>0.008046169446811009</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0116134749528447</v>
+        <v>0.008084583199793714</v>
       </c>
       <c r="H4" t="n">
-        <v>0.009372539255885525</v>
+        <v>0.008208525548172405</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01004038709435169</v>
+        <v>0.008898854424478568</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01052874178364427</v>
+        <v>0.008628198911131786</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01100548108237016</v>
+        <v>0.009891573366213538</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01213489724373527</v>
+        <v>0.009425528951590533</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01254378360919656</v>
+        <v>0.01330258782769781</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01008540132502525</v>
+        <v>0.05272152432887288</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01034195237828724</v>
+        <v>0.00826443199361636</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01026342101039378</v>
+        <v>0.007864255141244367</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.009099593200676295</v>
+        <v>0.007921694307098945</v>
       </c>
       <c r="R4" t="n">
-        <v>0.009073343072920865</v>
+        <v>0.007950500955496037</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01055026497306221</v>
+        <v>0.008554433538578854</v>
       </c>
       <c r="T4" t="n">
-        <v>0.01010109369362163</v>
+        <v>0.00888239031895457</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01195639450702453</v>
+        <v>0.01102825575533929</v>
       </c>
       <c r="V4" t="n">
-        <v>0.008835420769427046</v>
+        <v>0.007643974162975859</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0103704836556645</v>
+        <v>0.009345108409209707</v>
       </c>
       <c r="X4" t="n">
-        <v>0.00979764351126821</v>
+        <v>0.009538960635868819</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.01041359168895357</v>
+        <v>0.01044435526646007</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.009670395352647286</v>
+        <v>0.007865166453971839</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01045756023486664</v>
+        <v>0.009380540988859473</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.01344107857433497</v>
+        <v>0.0127417435822919</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05943222695697745</v>
+        <v>0.044040901236466</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02017587652762347</v>
+        <v>0.01614825924167981</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05148054578874679</v>
+        <v>0.05153583717977615</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03285772109074125</v>
+        <v>0.02255448260692945</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03850720200791583</v>
+        <v>0.03387757666265365</v>
       </c>
       <c r="G5" t="n">
-        <v>0.08072869676011507</v>
+        <v>0.03145337423595931</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04231872197073493</v>
+        <v>0.03799280319889021</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05563546596524061</v>
+        <v>0.05190147953311982</v>
       </c>
       <c r="J5" t="n">
-        <v>0.06148378269833901</v>
+        <v>0.04375861302327589</v>
       </c>
       <c r="K5" t="n">
-        <v>0.07502817296566838</v>
+        <v>0.07193298227979558</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09442411994233939</v>
+        <v>0.05941866425918418</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1096145088787172</v>
+        <v>0.1467848251833351</v>
       </c>
       <c r="N5" t="n">
-        <v>0.08804433079195326</v>
+        <v>0.05272152432887288</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05395259327934612</v>
+        <v>0.03359970184110064</v>
       </c>
       <c r="P5" t="n">
-        <v>0.05425949940561923</v>
+        <v>0.0269772649563173</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03447375601992612</v>
+        <v>0.03007205254476869</v>
       </c>
       <c r="R5" t="n">
-        <v>0.03517556984416989</v>
+        <v>0.03181196975579498</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0605058852061755</v>
+        <v>0.04059981683046308</v>
       </c>
       <c r="T5" t="n">
-        <v>0.05655657701532817</v>
+        <v>0.05119573235399745</v>
       </c>
       <c r="U5" t="n">
-        <v>0.08995188373592461</v>
+        <v>0.09016878285551397</v>
       </c>
       <c r="V5" t="n">
-        <v>0.02762661927586626</v>
+        <v>0.02315219962089007</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0594635915934056</v>
+        <v>0.0582433235443924</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0493430822955046</v>
+        <v>0.06418972519984315</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.06113159569524531</v>
+        <v>0.08078873585539756</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.04342653869740336</v>
+        <v>0.0272413358120987</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.06159952698547083</v>
+        <v>0.05932765302177007</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1328484431906181</v>
+        <v>0.1388407596952838</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0119911352975019</v>
+        <v>0.009143247687484016</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00981905552299254</v>
+        <v>0.008485580137475671</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0102281419285286</v>
+        <v>0.01014399094995186</v>
       </c>
       <c r="E6" t="n">
-        <v>0.009467757653449144</v>
+        <v>0.00886999259497538</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01063892593000147</v>
+        <v>0.00839559016938753</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01302538526539597</v>
+        <v>0.009321696826741993</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01078444956843679</v>
+        <v>0.009445639175120689</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01039667102361897</v>
+        <v>0.009248275147055099</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01194065209619554</v>
+        <v>0.008977619633708311</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01136176501163745</v>
+        <v>0.01112868699316181</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01249118117300257</v>
+        <v>0.01066264257853882</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01290006753846385</v>
+        <v>0.0145397014546461</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01044664206167219</v>
+        <v>0.05272152432887288</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01175818808380584</v>
+        <v>0.008621152469315163</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01167965711469463</v>
+        <v>0.009101963946440018</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.009455877129943583</v>
+        <v>0.009158807934047233</v>
       </c>
       <c r="R6" t="n">
-        <v>0.009429627002188154</v>
+        <v>0.009187614582444319</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01196217528561347</v>
+        <v>0.008903854261155376</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01045737762288891</v>
+        <v>0.009231811041531091</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01234923819826389</v>
+        <v>0.01139049884335748</v>
       </c>
       <c r="V6" t="n">
-        <v>0.01024733108197831</v>
+        <v>0.008881087789924139</v>
       </c>
       <c r="W6" t="n">
-        <v>0.01178671966707292</v>
+        <v>0.01058281782623015</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01120955382381947</v>
+        <v>0.01077607426281711</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01083081925964454</v>
+        <v>0.01083579903635857</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.01002667928191458</v>
+        <v>0.008214587176548365</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.01081384416413393</v>
+        <v>0.01061765461580776</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0138249509946607</v>
+        <v>0.0131236594522961</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01142114152199846</v>
+        <v>0.009545727839214075</v>
       </c>
       <c r="C7" t="n">
-        <v>0.009249061747489098</v>
+        <v>0.008000367384833977</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01071377453630913</v>
+        <v>0.009658778197310149</v>
       </c>
       <c r="E7" t="n">
-        <v>0.009953390261229678</v>
+        <v>0.008384779842333682</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01006893215449803</v>
+        <v>0.008798070321117591</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01245539148989252</v>
+        <v>0.008836484074100303</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01021445579293335</v>
+        <v>0.008960426422478988</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01088230363139951</v>
+        <v>0.009650755298785155</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01137065832069209</v>
+        <v>0.009380099785438372</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01184739761941798</v>
+        <v>0.01064347424052012</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0129768137807831</v>
+        <v>0.01017742982589713</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01338570014624438</v>
+        <v>0.01405448870200439</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01092731786207307</v>
+        <v>0.05272152432887288</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01118384134046265</v>
+        <v>0.009016306010960698</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0111053099725692</v>
+        <v>0.008616129158588698</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.009941509737724117</v>
+        <v>0.008673595181405524</v>
       </c>
       <c r="R7" t="n">
-        <v>0.009915259609968684</v>
+        <v>0.008702401829802626</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01139218151011003</v>
+        <v>0.009306334412885434</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01094301023066944</v>
+        <v>0.009634291193261153</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01283385089095073</v>
+        <v>0.01179265821217137</v>
       </c>
       <c r="V7" t="n">
-        <v>0.009677337306474873</v>
+        <v>0.008395875037282438</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01121240019271232</v>
+        <v>0.01009700928351628</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01063956004831603</v>
+        <v>0.0102908615101754</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01129206798797346</v>
+        <v>0.01120907850620832</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01051231188969511</v>
+        <v>0.008617067328278428</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01129947677191446</v>
+        <v>0.01013244186316606</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01428299511138278</v>
+        <v>0.01349364445659848</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01299383581141072</v>
+        <v>0.01105437102106633</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01250309083858722</v>
+        <v>0.01106470415405096</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01396780362740726</v>
+        <v>0.01272311496652713</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01231215816672619</v>
+        <v>0.0106207556663798</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01190355875582718</v>
+        <v>0.01054907238210097</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01605805630499009</v>
+        <v>0.01222340404305491</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01346848488403149</v>
+        <v>0.01202476319169597</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01413633272249763</v>
+        <v>0.01271509206800214</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01462468741179023</v>
+        <v>0.01244443655465536</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01510142671051612</v>
+        <v>0.01370781100973711</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01623084287188123</v>
+        <v>0.0132417665951141</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01663972923734238</v>
+        <v>0.01711882547122138</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01287803120065466</v>
+        <v>0.05272152432887288</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01349274473915744</v>
+        <v>0.01120614489914618</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01332641909171781</v>
+        <v>0.01072473437601857</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01118378336404161</v>
+        <v>0.009876509066382462</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01316928870106682</v>
+        <v>0.0117667385990196</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01464621060120816</v>
+        <v>0.01237067118210242</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01419703932176757</v>
+        <v>0.01269862796247813</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01526749378159184</v>
+        <v>0.01409777470249325</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01247098401689845</v>
+        <v>0.01103476605139509</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01446675971417251</v>
+        <v>0.01316165179104969</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01203593135000738</v>
+        <v>0.01163635780361371</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01621649440018978</v>
+        <v>0.01581981632490726</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01205377452197816</v>
+        <v>0.01009681270305635</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01455350586301259</v>
+        <v>0.01319677863238305</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01929331899367226</v>
+        <v>0.01818303326275194</v>
       </c>
     </row>
     <row r="9">
@@ -1202,85 +1202,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01402688207047042</v>
+        <v>0.011430110058535</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01287230340009266</v>
+        <v>0.01066578438976299</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01433701618891269</v>
+        <v>0.01232419520223919</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01334179683753518</v>
+        <v>0.01086993637428816</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01134655601178581</v>
+        <v>0.009662990389446855</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01607863317918869</v>
+        <v>0.01150189999968109</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01383769744553691</v>
+        <v>0.01162584342740802</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01450554528400308</v>
+        <v>0.01231617230371419</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01499389997329566</v>
+        <v>0.0120455167903674</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01547063927202155</v>
+        <v>0.01330889124544915</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01660005543338666</v>
+        <v>0.01284284683082616</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01700894179884794</v>
+        <v>0.01671990570693342</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01455055951467663</v>
+        <v>0.05272152432887288</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01514430915039635</v>
+        <v>0.01194058234108189</v>
       </c>
       <c r="P9" t="n">
-        <v>0.01513911268085407</v>
+        <v>0.01159669734447234</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.01356475142702029</v>
+        <v>0.01133901110698631</v>
       </c>
       <c r="R9" t="n">
-        <v>0.01353850126257226</v>
+        <v>0.01136781883473165</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0150154231627136</v>
+        <v>0.01197175141781446</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01456625188327301</v>
+        <v>0.01229970819819018</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01645811245864799</v>
+        <v>0.01445839600001657</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0144747520382415</v>
+        <v>0.01196258627443316</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01483564184531589</v>
+        <v>0.01276242628844531</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01426280170091959</v>
+        <v>0.01295627851510444</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.01491530964057703</v>
+        <v>0.01387449551113735</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.01352209087080598</v>
+        <v>0.01081158938121151</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.01492271842451802</v>
+        <v>0.01279785886809509</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.01790623676398634</v>
+        <v>0.01615906146152753</v>
       </c>
     </row>
   </sheetData>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003713420773599496</v>
+        <v>0.003717247939742315</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003298393310672761</v>
+        <v>0.003301666177617807</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00371973769291364</v>
+        <v>0.003723482485583252</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003719689162554137</v>
+        <v>0.003723224211454135</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003723524963300827</v>
+        <v>0.003727235216085839</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003730133553932607</v>
+        <v>0.003729891012457081</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003721679599376586</v>
+        <v>0.003725445329840645</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003722730234166605</v>
+        <v>0.003725847890252427</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003735179872189336</v>
+        <v>0.003738359047546819</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003732100584313301</v>
+        <v>0.00373475146011861</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003736124611386513</v>
+        <v>0.00373918792240103</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003721615464065394</v>
+        <v>0.003730346125362584</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003724275073632431</v>
+        <v>0.00372821666825625</v>
       </c>
       <c r="O2" t="n">
-        <v>0.00540675470515146</v>
+        <v>0.005408643836908493</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003728044859943878</v>
+        <v>0.003731572538517064</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.00371883584011651</v>
+        <v>0.003722587183373334</v>
       </c>
       <c r="R2" t="n">
-        <v>0.00373745600263477</v>
+        <v>0.003740910297822764</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003731970895124054</v>
+        <v>0.003735196952684489</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003722706359580097</v>
+        <v>0.003725708753697612</v>
       </c>
       <c r="U2" t="n">
-        <v>0.003593286217671968</v>
+        <v>0.003591228345904864</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003731272603195401</v>
+        <v>0.003734804886553679</v>
       </c>
       <c r="W2" t="n">
-        <v>0.003565222865256889</v>
+        <v>0.003563434871944602</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00413559094504944</v>
+        <v>0.00413891388722991</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003961537823240249</v>
+        <v>0.00396524879995471</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.00472461648617646</v>
+        <v>0.004726362540806549</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003764487350899706</v>
+        <v>0.003767642324405839</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.003714872630915942</v>
+        <v>0.003721364190061453</v>
       </c>
     </row>
     <row r="3">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003501493555079836</v>
+        <v>0.003507055611520336</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002834061618692768</v>
+        <v>0.002838131895679362</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003546966705219042</v>
+        <v>0.003551948685550313</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003544761105244294</v>
+        <v>0.003548280213151346</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003574106176940842</v>
+        <v>0.003578838291707366</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003620118977130851</v>
+        <v>0.003596834409113499</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003561228197813699</v>
+        <v>0.003566355657542615</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003568460765436038</v>
+        <v>0.003568954307223814</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003656512344118931</v>
+        <v>0.00365751404215615</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003634667953625595</v>
+        <v>0.003631891701122576</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003662944060899614</v>
+        <v>0.003663091267044756</v>
       </c>
       <c r="M3" t="n">
-        <v>0.003565447177186034</v>
+        <v>0.003605565194302968</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003579283220797366</v>
+        <v>0.003585661329083995</v>
       </c>
       <c r="O3" t="n">
-        <v>0.006373998615432726</v>
+        <v>0.006375757136138493</v>
       </c>
       <c r="P3" t="n">
-        <v>0.00360523472180605</v>
+        <v>0.003608672850478436</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003540293053343459</v>
+        <v>0.003545318972446641</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003674077239661177</v>
+        <v>0.003676971138463329</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003633191611233592</v>
+        <v>0.003634490914768565</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003568268645872677</v>
+        <v>0.003567931434635721</v>
       </c>
       <c r="U3" t="n">
-        <v>0.003472357971296795</v>
+        <v>0.003462484691911708</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003628282925322868</v>
+        <v>0.003631759515160563</v>
       </c>
       <c r="W3" t="n">
-        <v>0.003395583478053736</v>
+        <v>0.003390696500477267</v>
       </c>
       <c r="X3" t="n">
-        <v>0.006510647988657262</v>
+        <v>0.006512621505500075</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.005274108278873396</v>
+        <v>0.005278837841429932</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.005264410807348637</v>
+        <v>0.005263515824931566</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003866337763457011</v>
+        <v>0.003867096510318164</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.003516981533663207</v>
+        <v>0.003541279457071391</v>
       </c>
     </row>
     <row r="4">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.007230781795339934</v>
+        <v>0.006720761407852213</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007267632173020865</v>
+        <v>0.006756422684424841</v>
       </c>
       <c r="D4" t="n">
-        <v>0.007302134304919604</v>
+        <v>0.006791183471158331</v>
       </c>
       <c r="E4" t="n">
-        <v>0.007301586132183987</v>
+        <v>0.006788266146057997</v>
       </c>
       <c r="F4" t="n">
-        <v>0.007344913266173378</v>
+        <v>0.006833572288526401</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007419560337461167</v>
+        <v>0.006863570730266257</v>
       </c>
       <c r="H4" t="n">
-        <v>0.007324069031739658</v>
+        <v>0.006813354699998595</v>
       </c>
       <c r="I4" t="n">
-        <v>0.007335936435008852</v>
+        <v>0.006817901805036628</v>
       </c>
       <c r="J4" t="n">
-        <v>0.007473542407354657</v>
+        <v>0.006956217689766861</v>
       </c>
       <c r="K4" t="n">
-        <v>0.007441778850489805</v>
+        <v>0.006918471722519558</v>
       </c>
       <c r="L4" t="n">
-        <v>0.007487232087425629</v>
+        <v>0.006968583604873082</v>
       </c>
       <c r="M4" t="n">
-        <v>0.007332415121802082</v>
+        <v>0.006876937997629257</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01158961008737803</v>
+        <v>0.01112980040466693</v>
       </c>
       <c r="O4" t="n">
-        <v>0.00739123956248808</v>
+        <v>0.006879952603735668</v>
       </c>
       <c r="P4" t="n">
-        <v>0.007395967578011821</v>
+        <v>0.006882564340653986</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.007291947462703255</v>
+        <v>0.006781070620837966</v>
       </c>
       <c r="R4" t="n">
-        <v>0.007502270764044931</v>
+        <v>0.006988038627593398</v>
       </c>
       <c r="S4" t="n">
-        <v>0.007440313951437261</v>
+        <v>0.006923503765987918</v>
       </c>
       <c r="T4" t="n">
-        <v>0.007335666760571371</v>
+        <v>0.006816330193644016</v>
       </c>
       <c r="U4" t="n">
-        <v>0.007567447708847467</v>
+        <v>0.007047280071466721</v>
       </c>
       <c r="V4" t="n">
-        <v>0.007412004799961937</v>
+        <v>0.006898753329366184</v>
       </c>
       <c r="W4" t="n">
-        <v>0.007516141163222327</v>
+        <v>0.007003694047621373</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01199938808974082</v>
+        <v>0.01148367226064383</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.01001953275154996</v>
+        <v>0.009509949016722138</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.007425740013333521</v>
+        <v>0.006909424252434897</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.007807602277731991</v>
+        <v>0.007289989165188989</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.007255488739521767</v>
+        <v>0.006774899742606196</v>
       </c>
     </row>
     <row r="5">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.009254289799712693</v>
+        <v>0.008771946170555107</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01009823194062402</v>
+        <v>0.009599830696085642</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01071785678747123</v>
+        <v>0.01022311307159407</v>
       </c>
       <c r="E5" t="n">
-        <v>0.009744659274076542</v>
+        <v>0.009225673931602372</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01153123661579586</v>
+        <v>0.01102785511664598</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01225395915531031</v>
+        <v>0.01106174306879824</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01131413979796106</v>
+        <v>0.01082152959512993</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01138625647386159</v>
+        <v>0.01075972897363942</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01345473998675165</v>
+        <v>0.01287632197568863</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01291131943906625</v>
+        <v>0.01222348239828817</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0134853636581417</v>
+        <v>0.01286949991384129</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01133142929594206</v>
+        <v>0.01182311025185924</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01158961008737803</v>
+        <v>0.01112980040466693</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01178689718900643</v>
+        <v>0.01128771614184683</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01184852774842604</v>
+        <v>0.01131336438929064</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01041482315109271</v>
+        <v>0.009919930288438478</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01459655795360036</v>
+        <v>0.01403611624499386</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0126000010551628</v>
+        <v>0.01201176230763606</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01137022817249721</v>
+        <v>0.01071646443143492</v>
       </c>
       <c r="U5" t="n">
-        <v>0.01487165450401676</v>
+        <v>0.0142085370355556</v>
       </c>
       <c r="V5" t="n">
-        <v>0.01247897258859763</v>
+        <v>0.01194772920983328</v>
       </c>
       <c r="W5" t="n">
-        <v>0.01436071279910377</v>
+        <v>0.01383467697048949</v>
       </c>
       <c r="X5" t="n">
-        <v>0.09157641048637413</v>
+        <v>0.09099858420489511</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.05975095408509202</v>
+        <v>0.05924371707141116</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01221511381055931</v>
+        <v>0.01164006652825548</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01965297834119811</v>
+        <v>0.01903331984838084</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.01000860425207211</v>
+        <v>0.0100886808101014</v>
       </c>
     </row>
     <row r="6">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.007467185762395059</v>
+        <v>0.006956659512021165</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007504036140075992</v>
+        <v>0.007643409808263068</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008191623148732194</v>
+        <v>0.007027081575327289</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00753799009923911</v>
+        <v>0.007675253269896222</v>
       </c>
       <c r="F6" t="n">
-        <v>0.007581317233228503</v>
+        <v>0.00772055941236463</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00830904918127375</v>
+        <v>0.007099468834435216</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008213557875552243</v>
+        <v>0.007049252804167549</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008225425278821438</v>
+        <v>0.007053799909205584</v>
       </c>
       <c r="J6" t="n">
-        <v>0.008363031251167243</v>
+        <v>0.007843204813605086</v>
       </c>
       <c r="K6" t="n">
-        <v>0.007678182817544927</v>
+        <v>0.007154369826688511</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008376720931238216</v>
+        <v>0.007855570728711308</v>
       </c>
       <c r="M6" t="n">
-        <v>0.008221903965614671</v>
+        <v>0.007112836101798209</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01158961008737803</v>
+        <v>0.01112980040466693</v>
       </c>
       <c r="O6" t="n">
-        <v>0.008291237360358431</v>
+        <v>0.007776561365518453</v>
       </c>
       <c r="P6" t="n">
-        <v>0.008290209905718538</v>
+        <v>0.007103621417586276</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.008181436306515844</v>
+        <v>0.007016968725006922</v>
       </c>
       <c r="R6" t="n">
-        <v>0.00839175960785752</v>
+        <v>0.007223936731762354</v>
       </c>
       <c r="S6" t="n">
-        <v>0.008329802795249849</v>
+        <v>0.007810490889826147</v>
       </c>
       <c r="T6" t="n">
-        <v>0.007572070727626494</v>
+        <v>0.007052228297812973</v>
       </c>
       <c r="U6" t="n">
-        <v>0.008470781811624218</v>
+        <v>0.007946363388566195</v>
       </c>
       <c r="V6" t="n">
-        <v>0.008301493643774523</v>
+        <v>0.007134651433535141</v>
       </c>
       <c r="W6" t="n">
-        <v>0.007773399610189626</v>
+        <v>0.007260395334884658</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01223579205679596</v>
+        <v>0.01237065938448207</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01029170359901406</v>
+        <v>0.009779908915675361</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.007662143980388644</v>
+        <v>0.007145322356603855</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.008044006244787112</v>
+        <v>0.008176976289027214</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.007491694594443667</v>
+        <v>0.007010891590922452</v>
       </c>
     </row>
     <row r="7">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007771520560952809</v>
+        <v>0.007261919501797367</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007808370938633743</v>
+        <v>0.007297580778369999</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007842873070532478</v>
+        <v>0.00733234156510349</v>
       </c>
       <c r="E7" t="n">
-        <v>0.007842324897796859</v>
+        <v>0.007329424240003154</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007885652031786254</v>
+        <v>0.007374730382471557</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007960299103074045</v>
+        <v>0.007404728824211415</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007864807797352534</v>
+        <v>0.00735451279394375</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007876675200621722</v>
+        <v>0.007359059898981784</v>
       </c>
       <c r="J7" t="n">
-        <v>0.008014281172967531</v>
+        <v>0.007497375783712013</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007982517616102681</v>
+        <v>0.007459629816464715</v>
       </c>
       <c r="L7" t="n">
-        <v>0.008027970853038505</v>
+        <v>0.007509741698818238</v>
       </c>
       <c r="M7" t="n">
-        <v>0.007873153887414955</v>
+        <v>0.007418096091574411</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01158961008737803</v>
+        <v>0.01112980040466693</v>
       </c>
       <c r="O7" t="n">
-        <v>0.007931956929167426</v>
+        <v>0.007421089037760756</v>
       </c>
       <c r="P7" t="n">
-        <v>0.007936684944691168</v>
+        <v>0.007423700774679075</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.007832686228316128</v>
+        <v>0.007322228714783122</v>
       </c>
       <c r="R7" t="n">
-        <v>0.008043009529657802</v>
+        <v>0.007529196721538553</v>
       </c>
       <c r="S7" t="n">
-        <v>0.007981052717050135</v>
+        <v>0.007464661859933076</v>
       </c>
       <c r="T7" t="n">
-        <v>0.007876405526184243</v>
+        <v>0.007357488287589172</v>
       </c>
       <c r="U7" t="n">
-        <v>0.00812069575906061</v>
+        <v>0.007599634322190687</v>
       </c>
       <c r="V7" t="n">
-        <v>0.007952743565574811</v>
+        <v>0.00743991142331134</v>
       </c>
       <c r="W7" t="n">
-        <v>0.008056879928835201</v>
+        <v>0.007544852141566528</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01254012685535369</v>
+        <v>0.012024830354589</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.010574116776127</v>
+        <v>0.01006320330392854</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.007966478778946391</v>
+        <v>0.00745058234638005</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.008348341043344863</v>
+        <v>0.007831147259134145</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.007796227505134643</v>
+        <v>0.007316057836551349</v>
       </c>
     </row>
     <row r="8">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.008966591875286704</v>
+        <v>0.00845525284785319</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01018964268186641</v>
+        <v>0.009674398646237042</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01022414481376514</v>
+        <v>0.009709159432970538</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009591979903369173</v>
+        <v>0.009076071510610321</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009265519509523652</v>
+        <v>0.008752436785352846</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01058753723261362</v>
+        <v>0.010026949917362</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01024607954058519</v>
+        <v>0.00973133066181079</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01025794694385439</v>
+        <v>0.009735877766848831</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01039555291620019</v>
+        <v>0.009874193651579054</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01036378935933534</v>
+        <v>0.00983644768433176</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01040924259627116</v>
+        <v>0.009886559566685283</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01025442563064744</v>
+        <v>0.009794913959441503</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01158961008737803</v>
+        <v>0.01112980040466693</v>
       </c>
       <c r="O8" t="n">
-        <v>0.009646433914413931</v>
+        <v>0.00913263914114304</v>
       </c>
       <c r="P8" t="n">
-        <v>0.009589222087876947</v>
+        <v>0.009073452852546203</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.008794642084674936</v>
+        <v>0.008282980340581161</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01042428127289047</v>
+        <v>0.009906014589405595</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0103623244602828</v>
+        <v>0.009841479727800114</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01025767726941691</v>
+        <v>0.009734306155456212</v>
       </c>
       <c r="U8" t="n">
-        <v>0.009923316115652005</v>
+        <v>0.009399028506976983</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01000868517930753</v>
+        <v>0.009492514312056064</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01043838479442103</v>
+        <v>0.009921902598078064</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01361080033802522</v>
+        <v>0.01309405068844637</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01413305779787531</v>
+        <v>0.01361556837965633</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.009139515811320019</v>
+        <v>0.008621931859839524</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01072961278657753</v>
+        <v>0.01020796512700119</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01141658478479816</v>
+        <v>0.01092912424883933</v>
       </c>
     </row>
     <row r="9">
@@ -2062,85 +2062,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008626918653870495</v>
+        <v>0.00823950588626654</v>
       </c>
       <c r="C9" t="n">
-        <v>0.009086128438443284</v>
+        <v>0.008730616920703749</v>
       </c>
       <c r="D9" t="n">
-        <v>0.009120630570342021</v>
+        <v>0.008765377707437228</v>
       </c>
       <c r="E9" t="n">
-        <v>0.009022603719737328</v>
+        <v>0.008657344568826298</v>
       </c>
       <c r="F9" t="n">
-        <v>0.008189755570558548</v>
+        <v>0.007757830303445165</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009238056798499985</v>
+        <v>0.008837765139267633</v>
       </c>
       <c r="H9" t="n">
-        <v>0.009142565297162076</v>
+        <v>0.008787548936277494</v>
       </c>
       <c r="I9" t="n">
-        <v>0.009154432700431267</v>
+        <v>0.008792096041315528</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009292038672777076</v>
+        <v>0.00893041192604576</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009260275115912219</v>
+        <v>0.008892665958798462</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009305728352848047</v>
+        <v>0.008942777841151982</v>
       </c>
       <c r="M9" t="n">
-        <v>0.009150911387224498</v>
+        <v>0.008851132233908158</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01158961008737803</v>
+        <v>0.01112980040466693</v>
       </c>
       <c r="O9" t="n">
-        <v>0.009349705442765446</v>
+        <v>0.009005082523372791</v>
       </c>
       <c r="P9" t="n">
-        <v>0.009384874405502753</v>
+        <v>0.009040520144237131</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.009110443923742086</v>
+        <v>0.008755265029839341</v>
       </c>
       <c r="R9" t="n">
-        <v>0.009320767029467346</v>
+        <v>0.008962232863872295</v>
       </c>
       <c r="S9" t="n">
-        <v>0.009258810216859677</v>
+        <v>0.008897698002266821</v>
       </c>
       <c r="T9" t="n">
-        <v>0.00915416302599379</v>
+        <v>0.008790524429922916</v>
       </c>
       <c r="U9" t="n">
-        <v>0.009399789233234045</v>
+        <v>0.009033570501006866</v>
       </c>
       <c r="V9" t="n">
-        <v>0.009717894905815051</v>
+        <v>0.009398526929042693</v>
       </c>
       <c r="W9" t="n">
-        <v>0.009334637428644739</v>
+        <v>0.008977888283900271</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01381788435516323</v>
+        <v>0.01345786649692274</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.01185187427593654</v>
+        <v>0.01149623944626228</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.008989591191741109</v>
+        <v>0.008609022853480299</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.009626098543154406</v>
+        <v>0.009264183401467889</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.009073985004944178</v>
+        <v>0.008749093978885094</v>
       </c>
     </row>
   </sheetData>
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004302273140983157</v>
+        <v>0.004030101591630132</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003788018389257376</v>
+        <v>0.003536640084176887</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004285389134520562</v>
+        <v>0.004080081305916832</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004159607524156993</v>
+        <v>0.003954381409662939</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004192109656813377</v>
+        <v>0.003957394232347484</v>
       </c>
       <c r="G2" t="n">
-        <v>0.004391746411352353</v>
+        <v>0.003996479054770221</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004146175938589169</v>
+        <v>0.003930987158074366</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004209988668137966</v>
+        <v>0.003989931425760231</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004293926079279423</v>
+        <v>0.004042576494121009</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004350333314198479</v>
+        <v>0.00412622170809474</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004393894628605897</v>
+        <v>0.004103562886015232</v>
       </c>
       <c r="M2" t="n">
-        <v>0.004247049138802044</v>
+        <v>0.004424063108518169</v>
       </c>
       <c r="N2" t="n">
-        <v>0.004232407368283385</v>
+        <v>0.004008756684681558</v>
       </c>
       <c r="O2" t="n">
-        <v>0.00621666702554414</v>
+        <v>0.005778985719242469</v>
       </c>
       <c r="P2" t="n">
-        <v>0.004367504259715293</v>
+        <v>0.003992302289559042</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.004185214709555182</v>
+        <v>0.003958546185443015</v>
       </c>
       <c r="R2" t="n">
-        <v>0.004154390524084811</v>
+        <v>0.003935228912832179</v>
       </c>
       <c r="S2" t="n">
-        <v>0.004336534340652126</v>
+        <v>0.004040778098060326</v>
       </c>
       <c r="T2" t="n">
-        <v>0.004263283448728453</v>
+        <v>0.004024088293147614</v>
       </c>
       <c r="U2" t="n">
-        <v>0.004480498811119222</v>
+        <v>0.004230037164575437</v>
       </c>
       <c r="V2" t="n">
-        <v>0.004157161594058754</v>
+        <v>0.003937965094514304</v>
       </c>
       <c r="W2" t="n">
-        <v>0.004316928088636355</v>
+        <v>0.004059958688690392</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004323128723509864</v>
+        <v>0.00417802910132303</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.004312334281948814</v>
+        <v>0.004172533685842775</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.005261624549574843</v>
+        <v>0.004984199988882528</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.004291779374205699</v>
+        <v>0.004061564946437663</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.004302772432069157</v>
+        <v>0.004399050820594807</v>
       </c>
     </row>
     <row r="3">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005174298136848635</v>
+        <v>0.004581911803785269</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003456129897723569</v>
+        <v>0.003195259441614894</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005063653633265562</v>
+        <v>0.004946817130724048</v>
       </c>
       <c r="E3" t="n">
-        <v>0.004160364983340498</v>
+        <v>0.004043958200591122</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004396111403389515</v>
+        <v>0.00406871754367577</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005812717073220079</v>
+        <v>0.004343890507666041</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004067860783236285</v>
+        <v>0.003880225472710428</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004524413132104924</v>
+        <v>0.004301951873161259</v>
       </c>
       <c r="J3" t="n">
-        <v>0.005118262241342438</v>
+        <v>0.004675298009786908</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005521395207126815</v>
+        <v>0.005270210689887381</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005833708429436865</v>
+        <v>0.005110010298095322</v>
       </c>
       <c r="M3" t="n">
-        <v>0.004799127001538849</v>
+        <v>0.007386659766836711</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004682788495073616</v>
+        <v>0.004434778985057482</v>
       </c>
       <c r="O3" t="n">
-        <v>0.008300800640740144</v>
+        <v>0.007246079039143967</v>
       </c>
       <c r="P3" t="n">
-        <v>0.005639718409118363</v>
+        <v>0.004313931306411436</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.004345675206112616</v>
+        <v>0.004076075634315151</v>
       </c>
       <c r="R3" t="n">
-        <v>0.004126421196474143</v>
+        <v>0.003910337027434164</v>
       </c>
       <c r="S3" t="n">
-        <v>0.005420124489210828</v>
+        <v>0.004659284363280456</v>
       </c>
       <c r="T3" t="n">
-        <v>0.004905343748026377</v>
+        <v>0.004545928796002902</v>
       </c>
       <c r="U3" t="n">
-        <v>0.006225521837719072</v>
+        <v>0.006007840665973714</v>
       </c>
       <c r="V3" t="n">
-        <v>0.004143025025904384</v>
+        <v>0.003927073895623419</v>
       </c>
       <c r="W3" t="n">
-        <v>0.005226463715967349</v>
+        <v>0.004990602606389177</v>
       </c>
       <c r="X3" t="n">
-        <v>0.005332183961237602</v>
+        <v>0.005645818790167156</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.005251679361733292</v>
+        <v>0.005601998640190402</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006359584248456922</v>
+        <v>0.00580970822039728</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.005105615413653617</v>
+        <v>0.004810834121720739</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.005194436376638233</v>
+        <v>0.007207948533944435</v>
       </c>
     </row>
     <row r="4">
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009947384417457735</v>
+        <v>0.008327100462443067</v>
       </c>
       <c r="C4" t="n">
-        <v>0.008143542860131019</v>
+        <v>0.007140161114559737</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009756671797435952</v>
+        <v>0.008891644327115806</v>
       </c>
       <c r="E4" t="n">
-        <v>0.008335910645980089</v>
+        <v>0.007471806174118981</v>
       </c>
       <c r="F4" t="n">
-        <v>0.008703037186053511</v>
+        <v>0.007505837392307777</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01095802616601559</v>
+        <v>0.00794731844147924</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008184194708156742</v>
+        <v>0.007207557340538578</v>
       </c>
       <c r="I4" t="n">
-        <v>0.008904988843716346</v>
+        <v>0.007873359959753251</v>
       </c>
       <c r="J4" t="n">
-        <v>0.009848612586012044</v>
+        <v>0.008464284802526438</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01049024618269678</v>
+        <v>0.009412821395348974</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01098229126812322</v>
+        <v>0.009156879576387828</v>
       </c>
       <c r="M4" t="n">
-        <v>0.00934082455015162</v>
+        <v>0.01273280759936471</v>
       </c>
       <c r="N4" t="n">
-        <v>0.009158218374970429</v>
+        <v>0.03297149078316958</v>
       </c>
       <c r="O4" t="n">
-        <v>0.009881432594946081</v>
+        <v>0.007867666557285892</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01068419991133433</v>
+        <v>0.007900139957012038</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.008625155584939821</v>
+        <v>0.007518849232446407</v>
       </c>
       <c r="R4" t="n">
-        <v>0.008276982230226092</v>
+        <v>0.007255469911831645</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01033438042864921</v>
+        <v>0.00844769651400773</v>
       </c>
       <c r="T4" t="n">
-        <v>0.009506977907296215</v>
+        <v>0.00825917748982904</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01146937197002782</v>
+        <v>0.01055700288846654</v>
       </c>
       <c r="V4" t="n">
-        <v>0.008277957822975667</v>
+        <v>0.007261220632305535</v>
       </c>
       <c r="W4" t="n">
-        <v>0.009991997275780073</v>
+        <v>0.009057800709497554</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01018295781613878</v>
+        <v>0.009998009734440738</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.01002997526565449</v>
+        <v>0.009911305334629188</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.009120356384072086</v>
+        <v>0.007607054131472678</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.009828852494335179</v>
+        <v>0.008682493528852394</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.009957631672156859</v>
+        <v>0.01243644431847349</v>
       </c>
     </row>
     <row r="5">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04732379549423119</v>
+        <v>0.0346343975626832</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01677652688413817</v>
+        <v>0.01470043602726599</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04920008599366237</v>
+        <v>0.0498678608026947</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01923368177488292</v>
+        <v>0.01983355148087462</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0282759063195393</v>
+        <v>0.02228821896844209</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06634601177937142</v>
+        <v>0.02853491205235853</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01823244132600953</v>
+        <v>0.0166353178794774</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0324827687751388</v>
+        <v>0.02980166055562299</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04750398513871003</v>
+        <v>0.03971546909689697</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05986240179214375</v>
+        <v>0.05643381480529251</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06995231462758034</v>
+        <v>0.05243803580378189</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04119908726291243</v>
+        <v>0.1274347467007054</v>
       </c>
       <c r="N5" t="n">
-        <v>0.07582332776271709</v>
+        <v>0.03297149078316958</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04523069613759211</v>
+        <v>0.02620743592045998</v>
       </c>
       <c r="P5" t="n">
-        <v>0.06117897600555774</v>
+        <v>0.0275597656581545</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.02612114376597994</v>
+        <v>0.02205403258352862</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01994932257229476</v>
+        <v>0.0174511139221184</v>
       </c>
       <c r="S5" t="n">
-        <v>0.055365446479924</v>
+        <v>0.03756742817998295</v>
       </c>
       <c r="T5" t="n">
-        <v>0.04417829539686315</v>
+        <v>0.0372065892412899</v>
       </c>
       <c r="U5" t="n">
-        <v>0.07816553572513822</v>
+        <v>0.07770746089314551</v>
       </c>
       <c r="V5" t="n">
-        <v>0.01874591163249567</v>
+        <v>0.01645789239764522</v>
       </c>
       <c r="W5" t="n">
-        <v>0.05167431636538316</v>
+        <v>0.05095009998457876</v>
       </c>
       <c r="X5" t="n">
-        <v>0.05680477261309209</v>
+        <v>0.07075541222193875</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.05257278138041042</v>
+        <v>0.06702393976634555</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.03357754032546514</v>
+        <v>0.02247648503297251</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.04853731923792333</v>
+        <v>0.04378273368313318</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.05534339586243267</v>
+        <v>0.1259028211815217</v>
       </c>
     </row>
     <row r="6">
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01037973942137702</v>
+        <v>0.008627301539816692</v>
       </c>
       <c r="C6" t="n">
-        <v>0.009527125559650605</v>
+        <v>0.008251261336513636</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01114025449695554</v>
+        <v>0.009191845404489432</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008768265649899369</v>
+        <v>0.008582906396072882</v>
       </c>
       <c r="F6" t="n">
-        <v>0.009135392189972799</v>
+        <v>0.007806038469681407</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01139038116993488</v>
+        <v>0.00905841866343314</v>
       </c>
       <c r="H6" t="n">
-        <v>0.009567777407676323</v>
+        <v>0.008318657562492475</v>
       </c>
       <c r="I6" t="n">
-        <v>0.009337343847635625</v>
+        <v>0.008984460181707147</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01123219528553162</v>
+        <v>0.009575385024480333</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01187382888221637</v>
+        <v>0.00971302247272259</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0114146462720425</v>
+        <v>0.01026797979834172</v>
       </c>
       <c r="M6" t="n">
-        <v>0.009773179554070902</v>
+        <v>0.01384390782131861</v>
       </c>
       <c r="N6" t="n">
-        <v>0.009596093138066418</v>
+        <v>0.03297149078316958</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01126807809332104</v>
+        <v>0.00817256947364145</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01207083810665821</v>
+        <v>0.009013880938011301</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0100087382844594</v>
+        <v>0.007819050309820039</v>
       </c>
       <c r="R6" t="n">
-        <v>0.009660564929745671</v>
+        <v>0.008366570133785545</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01171796312816879</v>
+        <v>0.00874789759138136</v>
       </c>
       <c r="T6" t="n">
-        <v>0.009939332911215491</v>
+        <v>0.008559378567202664</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0119327813413109</v>
+        <v>0.01088183511978626</v>
       </c>
       <c r="V6" t="n">
-        <v>0.009661540522495255</v>
+        <v>0.007561421709679167</v>
       </c>
       <c r="W6" t="n">
-        <v>0.01137863560076826</v>
+        <v>0.009391385754882336</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01156654051565837</v>
+        <v>0.01110910995639464</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01052224019606419</v>
+        <v>0.0102594948737745</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.01050393908359167</v>
+        <v>0.007907255208846319</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.01026120749825446</v>
+        <v>0.009793593750806295</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01039970133216694</v>
+        <v>0.0127781139540409</v>
       </c>
     </row>
     <row r="7">
@@ -2746,85 +2746,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01066071660100212</v>
+        <v>0.009004151041548307</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0088568750436754</v>
+        <v>0.007817211693664977</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01047000398098033</v>
+        <v>0.009568694906221047</v>
       </c>
       <c r="E7" t="n">
-        <v>0.009049242829524467</v>
+        <v>0.008148856753224222</v>
       </c>
       <c r="F7" t="n">
-        <v>0.009416369369597898</v>
+        <v>0.008182887971413021</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01167135834955997</v>
+        <v>0.008624369020584482</v>
       </c>
       <c r="H7" t="n">
-        <v>0.008897526891701125</v>
+        <v>0.00788460791964382</v>
       </c>
       <c r="I7" t="n">
-        <v>0.009618321027260729</v>
+        <v>0.008550410538858487</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01056194476955643</v>
+        <v>0.00914133538163168</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01120357836624117</v>
+        <v>0.01008987197445421</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0116956234516676</v>
+        <v>0.009833930155493078</v>
       </c>
       <c r="M7" t="n">
-        <v>0.010054156733696</v>
+        <v>0.01340985817846996</v>
       </c>
       <c r="N7" t="n">
-        <v>0.009871550558514817</v>
+        <v>0.03297149078316958</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01059473918452504</v>
+        <v>0.008544692991916807</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01139750650091329</v>
+        <v>0.00857716639164295</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.009338487768484203</v>
+        <v>0.008195899811551647</v>
       </c>
       <c r="R7" t="n">
-        <v>0.008990314413770475</v>
+        <v>0.007932520490936887</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0110477126121936</v>
+        <v>0.009124747093112969</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0102203100908406</v>
+        <v>0.008936228068934279</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01221277698824043</v>
+        <v>0.01125830477185539</v>
       </c>
       <c r="V7" t="n">
-        <v>0.008991290006520053</v>
+        <v>0.007938271211410778</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01070532945932445</v>
+        <v>0.009734851288602788</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01089628999968316</v>
+        <v>0.01067506031354599</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01077436181656267</v>
+        <v>0.01061298706768052</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.009833688567616471</v>
+        <v>0.008284104710577923</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01054218467787956</v>
+        <v>0.009359544107957625</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01067096385570124</v>
+        <v>0.01311349489757873</v>
       </c>
     </row>
     <row r="8">
@@ -2834,85 +2834,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01210006539724169</v>
+        <v>0.01038005001348973</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01180961633005829</v>
+        <v>0.01060401614530916</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01342274526736322</v>
+        <v>0.01235549935786523</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01119614725721185</v>
+        <v>0.01018439565604281</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01109148702839938</v>
+        <v>0.009778589527487338</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01493791142760152</v>
+        <v>0.01170373391463624</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01185026817808401</v>
+        <v>0.010671412371288</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01257106231364362</v>
+        <v>0.01133721499050267</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0135146860559393</v>
+        <v>0.01192813983327586</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01415631965262406</v>
+        <v>0.01287667642609838</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01464836473805049</v>
+        <v>0.01262073460713725</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01300689802007871</v>
+        <v>0.01619666263011435</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01165115947996402</v>
+        <v>0.03297149078316958</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01269676065991275</v>
+        <v>0.01053838870185203</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01342050314245551</v>
+        <v>0.01049718883317992</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01048042039894057</v>
+        <v>0.009294523654397131</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01194305570015336</v>
+        <v>0.01071932494258107</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01400045389857648</v>
+        <v>0.01191155154475716</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01317305137722348</v>
+        <v>0.01172303252057846</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01442709230279679</v>
+        <v>0.01335656927685271</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01152958119333358</v>
+        <v>0.0103391498735619</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01365836817059902</v>
+        <v>0.01252193302356309</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01217692805895817</v>
+        <v>0.0119029964470947</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01523056746586462</v>
+        <v>0.01480215114466819</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01124492532138406</v>
+        <v>0.009633795388877882</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01349492596426245</v>
+        <v>0.01214634855960181</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01520457014576871</v>
+        <v>0.01737410810073392</v>
       </c>
     </row>
     <row r="9">
@@ -2922,85 +2922,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01266146236171374</v>
+        <v>0.01050473586472888</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01167158675640937</v>
+        <v>0.00996638160292064</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01328471569371431</v>
+        <v>0.01171786481547671</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01167609505403282</v>
+        <v>0.01014833513793589</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01035466650541079</v>
+        <v>0.008836893484095321</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01448607075573084</v>
+        <v>0.01077353797793641</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01171223860443509</v>
+        <v>0.01003377782889948</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01243303273999469</v>
+        <v>0.01069958044811414</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0133766564822904</v>
+        <v>0.01129050529088735</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01401829007897514</v>
+        <v>0.01223904188370986</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01451033516440157</v>
+        <v>0.01198310006474873</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01286886844642997</v>
+        <v>0.0155590280877256</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01268626227124878</v>
+        <v>0.03297149078316958</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01367922466516817</v>
+        <v>0.010908826026559</v>
       </c>
       <c r="P9" t="n">
-        <v>0.01454065743047931</v>
+        <v>0.01098804517392441</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.01215320017465506</v>
+        <v>0.01034506876890358</v>
       </c>
       <c r="R9" t="n">
-        <v>0.01180502612650444</v>
+        <v>0.01008169040019255</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01386242432492756</v>
+        <v>0.01127391700236863</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01303502180357456</v>
+        <v>0.01108539797818994</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01502847023366998</v>
+        <v>0.01340785453077353</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0127453012493229</v>
+        <v>0.01083589161020357</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01352004117205842</v>
+        <v>0.01188402119785846</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01371100171241714</v>
+        <v>0.01282423022280165</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.01358907352929664</v>
+        <v>0.01276215697693618</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.01215765146731363</v>
+        <v>0.01004223510937602</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.01335689639061353</v>
+        <v>0.01150871401721329</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.01348567556843521</v>
+        <v>0.01526266480683436</v>
       </c>
     </row>
   </sheetData>
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004415065367693025</v>
+        <v>0.00399456607521661</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004003415423593327</v>
+        <v>0.003521763962937451</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004470187714911665</v>
+        <v>0.004104246026388357</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00434893006447886</v>
+        <v>0.003948763468802637</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004359131415316873</v>
+        <v>0.003950727475349812</v>
       </c>
       <c r="G2" t="n">
-        <v>0.004525603678828764</v>
+        <v>0.003983737821440282</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00427173217831005</v>
+        <v>0.003901777856795476</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004411544266561277</v>
+        <v>0.004020717068126793</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0044339434561337</v>
+        <v>0.004035382589679567</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004473100949035378</v>
+        <v>0.004073223503473232</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004494335834809565</v>
+        <v>0.004064533138609716</v>
       </c>
       <c r="M2" t="n">
-        <v>0.004366279363027865</v>
+        <v>0.004346266327354472</v>
       </c>
       <c r="N2" t="n">
-        <v>0.004347336192422674</v>
+        <v>0.003964842312573338</v>
       </c>
       <c r="O2" t="n">
-        <v>0.006365710050447092</v>
+        <v>0.005726995297872798</v>
       </c>
       <c r="P2" t="n">
-        <v>0.004514450182457483</v>
+        <v>0.003977921493915356</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.00432610601910695</v>
+        <v>0.003942433930689932</v>
       </c>
       <c r="R2" t="n">
-        <v>0.004281705035253211</v>
+        <v>0.00390805804771761</v>
       </c>
       <c r="S2" t="n">
-        <v>0.004461549177406344</v>
+        <v>0.004022092996012954</v>
       </c>
       <c r="T2" t="n">
-        <v>0.004403573169186957</v>
+        <v>0.00400557638360073</v>
       </c>
       <c r="U2" t="n">
-        <v>0.004686775475786237</v>
+        <v>0.004177369872237374</v>
       </c>
       <c r="V2" t="n">
-        <v>0.004321344125383367</v>
+        <v>0.003943784428996081</v>
       </c>
       <c r="W2" t="n">
-        <v>0.00450550373537078</v>
+        <v>0.004028736351977564</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004756973589622615</v>
+        <v>0.004443119376221681</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.004697633532903654</v>
+        <v>0.004443832545178131</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.00537490863751219</v>
+        <v>0.004974036989107618</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.004455774106202255</v>
+        <v>0.004058914240346221</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.004399772191544986</v>
+        <v>0.004361701974654029</v>
       </c>
     </row>
     <row r="3">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005071393288354365</v>
+        <v>0.00436666110765296</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003683920832798929</v>
+        <v>0.003132414567038807</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005472559568051202</v>
+        <v>0.00515594073255536</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00460161974536795</v>
+        <v>0.004040778793970113</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004677986732100783</v>
+        <v>0.004057612810175436</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00585692283495141</v>
+        <v>0.004289467390136522</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004053086068079554</v>
+        <v>0.00370771278861456</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005054088761955042</v>
+        <v>0.004559265476039723</v>
       </c>
       <c r="J3" t="n">
-        <v>0.005207125533844537</v>
+        <v>0.004660718088716801</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005484344206684978</v>
+        <v>0.00492622523960201</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00564022118079924</v>
+        <v>0.004868016261145691</v>
       </c>
       <c r="M3" t="n">
-        <v>0.00474246072662936</v>
+        <v>0.006871618056570643</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004592820590007523</v>
+        <v>0.004157904655258587</v>
       </c>
       <c r="O3" t="n">
-        <v>0.00829287845237817</v>
+        <v>0.007037997472512392</v>
       </c>
       <c r="P3" t="n">
-        <v>0.005777465914130682</v>
+        <v>0.004247991143788181</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.004440655892618804</v>
+        <v>0.003997421687418658</v>
       </c>
       <c r="R3" t="n">
-        <v>0.004124385427746242</v>
+        <v>0.003752564866536732</v>
       </c>
       <c r="S3" t="n">
-        <v>0.005402270389420242</v>
+        <v>0.004562632950367268</v>
       </c>
       <c r="T3" t="n">
-        <v>0.004996563540060019</v>
+        <v>0.004450481357447488</v>
       </c>
       <c r="U3" t="n">
-        <v>0.006316664543535297</v>
+        <v>0.005693975684289497</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0044040205035437</v>
+        <v>0.004004784462544816</v>
       </c>
       <c r="W3" t="n">
-        <v>0.005118112858482764</v>
+        <v>0.004833854261760803</v>
       </c>
       <c r="X3" t="n">
-        <v>0.007521547598336969</v>
+        <v>0.007577282678540869</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.007091503139868149</v>
+        <v>0.007575037038004701</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.00646297503496977</v>
+        <v>0.005793366436081757</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.005366309192609426</v>
+        <v>0.004828936955748125</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.004980083711083459</v>
+        <v>0.006980201644754007</v>
       </c>
     </row>
     <row r="4">
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009600396623932405</v>
+        <v>0.007975770326985277</v>
       </c>
       <c r="C4" t="n">
-        <v>0.008133079444007974</v>
+        <v>0.007035780572255179</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01022302889329951</v>
+        <v>0.00921465583074039</v>
       </c>
       <c r="E4" t="n">
-        <v>0.008853367950385872</v>
+        <v>0.00745840881729955</v>
       </c>
       <c r="F4" t="n">
-        <v>0.008968596900954463</v>
+        <v>0.007480593174737519</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01084897769834599</v>
+        <v>0.007853460219338805</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00798138231332695</v>
+        <v>0.006927684715229265</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009560624166862781</v>
+        <v>0.008271157821956936</v>
       </c>
       <c r="J4" t="n">
-        <v>0.009809430594326858</v>
+        <v>0.008433344915236847</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01025593521288067</v>
+        <v>0.008864242163348508</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01049579301623026</v>
+        <v>0.008766080494449812</v>
       </c>
       <c r="M4" t="n">
-        <v>0.00907209615581935</v>
+        <v>0.01191288500804202</v>
       </c>
       <c r="N4" t="n">
-        <v>0.008835364432293786</v>
+        <v>0.02342734401567639</v>
       </c>
       <c r="O4" t="n">
-        <v>0.00960951645500701</v>
+        <v>0.007588601155589952</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01072299382597054</v>
+        <v>0.007787762124301895</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.008595559858330517</v>
+        <v>0.007386913772585122</v>
       </c>
       <c r="R4" t="n">
-        <v>0.008094030320240793</v>
+        <v>0.006998622360725303</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01012545263825333</v>
+        <v>0.008286699560389221</v>
       </c>
       <c r="T4" t="n">
-        <v>0.009470586955133876</v>
+        <v>0.008100136825175979</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01121525799640028</v>
+        <v>0.01007105754889803</v>
       </c>
       <c r="V4" t="n">
-        <v>0.008513363443148118</v>
+        <v>0.007378741925142513</v>
       </c>
       <c r="W4" t="n">
-        <v>0.009380677059049986</v>
+        <v>0.008815423098825782</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01346240727617998</v>
+        <v>0.01304238620655057</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.01276577532786747</v>
+        <v>0.01303106922579695</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.009205897186131049</v>
+        <v>0.007584983642889462</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01006022055233915</v>
+        <v>0.008702612453742665</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.009441818206943359</v>
+        <v>0.01206924119309313</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03844846838582193</v>
+        <v>0.02761209780596947</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01465372142704873</v>
+        <v>0.01245326177926406</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05347975588141737</v>
+        <v>0.05288625308678496</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02639551624471174</v>
+        <v>0.0189867563415854</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03027811859797563</v>
+        <v>0.02083886043202621</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05877599653004886</v>
+        <v>0.02549448151019955</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01223306677186347</v>
+        <v>0.01077776807629338</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04180052254375435</v>
+        <v>0.03592690879694007</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04273309732656815</v>
+        <v>0.03718672065028883</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04939397478847922</v>
+        <v>0.04238413113682189</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05587630053071033</v>
+        <v>0.04262479409825139</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0326750036117008</v>
+        <v>0.1045759108827802</v>
       </c>
       <c r="N5" t="n">
-        <v>0.06484267164585669</v>
+        <v>0.02342734401567639</v>
       </c>
       <c r="O5" t="n">
-        <v>0.03713768721141866</v>
+        <v>0.02060807100604821</v>
       </c>
       <c r="P5" t="n">
-        <v>0.05662349659226042</v>
+        <v>0.02435072988459288</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.02283722229989293</v>
+        <v>0.01866392622131481</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01428895793304689</v>
+        <v>0.01204798601881441</v>
       </c>
       <c r="S5" t="n">
-        <v>0.04727882658168974</v>
+        <v>0.0328578978892877</v>
       </c>
       <c r="T5" t="n">
-        <v>0.03987894006173294</v>
+        <v>0.03252677098952758</v>
       </c>
       <c r="U5" t="n">
-        <v>0.06724892391986029</v>
+        <v>0.06418549885485579</v>
       </c>
       <c r="V5" t="n">
-        <v>0.02048444335311349</v>
+        <v>0.01773092587376963</v>
       </c>
       <c r="W5" t="n">
-        <v>0.03671581100201095</v>
+        <v>0.04399537881621741</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1119047642795586</v>
+        <v>0.1220297315282961</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.09666508353066379</v>
+        <v>0.1183707378645816</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0308485727193156</v>
+        <v>0.02055526951575417</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.04884876142977888</v>
+        <v>0.04203242766514149</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0408998057498965</v>
+        <v>0.1115889521024309</v>
       </c>
     </row>
     <row r="6">
@@ -3518,85 +3518,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01030378232539556</v>
+        <v>0.009025720763750513</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008836465145471135</v>
+        <v>0.00732771879803092</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01189414609677663</v>
+        <v>0.01026460626750562</v>
       </c>
       <c r="E6" t="n">
-        <v>0.009556753651849027</v>
+        <v>0.008508359254064787</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01063971410443158</v>
+        <v>0.007772531400513262</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01155236339980915</v>
+        <v>0.008145398445114544</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008684768014790109</v>
+        <v>0.00721962294100501</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01026400986832593</v>
+        <v>0.00856309604773268</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01148054779780397</v>
+        <v>0.009483295352002088</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01192705241635778</v>
+        <v>0.009914192600113744</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01119917871769341</v>
+        <v>0.009816030931215041</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01074321335929646</v>
+        <v>0.01220482323381776</v>
       </c>
       <c r="N6" t="n">
-        <v>0.009542147545114532</v>
+        <v>0.02342734401567639</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01031629956782776</v>
+        <v>0.008639860251791439</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01239914413896595</v>
+        <v>0.008839292396593867</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01026667706180764</v>
+        <v>0.008436864209350355</v>
       </c>
       <c r="R6" t="n">
-        <v>0.009765147523717908</v>
+        <v>0.007290560586501047</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01082883833971649</v>
+        <v>0.009336649997154459</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01017397265659704</v>
+        <v>0.008392075050951726</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01194500240776056</v>
+        <v>0.01038236832686443</v>
       </c>
       <c r="V6" t="n">
-        <v>0.01018448064662523</v>
+        <v>0.008428692361907748</v>
       </c>
       <c r="W6" t="n">
-        <v>0.01013658628074778</v>
+        <v>0.009866672309704087</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01416579297764314</v>
+        <v>0.01333432443232632</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01353723334133833</v>
+        <v>0.01336600011451571</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.009909282887594203</v>
+        <v>0.008634934079654693</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.01173133775581626</v>
+        <v>0.009752562890507901</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01014856821204261</v>
+        <v>0.01242645231025853</v>
       </c>
     </row>
     <row r="7">
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01020704460102515</v>
+        <v>0.008598824332920202</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008739727421100725</v>
+        <v>0.007658834578190098</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01082967687039227</v>
+        <v>0.009837709836675311</v>
       </c>
       <c r="E7" t="n">
-        <v>0.009460015927478622</v>
+        <v>0.008081462823234471</v>
       </c>
       <c r="F7" t="n">
-        <v>0.009575244878047213</v>
+        <v>0.008103647180672436</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01145562567543875</v>
+        <v>0.008476514225273729</v>
       </c>
       <c r="H7" t="n">
-        <v>0.008588030290419702</v>
+        <v>0.007550738721164185</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01016727214395553</v>
+        <v>0.008894211827891855</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01041607857141961</v>
+        <v>0.009056398921171771</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01086258318997343</v>
+        <v>0.009487296169283434</v>
       </c>
       <c r="L7" t="n">
-        <v>0.011102440993323</v>
+        <v>0.009389134500384734</v>
       </c>
       <c r="M7" t="n">
-        <v>0.009678744132912103</v>
+        <v>0.01253593901397694</v>
       </c>
       <c r="N7" t="n">
-        <v>0.009442012409386542</v>
+        <v>0.02342734401567639</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01021613997164719</v>
+        <v>0.008211632772280252</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01132961734261071</v>
+        <v>0.0084107937409922</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.009202207835423271</v>
+        <v>0.008009967778520045</v>
       </c>
       <c r="R7" t="n">
-        <v>0.008700678297333543</v>
+        <v>0.007621676366660224</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01073210061534609</v>
+        <v>0.008909753566324145</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01007723493222663</v>
+        <v>0.008723190831110899</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01184689356738439</v>
+        <v>0.01071268844020142</v>
       </c>
       <c r="V7" t="n">
-        <v>0.009120011420240865</v>
+        <v>0.008001795931077443</v>
       </c>
       <c r="W7" t="n">
-        <v>0.009987325036142743</v>
+        <v>0.009438477104760696</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01406905525327273</v>
+        <v>0.01366544021248548</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01339878201485734</v>
+        <v>0.01367349578392253</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.009812545163223798</v>
+        <v>0.008208037648824386</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0106668685294319</v>
+        <v>0.009325666459677589</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01004846618403611</v>
+        <v>0.01269229519902805</v>
       </c>
     </row>
     <row r="8">
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0116051054047865</v>
+        <v>0.0098694463234402</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01159071059540039</v>
+        <v>0.01022962112352967</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01368066004469194</v>
+        <v>0.01240849638201489</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01153736079801796</v>
+        <v>0.009959950095593305</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01119965400646279</v>
+        <v>0.009576819613486573</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01460788176816982</v>
+        <v>0.01131689836083738</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01143901346471937</v>
+        <v>0.01012152526650376</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0130182553182552</v>
+        <v>0.01146499837323143</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01326706174571927</v>
+        <v>0.01162718546651134</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01371356636427309</v>
+        <v>0.012058082714623</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01395342416762267</v>
+        <v>0.0119599210457243</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01252972730721162</v>
+        <v>0.01510672555931704</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01116673767787248</v>
+        <v>0.02342734401567639</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0122503951521807</v>
+        <v>0.01005156123279826</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01328800525826376</v>
+        <v>0.01018283149331646</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01031473623206977</v>
+        <v>0.009025077759218327</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01155166147163321</v>
+        <v>0.0101924629119998</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01358308378964574</v>
+        <v>0.01148054011166371</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0129282181065263</v>
+        <v>0.01129397737645048</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01398905221550552</v>
+        <v>0.01264907841510329</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01157273791536184</v>
+        <v>0.01021656692093233</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01283859375120749</v>
+        <v>0.01200951916966428</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01531474687211113</v>
+        <v>0.01479971285808417</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01769258749277148</v>
+        <v>0.01753598117388911</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01118361718803065</v>
+        <v>0.009454508415236002</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01351785170373157</v>
+        <v>0.01189645300501717</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01441714826565105</v>
+        <v>0.01662121233984539</v>
       </c>
     </row>
     <row r="9">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01193825375855498</v>
+        <v>0.009877940084845915</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01119545931467686</v>
+        <v>0.009506201286091599</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0132854087639684</v>
+        <v>0.01168507654457682</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01174853151552194</v>
+        <v>0.009797678977897883</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01036075312848894</v>
+        <v>0.008641041278719607</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01391135833171526</v>
+        <v>0.01032388021756239</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01104376218399584</v>
+        <v>0.009398105429065695</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01262300403753167</v>
+        <v>0.01074157853579336</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01287181046499574</v>
+        <v>0.01090376562907328</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01331831508354956</v>
+        <v>0.01133466287718493</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01355817288689915</v>
+        <v>0.01123650120828624</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01213447602648823</v>
+        <v>0.01438330572187847</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01189774430296268</v>
+        <v>0.02342734401567639</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01291200322717842</v>
+        <v>0.01024733853940965</v>
       </c>
       <c r="P9" t="n">
-        <v>0.01407769956380382</v>
+        <v>0.01048745530850654</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.01165794049169979</v>
+        <v>0.009857333770808711</v>
       </c>
       <c r="R9" t="n">
-        <v>0.01115641019090968</v>
+        <v>0.009469043074561726</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01318783250892223</v>
+        <v>0.01075712027422565</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01253296682580275</v>
+        <v>0.0105705575390124</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01430399657696629</v>
+        <v>0.01256085081492512</v>
       </c>
       <c r="V9" t="n">
-        <v>0.01241182749964322</v>
+        <v>0.01050490987070329</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01244305692971888</v>
+        <v>0.01128584381266221</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01652478714684885</v>
+        <v>0.015512806920387</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.01585451390843349</v>
+        <v>0.01552086249182404</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.01183145457689935</v>
+        <v>0.009712799276957137</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.01312260042300804</v>
+        <v>0.01117303316757909</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.01250419807761224</v>
+        <v>0.01453966190692955</v>
       </c>
     </row>
   </sheetData>
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004166456991908827</v>
+        <v>0.003974342344336124</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003654459516349168</v>
+        <v>0.003480025254382845</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004181966274925444</v>
+        <v>0.004035819590429869</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004099020519234397</v>
+        <v>0.00392684247977157</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004151931497932118</v>
+        <v>0.003955734916750234</v>
       </c>
       <c r="G2" t="n">
-        <v>0.004269907591629528</v>
+        <v>0.003968648396365589</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004049124587820165</v>
+        <v>0.003897944013643519</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004188942057528043</v>
+        <v>0.004016300752072319</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004193507562392806</v>
+        <v>0.004026582628959283</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004290119537013493</v>
+        <v>0.004102489866327038</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0042233777829216</v>
+        <v>0.004031728522204709</v>
       </c>
       <c r="M2" t="n">
-        <v>0.004126687049752296</v>
+        <v>0.004262399105687043</v>
       </c>
       <c r="N2" t="n">
-        <v>0.004090593282381866</v>
+        <v>0.003935238995352395</v>
       </c>
       <c r="O2" t="n">
-        <v>0.005960444331515828</v>
+        <v>0.005687728720697316</v>
       </c>
       <c r="P2" t="n">
-        <v>0.00425993483656234</v>
+        <v>0.003960764707794986</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.004106424984343776</v>
+        <v>0.003939220700154204</v>
       </c>
       <c r="R2" t="n">
-        <v>0.004082575360882912</v>
+        <v>0.00392453354749563</v>
       </c>
       <c r="S2" t="n">
-        <v>0.004226513492466696</v>
+        <v>0.004010786022564048</v>
       </c>
       <c r="T2" t="n">
-        <v>0.004181735044758279</v>
+        <v>0.004001622626480112</v>
       </c>
       <c r="U2" t="n">
-        <v>0.004293641261479725</v>
+        <v>0.004086888749550316</v>
       </c>
       <c r="V2" t="n">
-        <v>0.004138352839961962</v>
+        <v>0.003970234574966036</v>
       </c>
       <c r="W2" t="n">
-        <v>0.004034545802303917</v>
+        <v>0.003901051632388437</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004646133772721247</v>
+        <v>0.004550956177447636</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.004676378821027553</v>
+        <v>0.004741848481448845</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.00518460323304301</v>
+        <v>0.004955867350207296</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.004247032686219918</v>
+        <v>0.004066742485299926</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.004162771913018217</v>
+        <v>0.004302847102272585</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004660627386928749</v>
+        <v>0.0042526571457982</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003262266503615203</v>
+        <v>0.003071644579769124</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004776378827801562</v>
+        <v>0.00469494195301362</v>
       </c>
       <c r="E3" t="n">
-        <v>0.004181162408797282</v>
+        <v>0.003914500343359151</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004563318468968561</v>
+        <v>0.004124129203694277</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00539454164818911</v>
+        <v>0.004212078431478546</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003828564419986445</v>
+        <v>0.003711217665844782</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004828564628477471</v>
+        <v>0.004557684488400047</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004854565293080617</v>
+        <v>0.0046274812617572</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005541723454940562</v>
+        <v>0.005165158207490578</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005068222905167005</v>
+        <v>0.004662816368262748</v>
       </c>
       <c r="M3" t="n">
-        <v>0.004393551458136424</v>
+        <v>0.006300052859725807</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004124433380747146</v>
+        <v>0.003977285082549363</v>
       </c>
       <c r="O3" t="n">
-        <v>0.007438541060675863</v>
+        <v>0.0068792429058345</v>
       </c>
       <c r="P3" t="n">
-        <v>0.005323532338572369</v>
+        <v>0.004155964590499598</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.004236447375150137</v>
+        <v>0.004004880797833441</v>
       </c>
       <c r="R3" t="n">
-        <v>0.004068196267538556</v>
+        <v>0.003901670646472604</v>
       </c>
       <c r="S3" t="n">
-        <v>0.005088512981347694</v>
+        <v>0.004512383555498769</v>
       </c>
       <c r="T3" t="n">
-        <v>0.00477764700520645</v>
+        <v>0.004453181459585457</v>
       </c>
       <c r="U3" t="n">
-        <v>0.00596155711534051</v>
+        <v>0.005672729110890629</v>
       </c>
       <c r="V3" t="n">
-        <v>0.00446025686685087</v>
+        <v>0.004222818354617452</v>
       </c>
       <c r="W3" t="n">
-        <v>0.004227663805874277</v>
+        <v>0.004471958408658457</v>
       </c>
       <c r="X3" t="n">
-        <v>0.008088606168304707</v>
+        <v>0.008370924285599919</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.008308789030032571</v>
+        <v>0.009739148290660778</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006223268526085681</v>
+        <v>0.005721245459328413</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.005241286204723563</v>
+        <v>0.004916087463002086</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.004650318700041592</v>
+        <v>0.006589882115844948</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009116342615031369</v>
+        <v>0.007809545180607812</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007966772763896153</v>
+        <v>0.007051484841024355</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009291527101326745</v>
+        <v>0.008503958956167155</v>
       </c>
       <c r="E4" t="n">
-        <v>0.008354616633863648</v>
+        <v>0.007273012359333957</v>
       </c>
       <c r="F4" t="n">
-        <v>0.008952270478507164</v>
+        <v>0.007599365726185602</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01028486472850378</v>
+        <v>0.007745229418935152</v>
       </c>
       <c r="H4" t="n">
-        <v>0.007791019135277429</v>
+        <v>0.006946590890466397</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0093703217748417</v>
+        <v>0.008283484697809288</v>
       </c>
       <c r="J4" t="n">
-        <v>0.009418296483961306</v>
+        <v>0.008396606771908817</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01051316794957</v>
+        <v>0.009257030392267804</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009759289134378245</v>
+        <v>0.008457748458579569</v>
       </c>
       <c r="M4" t="n">
-        <v>0.008687332706640051</v>
+        <v>0.01103604525879262</v>
       </c>
       <c r="N4" t="n">
-        <v>0.008259427116893812</v>
+        <v>0.01821224625945391</v>
       </c>
       <c r="O4" t="n">
-        <v>0.00873741807643884</v>
+        <v>0.007392097510920871</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01017221787232593</v>
+        <v>0.007656179529854276</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.008438253473496225</v>
+        <v>0.007412830052818473</v>
       </c>
       <c r="R4" t="n">
-        <v>0.008168861005136989</v>
+        <v>0.007246931907115832</v>
       </c>
       <c r="S4" t="n">
-        <v>0.009794708416187795</v>
+        <v>0.008221193291112492</v>
       </c>
       <c r="T4" t="n">
-        <v>0.00928891525021751</v>
+        <v>0.008117688516973911</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01135280079579315</v>
+        <v>0.01034837072050078</v>
       </c>
       <c r="V4" t="n">
-        <v>0.008774582510577522</v>
+        <v>0.007742754709384797</v>
       </c>
       <c r="W4" t="n">
-        <v>0.008663277450526486</v>
+        <v>0.00850287282546331</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01453451251652879</v>
+        <v>0.01432266368107064</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.01485754433475378</v>
+        <v>0.01646531844414828</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.008877062271187643</v>
+        <v>0.007498151554938336</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01002648214892585</v>
+        <v>0.008853247278958863</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.009086737447572591</v>
+        <v>0.01147339711442709</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03252457912627839</v>
+        <v>0.02410140197170515</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01468346379443617</v>
+        <v>0.01241377558846662</v>
       </c>
       <c r="D5" t="n">
-        <v>0.038245696793684</v>
+        <v>0.03820670003507504</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02000183932017073</v>
+        <v>0.01505351236627349</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03291873461864759</v>
+        <v>0.02259902544226457</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05090239437773299</v>
+        <v>0.02299458998702835</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01185356881435598</v>
+        <v>0.01081784272595764</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04088268319139636</v>
+        <v>0.03536932857122994</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03837941065912018</v>
+        <v>0.03556232188918421</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05645775054135007</v>
+        <v>0.04861730493940938</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04459523185270241</v>
+        <v>0.03587232627982848</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02793408510184548</v>
+        <v>0.08444089321485711</v>
       </c>
       <c r="N5" t="n">
-        <v>0.06703449194705631</v>
+        <v>0.01821224625945391</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02616378043955455</v>
+        <v>0.01728207843246081</v>
       </c>
       <c r="P5" t="n">
-        <v>0.04899645786492345</v>
+        <v>0.02149859255997007</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.02274500841984299</v>
+        <v>0.01858177242066295</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0189985887222937</v>
+        <v>0.01648337720003967</v>
       </c>
       <c r="S5" t="n">
-        <v>0.04413877771526859</v>
+        <v>0.03118829386816924</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0397119295476322</v>
+        <v>0.03256934829970641</v>
       </c>
       <c r="U5" t="n">
-        <v>0.07014646554175985</v>
+        <v>0.06640566400721361</v>
       </c>
       <c r="V5" t="n">
-        <v>0.02699459098793026</v>
+        <v>0.02299014399485122</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02701969997836057</v>
+        <v>0.03818914399193571</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1306867382070007</v>
+        <v>0.1408230641245804</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1389690564089067</v>
+        <v>0.1819733633418557</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.02737331955046499</v>
+        <v>0.01841248699824168</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.05151673829076204</v>
+        <v>0.04461622557243106</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.03690413164916716</v>
+        <v>0.09827010538445492</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01028575381592654</v>
+        <v>0.008112367246076063</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008302045451124505</v>
+        <v>0.007354306906492597</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009626799788555098</v>
+        <v>0.009540329555873072</v>
       </c>
       <c r="E6" t="n">
-        <v>0.009524027834758813</v>
+        <v>0.008309382959039872</v>
       </c>
       <c r="F6" t="n">
-        <v>0.009287543165735514</v>
+        <v>0.007902187791653852</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01145427592939895</v>
+        <v>0.008048051484403402</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008126291822505778</v>
+        <v>0.007982961490172302</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00970559446207005</v>
+        <v>0.008586306763277533</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01058770768485647</v>
+        <v>0.009432977371614736</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01168257915046516</v>
+        <v>0.01029340099197373</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01092870033527342</v>
+        <v>0.008760570524047828</v>
       </c>
       <c r="M6" t="n">
-        <v>0.009022605393868401</v>
+        <v>0.01133886732426087</v>
       </c>
       <c r="N6" t="n">
-        <v>0.008601825014165636</v>
+        <v>0.01821224625945391</v>
       </c>
       <c r="O6" t="n">
-        <v>0.009910167364208243</v>
+        <v>0.007737386998057485</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01048455207031501</v>
+        <v>0.008695712688338218</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.009607664674391394</v>
+        <v>0.008449200652524384</v>
       </c>
       <c r="R6" t="n">
-        <v>0.009338272206032158</v>
+        <v>0.008283302506821752</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01096411961708296</v>
+        <v>0.008524015356580731</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01045832645111268</v>
+        <v>0.009154059116679832</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01170667339882585</v>
+        <v>0.01139830294562106</v>
       </c>
       <c r="V6" t="n">
-        <v>0.009109855197805869</v>
+        <v>0.00804557677485304</v>
       </c>
       <c r="W6" t="n">
-        <v>0.009836025895301586</v>
+        <v>0.008836390526106594</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01486978520375714</v>
+        <v>0.01462548574653887</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01523882210624927</v>
+        <v>0.01681419219972051</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.01004647347208281</v>
+        <v>0.007800973620406578</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.01119589334982102</v>
+        <v>0.009889617878664771</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.009426149763699215</v>
+        <v>0.01179955270923668</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.009759335518676632</v>
+        <v>0.008430049220740954</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008609765667541418</v>
+        <v>0.007671988881157491</v>
       </c>
       <c r="D7" t="n">
-        <v>0.009934520004972006</v>
+        <v>0.009124462996300292</v>
       </c>
       <c r="E7" t="n">
-        <v>0.008997609537508909</v>
+        <v>0.007893516399467093</v>
       </c>
       <c r="F7" t="n">
-        <v>0.009595263382152431</v>
+        <v>0.008219869766318742</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01092785763214904</v>
+        <v>0.008365733459068294</v>
       </c>
       <c r="H7" t="n">
-        <v>0.008434012038922694</v>
+        <v>0.007567094930599537</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01001331467848697</v>
+        <v>0.008903988737942419</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01006128938760657</v>
+        <v>0.009017110812041958</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01115616085321526</v>
+        <v>0.009877534432400945</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01040228203802352</v>
+        <v>0.009078252498712707</v>
       </c>
       <c r="M7" t="n">
-        <v>0.009330325610285317</v>
+        <v>0.01165654929892577</v>
       </c>
       <c r="N7" t="n">
-        <v>0.008902420020539073</v>
+        <v>0.01821224625945391</v>
       </c>
       <c r="O7" t="n">
-        <v>0.009380387183483238</v>
+        <v>0.008012578918186707</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01081518697937034</v>
+        <v>0.008276660937120105</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.009081246377141488</v>
+        <v>0.00803333409295161</v>
       </c>
       <c r="R7" t="n">
-        <v>0.008811853908782252</v>
+        <v>0.007867435947248974</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01043770131983306</v>
+        <v>0.008841697331245632</v>
       </c>
       <c r="T7" t="n">
-        <v>0.009931908153862773</v>
+        <v>0.008738192557107052</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01201290123593426</v>
+        <v>0.01098142567599259</v>
       </c>
       <c r="V7" t="n">
-        <v>0.009417575414222784</v>
+        <v>0.008363258749517936</v>
       </c>
       <c r="W7" t="n">
-        <v>0.009306270354171753</v>
+        <v>0.009123376865596462</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01517750542017403</v>
+        <v>0.01494316772120376</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01551913715420339</v>
+        <v>0.01709938410969578</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.009520055174832903</v>
+        <v>0.008118655595071475</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01066947505257111</v>
+        <v>0.009473751319091993</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.009729730351217854</v>
+        <v>0.01209390115456024</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01106339215927875</v>
+        <v>0.009694356854384946</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01127304712683278</v>
+        <v>0.01022936809857665</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01259780146426336</v>
+        <v>0.01168184221371946</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01093714387548823</v>
+        <v>0.009762373141755511</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01111107136390203</v>
+        <v>0.009685622840266235</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01387298321211569</v>
+        <v>0.01119123949295946</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01109729349821405</v>
+        <v>0.0101244741480187</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01267659613777833</v>
+        <v>0.01146136795536159</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01272457084689792</v>
+        <v>0.01157449002946112</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01381944231250662</v>
+        <v>0.0124349136498201</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01306556349731487</v>
+        <v>0.01163563171613187</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01199360706957655</v>
+        <v>0.01421392851634566</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01051207485196856</v>
+        <v>0.01821224625945391</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01127961155729869</v>
+        <v>0.00984308756973038</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0126434366944915</v>
+        <v>0.01003964925422312</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01011818431810092</v>
+        <v>0.009043523647471182</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01147513536807361</v>
+        <v>0.01042481516466814</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01310098277912442</v>
+        <v>0.01139907654866479</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01259518961315413</v>
+        <v>0.01129557177452621</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01401311746630994</v>
+        <v>0.01290791888628442</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0117081049277517</v>
+        <v>0.01056637742200253</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01196981894001037</v>
+        <v>0.01168101020861469</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01633901901654006</v>
+        <v>0.01607186985573823</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01953191792816646</v>
+        <v>0.02094112501988353</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01079886351660841</v>
+        <v>0.009358943760185024</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01333275651186247</v>
+        <v>0.01203113053651116</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01381283579008798</v>
+        <v>0.01600200176610372</v>
       </c>
     </row>
     <row r="9">
@@ -4642,85 +4642,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01127301058105218</v>
+        <v>0.009614233376381382</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01077301860678203</v>
+        <v>0.009396829081260662</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01209777294421262</v>
+        <v>0.01084930319640347</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01101094301334375</v>
+        <v>0.009493574934111149</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01026106124632791</v>
+        <v>0.008698350998172613</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01309111117070366</v>
+        <v>0.01009057306675006</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0105972649781633</v>
+        <v>0.009291935130702702</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01217656761772757</v>
+        <v>0.01062882893804559</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01222454232684718</v>
+        <v>0.01074195101214514</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01331941379245587</v>
+        <v>0.01160237463250412</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01256553497726412</v>
+        <v>0.01080309269881589</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01149357854952592</v>
+        <v>0.01338138949902894</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01106567295977969</v>
+        <v>0.01821224625945391</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01175893397509408</v>
+        <v>0.009916613667614399</v>
       </c>
       <c r="P9" t="n">
-        <v>0.01324055118435832</v>
+        <v>0.01021966263314634</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.01124449991569611</v>
+        <v>0.00975817370063338</v>
       </c>
       <c r="R9" t="n">
-        <v>0.01097510684802286</v>
+        <v>0.009592276147352139</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01260095425907366</v>
+        <v>0.0105665375313488</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01209516109310339</v>
+        <v>0.01046303275721022</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01417764655448337</v>
+        <v>0.01270727658615145</v>
       </c>
       <c r="V9" t="n">
-        <v>0.01233042771657539</v>
+        <v>0.01071200266889507</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01146952329341236</v>
+        <v>0.01084821706569962</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01734075835941463</v>
+        <v>0.01666800792130697</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.01768239009344399</v>
+        <v>0.01882422430979895</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0112916706550234</v>
+        <v>0.00951752804213094</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.01283272799181173</v>
+        <v>0.01119859151919516</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.01189298329045847</v>
+        <v>0.0138187413546634</v>
       </c>
     </row>
   </sheetData>
@@ -4886,85 +4886,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003881658471006691</v>
+        <v>0.00378061197692846</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003499259087885846</v>
+        <v>0.003375213241705778</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003928365579078565</v>
+        <v>0.003832814918836051</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003882535624564618</v>
+        <v>0.003787387430864775</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003870380710197176</v>
+        <v>0.003772874465822173</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003931505629238636</v>
+        <v>0.003791082764287807</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00388392466845144</v>
+        <v>0.003786910752904397</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003899143045175846</v>
+        <v>0.003800536325240289</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003913734509460385</v>
+        <v>0.003812497952738607</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003953106861082458</v>
+        <v>0.00385658518638563</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003942777130248606</v>
+        <v>0.003830353303445491</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003903336493579151</v>
+        <v>0.00392699509481379</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003923339218874476</v>
+        <v>0.003826848654270893</v>
       </c>
       <c r="O2" t="n">
-        <v>0.00561845327450038</v>
+        <v>0.005476357971210832</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003930226790258163</v>
+        <v>0.003805660662198954</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003890022475948827</v>
+        <v>0.003792616016020762</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003882177311272368</v>
+        <v>0.003784127299252832</v>
       </c>
       <c r="S2" t="n">
-        <v>0.00389941745986258</v>
+        <v>0.003796310080381286</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003885884589932644</v>
+        <v>0.003787309446181521</v>
       </c>
       <c r="U2" t="n">
-        <v>0.003983763111971479</v>
+        <v>0.003854892520862564</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003871941291022009</v>
+        <v>0.003775281727414695</v>
       </c>
       <c r="W2" t="n">
-        <v>0.003901811916171427</v>
+        <v>0.003781105499413416</v>
       </c>
       <c r="X2" t="n">
-        <v>0.003938104113064211</v>
+        <v>0.003847810371179243</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003896827346209441</v>
+        <v>0.003805542531905559</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.00489524243177924</v>
+        <v>0.004798238158758235</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003946782848892006</v>
+        <v>0.003842033580521241</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.004292114978774202</v>
+        <v>0.00426122480116084</v>
       </c>
     </row>
     <row r="3">
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003801718855312581</v>
+        <v>0.003672906620782665</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003030825266089499</v>
+        <v>0.00289407730239628</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004137273073521151</v>
+        <v>0.004047483381044248</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003807332804790462</v>
+        <v>0.003720434683062388</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003722662476694246</v>
+        <v>0.00361888138516939</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004154430508024483</v>
+        <v>0.003746902392248686</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003820172820599441</v>
+        <v>0.00371987977212596</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003928570949368195</v>
+        <v>0.003816904799883917</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004029866118009723</v>
+        <v>0.003900218628238038</v>
       </c>
       <c r="K3" t="n">
-        <v>0.004310854827787225</v>
+        <v>0.004214122743857769</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00423512259401521</v>
+        <v>0.004025681899397462</v>
       </c>
       <c r="M3" t="n">
-        <v>0.003962837320244076</v>
+        <v>0.004712021017556963</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004099988708790298</v>
+        <v>0.004003499114387314</v>
       </c>
       <c r="O3" t="n">
-        <v>0.006673241396617205</v>
+        <v>0.006474061740413803</v>
       </c>
       <c r="P3" t="n">
-        <v>0.00414714113622686</v>
+        <v>0.003851067548979774</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003862204333339799</v>
+        <v>0.00375918460072457</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003807409135836014</v>
+        <v>0.003699703620182201</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003926640641581829</v>
+        <v>0.003783418531269063</v>
       </c>
       <c r="T3" t="n">
-        <v>0.00383315277244698</v>
+        <v>0.003721761860561874</v>
       </c>
       <c r="U3" t="n">
-        <v>0.004537202623962103</v>
+        <v>0.004400946011186751</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003732812642087241</v>
+        <v>0.00363514255466479</v>
       </c>
       <c r="W3" t="n">
-        <v>0.00414449903006537</v>
+        <v>0.00408902333807779</v>
       </c>
       <c r="X3" t="n">
-        <v>0.004206442777863059</v>
+        <v>0.004154223644559809</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.003910878435814205</v>
+        <v>0.003851521771148456</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.005568623174113261</v>
+        <v>0.005436852796716112</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.004267546191620428</v>
+        <v>0.004112109360131067</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.006712641572959446</v>
+        <v>0.007078566736363708</v>
       </c>
     </row>
     <row r="4">
@@ -5062,85 +5062,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.007689313390985734</v>
+        <v>0.006960489439598608</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007399877131322132</v>
+        <v>0.006733561854906357</v>
       </c>
       <c r="D4" t="n">
-        <v>0.008216891662988878</v>
+        <v>0.007550145682984583</v>
       </c>
       <c r="E4" t="n">
-        <v>0.007699221243933106</v>
+        <v>0.00703702130867212</v>
       </c>
       <c r="F4" t="n">
-        <v>0.007561925894616051</v>
+        <v>0.006873090692222151</v>
       </c>
       <c r="G4" t="n">
-        <v>0.008252359974041343</v>
+        <v>0.007078761799622613</v>
       </c>
       <c r="H4" t="n">
-        <v>0.007714911133626549</v>
+        <v>0.007031637011826975</v>
       </c>
       <c r="I4" t="n">
-        <v>0.007886809699527941</v>
+        <v>0.007185544119433815</v>
       </c>
       <c r="J4" t="n">
-        <v>0.008047970290629331</v>
+        <v>0.007317174150773715</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00849635582477491</v>
+        <v>0.007818641789820361</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008379676763095591</v>
+        <v>0.007522340604749145</v>
       </c>
       <c r="M4" t="n">
-        <v>0.00794455152424842</v>
+        <v>0.008606384543527074</v>
       </c>
       <c r="N4" t="n">
-        <v>0.008160116612243742</v>
+        <v>0.02269325332246965</v>
       </c>
       <c r="O4" t="n">
-        <v>0.00769926735622395</v>
+        <v>0.006964912079475916</v>
       </c>
       <c r="P4" t="n">
-        <v>0.008237914899461901</v>
+        <v>0.007243425862693375</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.007783788674439602</v>
+        <v>0.007096080583276957</v>
       </c>
       <c r="R4" t="n">
-        <v>0.007695173930464956</v>
+        <v>0.007000196622380585</v>
       </c>
       <c r="S4" t="n">
-        <v>0.007889909339651537</v>
+        <v>0.007137806739582677</v>
       </c>
       <c r="T4" t="n">
-        <v>0.007737049348365195</v>
+        <v>0.007036140435800028</v>
       </c>
       <c r="U4" t="n">
-        <v>0.008847064397553358</v>
+        <v>0.008189579486083981</v>
       </c>
       <c r="V4" t="n">
-        <v>0.007554850382002324</v>
+        <v>0.006876762330011944</v>
       </c>
       <c r="W4" t="n">
-        <v>0.008324357600469222</v>
+        <v>0.007813671751055538</v>
       </c>
       <c r="X4" t="n">
-        <v>0.008326892884303619</v>
+        <v>0.007719526215449814</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.007847853257311358</v>
+        <v>0.007220917568941509</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.007884362782362086</v>
+        <v>0.007135461819935755</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.008424923197894384</v>
+        <v>0.00765427470751273</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0122708384131931</v>
+        <v>0.01232119574813673</v>
       </c>
     </row>
     <row r="5">
@@ -5150,85 +5150,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01427436157035502</v>
+        <v>0.01248517759395807</v>
       </c>
       <c r="C5" t="n">
-        <v>0.009468738301744375</v>
+        <v>0.008744379639181437</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02547510886656053</v>
+        <v>0.02474762567275827</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0141022353102078</v>
+        <v>0.01347135692677173</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01266300996474857</v>
+        <v>0.01149879117329755</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02322412791180391</v>
+        <v>0.0143128217063392</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01602638901706481</v>
+        <v>0.0149530075090698</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01915639914544371</v>
+        <v>0.01773995783676943</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0206869284110916</v>
+        <v>0.01914721072358979</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02909184120729445</v>
+        <v>0.02815018285431676</v>
       </c>
       <c r="L5" t="n">
-        <v>0.025768691865521</v>
+        <v>0.02186780315804469</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01952552941733621</v>
+        <v>0.04276218700882042</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03478789430679164</v>
+        <v>0.02269325332246965</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01434576685133382</v>
+        <v>0.01249526392420807</v>
       </c>
       <c r="P5" t="n">
-        <v>0.02397307938600794</v>
+        <v>0.01749410942411542</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01650069539632577</v>
+        <v>0.01538514634561782</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01549040883512554</v>
+        <v>0.0141858478665126</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01705223135358884</v>
+        <v>0.01498905633790462</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01588431614024399</v>
+        <v>0.01450235775996206</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03548764164921811</v>
+        <v>0.03507554077883553</v>
       </c>
       <c r="V5" t="n">
-        <v>0.01242225083290513</v>
+        <v>0.01147797438139023</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02687299129334453</v>
+        <v>0.02911715628005977</v>
       </c>
       <c r="X5" t="n">
-        <v>0.02736885829800335</v>
+        <v>0.02779285027428459</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.01801376829639027</v>
+        <v>0.01819038956892514</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01743963743831874</v>
+        <v>0.01533820219871398</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.02875681963489288</v>
+        <v>0.02606686315995941</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1071480050506686</v>
+        <v>0.120779060570038</v>
       </c>
     </row>
     <row r="6">
@@ -5238,85 +5238,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.008064947245576187</v>
+        <v>0.007216128274225465</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008590893131389521</v>
+        <v>0.006989200689533215</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00859252551757933</v>
+        <v>0.008557172105818097</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008074855098523558</v>
+        <v>0.008044047731505639</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00875294189468344</v>
+        <v>0.007128729526849008</v>
       </c>
       <c r="G6" t="n">
-        <v>0.009443375974108733</v>
+        <v>0.00733440063424947</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008090544988216998</v>
+        <v>0.008038663434660486</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008262443554118391</v>
+        <v>0.00819257054226733</v>
       </c>
       <c r="J6" t="n">
-        <v>0.008423604145219785</v>
+        <v>0.007572812985400574</v>
       </c>
       <c r="K6" t="n">
-        <v>0.008871989679365365</v>
+        <v>0.008825668212653889</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008755310617686043</v>
+        <v>0.007777979439376009</v>
       </c>
       <c r="M6" t="n">
-        <v>0.00913556752431581</v>
+        <v>0.009613410966360578</v>
       </c>
       <c r="N6" t="n">
-        <v>0.008537021502963194</v>
+        <v>0.02269325332246965</v>
       </c>
       <c r="O6" t="n">
-        <v>0.008892558029736101</v>
+        <v>0.007975578185592578</v>
       </c>
       <c r="P6" t="n">
-        <v>0.008582742975031603</v>
+        <v>0.008254460242835765</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.008974804674506988</v>
+        <v>0.008103107006110468</v>
       </c>
       <c r="R6" t="n">
-        <v>0.008070807785055411</v>
+        <v>0.008007223045214102</v>
       </c>
       <c r="S6" t="n">
-        <v>0.008265543194241986</v>
+        <v>0.007393445574209533</v>
       </c>
       <c r="T6" t="n">
-        <v>0.008928065348432587</v>
+        <v>0.007291779270426887</v>
       </c>
       <c r="U6" t="n">
-        <v>0.009235497809260701</v>
+        <v>0.008466392278456147</v>
       </c>
       <c r="V6" t="n">
-        <v>0.008745866382069714</v>
+        <v>0.00788378875284545</v>
       </c>
       <c r="W6" t="n">
-        <v>0.008731944749363169</v>
+        <v>0.008824471060430921</v>
       </c>
       <c r="X6" t="n">
-        <v>0.00870252673889407</v>
+        <v>0.007975165050076673</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.008260359788097747</v>
+        <v>0.007515774108421357</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.009075378782429477</v>
+        <v>0.007391100654562612</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.009615939197961774</v>
+        <v>0.008661301130346242</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01267367951230727</v>
+        <v>0.01262024539215192</v>
       </c>
     </row>
     <row r="7">
@@ -5326,85 +5326,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.008291352807723085</v>
+        <v>0.007564194074204954</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008001916548059483</v>
+        <v>0.007337266489512701</v>
       </c>
       <c r="D7" t="n">
-        <v>0.008818931079726231</v>
+        <v>0.00815385031759093</v>
       </c>
       <c r="E7" t="n">
-        <v>0.008301260660670457</v>
+        <v>0.007640725943278464</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008163965311353402</v>
+        <v>0.0074767953268285</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008854399390778698</v>
+        <v>0.007682466434228959</v>
       </c>
       <c r="H7" t="n">
-        <v>0.008316950550363899</v>
+        <v>0.007635341646433324</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00848884911626529</v>
+        <v>0.007789248754040161</v>
       </c>
       <c r="J7" t="n">
-        <v>0.008650009707366681</v>
+        <v>0.007920878785380062</v>
       </c>
       <c r="K7" t="n">
-        <v>0.009098395241512262</v>
+        <v>0.00842234642442671</v>
       </c>
       <c r="L7" t="n">
-        <v>0.008981716179832944</v>
+        <v>0.008126045239355497</v>
       </c>
       <c r="M7" t="n">
-        <v>0.008546590940985772</v>
+        <v>0.009210089178133412</v>
       </c>
       <c r="N7" t="n">
-        <v>0.008762156028981094</v>
+        <v>0.02269325332246965</v>
       </c>
       <c r="O7" t="n">
-        <v>0.00830128298108827</v>
+        <v>0.00756859382205576</v>
       </c>
       <c r="P7" t="n">
-        <v>0.008839930524326222</v>
+        <v>0.007847107605273223</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.008385828091176955</v>
+        <v>0.007699785217883301</v>
       </c>
       <c r="R7" t="n">
-        <v>0.008297213347202305</v>
+        <v>0.007603901256986931</v>
       </c>
       <c r="S7" t="n">
-        <v>0.008491948756388886</v>
+        <v>0.007741511374189025</v>
       </c>
       <c r="T7" t="n">
-        <v>0.008339088765102549</v>
+        <v>0.007639845070406373</v>
       </c>
       <c r="U7" t="n">
-        <v>0.009460819028066152</v>
+        <v>0.008813576800441182</v>
       </c>
       <c r="V7" t="n">
-        <v>0.008156889798739676</v>
+        <v>0.007480466964618307</v>
       </c>
       <c r="W7" t="n">
-        <v>0.008926397017206576</v>
+        <v>0.008417376385661885</v>
       </c>
       <c r="X7" t="n">
-        <v>0.008928932301040972</v>
+        <v>0.008323230850056164</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.008462692231165603</v>
+        <v>0.007845796161293167</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.008486402199099437</v>
+        <v>0.0077391664545421</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.009026962614631737</v>
+        <v>0.00825797934211908</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01287287782993043</v>
+        <v>0.01292490038274309</v>
       </c>
     </row>
     <row r="8">
@@ -5414,85 +5414,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00963706026664214</v>
+        <v>0.008876212825899888</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01070263361582679</v>
+        <v>0.009959018322108902</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01151964814749354</v>
+        <v>0.01077560215018713</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01028047508201856</v>
+        <v>0.009565083545004148</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00972076743099348</v>
+        <v>0.008992855185353602</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01183608652800272</v>
+        <v>0.01057579995326666</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01101766761813121</v>
+        <v>0.01025709347902952</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01118956618403261</v>
+        <v>0.01041100058663636</v>
       </c>
       <c r="J8" t="n">
-        <v>0.011350726775134</v>
+        <v>0.01054263061797626</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01179911230927957</v>
+        <v>0.01104409825702291</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01168243324760025</v>
+        <v>0.0107477970719517</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01124730800875283</v>
+        <v>0.0118318410107297</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01041251396170889</v>
+        <v>0.02269325332246965</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0102403125160902</v>
+        <v>0.009454109177431665</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01070820550629227</v>
+        <v>0.009664232612610114</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.009465245235385894</v>
+        <v>0.008754411525983628</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01099793041496962</v>
+        <v>0.01022565308958313</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0111926658241562</v>
+        <v>0.01036326320678522</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01103980583286986</v>
+        <v>0.01026159690300257</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01150043643282469</v>
+        <v>0.01079628144700099</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01048635577616949</v>
+        <v>0.009743515270743883</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01162738038313921</v>
+        <v>0.01103938561833424</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01013253876831625</v>
+        <v>0.009497896797498753</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0125092584768974</v>
+        <v>0.01176864777312273</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.009806939658875469</v>
+        <v>0.009026856241841632</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01172767968239905</v>
+        <v>0.01087973117471528</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01698901573815472</v>
+        <v>0.01691477793643793</v>
       </c>
     </row>
     <row r="9">
@@ -5502,85 +5502,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.009687554656318358</v>
+        <v>0.008825897599052756</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01000185540712718</v>
+        <v>0.00915512129845786</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01081886993879393</v>
+        <v>0.009971705126536085</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01016185965087295</v>
+        <v>0.009330223125148389</v>
       </c>
       <c r="F9" t="n">
-        <v>0.008772125296404394</v>
+        <v>0.008012569941938818</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01085433847157354</v>
+        <v>0.009500321010199122</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0103168894094316</v>
+        <v>0.009453196455378475</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01048878797533299</v>
+        <v>0.009607103562985313</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01064994856643439</v>
+        <v>0.00973873359432522</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01109833410057997</v>
+        <v>0.01024020123337187</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01098165503890065</v>
+        <v>0.009943900048300647</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01054652980005347</v>
+        <v>0.01102794398707858</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0107620948880488</v>
+        <v>0.02269325332246965</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01050132358198064</v>
+        <v>0.009570779020176702</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0110834845983517</v>
+        <v>0.009889376572508083</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.01038576717197181</v>
+        <v>0.009517639793853462</v>
       </c>
       <c r="R9" t="n">
-        <v>0.01029715220627001</v>
+        <v>0.009421756065932086</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01049188761545659</v>
+        <v>0.009559366183134176</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01033902762417025</v>
+        <v>0.009457699879351531</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0114618422304753</v>
+        <v>0.0106323128873808</v>
       </c>
       <c r="V9" t="n">
-        <v>0.01085352815406552</v>
+        <v>0.009940107493510876</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01092633587627428</v>
+        <v>0.01023523119460704</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01092887116010867</v>
+        <v>0.01014108565900131</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0104626310902333</v>
+        <v>0.009663650970238327</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.01012234141528731</v>
+        <v>0.009221711401566529</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.01102690147369944</v>
+        <v>0.01007583415106423</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.01487281668899815</v>
+        <v>0.01474275519168824</v>
       </c>
     </row>
   </sheetData>
@@ -5746,85 +5746,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003881123028789562</v>
+        <v>0.003719927467596873</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003572163244156304</v>
+        <v>0.003341101735902524</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003896482115266013</v>
+        <v>0.003733224359631671</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00389289673346452</v>
+        <v>0.003729856158419683</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003889867977195536</v>
+        <v>0.003727662134037216</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003888614325528174</v>
+        <v>0.003726480970339121</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003890695893106883</v>
+        <v>0.003728723122056</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003891398062849114</v>
+        <v>0.003729129558657142</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003894490657562979</v>
+        <v>0.003732338521982052</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003888570071506579</v>
+        <v>0.003726989195418299</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003892277177157333</v>
+        <v>0.003730002255728383</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003882137981284845</v>
+        <v>0.003721272251973345</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003891905964811791</v>
+        <v>0.003729735304660732</v>
       </c>
       <c r="O2" t="n">
-        <v>0.005634702035572605</v>
+        <v>0.005407198355078673</v>
       </c>
       <c r="P2" t="n">
-        <v>0.00389259577715937</v>
+        <v>0.003729764899674782</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003880417273954626</v>
+        <v>0.003719054337345993</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003905150694019985</v>
+        <v>0.003740162220649536</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003895346875284529</v>
+        <v>0.00373252233088747</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003882358704641249</v>
+        <v>0.003720054528455498</v>
       </c>
       <c r="U2" t="n">
-        <v>0.003919929744865181</v>
+        <v>0.003668769052198066</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003893039085238872</v>
+        <v>0.003730637213934809</v>
       </c>
       <c r="W2" t="n">
-        <v>0.003924609538348818</v>
+        <v>0.003657041766419435</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004051597018974302</v>
+        <v>0.003889861682554793</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003992532193839389</v>
+        <v>0.003830559961541156</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.004863720228724169</v>
+        <v>0.004730173209076681</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003913595053049378</v>
+        <v>0.003751597417601561</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.003875238378919063</v>
+        <v>0.003713868074792603</v>
       </c>
     </row>
     <row r="3">
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003705980642734144</v>
+        <v>0.003535991623550937</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003212456478895372</v>
+        <v>0.002926606696150605</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00381602422412155</v>
+        <v>0.003631310189688488</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003788736962029447</v>
+        <v>0.003605576999368655</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003769038439540231</v>
+        <v>0.003591802490588049</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003759055731266565</v>
+        <v>0.003582443284834408</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003775477584489053</v>
+        <v>0.003599864409313305</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003780063706575772</v>
+        <v>0.003602369163486553</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003801183504421968</v>
+        <v>0.00362439995497361</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003759436594749284</v>
+        <v>0.003586689501014548</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003784974529906779</v>
+        <v>0.003607375180322506</v>
       </c>
       <c r="M3" t="n">
-        <v>0.00372012591751045</v>
+        <v>0.003551493790162968</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003783129360073817</v>
+        <v>0.003606174503085794</v>
       </c>
       <c r="O3" t="n">
-        <v>0.00667036293219398</v>
+        <v>0.006384064912024427</v>
       </c>
       <c r="P3" t="n">
-        <v>0.00378743172390511</v>
+        <v>0.003605828674254957</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003701193627099285</v>
+        <v>0.00353001344485114</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003878652221465688</v>
+        <v>0.003681478192708846</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003806537550792126</v>
+        <v>0.003625041626453038</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003715402729727272</v>
+        <v>0.003537484215345515</v>
       </c>
       <c r="U3" t="n">
-        <v>0.003778018012624017</v>
+        <v>0.003457669427350699</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003790547816962856</v>
+        <v>0.003612012109658214</v>
       </c>
       <c r="W3" t="n">
-        <v>0.003948169684959034</v>
+        <v>0.003592821230227748</v>
       </c>
       <c r="X3" t="n">
-        <v>0.004920724755106529</v>
+        <v>0.004746869043147054</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.004501619615262996</v>
+        <v>0.004326062013210531</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.005422133970853373</v>
+        <v>0.005291397862664414</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003938083691790753</v>
+        <v>0.003762346858415931</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.003670351631073315</v>
+        <v>0.00349841173113694</v>
       </c>
     </row>
     <row r="4">
@@ -5922,85 +5922,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00741814174975667</v>
+        <v>0.006767706609872022</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007452165079104754</v>
+        <v>0.006800796887416283</v>
       </c>
       <c r="D4" t="n">
-        <v>0.007591629697037044</v>
+        <v>0.006917901122277629</v>
       </c>
       <c r="E4" t="n">
-        <v>0.007551131160232128</v>
+        <v>0.006879855740139129</v>
       </c>
       <c r="F4" t="n">
-        <v>0.007516919964877204</v>
+        <v>0.006855073225438102</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0075027593925861</v>
+        <v>0.006841731438105928</v>
       </c>
       <c r="H4" t="n">
-        <v>0.007526271655956</v>
+        <v>0.006867057573188861</v>
       </c>
       <c r="I4" t="n">
-        <v>0.007534202986208486</v>
+        <v>0.006871648461568814</v>
       </c>
       <c r="J4" t="n">
-        <v>0.007565937466530147</v>
+        <v>0.006904699744820885</v>
       </c>
       <c r="K4" t="n">
-        <v>0.007502259523054316</v>
+        <v>0.006847472074170339</v>
       </c>
       <c r="L4" t="n">
-        <v>0.007544132986732498</v>
+        <v>0.006881505976449001</v>
       </c>
       <c r="M4" t="n">
-        <v>0.00744110562152262</v>
+        <v>0.006792620463227715</v>
       </c>
       <c r="N4" t="n">
-        <v>0.00753993997252342</v>
+        <v>0.011649980752903</v>
       </c>
       <c r="O4" t="n">
-        <v>0.00756304972443187</v>
+        <v>0.006898360300326566</v>
       </c>
       <c r="P4" t="n">
-        <v>0.007547731720318715</v>
+        <v>0.006878824930634396</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.00741016992423284</v>
+        <v>0.006757844202028604</v>
       </c>
       <c r="R4" t="n">
-        <v>0.007689545281806475</v>
+        <v>0.006996267454048162</v>
       </c>
       <c r="S4" t="n">
-        <v>0.00757880663920997</v>
+        <v>0.006909971384662744</v>
       </c>
       <c r="T4" t="n">
-        <v>0.00743209927694051</v>
+        <v>0.006769141820721108</v>
       </c>
       <c r="U4" t="n">
-        <v>0.007428262994256357</v>
+        <v>0.006766089931418573</v>
       </c>
       <c r="V4" t="n">
-        <v>0.007531121643994314</v>
+        <v>0.006867070330967959</v>
       </c>
       <c r="W4" t="n">
-        <v>0.007769747548865218</v>
+        <v>0.007099141632800633</v>
       </c>
       <c r="X4" t="n">
-        <v>0.009343723890803301</v>
+        <v>0.008687191741422854</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.00867064806794509</v>
+        <v>0.00800357333651568</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.007613918421487684</v>
+        <v>0.006950200263581199</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.007784928201640512</v>
+        <v>0.007125433264071764</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.007362030881444678</v>
+        <v>0.00670840355168542</v>
       </c>
     </row>
     <row r="5">
@@ -6010,85 +6010,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01033894214523506</v>
+        <v>0.009595302870047534</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01120786222310443</v>
+        <v>0.01043379532978912</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01362761630392676</v>
+        <v>0.01246835070556787</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01203127674146093</v>
+        <v>0.01091749445426233</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01242007871173035</v>
+        <v>0.01145569281356494</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01163309008508489</v>
+        <v>0.01073819647581603</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01286027666828269</v>
+        <v>0.01192137564991776</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01278015522171711</v>
+        <v>0.01179735398373816</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01290133641091181</v>
+        <v>0.01198348450725685</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01198529964219891</v>
+        <v>0.01116050418963264</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01224920540377403</v>
+        <v>0.01133818852395688</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01108380280160208</v>
+        <v>0.01035785954807074</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01080650192197832</v>
+        <v>0.011649980752903</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0125884727827258</v>
+        <v>0.0116280653947963</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01240786102450918</v>
+        <v>0.01136721619460428</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01032749917908182</v>
+        <v>0.009552185677115766</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01575322358206302</v>
+        <v>0.01419234522996689</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01268338446482555</v>
+        <v>0.01167609630350436</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01089829707000719</v>
+        <v>0.009924238141939098</v>
       </c>
       <c r="U5" t="n">
-        <v>0.01070073639550863</v>
+        <v>0.009900634304549729</v>
       </c>
       <c r="V5" t="n">
-        <v>0.01245002627448674</v>
+        <v>0.01149794969007611</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0163641774381362</v>
+        <v>0.01527653657629606</v>
       </c>
       <c r="X5" t="n">
-        <v>0.04339210692173694</v>
+        <v>0.0425332265039628</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03285846623330944</v>
+        <v>0.03194647958218209</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01333788419787346</v>
+        <v>0.01239335176335405</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01700681534984783</v>
+        <v>0.01609082756365026</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.009730946736692348</v>
+        <v>0.008909208770902566</v>
       </c>
     </row>
     <row r="6">
@@ -6098,85 +6098,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.007926860105606469</v>
+        <v>0.007665502683299183</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007960883434954552</v>
+        <v>0.007034083781072778</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008100348052886839</v>
+        <v>0.007151188015934123</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008804336144790021</v>
+        <v>0.007113142633795623</v>
       </c>
       <c r="F6" t="n">
-        <v>0.008770124949435092</v>
+        <v>0.007752869298865262</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008011477748435896</v>
+        <v>0.007739527511533085</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0080349900118058</v>
+        <v>0.007764853646616018</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008042921342058286</v>
+        <v>0.007769444534995972</v>
       </c>
       <c r="J6" t="n">
-        <v>0.008074655822379944</v>
+        <v>0.007802495818248044</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00801097787890411</v>
+        <v>0.007745268147597498</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008797337971290389</v>
+        <v>0.007114792870105494</v>
       </c>
       <c r="M6" t="n">
-        <v>0.008694310606080509</v>
+        <v>0.007690416536654874</v>
       </c>
       <c r="N6" t="n">
-        <v>0.00804894594859195</v>
+        <v>0.011649980752903</v>
       </c>
       <c r="O6" t="n">
-        <v>0.008072055700500397</v>
+        <v>0.007797318576701464</v>
       </c>
       <c r="P6" t="n">
-        <v>0.00801603031846774</v>
+        <v>0.007094497391715026</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.007918888280082635</v>
+        <v>0.007655640275455765</v>
       </c>
       <c r="R6" t="n">
-        <v>0.008942750266364364</v>
+        <v>0.007229554347704658</v>
       </c>
       <c r="S6" t="n">
-        <v>0.008087524995059768</v>
+        <v>0.007807767458089903</v>
       </c>
       <c r="T6" t="n">
-        <v>0.008685304261498402</v>
+        <v>0.007002428714377603</v>
       </c>
       <c r="U6" t="n">
-        <v>0.007942892801903526</v>
+        <v>0.007013155010993768</v>
       </c>
       <c r="V6" t="n">
-        <v>0.008784326628552205</v>
+        <v>0.007100357224624454</v>
       </c>
       <c r="W6" t="n">
-        <v>0.008315536929256125</v>
+        <v>0.007353118158635772</v>
       </c>
       <c r="X6" t="n">
-        <v>0.009852442246653095</v>
+        <v>0.009584987814850019</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.009216344008992973</v>
+        <v>0.008267077055284433</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.008867123406045578</v>
+        <v>0.007183487157237694</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.009038133186198406</v>
+        <v>0.008023229337498924</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.007869779337010573</v>
+        <v>0.006980589881187864</v>
       </c>
     </row>
     <row r="7">
@@ -6186,85 +6186,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007920584064431791</v>
+        <v>0.007304850906796989</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007954607393779877</v>
+        <v>0.007337941184341249</v>
       </c>
       <c r="D7" t="n">
-        <v>0.008094072011712168</v>
+        <v>0.007455045419202595</v>
       </c>
       <c r="E7" t="n">
-        <v>0.008053573474907254</v>
+        <v>0.007417000037064097</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008019362279552326</v>
+        <v>0.007392217522363072</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008005201707261222</v>
+        <v>0.007378875735030893</v>
       </c>
       <c r="H7" t="n">
-        <v>0.008028713970631127</v>
+        <v>0.007404201870113827</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00803664530088361</v>
+        <v>0.007408792758493777</v>
       </c>
       <c r="J7" t="n">
-        <v>0.008068379781205269</v>
+        <v>0.007441844041745853</v>
       </c>
       <c r="K7" t="n">
-        <v>0.008004701837729439</v>
+        <v>0.007384616371095305</v>
       </c>
       <c r="L7" t="n">
-        <v>0.008046575301407621</v>
+        <v>0.007418650273373967</v>
       </c>
       <c r="M7" t="n">
-        <v>0.00794354793619774</v>
+        <v>0.007329764760152684</v>
       </c>
       <c r="N7" t="n">
-        <v>0.008042382287198543</v>
+        <v>0.011649980752903</v>
       </c>
       <c r="O7" t="n">
-        <v>0.008065469740007014</v>
+        <v>0.007435483032827185</v>
       </c>
       <c r="P7" t="n">
-        <v>0.008050151735893855</v>
+        <v>0.007415947663135015</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.007912612238907964</v>
+        <v>0.007294988498953573</v>
       </c>
       <c r="R7" t="n">
-        <v>0.008191987596481598</v>
+        <v>0.00753341175097313</v>
       </c>
       <c r="S7" t="n">
-        <v>0.008081248953885097</v>
+        <v>0.007447115681587714</v>
       </c>
       <c r="T7" t="n">
-        <v>0.007934541591615631</v>
+        <v>0.007306286117646075</v>
       </c>
       <c r="U7" t="n">
-        <v>0.007935385914335374</v>
+        <v>0.00731623303777594</v>
       </c>
       <c r="V7" t="n">
-        <v>0.008033563958669434</v>
+        <v>0.007404214627892928</v>
       </c>
       <c r="W7" t="n">
-        <v>0.008272189863540341</v>
+        <v>0.007636285929725599</v>
       </c>
       <c r="X7" t="n">
-        <v>0.009846166205478421</v>
+        <v>0.009224336038347819</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.00917900183441759</v>
+        <v>0.008554495819359346</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.008116360736162806</v>
+        <v>0.007487344560506164</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.00828737051631564</v>
+        <v>0.007662577560996734</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.007864473196119801</v>
+        <v>0.007245547848610389</v>
       </c>
     </row>
     <row r="8">
@@ -6274,85 +6274,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.009178415093836895</v>
+        <v>0.008494659864557217</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01045849866913974</v>
+        <v>0.009705667649268007</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01059796328707203</v>
+        <v>0.009822771884129356</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009893974425779165</v>
+        <v>0.009157520175812089</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009471314932259707</v>
+        <v>0.008765532261130377</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01076747169194465</v>
+        <v>0.00999085106848911</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01053260524599099</v>
+        <v>0.009771928335040588</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01054053657624347</v>
+        <v>0.009776519223420528</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01057227105656513</v>
+        <v>0.009809570506672605</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01050859311308929</v>
+        <v>0.00975234283602206</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01055046657676748</v>
+        <v>0.009786376738300727</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01044743921155728</v>
+        <v>0.009697491225079315</v>
       </c>
       <c r="N8" t="n">
-        <v>0.00958036841059757</v>
+        <v>0.011649980752903</v>
       </c>
       <c r="O8" t="n">
-        <v>0.00986891728506597</v>
+        <v>0.009141071104954863</v>
       </c>
       <c r="P8" t="n">
-        <v>0.009788533738106201</v>
+        <v>0.009060028402617945</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.008925563990053263</v>
+        <v>0.008253309781893875</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01069587887184146</v>
+        <v>0.009901138215899885</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01058514022924495</v>
+        <v>0.00981484214651447</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0104384328669755</v>
+        <v>0.009674012582572835</v>
       </c>
       <c r="U8" t="n">
-        <v>0.009831386066516614</v>
+        <v>0.009109225779701319</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01019585514417276</v>
+        <v>0.00944935071829169</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01077632602541421</v>
+        <v>0.01000424388922132</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01097332185410777</v>
+        <v>0.0102906158013945</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01292022020949295</v>
+        <v>0.01209239417549243</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.00935104555677289</v>
+        <v>0.008655273095824841</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0107912617916755</v>
+        <v>0.01003030402592348</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01166997859221684</v>
+        <v>0.01084370764565787</v>
       </c>
     </row>
     <row r="9">
@@ -6362,85 +6362,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00901376993720391</v>
+        <v>0.008346500582280321</v>
       </c>
       <c r="C9" t="n">
-        <v>0.009544611707495735</v>
+        <v>0.008851309232352151</v>
       </c>
       <c r="D9" t="n">
-        <v>0.009684076325428025</v>
+        <v>0.008968413467213497</v>
       </c>
       <c r="E9" t="n">
-        <v>0.009528914318747682</v>
+        <v>0.00882149757107817</v>
       </c>
       <c r="F9" t="n">
-        <v>0.008464064153217255</v>
+        <v>0.007818145702167042</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009595206280737654</v>
+        <v>0.008892243994010972</v>
       </c>
       <c r="H9" t="n">
-        <v>0.009618718284346984</v>
+        <v>0.008917569918124727</v>
       </c>
       <c r="I9" t="n">
-        <v>0.009626649614599471</v>
+        <v>0.008922160806504681</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009658384094921129</v>
+        <v>0.008955212089756756</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009594706151445295</v>
+        <v>0.008897984419106213</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009636579615123481</v>
+        <v>0.008932018321384872</v>
       </c>
       <c r="M9" t="n">
-        <v>0.009533552249913597</v>
+        <v>0.008843132808163583</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0096323866009144</v>
+        <v>0.011649980752903</v>
       </c>
       <c r="O9" t="n">
-        <v>0.009820141679468267</v>
+        <v>0.009105199777139656</v>
       </c>
       <c r="P9" t="n">
-        <v>0.009840631152568932</v>
+        <v>0.009119662830626707</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.009502616812384396</v>
+        <v>0.008808356757933655</v>
       </c>
       <c r="R9" t="n">
-        <v>0.009781991910197454</v>
+        <v>0.009046779798984033</v>
       </c>
       <c r="S9" t="n">
-        <v>0.009671253267600951</v>
+        <v>0.008960483729598619</v>
       </c>
       <c r="T9" t="n">
-        <v>0.009524545905331486</v>
+        <v>0.008819654165656977</v>
       </c>
       <c r="U9" t="n">
-        <v>0.009526621074444713</v>
+        <v>0.008830380462273146</v>
       </c>
       <c r="V9" t="n">
-        <v>0.01019688631364706</v>
+        <v>0.009461935731238243</v>
       </c>
       <c r="W9" t="n">
-        <v>0.009862194177256199</v>
+        <v>0.009149653977736502</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01143617051919428</v>
+        <v>0.01073770408635872</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.01076900614813345</v>
+        <v>0.01006786386737025</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.009406827811957126</v>
+        <v>0.008716308460490789</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.009877374830031494</v>
+        <v>0.009175945609007636</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.009454477509835659</v>
+        <v>0.008758915896621294</v>
       </c>
     </row>
   </sheetData>
@@ -6606,85 +6606,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003753891341813414</v>
+        <v>0.003719496730968309</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003345933605001261</v>
+        <v>0.003298500630514835</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003758703228328576</v>
+        <v>0.003724327767735262</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003764942324250911</v>
+        <v>0.003730237526854597</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003755361878445198</v>
+        <v>0.00372045489888539</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003751769339052948</v>
+        <v>0.0037173698561408</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003753118869359136</v>
+        <v>0.003718643691939121</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003753137081410384</v>
+        <v>0.003718547481274779</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003759494875103357</v>
+        <v>0.003725099386233088</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003752242136436274</v>
+        <v>0.003717827245376119</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003759811607370264</v>
+        <v>0.003725245303639581</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003749504958223863</v>
+        <v>0.003715184722843513</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003752879518718742</v>
+        <v>0.003718496344346919</v>
       </c>
       <c r="O2" t="n">
-        <v>0.005454953568144245</v>
+        <v>0.005412080652775575</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003760442184812256</v>
+        <v>0.00372691838433303</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003747778013822979</v>
+        <v>0.003713488456775702</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003770592308639911</v>
+        <v>0.00373461110208357</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003759238749154385</v>
+        <v>0.00372431391500053</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003748224852804322</v>
+        <v>0.00371358790737681</v>
       </c>
       <c r="U2" t="n">
-        <v>0.003627059494511486</v>
+        <v>0.003555198986957071</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003763912173406911</v>
+        <v>0.003729300854951447</v>
       </c>
       <c r="W2" t="n">
-        <v>0.003626907601488845</v>
+        <v>0.003550080817832747</v>
       </c>
       <c r="X2" t="n">
-        <v>0.003970883051158397</v>
+        <v>0.003937204529351535</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003846361357404329</v>
+        <v>0.003811960490298973</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.004752296538290251</v>
+        <v>0.004715445247181514</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.00378163182793526</v>
+        <v>0.003747152431731161</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.003747490051483502</v>
+        <v>0.003712990538847193</v>
       </c>
     </row>
     <row r="3">
@@ -6694,85 +6694,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003606220252701861</v>
+        <v>0.003570942570768011</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002918078713698462</v>
+        <v>0.002861016786853695</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003641290702336829</v>
+        <v>0.003606138634766626</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003683579457580593</v>
+        <v>0.003646094616950283</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003617639360286709</v>
+        <v>0.003578684139332817</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003591175469697648</v>
+        <v>0.003555864682284358</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003601866937410855</v>
+        <v>0.003565993744737874</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003601720290061974</v>
+        <v>0.003565033950374654</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003646380695039543</v>
+        <v>0.003611089030562455</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00359509066591198</v>
+        <v>0.003559660381634589</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003648255264470276</v>
+        <v>0.003611763459141447</v>
       </c>
       <c r="M3" t="n">
-        <v>0.003581025954266781</v>
+        <v>0.003545984048841107</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003599520664994491</v>
+        <v>0.003564315985633932</v>
       </c>
       <c r="O3" t="n">
-        <v>0.006456131310080486</v>
+        <v>0.006441993463920184</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003652586810641031</v>
+        <v>0.003623488569183115</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003563098137250032</v>
+        <v>0.003528562794587471</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003726836493633805</v>
+        <v>0.00368018105461583</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003644128800739627</v>
+        <v>0.003605091100451479</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003566549989793678</v>
+        <v>0.003529529584566156</v>
       </c>
       <c r="U3" t="n">
-        <v>0.003382107221934301</v>
+        <v>0.003284388453076776</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003677390642202208</v>
+        <v>0.003640575258491967</v>
       </c>
       <c r="W3" t="n">
-        <v>0.003480969805342704</v>
+        <v>0.003372624515463502</v>
       </c>
       <c r="X3" t="n">
-        <v>0.005151137751040705</v>
+        <v>0.00512095054233769</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.004267361096558297</v>
+        <v>0.004232028573353571</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0052849547376009</v>
+        <v>0.005244863822000686</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003804779707650774</v>
+        <v>0.003768887609563164</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.003565899112956046</v>
+        <v>0.003529675265595672</v>
       </c>
     </row>
     <row r="4">
@@ -6782,85 +6782,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.007381624018917553</v>
+        <v>0.006829353273362562</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007351193177459068</v>
+        <v>0.006798431220921704</v>
       </c>
       <c r="D4" t="n">
-        <v>0.007435976490683452</v>
+        <v>0.006883922056032101</v>
       </c>
       <c r="E4" t="n">
-        <v>0.007506449949252161</v>
+        <v>0.006950675503908413</v>
       </c>
       <c r="F4" t="n">
-        <v>0.007398234406653801</v>
+        <v>0.006840176220765057</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007357655021568586</v>
+        <v>0.006805329243775088</v>
       </c>
       <c r="H4" t="n">
-        <v>0.007372898587191604</v>
+        <v>0.006819717805110566</v>
       </c>
       <c r="I4" t="n">
-        <v>0.007373104300688435</v>
+        <v>0.006818631061397759</v>
       </c>
       <c r="J4" t="n">
-        <v>0.007441949994016818</v>
+        <v>0.006889663568913678</v>
       </c>
       <c r="K4" t="n">
-        <v>0.007362995485510769</v>
+        <v>0.006810495665597456</v>
       </c>
       <c r="L4" t="n">
-        <v>0.007448496141838862</v>
+        <v>0.006894286046158676</v>
       </c>
       <c r="M4" t="n">
-        <v>0.007341723079660521</v>
+        <v>0.00678977096611211</v>
       </c>
       <c r="N4" t="n">
-        <v>0.007370195011601605</v>
+        <v>0.0106513090211263</v>
       </c>
       <c r="O4" t="n">
-        <v>0.007468935620690684</v>
+        <v>0.006989611407279073</v>
       </c>
       <c r="P4" t="n">
-        <v>0.007455618804126109</v>
+        <v>0.006913184262246362</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.007312571166995741</v>
+        <v>0.006761487052414442</v>
       </c>
       <c r="R4" t="n">
-        <v>0.007570269122047144</v>
+        <v>0.007000077048063692</v>
       </c>
       <c r="S4" t="n">
-        <v>0.00744202544476269</v>
+        <v>0.006883765583020702</v>
       </c>
       <c r="T4" t="n">
-        <v>0.007317618418846109</v>
+        <v>0.006762610392703462</v>
       </c>
       <c r="U4" t="n">
-        <v>0.007347466053688582</v>
+        <v>0.006786197647307926</v>
       </c>
       <c r="V4" t="n">
-        <v>0.007474730342286809</v>
+        <v>0.006919970805342427</v>
       </c>
       <c r="W4" t="n">
-        <v>0.00755494218504171</v>
+        <v>0.006996438252296981</v>
       </c>
       <c r="X4" t="n">
-        <v>0.00983264519708707</v>
+        <v>0.009288463006636395</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.008422970436182927</v>
+        <v>0.007862872552232227</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.007445850651280359</v>
+        <v>0.006891993980099088</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.007694965570917867</v>
+        <v>0.007141737135729923</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.007317351542833672</v>
+        <v>0.006763570110933379</v>
       </c>
     </row>
     <row r="5">
@@ -6870,85 +6870,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01117247920985321</v>
+        <v>0.01058519973930574</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01099186955764026</v>
+        <v>0.01039091389008361</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01251094368648398</v>
+        <v>0.01192175746188536</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01259656842342126</v>
+        <v>0.01195077067524544</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01194500471232285</v>
+        <v>0.01124461788645133</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01080039967855075</v>
+        <v>0.01021301060019889</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01161922317285667</v>
+        <v>0.01100522300388005</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0114795062720985</v>
+        <v>0.01084445734009098</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01237590819755123</v>
+        <v>0.01178444891510784</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01117511968441958</v>
+        <v>0.01057971466480015</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01224213676306893</v>
+        <v>0.011626390490136</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01091817278235978</v>
+        <v>0.010330456229376</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01078167360205665</v>
+        <v>0.0106513090211263</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01250319101361132</v>
+        <v>0.01305251733017672</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01228057611658607</v>
+        <v>0.01184882950999558</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0102149477307912</v>
+        <v>0.009644802827571027</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0152451733307774</v>
+        <v>0.01431286663114705</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01210802720969082</v>
+        <v>0.01142736750583091</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01044037529761296</v>
+        <v>0.009797857847677871</v>
       </c>
       <c r="U5" t="n">
-        <v>0.01076208959128643</v>
+        <v>0.01015579178643567</v>
       </c>
       <c r="V5" t="n">
-        <v>0.01297359677143802</v>
+        <v>0.01234762147926137</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0143292839569876</v>
+        <v>0.01363280174537473</v>
       </c>
       <c r="X5" t="n">
-        <v>0.05257267671875709</v>
+        <v>0.05211794194808415</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03025636272345644</v>
+        <v>0.02966255265963691</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01204317182330283</v>
+        <v>0.01143420315152144</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01701201792292639</v>
+        <v>0.01640298125293267</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.01055428899847168</v>
+        <v>0.009929678621106039</v>
       </c>
     </row>
     <row r="6">
@@ -6958,85 +6958,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.008324948407266788</v>
+        <v>0.007717569352188174</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008294517565808303</v>
+        <v>0.007686647299747314</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008379300879032686</v>
+        <v>0.007772138134857711</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008449774337601398</v>
+        <v>0.007186958795620007</v>
       </c>
       <c r="F6" t="n">
-        <v>0.008341558795003036</v>
+        <v>0.007728392299590668</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008300979409917824</v>
+        <v>0.007693545322600699</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007643866995909053</v>
+        <v>0.007707933883936176</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007644072709405886</v>
+        <v>0.007706847140223366</v>
       </c>
       <c r="J6" t="n">
-        <v>0.007712918402734268</v>
+        <v>0.00712594686062527</v>
       </c>
       <c r="K6" t="n">
-        <v>0.008306319873860008</v>
+        <v>0.007046778957309052</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008391820530188096</v>
+        <v>0.007782502124984287</v>
       </c>
       <c r="M6" t="n">
-        <v>0.00828504746800976</v>
+        <v>0.007677987044937719</v>
       </c>
       <c r="N6" t="n">
-        <v>0.00764117331130363</v>
+        <v>0.0106513090211263</v>
       </c>
       <c r="O6" t="n">
-        <v>0.008409444380760538</v>
+        <v>0.007259945487928248</v>
       </c>
       <c r="P6" t="n">
-        <v>0.008396115047900544</v>
+        <v>0.007800781414891187</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.008255895555344974</v>
+        <v>0.00764970313124005</v>
       </c>
       <c r="R6" t="n">
-        <v>0.007841237530764588</v>
+        <v>0.0078882931268893</v>
       </c>
       <c r="S6" t="n">
-        <v>0.007712993853480134</v>
+        <v>0.007771981661846312</v>
       </c>
       <c r="T6" t="n">
-        <v>0.008260942807195342</v>
+        <v>0.006998893684415056</v>
       </c>
       <c r="U6" t="n">
-        <v>0.008293935389180615</v>
+        <v>0.007685315144334512</v>
       </c>
       <c r="V6" t="n">
-        <v>0.007745698751004258</v>
+        <v>0.007156254097054021</v>
       </c>
       <c r="W6" t="n">
-        <v>0.008495461913881626</v>
+        <v>0.007883393522117822</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01010361360580452</v>
+        <v>0.009524746298347986</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.008715354822071622</v>
+        <v>0.008130352293658352</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.007716819059997809</v>
+        <v>0.007128277271810682</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.007965933979635317</v>
+        <v>0.008029953214555534</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.007587346470001801</v>
+        <v>0.00699900501137975</v>
       </c>
     </row>
     <row r="7">
@@ -7046,85 +7046,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007908275656771021</v>
+        <v>0.007364569340780264</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007877844815312536</v>
+        <v>0.007333647288339404</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007962628128536917</v>
+        <v>0.007419138123449802</v>
       </c>
       <c r="E7" t="n">
-        <v>0.008033101587105629</v>
+        <v>0.007485891571326111</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007924886044507268</v>
+        <v>0.007375392288182757</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007884306659422056</v>
+        <v>0.007340545311192787</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007899550225045071</v>
+        <v>0.007354933872528267</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007899755938541904</v>
+        <v>0.007353847128815461</v>
       </c>
       <c r="J7" t="n">
-        <v>0.007968601631870284</v>
+        <v>0.007424879636331376</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007889647123364242</v>
+        <v>0.007345711733015158</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00797514777969233</v>
+        <v>0.007429502113576375</v>
       </c>
       <c r="M7" t="n">
-        <v>0.00786837471751399</v>
+        <v>0.007324987033529811</v>
       </c>
       <c r="N7" t="n">
-        <v>0.007896846649455072</v>
+        <v>0.0106513090211263</v>
       </c>
       <c r="O7" t="n">
-        <v>0.007995565117330647</v>
+        <v>0.007524805736446928</v>
       </c>
       <c r="P7" t="n">
-        <v>0.007982248300766074</v>
+        <v>0.007448378591414219</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.007839222804849206</v>
+        <v>0.007296703119832141</v>
       </c>
       <c r="R7" t="n">
-        <v>0.008096920759900608</v>
+        <v>0.007535293115481393</v>
       </c>
       <c r="S7" t="n">
-        <v>0.007968677082616159</v>
+        <v>0.007418981650438402</v>
       </c>
       <c r="T7" t="n">
-        <v>0.007844270056699576</v>
+        <v>0.00729782646012116</v>
       </c>
       <c r="U7" t="n">
-        <v>0.007876206057496905</v>
+        <v>0.007331571348616354</v>
       </c>
       <c r="V7" t="n">
-        <v>0.008001381980140276</v>
+        <v>0.007455186872760129</v>
       </c>
       <c r="W7" t="n">
-        <v>0.008081593822895177</v>
+        <v>0.007531654319714681</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01035929683494054</v>
+        <v>0.009823679074054095</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.008952767021179191</v>
+        <v>0.008408990037850903</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.007972502289133822</v>
+        <v>0.007427210047516788</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.008221617208771338</v>
+        <v>0.007676953203147624</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.007844003180687139</v>
+        <v>0.007298786178351079</v>
       </c>
     </row>
     <row r="8">
@@ -7134,85 +7134,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.009113369414750239</v>
+        <v>0.00855170510430402</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01027651233991045</v>
+        <v>0.009694890537301328</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01036129565313483</v>
+        <v>0.009780381372411729</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009796226289200516</v>
+        <v>0.009221957218288432</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009315924645735467</v>
+        <v>0.008745440275858352</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0105304694799385</v>
+        <v>0.009945247395861825</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01029821774964298</v>
+        <v>0.009716177121490189</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01029842346313981</v>
+        <v>0.009715090377777381</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01036726915646819</v>
+        <v>0.0097861228852933</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01028831464796215</v>
+        <v>0.009706954981977078</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01037381530429024</v>
+        <v>0.009790745362538301</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01026704224211159</v>
+        <v>0.009686230282491541</v>
       </c>
       <c r="N8" t="n">
-        <v>0.009370294824384486</v>
+        <v>0.0106513090211263</v>
       </c>
       <c r="O8" t="n">
-        <v>0.00972329374431425</v>
+        <v>0.009226052549556722</v>
       </c>
       <c r="P8" t="n">
-        <v>0.009647652072019621</v>
+        <v>0.009088317019827536</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.008809752075693901</v>
+        <v>0.008253099964761515</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01049558828449852</v>
+        <v>0.009896536364443313</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01036734460721407</v>
+        <v>0.009780224899400329</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01024293758129749</v>
+        <v>0.009659069709083085</v>
       </c>
       <c r="U8" t="n">
-        <v>0.009692561072666478</v>
+        <v>0.009119932620935417</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01007294358373288</v>
+        <v>0.009494911655480767</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01048049591894836</v>
+        <v>0.009893128314479922</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01143921951316914</v>
+        <v>0.01088768520303574</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01253680635785632</v>
+        <v>0.01193666437718584</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.009155424801615518</v>
+        <v>0.008592536161707447</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01062028473336924</v>
+        <v>0.01003819645210955</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01148945830954268</v>
+        <v>0.01088648287316179</v>
       </c>
     </row>
     <row r="9">
@@ -7222,85 +7222,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008898105157733281</v>
+        <v>0.008338173049968299</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00932764892822701</v>
+        <v>0.008759231899379185</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00941243224145139</v>
+        <v>0.008844722734489583</v>
       </c>
       <c r="E9" t="n">
-        <v>0.009376745584029001</v>
+        <v>0.008807160975458994</v>
       </c>
       <c r="F9" t="n">
-        <v>0.008314322886330367</v>
+        <v>0.007759037322804957</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009334110965061988</v>
+        <v>0.008766130106376132</v>
       </c>
       <c r="H9" t="n">
-        <v>0.009349354337959543</v>
+        <v>0.008780518483568048</v>
       </c>
       <c r="I9" t="n">
-        <v>0.009349560051456381</v>
+        <v>0.008779431739855244</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009418405744784756</v>
+        <v>0.008850464247371159</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00933945123627871</v>
+        <v>0.008771296344054939</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009424951892606802</v>
+        <v>0.008855086724616159</v>
       </c>
       <c r="M9" t="n">
-        <v>0.00931817883042846</v>
+        <v>0.008750571644569596</v>
       </c>
       <c r="N9" t="n">
-        <v>0.009346650762369547</v>
+        <v>0.0106513090211263</v>
       </c>
       <c r="O9" t="n">
-        <v>0.00959782661216867</v>
+        <v>0.009100198209960228</v>
       </c>
       <c r="P9" t="n">
-        <v>0.009617661803195759</v>
+        <v>0.009056346937000997</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.009289027110489156</v>
+        <v>0.008722287915015484</v>
       </c>
       <c r="R9" t="n">
-        <v>0.00954672487281508</v>
+        <v>0.008960877726521174</v>
       </c>
       <c r="S9" t="n">
-        <v>0.009418481195530624</v>
+        <v>0.008844566261478186</v>
       </c>
       <c r="T9" t="n">
-        <v>0.00929407416961405</v>
+        <v>0.008723411071160942</v>
       </c>
       <c r="U9" t="n">
-        <v>0.009327066751599323</v>
+        <v>0.008757899743966383</v>
       </c>
       <c r="V9" t="n">
-        <v>0.009981987077119931</v>
+        <v>0.009402347898072585</v>
       </c>
       <c r="W9" t="n">
-        <v>0.009531397935809647</v>
+        <v>0.008957238930754464</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01180910094785502</v>
+        <v>0.01124926368509388</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.01040257113409366</v>
+        <v>0.009834574648890688</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.00914498269010865</v>
+        <v>0.008580290439571281</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.009671421321685815</v>
+        <v>0.009102537814187406</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.009293807293601613</v>
+        <v>0.00872437078939086</v>
       </c>
     </row>
   </sheetData>
@@ -7466,85 +7466,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00416176407252162</v>
+        <v>0.003940103912448254</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003711652095807796</v>
+        <v>0.003485709937841947</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004171631867455728</v>
+        <v>0.003982328326586782</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004087953920326843</v>
+        <v>0.003903412905599441</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004099791854018041</v>
+        <v>0.00389956813609461</v>
       </c>
       <c r="G2" t="n">
-        <v>0.004320263855006889</v>
+        <v>0.003957144900433602</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004086045530175887</v>
+        <v>0.00389446420277477</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004149143452654195</v>
+        <v>0.003954329989250814</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004210778926235952</v>
+        <v>0.003988788839830577</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004205213629546969</v>
+        <v>0.004011411537652975</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00429908378677162</v>
+        <v>0.004042089945954244</v>
       </c>
       <c r="M2" t="n">
-        <v>0.004186358278763709</v>
+        <v>0.004371396573337336</v>
       </c>
       <c r="N2" t="n">
-        <v>0.00418891994706299</v>
+        <v>0.003989458396433537</v>
       </c>
       <c r="O2" t="n">
-        <v>0.005981250467427236</v>
+        <v>0.005674057880671554</v>
       </c>
       <c r="P2" t="n">
-        <v>0.004242576811662825</v>
+        <v>0.003943305520990648</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.004101012226520958</v>
+        <v>0.003904606044791308</v>
       </c>
       <c r="R2" t="n">
-        <v>0.00410151838910781</v>
+        <v>0.003905999017053341</v>
       </c>
       <c r="S2" t="n">
-        <v>0.004183522056539219</v>
+        <v>0.003950073149472851</v>
       </c>
       <c r="T2" t="n">
-        <v>0.004148034514299804</v>
+        <v>0.003945427817881905</v>
       </c>
       <c r="U2" t="n">
-        <v>0.004352222749802174</v>
+        <v>0.004123534850679608</v>
       </c>
       <c r="V2" t="n">
-        <v>0.004088455905730583</v>
+        <v>0.00389439880146457</v>
       </c>
       <c r="W2" t="n">
-        <v>0.004166368362259253</v>
+        <v>0.003938995894990627</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004368798056780007</v>
+        <v>0.004230711542886612</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.004266591798016342</v>
+        <v>0.004136074459375198</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.005159852585956761</v>
+        <v>0.004931264977233492</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.004211694479398789</v>
+        <v>0.004006463866294023</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.004218443773948943</v>
+        <v>0.004295968400456064</v>
       </c>
     </row>
     <row r="3">
@@ -7554,85 +7554,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004545749281182105</v>
+        <v>0.004163061264062324</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003292344486738072</v>
+        <v>0.003055525485893288</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00462253938770949</v>
+        <v>0.004469734341168704</v>
       </c>
       <c r="E3" t="n">
-        <v>0.004020986673423004</v>
+        <v>0.003902176581999764</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004108236301547202</v>
+        <v>0.003877275093840604</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00567062027819995</v>
+        <v>0.004283827130749745</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004010593994230018</v>
+        <v>0.003841427440584802</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004461631347956491</v>
+        <v>0.004269366560104719</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004895213682503705</v>
+        <v>0.0045113045676298</v>
       </c>
       <c r="K3" t="n">
-        <v>0.004856474131060814</v>
+        <v>0.004671537733508794</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005525732002931357</v>
+        <v>0.004890840331938086</v>
       </c>
       <c r="M3" t="n">
-        <v>0.00473102378994049</v>
+        <v>0.00721534401019071</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004744473456768857</v>
+        <v>0.004519079627109622</v>
       </c>
       <c r="O3" t="n">
-        <v>0.007460234555254967</v>
+        <v>0.006921801452181111</v>
       </c>
       <c r="P3" t="n">
-        <v>0.005121536117509271</v>
+        <v>0.004186468276589812</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.00411599563719063</v>
+        <v>0.003912470415321796</v>
       </c>
       <c r="R3" t="n">
-        <v>0.004121219967154999</v>
+        <v>0.003923849781106837</v>
       </c>
       <c r="S3" t="n">
-        <v>0.004699051663838982</v>
+        <v>0.004233066939390458</v>
       </c>
       <c r="T3" t="n">
-        <v>0.004453552060828792</v>
+        <v>0.00420552029227207</v>
       </c>
       <c r="U3" t="n">
-        <v>0.00577788792554578</v>
+        <v>0.005578311340238709</v>
       </c>
       <c r="V3" t="n">
-        <v>0.004024998074629393</v>
+        <v>0.003838372515830815</v>
       </c>
       <c r="W3" t="n">
-        <v>0.004638383738370099</v>
+        <v>0.004479741177440371</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00603141644012022</v>
+        <v>0.006244825324917035</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.005296890758373693</v>
+        <v>0.005563389354881701</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006095269175545405</v>
+        <v>0.005694889174587645</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.004905911766745539</v>
+        <v>0.004639415637617134</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.004962437933401569</v>
+        <v>0.006694950440311221</v>
       </c>
     </row>
     <row r="4">
@@ -7642,85 +7642,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.008929483491384288</v>
+        <v>0.0076797930137208</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007869812571557175</v>
+        <v>0.006938173510755482</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009040944774574922</v>
+        <v>0.008156737195605569</v>
       </c>
       <c r="E4" t="n">
-        <v>0.008095763867996738</v>
+        <v>0.007265351212666311</v>
       </c>
       <c r="F4" t="n">
-        <v>0.008229478774757298</v>
+        <v>0.007221922772427953</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01071981144805762</v>
+        <v>0.007872278812257045</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008074207723338821</v>
+        <v>0.007164271497655005</v>
       </c>
       <c r="I4" t="n">
-        <v>0.008786927784209713</v>
+        <v>0.007840483095524263</v>
       </c>
       <c r="J4" t="n">
-        <v>0.009478721102865191</v>
+        <v>0.008226004658085685</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009420266225769308</v>
+        <v>0.008485245443536321</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01048057283402755</v>
+        <v>0.008831772178064169</v>
       </c>
       <c r="M4" t="n">
-        <v>0.009219373994985151</v>
+        <v>0.01250627554421347</v>
       </c>
       <c r="N4" t="n">
-        <v>0.009236221586648495</v>
+        <v>0.0363615153000075</v>
       </c>
       <c r="O4" t="n">
-        <v>0.008746982143584809</v>
+        <v>0.007466449528530761</v>
       </c>
       <c r="P4" t="n">
-        <v>0.009842300555680908</v>
+        <v>0.007715956655019788</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.008243263443576905</v>
+        <v>0.007278828268709693</v>
       </c>
       <c r="R4" t="n">
-        <v>0.008248980782841659</v>
+        <v>0.00729456253120818</v>
       </c>
       <c r="S4" t="n">
-        <v>0.009175249930030173</v>
+        <v>0.00779240013198918</v>
       </c>
       <c r="T4" t="n">
-        <v>0.008774401815360032</v>
+        <v>0.007739928974711332</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01078894827415498</v>
+        <v>0.009946809162058168</v>
       </c>
       <c r="V4" t="n">
-        <v>0.008071645167229151</v>
+        <v>0.007138497001192967</v>
       </c>
       <c r="W4" t="n">
-        <v>0.009096604513504679</v>
+        <v>0.008329713755712755</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01126802758392089</v>
+        <v>0.01096233988563686</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.01008398151205764</v>
+        <v>0.009868175702997257</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.008725863992830379</v>
+        <v>0.007463433611166882</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.009493470406183861</v>
+        <v>0.008429359219495725</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.009572863854877928</v>
+        <v>0.01164905134855173</v>
       </c>
     </row>
     <row r="5">
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0309412860049055</v>
+        <v>0.02372237155207518</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01313863743382652</v>
+        <v>0.0113165212164278</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03658767226405676</v>
+        <v>0.03569651847363715</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01630311834534573</v>
+        <v>0.0164316546846572</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02036731561374602</v>
+        <v>0.01702248627131342</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06126115149941677</v>
+        <v>0.02688552240953428</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01769057185495119</v>
+        <v>0.01625464123250715</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0315583324491026</v>
+        <v>0.02941524163138069</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04120657525034035</v>
+        <v>0.03454835380473047</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04056755057376231</v>
+        <v>0.03870173953227148</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06022746574244089</v>
+        <v>0.04544808068110114</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03818939307325232</v>
+        <v>0.1142387892132546</v>
       </c>
       <c r="N5" t="n">
-        <v>0.06517488426045225</v>
+        <v>0.0363615153000075</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02734230082729382</v>
+        <v>0.01977509526856564</v>
       </c>
       <c r="P5" t="n">
-        <v>0.04765698738261825</v>
+        <v>0.0247159118797009</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.02009931889267101</v>
+        <v>0.01767550505141343</v>
       </c>
       <c r="R5" t="n">
-        <v>0.02110384042631987</v>
+        <v>0.01877256110908236</v>
       </c>
       <c r="S5" t="n">
-        <v>0.03448401079305683</v>
+        <v>0.02521459375811649</v>
       </c>
       <c r="T5" t="n">
-        <v>0.03122987276628153</v>
+        <v>0.02734099556081708</v>
       </c>
       <c r="U5" t="n">
-        <v>0.06675719030988435</v>
+        <v>0.06654249493075891</v>
       </c>
       <c r="V5" t="n">
-        <v>0.01661896626947279</v>
+        <v>0.0147762307389829</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0362485866062749</v>
+        <v>0.03758663589692036</v>
       </c>
       <c r="X5" t="n">
-        <v>0.07963822330785704</v>
+        <v>0.09006132485469065</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.05498747251652848</v>
+        <v>0.06650888789221933</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.02758790687589851</v>
+        <v>0.02008972873897236</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.04372219180651579</v>
+        <v>0.03941899655359857</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.04891666252729748</v>
+        <v>0.1095882607136975</v>
       </c>
     </row>
     <row r="6">
@@ -7818,85 +7818,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01026149703975972</v>
+        <v>0.007960435459393031</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008273133134581485</v>
+        <v>0.00721881595642771</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01037295832295036</v>
+        <v>0.008437379641277798</v>
       </c>
       <c r="E6" t="n">
-        <v>0.009427777416372176</v>
+        <v>0.008342839428449041</v>
       </c>
       <c r="F6" t="n">
-        <v>0.009561492323132735</v>
+        <v>0.00750256521810018</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01112313201108192</v>
+        <v>0.008949767028039766</v>
       </c>
       <c r="H6" t="n">
-        <v>0.009406221271714256</v>
+        <v>0.007444913943327233</v>
       </c>
       <c r="I6" t="n">
-        <v>0.009190248347234021</v>
+        <v>0.00812112554119649</v>
       </c>
       <c r="J6" t="n">
-        <v>0.009882041665889501</v>
+        <v>0.008506647103757915</v>
       </c>
       <c r="K6" t="n">
-        <v>0.009823586788793616</v>
+        <v>0.009562733659319046</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01181258638240299</v>
+        <v>0.009909260393846894</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01055138754336059</v>
+        <v>0.0127869179898857</v>
       </c>
       <c r="N6" t="n">
-        <v>0.009644360772964773</v>
+        <v>0.0363615153000075</v>
       </c>
       <c r="O6" t="n">
-        <v>0.009155121329901086</v>
+        <v>0.008549301707330642</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01118010309553992</v>
+        <v>0.008799181560775672</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.009575276991952342</v>
+        <v>0.00755947071438192</v>
       </c>
       <c r="R6" t="n">
-        <v>0.009580994331217094</v>
+        <v>0.008372050746990904</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01050726347840561</v>
+        <v>0.008073042577661406</v>
       </c>
       <c r="T6" t="n">
-        <v>0.009177722378384339</v>
+        <v>0.00802057142038356</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01215054118445604</v>
+        <v>0.0110494921670097</v>
       </c>
       <c r="V6" t="n">
-        <v>0.009403658715604587</v>
+        <v>0.007419139446865197</v>
       </c>
       <c r="W6" t="n">
-        <v>0.009537206902491381</v>
+        <v>0.008639475521895085</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0116713481469452</v>
+        <v>0.01203982810141958</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01054370545236898</v>
+        <v>0.0101960416254818</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.009129184555854689</v>
+        <v>0.008540921826949608</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0108254839545593</v>
+        <v>0.009506847435278448</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.009985041045931144</v>
+        <v>0.01196772328096821</v>
       </c>
     </row>
     <row r="7">
@@ -7906,85 +7906,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.009614726291285175</v>
+        <v>0.008336386940575131</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008555055371458065</v>
+        <v>0.007594767437609814</v>
       </c>
       <c r="D7" t="n">
-        <v>0.009726187574475817</v>
+        <v>0.008813331122459902</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00878100666789763</v>
+        <v>0.007921945139520646</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008914721574658186</v>
+        <v>0.007878516699282285</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01140505424795851</v>
+        <v>0.008528872739111383</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00875945052323971</v>
+        <v>0.007820865424509339</v>
       </c>
       <c r="I7" t="n">
-        <v>0.009472170584110606</v>
+        <v>0.008497077022378598</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01016396390276609</v>
+        <v>0.00888259858494002</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01010550902567019</v>
+        <v>0.009141839370390661</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01116581563392845</v>
+        <v>0.009488366104918509</v>
       </c>
       <c r="M7" t="n">
-        <v>0.00990461679488604</v>
+        <v>0.01316286947106779</v>
       </c>
       <c r="N7" t="n">
-        <v>0.009921464386549391</v>
+        <v>0.0363615153000075</v>
       </c>
       <c r="O7" t="n">
-        <v>0.009432199819232948</v>
+        <v>0.008123019797841484</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01052751823132904</v>
+        <v>0.008372526924330511</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.008928506243477793</v>
+        <v>0.007935422195564024</v>
       </c>
       <c r="R7" t="n">
-        <v>0.008934223582742548</v>
+        <v>0.007951156458062514</v>
       </c>
       <c r="S7" t="n">
-        <v>0.009860492729931057</v>
+        <v>0.00844899405884351</v>
       </c>
       <c r="T7" t="n">
-        <v>0.009459644615260922</v>
+        <v>0.008396522901565664</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01150265261259125</v>
+        <v>0.01062797048933927</v>
       </c>
       <c r="V7" t="n">
-        <v>0.008756887967130041</v>
+        <v>0.0077950909280473</v>
       </c>
       <c r="W7" t="n">
-        <v>0.009781847313405569</v>
+        <v>0.008986307682567085</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01195327038382177</v>
+        <v>0.0116189338124912</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01079880367388417</v>
+        <v>0.01054996441902041</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.009411106792731272</v>
+        <v>0.008120027538021213</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01017871320608475</v>
+        <v>0.009085953146350063</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01025810665477882</v>
+        <v>0.01230564527540605</v>
       </c>
     </row>
     <row r="8">
@@ -7994,85 +7994,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01103010252691001</v>
+        <v>0.009695147033321536</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01144446349363395</v>
+        <v>0.01033701715943071</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0126155956966517</v>
+        <v>0.01155558084428078</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01088553629172429</v>
+        <v>0.009927527444257013</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01055973475082295</v>
+        <v>0.009452808307050208</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01460011248422789</v>
+        <v>0.01155799804811474</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01164885864541559</v>
+        <v>0.01056311514633023</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01236157870628649</v>
+        <v>0.01123932674419949</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01305337202494197</v>
+        <v>0.0116248483067609</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01299491714784608</v>
+        <v>0.01188408909221155</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01405522375610432</v>
+        <v>0.01223061582673939</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01279402491706169</v>
+        <v>0.01590511919288897</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01166825119646249</v>
+        <v>0.0363615153000075</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01149301401117766</v>
+        <v>0.01008757196321063</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0125113628825386</v>
+        <v>0.0102648373951024</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01005420157028568</v>
+        <v>0.009022294999597443</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01182363170491843</v>
+        <v>0.01069340617988341</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01274990085210693</v>
+        <v>0.0111912437806644</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0123490527374368</v>
+        <v>0.01113877262338655</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01367287645295338</v>
+        <v>0.01269511690030358</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01124248693677714</v>
+        <v>0.01015869601924325</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01267154512499216</v>
+        <v>0.01172882929971009</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01321406366192169</v>
+        <v>0.01283260619004557</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01515235949559542</v>
+        <v>0.0146669859875833</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.01079910212930307</v>
+        <v>0.009453088600626295</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01306812132826063</v>
+        <v>0.01182820286817095</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01468726433891222</v>
+        <v>0.01649306560028646</v>
       </c>
     </row>
     <row r="9">
@@ -8082,85 +8082,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01152440606613511</v>
+        <v>0.009788775162097096</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01124301438581024</v>
+        <v>0.009675218750141977</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01241414658882799</v>
+        <v>0.01089378243499206</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01128934242050225</v>
+        <v>0.009857441303135893</v>
       </c>
       <c r="F9" t="n">
-        <v>0.009808533829955755</v>
+        <v>0.008511112443911218</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01409301379817156</v>
+        <v>0.01060932307747497</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01144740953759189</v>
+        <v>0.009901316737041496</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01216012959846278</v>
+        <v>0.01057752833491076</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01285192291711826</v>
+        <v>0.01096304989747217</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01279346804002237</v>
+        <v>0.01122229068292283</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01385377464828062</v>
+        <v>0.01156881741745067</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01259257580923821</v>
+        <v>0.01524332078359997</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01260942340090157</v>
+        <v>0.0363615153000075</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01237810539218371</v>
+        <v>0.01041163275689283</v>
       </c>
       <c r="P9" t="n">
-        <v>0.01352951717452289</v>
+        <v>0.0107064065368025</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.01161646579369084</v>
+        <v>0.01001587253392761</v>
       </c>
       <c r="R9" t="n">
-        <v>0.01162218259709472</v>
+        <v>0.01003160777059468</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01254845174428323</v>
+        <v>0.01052944537137568</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0121476036296131</v>
+        <v>0.01047697421409782</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01419172945033368</v>
+        <v>0.01270904919061347</v>
       </c>
       <c r="V9" t="n">
-        <v>0.01234296465760827</v>
+        <v>0.01060031084032843</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01246980632775774</v>
+        <v>0.01106675899509925</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01464122939817395</v>
+        <v>0.01369938512502336</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.01348676268823635</v>
+        <v>0.01263041573155256</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.01162983284573826</v>
+        <v>0.009821812269391819</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.01286667222043692</v>
+        <v>0.01116640445888222</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.012946065669131</v>
+        <v>0.01438609658793824</v>
       </c>
     </row>
   </sheetData>
@@ -8326,85 +8326,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004124613077914797</v>
+        <v>0.003815093471769076</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003840004689084397</v>
+        <v>0.003431928902596505</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004146193782629318</v>
+        <v>0.003835532269870233</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004141250237547776</v>
+        <v>0.003829158159508395</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004132982402317519</v>
+        <v>0.003821953545793705</v>
       </c>
       <c r="G2" t="n">
-        <v>0.004332546037331233</v>
+        <v>0.00389076489197997</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004132370218054699</v>
+        <v>0.003822140946515484</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004139474595460053</v>
+        <v>0.003828162268963356</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004230322753276424</v>
+        <v>0.003882634942977412</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004154057790590924</v>
+        <v>0.003841905463573692</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004216996617806276</v>
+        <v>0.003885974276522062</v>
       </c>
       <c r="M2" t="n">
-        <v>0.004141397038354177</v>
+        <v>0.003858605717063106</v>
       </c>
       <c r="N2" t="n">
-        <v>0.004144500618129082</v>
+        <v>0.003832626041732633</v>
       </c>
       <c r="O2" t="n">
-        <v>0.005954992644810373</v>
+        <v>0.005523270456218045</v>
       </c>
       <c r="P2" t="n">
-        <v>0.004228834276731775</v>
+        <v>0.003869121239336907</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.004141782856146232</v>
+        <v>0.003829902864543988</v>
       </c>
       <c r="R2" t="n">
-        <v>0.004155180105403472</v>
+        <v>0.003839887786001725</v>
       </c>
       <c r="S2" t="n">
-        <v>0.004154225754375656</v>
+        <v>0.00383979326981827</v>
       </c>
       <c r="T2" t="n">
-        <v>0.004135933030939061</v>
+        <v>0.003823504117119589</v>
       </c>
       <c r="U2" t="n">
-        <v>0.004245491173623371</v>
+        <v>0.003812664794298036</v>
       </c>
       <c r="V2" t="n">
-        <v>0.004136152331425484</v>
+        <v>0.003825135941918613</v>
       </c>
       <c r="W2" t="n">
-        <v>0.004231063879309247</v>
+        <v>0.003781652881277615</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004506185292285067</v>
+        <v>0.004203549079402723</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.004570752304794943</v>
+        <v>0.004308466012889062</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.00508535105578739</v>
+        <v>0.004816786108156994</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.004165164455528027</v>
+        <v>0.003852466330550858</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.006931667323015631</v>
+        <v>0.006556942306285844</v>
       </c>
     </row>
     <row r="3">
@@ -8414,85 +8414,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003899083188792775</v>
+        <v>0.00360023638862956</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00345039658389551</v>
+        <v>0.002985264786844034</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004053740952519917</v>
+        <v>0.003746683969843337</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00401642177398137</v>
+        <v>0.003699226718408315</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003959435450241162</v>
+        <v>0.003649748175828233</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00537243469701739</v>
+        <v>0.004136566645137616</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003955404227722397</v>
+        <v>0.003651395161625393</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004005959236841482</v>
+        <v>0.003694226257382684</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004650880723558669</v>
+        <v>0.004081626248357599</v>
       </c>
       <c r="K3" t="n">
-        <v>0.004108925546511431</v>
+        <v>0.003791304587179731</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004555259750869109</v>
+        <v>0.004103734397202945</v>
       </c>
       <c r="M3" t="n">
-        <v>0.004028357712546736</v>
+        <v>0.003914375760472228</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004041481688368211</v>
+        <v>0.003725775668716057</v>
       </c>
       <c r="O3" t="n">
-        <v>0.00702992365264795</v>
+        <v>0.006484499319071784</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004639442749885927</v>
+        <v>0.003984022942304846</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.00402149182550534</v>
+        <v>0.003705830005548319</v>
       </c>
       <c r="R3" t="n">
-        <v>0.004118684285316175</v>
+        <v>0.003778407767458979</v>
       </c>
       <c r="S3" t="n">
-        <v>0.004109162645536985</v>
+        <v>0.003775472186145962</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003980509990175684</v>
+        <v>0.003660805454807614</v>
       </c>
       <c r="U3" t="n">
-        <v>0.004348843994831875</v>
+        <v>0.003834432418560748</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003981165997435891</v>
+        <v>0.003671678614355892</v>
       </c>
       <c r="W3" t="n">
-        <v>0.004338650635624376</v>
+        <v>0.003822991537147354</v>
       </c>
       <c r="X3" t="n">
-        <v>0.006622846399418934</v>
+        <v>0.006373085441259971</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.007082230945616364</v>
+        <v>0.007120328273726126</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.005593257034456289</v>
+        <v>0.005339628400137531</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.004188786221362329</v>
+        <v>0.003867225369838267</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.02377740883373661</v>
+        <v>0.02301322547414383</v>
       </c>
     </row>
     <row r="4">
@@ -8502,85 +8502,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.007730443743713953</v>
+        <v>0.006788523028819987</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007773393635946746</v>
+        <v>0.006824716205596319</v>
       </c>
       <c r="D4" t="n">
-        <v>0.007974207731079156</v>
+        <v>0.007019388655684181</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00791836811524003</v>
+        <v>0.006947390146911661</v>
       </c>
       <c r="F4" t="n">
-        <v>0.007824979112922159</v>
+        <v>0.006866010720718154</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01007914217420974</v>
+        <v>0.007643266530675112</v>
       </c>
       <c r="H4" t="n">
-        <v>0.007818064210054973</v>
+        <v>0.006868127498079253</v>
       </c>
       <c r="I4" t="n">
-        <v>0.007898311421023443</v>
+        <v>0.006936141105073125</v>
       </c>
       <c r="J4" t="n">
-        <v>0.008920452652056508</v>
+        <v>0.00754792799469015</v>
       </c>
       <c r="K4" t="n">
-        <v>0.008063035318627877</v>
+        <v>0.007091376810378722</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008773958325316239</v>
+        <v>0.007589154325286119</v>
       </c>
       <c r="M4" t="n">
-        <v>0.007936532565587059</v>
+        <v>0.007286656666863549</v>
       </c>
       <c r="N4" t="n">
-        <v>0.007955082659154865</v>
+        <v>0.01273869717951994</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0079574952164618</v>
+        <v>0.006922439247107543</v>
       </c>
       <c r="P4" t="n">
-        <v>0.008907670128471953</v>
+        <v>0.007398791517499655</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.007924384287326234</v>
+        <v>0.0069558019328699</v>
       </c>
       <c r="R4" t="n">
-        <v>0.008075712380725946</v>
+        <v>0.007068586214025822</v>
       </c>
       <c r="S4" t="n">
-        <v>0.008064932546843569</v>
+        <v>0.0070675186102541</v>
       </c>
       <c r="T4" t="n">
-        <v>0.007858307820558767</v>
+        <v>0.00688352513714208</v>
       </c>
       <c r="U4" t="n">
-        <v>0.008223131248611279</v>
+        <v>0.00726098210443831</v>
       </c>
       <c r="V4" t="n">
-        <v>0.007833540338164927</v>
+        <v>0.006878254031158316</v>
       </c>
       <c r="W4" t="n">
-        <v>0.008273119627959383</v>
+        <v>0.00736026495952224</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01204047743691705</v>
+        <v>0.01117630781545025</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.01274476474000445</v>
+        <v>0.01234098623399455</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.00795522376667432</v>
+        <v>0.006966826500983082</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.008188490208410767</v>
+        <v>0.007210666661124662</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.03900445614188339</v>
+        <v>0.03732961331750825</v>
       </c>
     </row>
     <row r="5">
@@ -8590,85 +8590,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01008996199019154</v>
+        <v>0.009024389465172707</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01111756174804411</v>
+        <v>0.009905021365644253</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01473050580391235</v>
+        <v>0.01340553580351304</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01268734368142881</v>
+        <v>0.01111385954274931</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01208326283198328</v>
+        <v>0.01068047917303075</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04609780114430194</v>
+        <v>0.02220354943221063</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01213610424729272</v>
+        <v>0.010878307117697</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01347804459663599</v>
+        <v>0.01200693552074958</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02982720923761134</v>
+        <v>0.02217377279052188</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01581380334992399</v>
+        <v>0.01423040549160956</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02690379478224867</v>
+        <v>0.02195055278447079</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01400361773346501</v>
+        <v>0.01782492890899358</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01829454560036652</v>
+        <v>0.01273869717951994</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01368170327674665</v>
+        <v>0.01116442084435913</v>
       </c>
       <c r="P5" t="n">
-        <v>0.02911170582988506</v>
+        <v>0.01887880739625658</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01345123475293939</v>
+        <v>0.01193025961947198</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01694424902682603</v>
+        <v>0.01460643884897797</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01534899945276271</v>
+        <v>0.01341584295181784</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0126809013619534</v>
+        <v>0.0109854694537689</v>
       </c>
       <c r="U5" t="n">
-        <v>0.01858762099532775</v>
+        <v>0.01710454133796101</v>
       </c>
       <c r="V5" t="n">
-        <v>0.01222632377362828</v>
+        <v>0.01088705019356411</v>
       </c>
       <c r="W5" t="n">
-        <v>0.01982564757248575</v>
+        <v>0.01926703494571608</v>
       </c>
       <c r="X5" t="n">
-        <v>0.08656011063882142</v>
+        <v>0.08684830277292042</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.09871638967579326</v>
+        <v>0.1070028797542557</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01361007554752626</v>
+        <v>0.01182060455924125</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01833939318510286</v>
+        <v>0.01662389287844776</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.6044076400564856</v>
+        <v>0.5893842039663295</v>
       </c>
     </row>
     <row r="6">
@@ -8678,85 +8678,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.008342280492284084</v>
+        <v>0.007911020078096093</v>
       </c>
       <c r="C6" t="n">
-        <v>0.009462109760092508</v>
+        <v>0.00794721325487243</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008586044479649287</v>
+        <v>0.008141885704960293</v>
       </c>
       <c r="E6" t="n">
-        <v>0.009607084239385786</v>
+        <v>0.007184268367155759</v>
       </c>
       <c r="F6" t="n">
-        <v>0.009513695237067918</v>
+        <v>0.00710288894096225</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01069097892277987</v>
+        <v>0.007880144750919211</v>
       </c>
       <c r="H6" t="n">
-        <v>0.009506780334200736</v>
+        <v>0.007105005718323348</v>
       </c>
       <c r="I6" t="n">
-        <v>0.009587027545169208</v>
+        <v>0.008058638154349236</v>
       </c>
       <c r="J6" t="n">
-        <v>0.009532289400626641</v>
+        <v>0.008670425043966258</v>
       </c>
       <c r="K6" t="n">
-        <v>0.009751751442773638</v>
+        <v>0.007328255030622817</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00938579507388637</v>
+        <v>0.008711651374562224</v>
       </c>
       <c r="M6" t="n">
-        <v>0.009625248689732819</v>
+        <v>0.007523534887107643</v>
       </c>
       <c r="N6" t="n">
-        <v>0.008568945788980886</v>
+        <v>0.01273869717951994</v>
       </c>
       <c r="O6" t="n">
-        <v>0.008571358346287894</v>
+        <v>0.008039528252794415</v>
       </c>
       <c r="P6" t="n">
-        <v>0.009471661471633154</v>
+        <v>0.007619028944206316</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.009613100411471997</v>
+        <v>0.007192680153113998</v>
       </c>
       <c r="R6" t="n">
-        <v>0.009764428504871707</v>
+        <v>0.008191083263301932</v>
       </c>
       <c r="S6" t="n">
-        <v>0.008676769295413696</v>
+        <v>0.007304396830498194</v>
       </c>
       <c r="T6" t="n">
-        <v>0.008470144569128894</v>
+        <v>0.007120403357386176</v>
       </c>
       <c r="U6" t="n">
-        <v>0.008859994802686223</v>
+        <v>0.008403885763072249</v>
       </c>
       <c r="V6" t="n">
-        <v>0.009522256462310683</v>
+        <v>0.007115132251402414</v>
       </c>
       <c r="W6" t="n">
-        <v>0.008930852465082883</v>
+        <v>0.007619663783241389</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01265231418548717</v>
+        <v>0.01229880486472637</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01341788285383917</v>
+        <v>0.01261611026696002</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.008567060515244449</v>
+        <v>0.008089323550259193</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.009877206332556529</v>
+        <v>0.007447544881368757</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.03978818974847478</v>
+        <v>0.0377743193769623</v>
       </c>
     </row>
     <row r="7">
@@ -8766,85 +8766,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00827930797975047</v>
+        <v>0.007357189148434479</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008322257871983261</v>
+        <v>0.007393382325210811</v>
       </c>
       <c r="D7" t="n">
-        <v>0.008523071967115672</v>
+        <v>0.007588054775298675</v>
       </c>
       <c r="E7" t="n">
-        <v>0.008467232351276544</v>
+        <v>0.007516056266526154</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00837384334895867</v>
+        <v>0.007434676840332648</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01062800641024625</v>
+        <v>0.008211932650289603</v>
       </c>
       <c r="H7" t="n">
-        <v>0.008366928446091489</v>
+        <v>0.007436793617693747</v>
       </c>
       <c r="I7" t="n">
-        <v>0.008447175657059958</v>
+        <v>0.007504807224687617</v>
       </c>
       <c r="J7" t="n">
-        <v>0.009469316888093021</v>
+        <v>0.008116594114304642</v>
       </c>
       <c r="K7" t="n">
-        <v>0.008611899554664395</v>
+        <v>0.007660042929993215</v>
       </c>
       <c r="L7" t="n">
-        <v>0.009322822561352757</v>
+        <v>0.008157820444900611</v>
       </c>
       <c r="M7" t="n">
-        <v>0.008485396801623571</v>
+        <v>0.007855322786478039</v>
       </c>
       <c r="N7" t="n">
-        <v>0.008503946895191378</v>
+        <v>0.01273869717951994</v>
       </c>
       <c r="O7" t="n">
-        <v>0.008506336542684465</v>
+        <v>0.007491083791190553</v>
       </c>
       <c r="P7" t="n">
-        <v>0.00945651145469462</v>
+        <v>0.007967436061582667</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.00847324852336275</v>
+        <v>0.007524468052484392</v>
       </c>
       <c r="R7" t="n">
-        <v>0.008624576616762462</v>
+        <v>0.007637252333640314</v>
       </c>
       <c r="S7" t="n">
-        <v>0.008613796782880082</v>
+        <v>0.00763618472986859</v>
       </c>
       <c r="T7" t="n">
-        <v>0.008407172056595283</v>
+        <v>0.007452191256756574</v>
       </c>
       <c r="U7" t="n">
-        <v>0.00879536944664659</v>
+        <v>0.007849129453692746</v>
       </c>
       <c r="V7" t="n">
-        <v>0.008382404574201445</v>
+        <v>0.007446920150772811</v>
       </c>
       <c r="W7" t="n">
-        <v>0.008821983863995898</v>
+        <v>0.007928931079136734</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01258934167295355</v>
+        <v>0.01174497393506476</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01331865578154578</v>
+        <v>0.01293005896296687</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.008504088002710835</v>
+        <v>0.007535492620597577</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.008737354444447279</v>
+        <v>0.007779332780739155</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.03955332037791989</v>
+        <v>0.03789827943712268</v>
       </c>
     </row>
     <row r="8">
@@ -8854,85 +8854,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.009640811908631291</v>
+        <v>0.008597663809960193</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01106098009033126</v>
+        <v>0.009871983102791361</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01126179418546368</v>
+        <v>0.01006665555287923</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01047262645590016</v>
+        <v>0.009335391409744154</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00994990179143712</v>
+        <v>0.008868037080454022</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01365230381265035</v>
+        <v>0.01094726694367517</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01110565066443949</v>
+        <v>0.009915394395274299</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01118589787540795</v>
+        <v>0.009983408002268176</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01220803910644103</v>
+        <v>0.0105951948918852</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01135062177301239</v>
+        <v>0.01013864370757377</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01206154477970076</v>
+        <v>0.01063642122248116</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01122411901997132</v>
+        <v>0.01033392356405863</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01017509453557695</v>
+        <v>0.01273869717951994</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01047088585645553</v>
+        <v>0.009273700243139867</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01134914654449422</v>
+        <v>0.009685401267237837</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.009564097624915658</v>
+        <v>0.008521622673357841</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01136329883511046</v>
+        <v>0.01011585311122087</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01135251900122808</v>
+        <v>0.01011478550744914</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01114589427494328</v>
+        <v>0.009930792034337131</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01086227948428273</v>
+        <v>0.009723642352769547</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01074331904107698</v>
+        <v>0.009586349842708583</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01156097674510518</v>
+        <v>0.01040777518397226</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01380641556725262</v>
+        <v>0.01285560527466685</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01742455390071685</v>
+        <v>0.0166385021309697</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.009840009394807954</v>
+        <v>0.0087529684538635</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01147607666279528</v>
+        <v>0.01025793355831971</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.04373066226064862</v>
+        <v>0.04167020647335135</v>
       </c>
     </row>
     <row r="9">
@@ -8942,85 +8942,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00974822243903431</v>
+        <v>0.008516374226646761</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01042031657848136</v>
+        <v>0.009068985620523476</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01062113067361378</v>
+        <v>0.009263658070611341</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01042008700859144</v>
+        <v>0.00907247198402034</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0090215530648616</v>
+        <v>0.007919795811778589</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01272606495663237</v>
+        <v>0.009887535477919839</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01046498715258959</v>
+        <v>0.009112396913006408</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01054523436355806</v>
+        <v>0.009180410520000288</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01156737559459113</v>
+        <v>0.009792197409617306</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01070995826116249</v>
+        <v>0.009335646225305881</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01142088126785086</v>
+        <v>0.009833423740213273</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01058345550812168</v>
+        <v>0.009530926081790705</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01060200560168948</v>
+        <v>0.01273869717951994</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01081291552555625</v>
+        <v>0.009337848360318014</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0118084350724024</v>
+        <v>0.009851420680536925</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.01057130706974887</v>
+        <v>0.00920007088011462</v>
       </c>
       <c r="R9" t="n">
-        <v>0.01072263532326057</v>
+        <v>0.00931285562895298</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01071185548937819</v>
+        <v>0.00931178802518126</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01050523076309339</v>
+        <v>0.009127794552069237</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01089508099665071</v>
+        <v>0.009525658128723297</v>
       </c>
       <c r="V9" t="n">
-        <v>0.01120648126014712</v>
+        <v>0.009718457604168897</v>
       </c>
       <c r="W9" t="n">
-        <v>0.010920042570494</v>
+        <v>0.009604534374449391</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01468740037945167</v>
+        <v>0.0134205772303774</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.01541671448804389</v>
+        <v>0.01460566225827954</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.01022282861024934</v>
+        <v>0.008899741466986784</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.01083541315094538</v>
+        <v>0.00945493607605182</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.04165137908441798</v>
+        <v>0.03957388273243544</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia acidification results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia acidification results.xlsx
@@ -798,7 +798,7 @@
         <v>0.01330258782769781</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05272152432887288</v>
+        <v>0.00902929144968583</v>
       </c>
       <c r="O4" t="n">
         <v>0.00826443199361636</v>
@@ -974,7 +974,7 @@
         <v>0.0145397014546461</v>
       </c>
       <c r="N6" t="n">
-        <v>0.05272152432887288</v>
+        <v>0.009386014528987711</v>
       </c>
       <c r="O6" t="n">
         <v>0.008621152469315163</v>
@@ -1062,7 +1062,7 @@
         <v>0.01405448870200439</v>
       </c>
       <c r="N7" t="n">
-        <v>0.05272152432887288</v>
+        <v>0.009781192323992419</v>
       </c>
       <c r="O7" t="n">
         <v>0.009016306010960698</v>
@@ -1150,7 +1150,7 @@
         <v>0.01711882547122138</v>
       </c>
       <c r="N8" t="n">
-        <v>0.05272152432887288</v>
+        <v>0.01163960630112208</v>
       </c>
       <c r="O8" t="n">
         <v>0.01120614489914618</v>
@@ -1238,7 +1238,7 @@
         <v>0.01671990570693342</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05272152432887288</v>
+        <v>0.01244660932892144</v>
       </c>
       <c r="O9" t="n">
         <v>0.01194058234108189</v>
@@ -1658,7 +1658,7 @@
         <v>0.006876937997629257</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01112980040466693</v>
+        <v>0.006844658242281478</v>
       </c>
       <c r="O4" t="n">
         <v>0.006879952603735668</v>
@@ -1834,7 +1834,7 @@
         <v>0.007112836101798209</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01112980040466693</v>
+        <v>0.00708329909134215</v>
       </c>
       <c r="O6" t="n">
         <v>0.007776561365518453</v>
@@ -1922,7 +1922,7 @@
         <v>0.007418096091574411</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01112980040466693</v>
+        <v>0.007385816336226631</v>
       </c>
       <c r="O7" t="n">
         <v>0.007421089037760756</v>
@@ -2010,7 +2010,7 @@
         <v>0.009794913959441503</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01112980040466693</v>
+        <v>0.008845235707048888</v>
       </c>
       <c r="O8" t="n">
         <v>0.00913263914114304</v>
@@ -2098,7 +2098,7 @@
         <v>0.008851132233908158</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01112980040466693</v>
+        <v>0.008818852478560379</v>
       </c>
       <c r="O9" t="n">
         <v>0.009005082523372791</v>
@@ -2518,7 +2518,7 @@
         <v>0.01273280759936471</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03297149078316958</v>
+        <v>0.008085999919316593</v>
       </c>
       <c r="O4" t="n">
         <v>0.007867666557285892</v>
@@ -2694,7 +2694,7 @@
         <v>0.01384390782131861</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03297149078316958</v>
+        <v>0.008391291106145806</v>
       </c>
       <c r="O6" t="n">
         <v>0.00817256947364145</v>
@@ -2782,7 +2782,7 @@
         <v>0.01340985817846996</v>
       </c>
       <c r="N7" t="n">
-        <v>0.03297149078316958</v>
+        <v>0.008763050498421833</v>
       </c>
       <c r="O7" t="n">
         <v>0.008544692991916807</v>
@@ -2870,7 +2870,7 @@
         <v>0.01619666263011435</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03297149078316958</v>
+        <v>0.01045616716394199</v>
       </c>
       <c r="O8" t="n">
         <v>0.01053838870185203</v>
@@ -2958,7 +2958,7 @@
         <v>0.0155590280877256</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03297149078316958</v>
+        <v>0.01091222040767749</v>
       </c>
       <c r="O9" t="n">
         <v>0.010908826026559</v>
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00399456607521661</v>
+        <v>0.003994566075216616</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003521763962937451</v>
+        <v>0.003521763962937453</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004104246026388357</v>
+        <v>0.004104246026388356</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003948763468802637</v>
+        <v>0.003948763468802644</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003950727475349812</v>
+        <v>0.003950727475349819</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003983737821440282</v>
+        <v>0.003983737821440288</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003901777856795476</v>
+        <v>0.003901777856795481</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004020717068126793</v>
+        <v>0.0040207170681268</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004035382589679567</v>
+        <v>0.004035382589679574</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004073223503473232</v>
+        <v>0.004073223503473236</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004064533138609716</v>
+        <v>0.004064533138609721</v>
       </c>
       <c r="M2" t="n">
-        <v>0.004346266327354472</v>
+        <v>0.004346266327354474</v>
       </c>
       <c r="N2" t="n">
         <v>0.003964842312573338</v>
       </c>
       <c r="O2" t="n">
-        <v>0.005726995297872798</v>
+        <v>0.005726995297872796</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003977921493915356</v>
+        <v>0.003977921493915357</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003942433930689932</v>
+        <v>0.003942433930689938</v>
       </c>
       <c r="R2" t="n">
-        <v>0.00390805804771761</v>
+        <v>0.003908058047717617</v>
       </c>
       <c r="S2" t="n">
-        <v>0.004022092996012954</v>
+        <v>0.004022092996012962</v>
       </c>
       <c r="T2" t="n">
-        <v>0.00400557638360073</v>
+        <v>0.004005576383600731</v>
       </c>
       <c r="U2" t="n">
-        <v>0.004177369872237374</v>
+        <v>0.004177369872237376</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003943784428996081</v>
+        <v>0.003943784428996087</v>
       </c>
       <c r="W2" t="n">
-        <v>0.004028736351977564</v>
+        <v>0.004028736351977562</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004443119376221681</v>
+        <v>0.004443119376221692</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.004443832545178131</v>
+        <v>0.004443832545178135</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.004974036989107618</v>
+        <v>0.004974036989107623</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.004058914240346221</v>
+        <v>0.004058914240346227</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.004361701974654029</v>
+        <v>0.00436170197465403</v>
       </c>
     </row>
     <row r="3">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00436666110765296</v>
+        <v>0.004366661107652958</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003132414567038807</v>
+        <v>0.003132414567038808</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00515594073255536</v>
+        <v>0.005155940732555356</v>
       </c>
       <c r="E3" t="n">
-        <v>0.004040778793970113</v>
+        <v>0.004040778793970111</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004057612810175436</v>
+        <v>0.004057612810175433</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004289467390136522</v>
+        <v>0.004289467390136524</v>
       </c>
       <c r="H3" t="n">
         <v>0.00370771278861456</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004559265476039723</v>
+        <v>0.004559265476039721</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004660718088716801</v>
+        <v>0.004660718088716797</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00492622523960201</v>
+        <v>0.004926225239602007</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004868016261145691</v>
+        <v>0.004868016261145678</v>
       </c>
       <c r="M3" t="n">
         <v>0.006871618056570643</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004157904655258587</v>
+        <v>0.004157904655258583</v>
       </c>
       <c r="O3" t="n">
         <v>0.007037997472512392</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004247991143788181</v>
+        <v>0.004247991143788182</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003997421687418658</v>
+        <v>0.003997421687418656</v>
       </c>
       <c r="R3" t="n">
         <v>0.003752564866536732</v>
       </c>
       <c r="S3" t="n">
-        <v>0.004562632950367268</v>
+        <v>0.004562632950367265</v>
       </c>
       <c r="T3" t="n">
-        <v>0.004450481357447488</v>
+        <v>0.004450481357447487</v>
       </c>
       <c r="U3" t="n">
-        <v>0.005693975684289497</v>
+        <v>0.005693975684289502</v>
       </c>
       <c r="V3" t="n">
-        <v>0.004004784462544816</v>
+        <v>0.004004784462544813</v>
       </c>
       <c r="W3" t="n">
-        <v>0.004833854261760803</v>
+        <v>0.004833854261760797</v>
       </c>
       <c r="X3" t="n">
-        <v>0.007577282678540869</v>
+        <v>0.00757728267854087</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.007575037038004701</v>
+        <v>0.007575037038004708</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.005793366436081757</v>
+        <v>0.005793366436081759</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.004828936955748125</v>
+        <v>0.004828936955748124</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.006980201644754007</v>
+        <v>0.006980201644754008</v>
       </c>
     </row>
     <row r="4">
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.007975770326985277</v>
+        <v>0.007975770326985274</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007035780572255179</v>
+        <v>0.007035780572255175</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00921465583074039</v>
+        <v>0.009214655830740383</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00745840881729955</v>
+        <v>0.007458408817299548</v>
       </c>
       <c r="F4" t="n">
-        <v>0.007480593174737519</v>
+        <v>0.007480593174737513</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007853460219338805</v>
+        <v>0.007853460219338802</v>
       </c>
       <c r="H4" t="n">
-        <v>0.006927684715229265</v>
+        <v>0.006927684715229261</v>
       </c>
       <c r="I4" t="n">
-        <v>0.008271157821956936</v>
+        <v>0.008271157821956927</v>
       </c>
       <c r="J4" t="n">
-        <v>0.008433344915236847</v>
+        <v>0.008433344915236844</v>
       </c>
       <c r="K4" t="n">
-        <v>0.008864242163348508</v>
+        <v>0.008864242163348504</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008766080494449812</v>
+        <v>0.008766080494449786</v>
       </c>
       <c r="M4" t="n">
         <v>0.01191288500804202</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02342734401567639</v>
+        <v>0.00764002675432309</v>
       </c>
       <c r="O4" t="n">
-        <v>0.007588601155589952</v>
+        <v>0.007588601155589946</v>
       </c>
       <c r="P4" t="n">
-        <v>0.007787762124301895</v>
+        <v>0.007787762124301894</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.007386913772585122</v>
+        <v>0.007386913772585118</v>
       </c>
       <c r="R4" t="n">
-        <v>0.006998622360725303</v>
+        <v>0.006998622360725297</v>
       </c>
       <c r="S4" t="n">
-        <v>0.008286699560389221</v>
+        <v>0.008286699560389216</v>
       </c>
       <c r="T4" t="n">
-        <v>0.008100136825175979</v>
+        <v>0.008100136825175977</v>
       </c>
       <c r="U4" t="n">
         <v>0.01007105754889803</v>
       </c>
       <c r="V4" t="n">
-        <v>0.007378741925142513</v>
+        <v>0.007378741925142512</v>
       </c>
       <c r="W4" t="n">
-        <v>0.008815423098825782</v>
+        <v>0.008815423098825778</v>
       </c>
       <c r="X4" t="n">
         <v>0.01304238620655057</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.01303106922579695</v>
+        <v>0.01303106922579694</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.007584983642889462</v>
+        <v>0.007584983642889454</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.008702612453742665</v>
+        <v>0.008702612453742655</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.01206924119309313</v>
+        <v>0.01206924119309312</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02761209780596947</v>
+        <v>0.02761209780596929</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01245326177926406</v>
+        <v>0.01245326177926405</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05288625308678496</v>
+        <v>0.05288625308678493</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0189867563415854</v>
+        <v>0.01898675634158539</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02083886043202621</v>
+        <v>0.0208388604320262</v>
       </c>
       <c r="G5" t="n">
         <v>0.02549448151019955</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01077776807629338</v>
+        <v>0.0107777680762934</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03592690879694007</v>
+        <v>0.03592690879694004</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03718672065028883</v>
+        <v>0.03718672065028877</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04238413113682189</v>
+        <v>0.04238413113682186</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04262479409825139</v>
+        <v>0.04262479409825114</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1045759108827802</v>
+        <v>0.1045759108827799</v>
       </c>
       <c r="N5" t="n">
-        <v>0.02342734401567639</v>
+        <v>0.0234273440156764</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02060807100604821</v>
+        <v>0.02060807100604825</v>
       </c>
       <c r="P5" t="n">
-        <v>0.02435072988459288</v>
+        <v>0.02435072988459291</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01866392622131481</v>
+        <v>0.0186639262213148</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01204798601881441</v>
+        <v>0.0120479860188144</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0328578978892877</v>
+        <v>0.03285789788928769</v>
       </c>
       <c r="T5" t="n">
-        <v>0.03252677098952758</v>
+        <v>0.03252677098952756</v>
       </c>
       <c r="U5" t="n">
-        <v>0.06418549885485579</v>
+        <v>0.06418549885485614</v>
       </c>
       <c r="V5" t="n">
-        <v>0.01773092587376963</v>
+        <v>0.01773092587376966</v>
       </c>
       <c r="W5" t="n">
-        <v>0.04399537881621741</v>
+        <v>0.04399537881621735</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1220297315282961</v>
+        <v>0.1220297315282964</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1183707378645816</v>
+        <v>0.1183707378645815</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.02055526951575417</v>
+        <v>0.02055526951575408</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.04203242766514149</v>
+        <v>0.04203242766514147</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1115889521024309</v>
+        <v>0.1115889521024308</v>
       </c>
     </row>
     <row r="6">
@@ -3518,34 +3518,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.009025720763750513</v>
+        <v>0.009025720763750507</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00732771879803092</v>
+        <v>0.007327718798030919</v>
       </c>
       <c r="D6" t="n">
         <v>0.01026460626750562</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008508359254064787</v>
+        <v>0.008508359254064781</v>
       </c>
       <c r="F6" t="n">
-        <v>0.007772531400513262</v>
+        <v>0.007772531400513261</v>
       </c>
       <c r="G6" t="n">
         <v>0.008145398445114544</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00721962294100501</v>
+        <v>0.007219622941005008</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00856309604773268</v>
+        <v>0.008563096047732676</v>
       </c>
       <c r="J6" t="n">
-        <v>0.009483295352002088</v>
+        <v>0.009483295352002083</v>
       </c>
       <c r="K6" t="n">
-        <v>0.009914192600113744</v>
+        <v>0.009914192600113737</v>
       </c>
       <c r="L6" t="n">
         <v>0.009816030931215041</v>
@@ -3554,46 +3554,46 @@
         <v>0.01220482323381776</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02342734401567639</v>
+        <v>0.007937797790489578</v>
       </c>
       <c r="O6" t="n">
-        <v>0.008639860251791439</v>
+        <v>0.008639860251791431</v>
       </c>
       <c r="P6" t="n">
-        <v>0.008839292396593867</v>
+        <v>0.008839292396593861</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.008436864209350355</v>
+        <v>0.008436864209350347</v>
       </c>
       <c r="R6" t="n">
-        <v>0.007290560586501047</v>
+        <v>0.007290560586501044</v>
       </c>
       <c r="S6" t="n">
-        <v>0.009336649997154459</v>
+        <v>0.009336649997154453</v>
       </c>
       <c r="T6" t="n">
-        <v>0.008392075050951726</v>
+        <v>0.008392075050951721</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01038236832686443</v>
+        <v>0.01038236832686444</v>
       </c>
       <c r="V6" t="n">
-        <v>0.008428692361907748</v>
+        <v>0.008428692361907745</v>
       </c>
       <c r="W6" t="n">
-        <v>0.009866672309704087</v>
+        <v>0.009866672309704084</v>
       </c>
       <c r="X6" t="n">
         <v>0.01333432443232632</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01336600011451571</v>
+        <v>0.01336600011451572</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.008634934079654693</v>
+        <v>0.008634934079654688</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.009752562890507901</v>
+        <v>0.009752562890507896</v>
       </c>
       <c r="AB6" t="n">
         <v>0.01242645231025853</v>
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.008598824332920202</v>
+        <v>0.008598824332920196</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007658834578190098</v>
+        <v>0.007658834578190095</v>
       </c>
       <c r="D7" t="n">
-        <v>0.009837709836675311</v>
+        <v>0.009837709836675309</v>
       </c>
       <c r="E7" t="n">
-        <v>0.008081462823234471</v>
+        <v>0.00808146282323447</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008103647180672436</v>
+        <v>0.008103647180672434</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008476514225273729</v>
+        <v>0.008476514225273724</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007550738721164185</v>
+        <v>0.007550738721164183</v>
       </c>
       <c r="I7" t="n">
-        <v>0.008894211827891855</v>
+        <v>0.008894211827891851</v>
       </c>
       <c r="J7" t="n">
-        <v>0.009056398921171771</v>
+        <v>0.009056398921171766</v>
       </c>
       <c r="K7" t="n">
-        <v>0.009487296169283434</v>
+        <v>0.00948729616928343</v>
       </c>
       <c r="L7" t="n">
-        <v>0.009389134500384734</v>
+        <v>0.009389134500384718</v>
       </c>
       <c r="M7" t="n">
         <v>0.01253593901397694</v>
       </c>
       <c r="N7" t="n">
-        <v>0.02342734401567639</v>
+        <v>0.008263080760258012</v>
       </c>
       <c r="O7" t="n">
-        <v>0.008211632772280252</v>
+        <v>0.00821163277228025</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0084107937409922</v>
+        <v>0.008410793740992196</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.008009967778520045</v>
+        <v>0.008009967778520042</v>
       </c>
       <c r="R7" t="n">
-        <v>0.007621676366660224</v>
+        <v>0.00762167636666022</v>
       </c>
       <c r="S7" t="n">
-        <v>0.008909753566324145</v>
+        <v>0.008909753566324138</v>
       </c>
       <c r="T7" t="n">
-        <v>0.008723190831110899</v>
+        <v>0.008723190831110896</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01071268844020142</v>
+        <v>0.01071268844020144</v>
       </c>
       <c r="V7" t="n">
-        <v>0.008001795931077443</v>
+        <v>0.00800179593107744</v>
       </c>
       <c r="W7" t="n">
-        <v>0.009438477104760696</v>
+        <v>0.009438477104760689</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01366544021248548</v>
+        <v>0.01366544021248547</v>
       </c>
       <c r="Y7" t="n">
         <v>0.01367349578392253</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.008208037648824386</v>
+        <v>0.008208037648824374</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.009325666459677589</v>
+        <v>0.009325666459677581</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01269229519902805</v>
+        <v>0.01269229519902804</v>
       </c>
     </row>
     <row r="8">
@@ -3703,13 +3703,13 @@
         <v>0.01240849638201489</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009959950095593305</v>
+        <v>0.009959950095593301</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009576819613486573</v>
+        <v>0.009576819613486571</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01131689836083738</v>
+        <v>0.01131689836083737</v>
       </c>
       <c r="H8" t="n">
         <v>0.01012152526650376</v>
@@ -3724,22 +3724,22 @@
         <v>0.012058082714623</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0119599210457243</v>
+        <v>0.01195992104572429</v>
       </c>
       <c r="M8" t="n">
         <v>0.01510672555931704</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02342734401567639</v>
+        <v>0.009826022262814347</v>
       </c>
       <c r="O8" t="n">
         <v>0.01005156123279826</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01018283149331646</v>
+        <v>0.01018283149331645</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.009025077759218327</v>
+        <v>0.009025077759218325</v>
       </c>
       <c r="R8" t="n">
         <v>0.0101924629119998</v>
@@ -3748,13 +3748,13 @@
         <v>0.01148054011166371</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01129397737645048</v>
+        <v>0.01129397737645047</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01264907841510329</v>
+        <v>0.01264907841510328</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01021656692093233</v>
+        <v>0.01021656692093234</v>
       </c>
       <c r="W8" t="n">
         <v>0.01200951916966428</v>
@@ -3763,7 +3763,7 @@
         <v>0.01479971285808417</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01753598117388911</v>
+        <v>0.0175359811738891</v>
       </c>
       <c r="Z8" t="n">
         <v>0.009454508415236002</v>
@@ -3772,7 +3772,7 @@
         <v>0.01189645300501717</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01662121233984539</v>
+        <v>0.01662121233984538</v>
       </c>
     </row>
     <row r="9">
@@ -3788,49 +3788,49 @@
         <v>0.009506201286091599</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01168507654457682</v>
+        <v>0.01168507654457681</v>
       </c>
       <c r="E9" t="n">
-        <v>0.009797678977897883</v>
+        <v>0.009797678977897876</v>
       </c>
       <c r="F9" t="n">
-        <v>0.008641041278719607</v>
+        <v>0.008641041278719605</v>
       </c>
       <c r="G9" t="n">
         <v>0.01032388021756239</v>
       </c>
       <c r="H9" t="n">
-        <v>0.009398105429065695</v>
+        <v>0.009398105429065688</v>
       </c>
       <c r="I9" t="n">
         <v>0.01074157853579336</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01090376562907328</v>
+        <v>0.01090376562907327</v>
       </c>
       <c r="K9" t="n">
         <v>0.01133466287718493</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01123650120828624</v>
+        <v>0.01123650120828622</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01438330572187847</v>
+        <v>0.01438330572187845</v>
       </c>
       <c r="N9" t="n">
-        <v>0.02342734401567639</v>
+        <v>0.01011044746815952</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01024733853940965</v>
+        <v>0.01024733853940966</v>
       </c>
       <c r="P9" t="n">
-        <v>0.01048745530850654</v>
+        <v>0.01048745530850653</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.009857333770808711</v>
+        <v>0.00985733377080871</v>
       </c>
       <c r="R9" t="n">
-        <v>0.009469043074561726</v>
+        <v>0.009469043074561721</v>
       </c>
       <c r="S9" t="n">
         <v>0.01075712027422565</v>
@@ -3839,7 +3839,7 @@
         <v>0.0105705575390124</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01256085081492512</v>
+        <v>0.01256085081492514</v>
       </c>
       <c r="V9" t="n">
         <v>0.01050490987070329</v>
@@ -3848,19 +3848,19 @@
         <v>0.01128584381266221</v>
       </c>
       <c r="X9" t="n">
-        <v>0.015512806920387</v>
+        <v>0.01551280692038699</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.01552086249182404</v>
+        <v>0.01552086249182403</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.009712799276957137</v>
+        <v>0.009712799276957125</v>
       </c>
       <c r="AA9" t="n">
         <v>0.01117303316757909</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.01453966190692955</v>
+        <v>0.01453966190692954</v>
       </c>
     </row>
   </sheetData>
@@ -4032,79 +4032,79 @@
         <v>0.003480025254382845</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004035819590429869</v>
+        <v>0.004035819590429873</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00392684247977157</v>
+        <v>0.003926842479771572</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003955734916750234</v>
+        <v>0.003955734916750235</v>
       </c>
       <c r="G2" t="n">
         <v>0.003968648396365589</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003897944013643519</v>
+        <v>0.003897944013643523</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004016300752072319</v>
+        <v>0.004016300752072321</v>
       </c>
       <c r="J2" t="n">
         <v>0.004026582628959283</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004102489866327038</v>
+        <v>0.00410248986632704</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004031728522204709</v>
+        <v>0.004031728522204714</v>
       </c>
       <c r="M2" t="n">
-        <v>0.004262399105687043</v>
+        <v>0.004262399105687042</v>
       </c>
       <c r="N2" t="n">
         <v>0.003935238995352395</v>
       </c>
       <c r="O2" t="n">
-        <v>0.005687728720697316</v>
+        <v>0.005687728720697318</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003960764707794986</v>
+        <v>0.003960764707794989</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003939220700154204</v>
+        <v>0.003939220700154207</v>
       </c>
       <c r="R2" t="n">
-        <v>0.00392453354749563</v>
+        <v>0.003924533547495628</v>
       </c>
       <c r="S2" t="n">
-        <v>0.004010786022564048</v>
+        <v>0.00401078602256405</v>
       </c>
       <c r="T2" t="n">
         <v>0.004001622626480112</v>
       </c>
       <c r="U2" t="n">
-        <v>0.004086888749550316</v>
+        <v>0.004086888749550313</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003970234574966036</v>
+        <v>0.003970234574966038</v>
       </c>
       <c r="W2" t="n">
-        <v>0.003901051632388437</v>
+        <v>0.003901051632388439</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004550956177447636</v>
+        <v>0.004550956177447637</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.004741848481448845</v>
+        <v>0.004741848481448843</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.004955867350207296</v>
+        <v>0.004955867350207294</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.004066742485299926</v>
+        <v>0.004066742485299928</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.004302847102272585</v>
+        <v>0.004302847102272584</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0042526571457982</v>
+        <v>0.004252657145798201</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003071644579769124</v>
+        <v>0.003071644579769125</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00469494195301362</v>
+        <v>0.004694941953013611</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003914500343359151</v>
+        <v>0.003914500343359146</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004124129203694277</v>
+        <v>0.004124129203694275</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004212078431478546</v>
+        <v>0.004212078431478547</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003711217665844782</v>
+        <v>0.003711217665844779</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004557684488400047</v>
+        <v>0.004557684488400045</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0046274812617572</v>
+        <v>0.004627481261757199</v>
       </c>
       <c r="K3" t="n">
         <v>0.005165158207490578</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004662816368262748</v>
+        <v>0.004662816368262747</v>
       </c>
       <c r="M3" t="n">
-        <v>0.006300052859725807</v>
+        <v>0.006300052859725805</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003977285082549363</v>
+        <v>0.003977285082549359</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0068792429058345</v>
+        <v>0.006879242905834499</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004155964590499598</v>
+        <v>0.004155964590499594</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.004004880797833441</v>
+        <v>0.00400488079783344</v>
       </c>
       <c r="R3" t="n">
         <v>0.003901670646472604</v>
       </c>
       <c r="S3" t="n">
-        <v>0.004512383555498769</v>
+        <v>0.00451238355549877</v>
       </c>
       <c r="T3" t="n">
-        <v>0.004453181459585457</v>
+        <v>0.004453181459585459</v>
       </c>
       <c r="U3" t="n">
-        <v>0.005672729110890629</v>
+        <v>0.005672729110890631</v>
       </c>
       <c r="V3" t="n">
-        <v>0.004222818354617452</v>
+        <v>0.004222818354617458</v>
       </c>
       <c r="W3" t="n">
-        <v>0.004471958408658457</v>
+        <v>0.004471958408658458</v>
       </c>
       <c r="X3" t="n">
         <v>0.008370924285599919</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.009739148290660778</v>
+        <v>0.009739148290660773</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.005721245459328413</v>
+        <v>0.005721245459328412</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.004916087463002086</v>
+        <v>0.004916087463002084</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.006589882115844948</v>
+        <v>0.006589882115844945</v>
       </c>
     </row>
     <row r="4">
@@ -4202,82 +4202,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.007809545180607812</v>
+        <v>0.007809545180607822</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007051484841024355</v>
+        <v>0.007051484841024359</v>
       </c>
       <c r="D4" t="n">
-        <v>0.008503958956167155</v>
+        <v>0.008503958956167158</v>
       </c>
       <c r="E4" t="n">
-        <v>0.007273012359333957</v>
+        <v>0.007273012359333963</v>
       </c>
       <c r="F4" t="n">
-        <v>0.007599365726185602</v>
+        <v>0.007599365726185611</v>
       </c>
       <c r="G4" t="n">
         <v>0.007745229418935152</v>
       </c>
       <c r="H4" t="n">
-        <v>0.006946590890466397</v>
+        <v>0.006946590890466399</v>
       </c>
       <c r="I4" t="n">
-        <v>0.008283484697809288</v>
+        <v>0.008283484697809294</v>
       </c>
       <c r="J4" t="n">
         <v>0.008396606771908817</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009257030392267804</v>
+        <v>0.00925703039226781</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008457748458579569</v>
+        <v>0.008457748458579585</v>
       </c>
       <c r="M4" t="n">
         <v>0.01103604525879262</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01821224625945391</v>
+        <v>0.007367854865407341</v>
       </c>
       <c r="O4" t="n">
-        <v>0.007392097510920871</v>
+        <v>0.007392097510920872</v>
       </c>
       <c r="P4" t="n">
-        <v>0.007656179529854276</v>
+        <v>0.007656179529854278</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.007412830052818473</v>
+        <v>0.007412830052818475</v>
       </c>
       <c r="R4" t="n">
-        <v>0.007246931907115832</v>
+        <v>0.007246931907115833</v>
       </c>
       <c r="S4" t="n">
-        <v>0.008221193291112492</v>
+        <v>0.008221193291112495</v>
       </c>
       <c r="T4" t="n">
-        <v>0.008117688516973911</v>
+        <v>0.008117688516973916</v>
       </c>
       <c r="U4" t="n">
         <v>0.01034837072050078</v>
       </c>
       <c r="V4" t="n">
-        <v>0.007742754709384797</v>
+        <v>0.007742754709384793</v>
       </c>
       <c r="W4" t="n">
-        <v>0.00850287282546331</v>
+        <v>0.008502872825463312</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01432266368107064</v>
+        <v>0.01432266368107065</v>
       </c>
       <c r="Y4" t="n">
         <v>0.01646531844414828</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.007498151554938336</v>
+        <v>0.007498151554938345</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.008853247278958863</v>
+        <v>0.008853247278958865</v>
       </c>
       <c r="AB4" t="n">
         <v>0.01147339711442709</v>
@@ -4290,37 +4290,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02410140197170515</v>
+        <v>0.02410140197170524</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01241377558846662</v>
+        <v>0.01241377558846663</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03820670003507504</v>
+        <v>0.0382067000350749</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01505351236627349</v>
+        <v>0.01505351236627351</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02259902544226457</v>
+        <v>0.02259902544226453</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02299458998702835</v>
+        <v>0.02299458998702825</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01081784272595764</v>
+        <v>0.01081784272595765</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03536932857122994</v>
+        <v>0.03536932857122993</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03556232188918421</v>
+        <v>0.03556232188918416</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04861730493940938</v>
+        <v>0.04861730493940952</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03587232627982848</v>
+        <v>0.03587232627982847</v>
       </c>
       <c r="M5" t="n">
         <v>0.08444089321485711</v>
@@ -4329,46 +4329,46 @@
         <v>0.01821224625945391</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01728207843246081</v>
+        <v>0.01728207843246073</v>
       </c>
       <c r="P5" t="n">
-        <v>0.02149859255997007</v>
+        <v>0.02149859255996994</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01858177242066295</v>
+        <v>0.01858177242066292</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01648337720003967</v>
+        <v>0.01648337720003966</v>
       </c>
       <c r="S5" t="n">
-        <v>0.03118829386816924</v>
+        <v>0.03118829386816925</v>
       </c>
       <c r="T5" t="n">
-        <v>0.03256934829970641</v>
+        <v>0.03256934829970643</v>
       </c>
       <c r="U5" t="n">
-        <v>0.06640566400721361</v>
+        <v>0.06640566400721362</v>
       </c>
       <c r="V5" t="n">
-        <v>0.02299014399485122</v>
+        <v>0.02299014399485125</v>
       </c>
       <c r="W5" t="n">
-        <v>0.03818914399193571</v>
+        <v>0.03818914399193572</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1408230641245804</v>
+        <v>0.1408230641245802</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1819733633418557</v>
+        <v>0.1819733633418559</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01841248699824168</v>
+        <v>0.01841248699824172</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.04461622557243106</v>
+        <v>0.04461622557243105</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.09827010538445492</v>
+        <v>0.09827010538445477</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.008112367246076063</v>
+        <v>0.008112367246076054</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007354306906492597</v>
+        <v>0.007354306906492594</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009540329555873072</v>
+        <v>0.009540329555873075</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008309382959039872</v>
+        <v>0.008309382959039879</v>
       </c>
       <c r="F6" t="n">
-        <v>0.007902187791653852</v>
+        <v>0.007902187791653843</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008048051484403402</v>
+        <v>0.008048051484403386</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007982961490172302</v>
+        <v>0.00798296149017232</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008586306763277533</v>
+        <v>0.00858630676327753</v>
       </c>
       <c r="J6" t="n">
-        <v>0.009432977371614736</v>
+        <v>0.009432977371614738</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01029340099197373</v>
+        <v>0.01029340099197374</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008760570524047828</v>
+        <v>0.008760570524047821</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01133886732426087</v>
+        <v>0.01133886732426086</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01821224625945391</v>
+        <v>0.007680201604957484</v>
       </c>
       <c r="O6" t="n">
-        <v>0.007737386998057485</v>
+        <v>0.00773738699805751</v>
       </c>
       <c r="P6" t="n">
-        <v>0.008695712688338218</v>
+        <v>0.008695712688338221</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.008449200652524384</v>
+        <v>0.008449200652524393</v>
       </c>
       <c r="R6" t="n">
-        <v>0.008283302506821752</v>
+        <v>0.008283302506821761</v>
       </c>
       <c r="S6" t="n">
-        <v>0.008524015356580731</v>
+        <v>0.008524015356580728</v>
       </c>
       <c r="T6" t="n">
-        <v>0.009154059116679832</v>
+        <v>0.009154059116679828</v>
       </c>
       <c r="U6" t="n">
         <v>0.01139830294562106</v>
       </c>
       <c r="V6" t="n">
-        <v>0.00804557677485304</v>
+        <v>0.008045576774853019</v>
       </c>
       <c r="W6" t="n">
-        <v>0.008836390526106594</v>
+        <v>0.008836390526106599</v>
       </c>
       <c r="X6" t="n">
         <v>0.01462548574653887</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01681419219972051</v>
+        <v>0.01681419219972048</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.007800973620406578</v>
+        <v>0.00780097362040658</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.009889617878664771</v>
+        <v>0.009889617878664774</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01179955270923668</v>
+        <v>0.0117995527092367</v>
       </c>
     </row>
     <row r="7">
@@ -4469,76 +4469,76 @@
         <v>0.008430049220740954</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007671988881157491</v>
+        <v>0.007671988881157494</v>
       </c>
       <c r="D7" t="n">
         <v>0.009124462996300292</v>
       </c>
       <c r="E7" t="n">
-        <v>0.007893516399467093</v>
+        <v>0.007893516399467098</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008219869766318742</v>
+        <v>0.008219869766318749</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008365733459068294</v>
+        <v>0.008365733459068291</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007567094930599537</v>
+        <v>0.007567094930599534</v>
       </c>
       <c r="I7" t="n">
-        <v>0.008903988737942419</v>
+        <v>0.008903988737942426</v>
       </c>
       <c r="J7" t="n">
-        <v>0.009017110812041958</v>
+        <v>0.009017110812041951</v>
       </c>
       <c r="K7" t="n">
-        <v>0.009877534432400945</v>
+        <v>0.00987753443240095</v>
       </c>
       <c r="L7" t="n">
-        <v>0.009078252498712707</v>
+        <v>0.009078252498712719</v>
       </c>
       <c r="M7" t="n">
         <v>0.01165654929892577</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01821224625945391</v>
+        <v>0.007988358905540484</v>
       </c>
       <c r="O7" t="n">
-        <v>0.008012578918186707</v>
+        <v>0.008012578918186708</v>
       </c>
       <c r="P7" t="n">
-        <v>0.008276660937120105</v>
+        <v>0.008276660937120104</v>
       </c>
       <c r="Q7" t="n">
         <v>0.00803333409295161</v>
       </c>
       <c r="R7" t="n">
-        <v>0.007867435947248974</v>
+        <v>0.007867435947248971</v>
       </c>
       <c r="S7" t="n">
-        <v>0.008841697331245632</v>
+        <v>0.008841697331245631</v>
       </c>
       <c r="T7" t="n">
-        <v>0.008738192557107052</v>
+        <v>0.008738192557107055</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01098142567599259</v>
+        <v>0.01098142567599258</v>
       </c>
       <c r="V7" t="n">
-        <v>0.008363258749517936</v>
+        <v>0.008363258749517927</v>
       </c>
       <c r="W7" t="n">
-        <v>0.009123376865596462</v>
+        <v>0.009123376865596463</v>
       </c>
       <c r="X7" t="n">
         <v>0.01494316772120376</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01709938410969578</v>
+        <v>0.01709938410969577</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.008118655595071475</v>
+        <v>0.008118655595071481</v>
       </c>
       <c r="AA7" t="n">
         <v>0.009473751319091993</v>
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.009694356854384946</v>
+        <v>0.009694356854384948</v>
       </c>
       <c r="C8" t="n">
         <v>0.01022936809857665</v>
@@ -4566,13 +4566,13 @@
         <v>0.009762373141755511</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009685622840266235</v>
+        <v>0.009685622840266231</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01119123949295946</v>
+        <v>0.01119123949295944</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0101244741480187</v>
+        <v>0.01012447414801869</v>
       </c>
       <c r="I8" t="n">
         <v>0.01146136795536159</v>
@@ -4584,34 +4584,34 @@
         <v>0.0124349136498201</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01163563171613187</v>
+        <v>0.01163563171613188</v>
       </c>
       <c r="M8" t="n">
         <v>0.01421392851634566</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01821224625945391</v>
+        <v>0.009543391319365794</v>
       </c>
       <c r="O8" t="n">
-        <v>0.00984308756973038</v>
+        <v>0.009843087569730374</v>
       </c>
       <c r="P8" t="n">
         <v>0.01003964925422312</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.009043523647471182</v>
+        <v>0.009043523647471186</v>
       </c>
       <c r="R8" t="n">
         <v>0.01042481516466814</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01139907654866479</v>
+        <v>0.01139907654866478</v>
       </c>
       <c r="T8" t="n">
         <v>0.01129557177452621</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01290791888628442</v>
+        <v>0.01290791888628441</v>
       </c>
       <c r="V8" t="n">
         <v>0.01056637742200253</v>
@@ -4620,16 +4620,16 @@
         <v>0.01168101020861469</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01607186985573823</v>
+        <v>0.01607186985573822</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.02094112501988353</v>
+        <v>0.02094112501988351</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.009358943760185024</v>
+        <v>0.009358943760185028</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01203113053651116</v>
+        <v>0.01203113053651115</v>
       </c>
       <c r="AB8" t="n">
         <v>0.01600200176610372</v>
@@ -4645,16 +4645,16 @@
         <v>0.009614233376381382</v>
       </c>
       <c r="C9" t="n">
-        <v>0.009396829081260662</v>
+        <v>0.00939682908126066</v>
       </c>
       <c r="D9" t="n">
         <v>0.01084930319640347</v>
       </c>
       <c r="E9" t="n">
-        <v>0.009493574934111149</v>
+        <v>0.00949357493411114</v>
       </c>
       <c r="F9" t="n">
-        <v>0.008698350998172613</v>
+        <v>0.008698350998172616</v>
       </c>
       <c r="G9" t="n">
         <v>0.01009057306675006</v>
@@ -4666,7 +4666,7 @@
         <v>0.01062882893804559</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01074195101214514</v>
+        <v>0.01074195101214513</v>
       </c>
       <c r="K9" t="n">
         <v>0.01160237463250412</v>
@@ -4675,19 +4675,19 @@
         <v>0.01080309269881589</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01338138949902894</v>
+        <v>0.01338138949902892</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01821224625945391</v>
+        <v>0.009713199105643645</v>
       </c>
       <c r="O9" t="n">
-        <v>0.009916613667614399</v>
+        <v>0.009916613667614394</v>
       </c>
       <c r="P9" t="n">
         <v>0.01021966263314634</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.00975817370063338</v>
+        <v>0.009758173700633378</v>
       </c>
       <c r="R9" t="n">
         <v>0.009592276147352139</v>
@@ -4696,7 +4696,7 @@
         <v>0.0105665375313488</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01046303275721022</v>
+        <v>0.01046303275721023</v>
       </c>
       <c r="U9" t="n">
         <v>0.01270727658615145</v>
@@ -4705,22 +4705,22 @@
         <v>0.01071200266889507</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01084821706569962</v>
+        <v>0.01084821706569963</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01666800792130697</v>
+        <v>0.01666800792130696</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.01882422430979895</v>
+        <v>0.01882422430979896</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.00951752804213094</v>
+        <v>0.009517528042130944</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.01119859151919516</v>
+        <v>0.01119859151919517</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0138187413546634</v>
+        <v>0.01381874135466341</v>
       </c>
     </row>
   </sheetData>
@@ -5098,7 +5098,7 @@
         <v>0.008606384543527074</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02269325332246965</v>
+        <v>0.007482753980103798</v>
       </c>
       <c r="O4" t="n">
         <v>0.006964912079475916</v>
@@ -5274,7 +5274,7 @@
         <v>0.009613410966360578</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02269325332246965</v>
+        <v>0.00773984539495814</v>
       </c>
       <c r="O6" t="n">
         <v>0.007975578185592578</v>
@@ -5362,7 +5362,7 @@
         <v>0.009210089178133412</v>
       </c>
       <c r="N7" t="n">
-        <v>0.02269325332246965</v>
+        <v>0.008086458614710145</v>
       </c>
       <c r="O7" t="n">
         <v>0.00756859382205576</v>
@@ -5450,7 +5450,7 @@
         <v>0.0118318410107297</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02269325332246965</v>
+        <v>0.009692948196035641</v>
       </c>
       <c r="O8" t="n">
         <v>0.009454109177431665</v>
@@ -5538,7 +5538,7 @@
         <v>0.01102794398707858</v>
       </c>
       <c r="N9" t="n">
-        <v>0.02269325332246965</v>
+        <v>0.0099043134236553</v>
       </c>
       <c r="O9" t="n">
         <v>0.009570779020176702</v>
@@ -5952,13 +5952,13 @@
         <v>0.006847472074170339</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006881505976449001</v>
+        <v>0.006881505976449</v>
       </c>
       <c r="M4" t="n">
         <v>0.006792620463227715</v>
       </c>
       <c r="N4" t="n">
-        <v>0.011649980752903</v>
+        <v>0.00687849064133627</v>
       </c>
       <c r="O4" t="n">
         <v>0.006898360300326566</v>
@@ -6134,7 +6134,7 @@
         <v>0.007690416536654874</v>
       </c>
       <c r="N6" t="n">
-        <v>0.011649980752903</v>
+        <v>0.007112810370367884</v>
       </c>
       <c r="O6" t="n">
         <v>0.007797318576701464</v>
@@ -6222,7 +6222,7 @@
         <v>0.007329764760152684</v>
       </c>
       <c r="N7" t="n">
-        <v>0.011649980752903</v>
+        <v>0.007415634938261235</v>
       </c>
       <c r="O7" t="n">
         <v>0.007435483032827185</v>
@@ -6310,7 +6310,7 @@
         <v>0.009697491225079315</v>
       </c>
       <c r="N8" t="n">
-        <v>0.011649980752903</v>
+        <v>0.00887027827383464</v>
       </c>
       <c r="O8" t="n">
         <v>0.009141071104954863</v>
@@ -6398,7 +6398,7 @@
         <v>0.008843132808163583</v>
       </c>
       <c r="N9" t="n">
-        <v>0.011649980752903</v>
+        <v>0.00892900298627214</v>
       </c>
       <c r="O9" t="n">
         <v>0.009105199777139656</v>
@@ -6818,7 +6818,7 @@
         <v>0.00678977096611211</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0106513090211263</v>
+        <v>0.006818053446273393</v>
       </c>
       <c r="O4" t="n">
         <v>0.006989611407279073</v>
@@ -6994,7 +6994,7 @@
         <v>0.007677987044937719</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0106513090211263</v>
+        <v>0.007055388772528804</v>
       </c>
       <c r="O6" t="n">
         <v>0.007259945487928248</v>
@@ -7082,7 +7082,7 @@
         <v>0.007324987033529811</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0106513090211263</v>
+        <v>0.007353269513691091</v>
       </c>
       <c r="O7" t="n">
         <v>0.007524805736446928</v>
@@ -7170,7 +7170,7 @@
         <v>0.009686230282491541</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0106513090211263</v>
+        <v>0.008804383037545112</v>
       </c>
       <c r="O8" t="n">
         <v>0.009226052549556722</v>
@@ -7258,7 +7258,7 @@
         <v>0.008750571644569596</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0106513090211263</v>
+        <v>0.008778854124730874</v>
       </c>
       <c r="O9" t="n">
         <v>0.009100198209960228</v>
@@ -7678,7 +7678,7 @@
         <v>0.01250627554421347</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0363615153000075</v>
+        <v>0.008237274614518874</v>
       </c>
       <c r="O4" t="n">
         <v>0.007466449528530761</v>
@@ -7854,7 +7854,7 @@
         <v>0.0127869179898857</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0363615153000075</v>
+        <v>0.00852268119522415</v>
       </c>
       <c r="O6" t="n">
         <v>0.008549301707330642</v>
@@ -7942,7 +7942,7 @@
         <v>0.01316286947106779</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0363615153000075</v>
+        <v>0.008893868541373209</v>
       </c>
       <c r="O7" t="n">
         <v>0.008123019797841484</v>
@@ -8030,7 +8030,7 @@
         <v>0.01590511919288897</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0363615153000075</v>
+        <v>0.01056368234788048</v>
       </c>
       <c r="O8" t="n">
         <v>0.01008757196321063</v>
@@ -8118,7 +8118,7 @@
         <v>0.01524332078359997</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0363615153000075</v>
+        <v>0.01097431985390537</v>
       </c>
       <c r="O9" t="n">
         <v>0.01041163275689283</v>
@@ -8538,7 +8538,7 @@
         <v>0.007286656666863549</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01273869717951994</v>
+        <v>0.006986561471939058</v>
       </c>
       <c r="O4" t="n">
         <v>0.006922439247107543</v>
@@ -8714,7 +8714,7 @@
         <v>0.007523534887107643</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01273869717951994</v>
+        <v>0.007226406434760077</v>
       </c>
       <c r="O6" t="n">
         <v>0.008039528252794415</v>
@@ -8802,7 +8802,7 @@
         <v>0.007855322786478039</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01273869717951994</v>
+        <v>0.007555227591553552</v>
       </c>
       <c r="O7" t="n">
         <v>0.007491083791190553</v>
@@ -8890,7 +8890,7 @@
         <v>0.01033392356405863</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01273869717951994</v>
+        <v>0.009074073495203739</v>
       </c>
       <c r="O8" t="n">
         <v>0.009273700243139867</v>
@@ -8978,7 +8978,7 @@
         <v>0.009530926081790705</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01273869717951994</v>
+        <v>0.009230830886866213</v>
       </c>
       <c r="O9" t="n">
         <v>0.009337848360318014</v>

--- a/Results/Phase 2/Ammonia/ammonia acidification results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia acidification results.xlsx
@@ -586,67 +586,67 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004116316214163042</v>
+        <v>0.004116316214163046</v>
       </c>
       <c r="C2" t="n">
         <v>0.003592553314559209</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004126324691716738</v>
+        <v>0.00412632469171674</v>
       </c>
       <c r="E2" t="n">
         <v>0.004013536159650488</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004050125238621357</v>
+        <v>0.00405012523862136</v>
       </c>
       <c r="G2" t="n">
-        <v>0.004053526052125667</v>
+        <v>0.004053526052125668</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004064498810041619</v>
+        <v>0.00406449881004162</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004125614415330573</v>
+        <v>0.004125614415330574</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004101922240287673</v>
+        <v>0.004101922240287679</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004213500959104579</v>
+        <v>0.004213500959104581</v>
       </c>
       <c r="L2" t="n">
         <v>0.004172241513833184</v>
       </c>
       <c r="M2" t="n">
-        <v>0.004519596152194601</v>
+        <v>0.004519596152194602</v>
       </c>
       <c r="N2" t="n">
-        <v>0.004137162154417322</v>
+        <v>0.004137162154417323</v>
       </c>
       <c r="O2" t="n">
         <v>0.005896372691256779</v>
       </c>
       <c r="P2" t="n">
-        <v>0.00403402015700444</v>
+        <v>0.004034020157004442</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.004039105312079051</v>
+        <v>0.00403910531207905</v>
       </c>
       <c r="R2" t="n">
-        <v>0.004041655597622013</v>
+        <v>0.004041655597622014</v>
       </c>
       <c r="S2" t="n">
-        <v>0.004095122440217853</v>
+        <v>0.004095122440217855</v>
       </c>
       <c r="T2" t="n">
-        <v>0.00412415682923042</v>
+        <v>0.004124156829230421</v>
       </c>
       <c r="U2" t="n">
-        <v>0.004359513622554973</v>
+        <v>0.004359513622554978</v>
       </c>
       <c r="V2" t="n">
-        <v>0.004016337980127826</v>
+        <v>0.004016337980127827</v>
       </c>
       <c r="W2" t="n">
         <v>0.00416948784082571</v>
@@ -655,10 +655,10 @@
         <v>0.004182283750630091</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.004263574551906475</v>
+        <v>0.004263574551906476</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.005068054346676956</v>
+        <v>0.005068054346676957</v>
       </c>
       <c r="AA2" t="n">
         <v>0.004168258678017678</v>
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004873172513615616</v>
+        <v>0.004917637951826812</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003263481022465203</v>
+        <v>0.003273866907221563</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004953383440213432</v>
+        <v>0.005001063185798485</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00414281042244523</v>
+        <v>0.004161427049361925</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004408996562734898</v>
+        <v>0.004437458079730133</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004427888049957835</v>
+        <v>0.00445666945139515</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004513004398341486</v>
+        <v>0.00454519139035433</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004949201192657067</v>
+        <v>0.004996786908081359</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004775480951717598</v>
+        <v>0.004816689506029475</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005576519605993596</v>
+        <v>0.005646240008697319</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005276783998050813</v>
+        <v>0.005335592132354951</v>
       </c>
       <c r="M3" t="n">
-        <v>0.007746253868559221</v>
+        <v>0.007893308181451009</v>
       </c>
       <c r="N3" t="n">
-        <v>0.005028578229170426</v>
+        <v>0.005078803734836041</v>
       </c>
       <c r="O3" t="n">
-        <v>0.007554716489297571</v>
+        <v>0.007587429646965555</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004288607589854999</v>
+        <v>0.00431245252437644</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.004328161446954817</v>
+        <v>0.004353631434663234</v>
       </c>
       <c r="R3" t="n">
-        <v>0.004348314360750659</v>
+        <v>0.004374591127923567</v>
       </c>
       <c r="S3" t="n">
-        <v>0.004724232994817289</v>
+        <v>0.004763516184597584</v>
       </c>
       <c r="T3" t="n">
-        <v>0.004938168739891872</v>
+        <v>0.004985326996845051</v>
       </c>
       <c r="U3" t="n">
-        <v>0.006367645191028866</v>
+        <v>0.006462346532497043</v>
       </c>
       <c r="V3" t="n">
-        <v>0.004162775103058753</v>
+        <v>0.004182273448174562</v>
       </c>
       <c r="W3" t="n">
-        <v>0.005233924444343134</v>
+        <v>0.005291034054078483</v>
       </c>
       <c r="X3" t="n">
-        <v>0.005352639995896313</v>
+        <v>0.005414471813471917</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.005929633346559138</v>
+        <v>0.006011685787360651</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.005996326383121189</v>
+        <v>0.006020260661684449</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.005249729461995022</v>
+        <v>0.005307675569994174</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.007398526987485315</v>
+        <v>0.007532450405297673</v>
       </c>
     </row>
     <row r="4">
@@ -771,61 +771,61 @@
         <v>0.008906877323003572</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0076328789680271</v>
+        <v>0.007632878968027098</v>
       </c>
       <c r="F4" t="n">
         <v>0.008046169446811009</v>
       </c>
       <c r="G4" t="n">
-        <v>0.008084583199793714</v>
+        <v>0.008084583199793716</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008208525548172405</v>
+        <v>0.008208525548172403</v>
       </c>
       <c r="I4" t="n">
         <v>0.008898854424478568</v>
       </c>
       <c r="J4" t="n">
-        <v>0.008628198911131786</v>
+        <v>0.008628198911131788</v>
       </c>
       <c r="K4" t="n">
         <v>0.009891573366213538</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009425528951590533</v>
+        <v>0.009425528951590543</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01330258782769781</v>
+        <v>0.0133025878276978</v>
       </c>
       <c r="N4" t="n">
-        <v>0.00902929144968583</v>
+        <v>0.009029291449685834</v>
       </c>
       <c r="O4" t="n">
-        <v>0.00826443199361636</v>
+        <v>0.008264431993616357</v>
       </c>
       <c r="P4" t="n">
-        <v>0.007864255141244367</v>
+        <v>0.007864255141244362</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.007921694307098945</v>
+        <v>0.007921694307098937</v>
       </c>
       <c r="R4" t="n">
-        <v>0.007950500955496037</v>
+        <v>0.007950500955496036</v>
       </c>
       <c r="S4" t="n">
-        <v>0.008554433538578854</v>
+        <v>0.008554433538578852</v>
       </c>
       <c r="T4" t="n">
         <v>0.00888239031895457</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01102825575533929</v>
+        <v>0.01102825575533928</v>
       </c>
       <c r="V4" t="n">
-        <v>0.007643974162975859</v>
+        <v>0.007643974162975861</v>
       </c>
       <c r="W4" t="n">
-        <v>0.009345108409209707</v>
+        <v>0.0093451084092097</v>
       </c>
       <c r="X4" t="n">
         <v>0.009538960635868819</v>
@@ -834,13 +834,13 @@
         <v>0.01044435526646007</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.007865166453971839</v>
+        <v>0.007865166453971836</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.009380540988859473</v>
+        <v>0.009380540988859475</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0127417435822919</v>
+        <v>0.01274174358229191</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.044040901236466</v>
+        <v>0.0440409012364658</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01614825924167981</v>
+        <v>0.0161482592416798</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05153583717977615</v>
+        <v>0.05153583717977604</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02255448260692945</v>
+        <v>0.02255448260692944</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03387757666265365</v>
+        <v>0.03387757666265367</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03145337423595931</v>
+        <v>0.03145337423595935</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03799280319889021</v>
+        <v>0.03799280319889017</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05190147953311982</v>
+        <v>0.05190147953311986</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04375861302327589</v>
+        <v>0.04375861302327591</v>
       </c>
       <c r="K5" t="n">
-        <v>0.07193298227979558</v>
+        <v>0.07193298227979555</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05941866425918418</v>
+        <v>0.05941866425918409</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1467848251833351</v>
+        <v>0.146784825183335</v>
       </c>
       <c r="N5" t="n">
-        <v>0.05272152432887288</v>
+        <v>0.05272152432887284</v>
       </c>
       <c r="O5" t="n">
-        <v>0.03359970184110064</v>
+        <v>0.03359970184110057</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0269772649563173</v>
+        <v>0.02697726495631734</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03007205254476869</v>
+        <v>0.0300720525447687</v>
       </c>
       <c r="R5" t="n">
-        <v>0.03181196975579498</v>
+        <v>0.03181196975579497</v>
       </c>
       <c r="S5" t="n">
-        <v>0.04059981683046308</v>
+        <v>0.04059981683046315</v>
       </c>
       <c r="T5" t="n">
-        <v>0.05119573235399745</v>
+        <v>0.05119573235399742</v>
       </c>
       <c r="U5" t="n">
-        <v>0.09016878285551397</v>
+        <v>0.09016878285551393</v>
       </c>
       <c r="V5" t="n">
-        <v>0.02315219962089007</v>
+        <v>0.02315219962089008</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0582433235443924</v>
+        <v>0.05824332354439234</v>
       </c>
       <c r="X5" t="n">
-        <v>0.06418972519984315</v>
+        <v>0.06418972519984312</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.08078873585539756</v>
+        <v>0.08078873585539748</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0272413358120987</v>
+        <v>0.02724133581209867</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.05932765302177007</v>
+        <v>0.05932765302177016</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1388407596952838</v>
+        <v>0.138840759695284</v>
       </c>
     </row>
     <row r="6">
@@ -938,28 +938,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.009143247687484016</v>
+        <v>0.009143247687484014</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008485580137475671</v>
+        <v>0.008485580137475673</v>
       </c>
       <c r="D6" t="n">
         <v>0.01014399094995186</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00886999259497538</v>
+        <v>0.008869992594975385</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00839559016938753</v>
+        <v>0.008395590169387528</v>
       </c>
       <c r="G6" t="n">
-        <v>0.009321696826741993</v>
+        <v>0.009321696826741999</v>
       </c>
       <c r="H6" t="n">
         <v>0.009445639175120689</v>
       </c>
       <c r="I6" t="n">
-        <v>0.009248275147055099</v>
+        <v>0.009248275147055092</v>
       </c>
       <c r="J6" t="n">
         <v>0.008977619633708311</v>
@@ -968,49 +968,49 @@
         <v>0.01112868699316181</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01066264257853882</v>
+        <v>0.01066264257853883</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0145397014546461</v>
+        <v>0.01453970145464609</v>
       </c>
       <c r="N6" t="n">
-        <v>0.009386014528987711</v>
+        <v>0.009386014528987683</v>
       </c>
       <c r="O6" t="n">
-        <v>0.008621152469315163</v>
+        <v>0.008621152469315151</v>
       </c>
       <c r="P6" t="n">
-        <v>0.009101963946440018</v>
+        <v>0.009101963946440021</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.009158807934047233</v>
+        <v>0.009158807934047232</v>
       </c>
       <c r="R6" t="n">
-        <v>0.009187614582444319</v>
+        <v>0.00918761458244432</v>
       </c>
       <c r="S6" t="n">
-        <v>0.008903854261155376</v>
+        <v>0.008903854261155371</v>
       </c>
       <c r="T6" t="n">
-        <v>0.009231811041531091</v>
+        <v>0.009231811041531089</v>
       </c>
       <c r="U6" t="n">
         <v>0.01139049884335748</v>
       </c>
       <c r="V6" t="n">
-        <v>0.008881087789924139</v>
+        <v>0.008881087789924141</v>
       </c>
       <c r="W6" t="n">
-        <v>0.01058281782623015</v>
+        <v>0.01058281782623014</v>
       </c>
       <c r="X6" t="n">
         <v>0.01077607426281711</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01083579903635857</v>
+        <v>0.01083579903635858</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.008214587176548365</v>
+        <v>0.008214587176548363</v>
       </c>
       <c r="AA6" t="n">
         <v>0.01061765461580776</v>
@@ -1026,31 +1026,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.009545727839214075</v>
+        <v>0.009545727839214074</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008000367384833977</v>
+        <v>0.008000367384833975</v>
       </c>
       <c r="D7" t="n">
-        <v>0.009658778197310149</v>
+        <v>0.009658778197310144</v>
       </c>
       <c r="E7" t="n">
-        <v>0.008384779842333682</v>
+        <v>0.008384779842333677</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008798070321117591</v>
+        <v>0.008798070321117589</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008836484074100303</v>
+        <v>0.008836484074100301</v>
       </c>
       <c r="H7" t="n">
-        <v>0.008960426422478988</v>
+        <v>0.008960426422478985</v>
       </c>
       <c r="I7" t="n">
-        <v>0.009650755298785155</v>
+        <v>0.009650755298785152</v>
       </c>
       <c r="J7" t="n">
-        <v>0.009380099785438372</v>
+        <v>0.009380099785438368</v>
       </c>
       <c r="K7" t="n">
         <v>0.01064347424052012</v>
@@ -1059,34 +1059,34 @@
         <v>0.01017742982589713</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01405448870200439</v>
+        <v>0.01405448870200438</v>
       </c>
       <c r="N7" t="n">
-        <v>0.009781192323992419</v>
+        <v>0.009781192323992417</v>
       </c>
       <c r="O7" t="n">
-        <v>0.009016306010960698</v>
+        <v>0.009016306010960691</v>
       </c>
       <c r="P7" t="n">
-        <v>0.008616129158588698</v>
+        <v>0.008616129158588691</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.008673595181405524</v>
+        <v>0.008673595181405529</v>
       </c>
       <c r="R7" t="n">
-        <v>0.008702401829802626</v>
+        <v>0.008702401829802619</v>
       </c>
       <c r="S7" t="n">
-        <v>0.009306334412885434</v>
+        <v>0.00930633441288543</v>
       </c>
       <c r="T7" t="n">
-        <v>0.009634291193261153</v>
+        <v>0.009634291193261146</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01179265821217137</v>
+        <v>0.01179265821217138</v>
       </c>
       <c r="V7" t="n">
-        <v>0.008395875037282438</v>
+        <v>0.008395875037282436</v>
       </c>
       <c r="W7" t="n">
         <v>0.01009700928351628</v>
@@ -1095,10 +1095,10 @@
         <v>0.0102908615101754</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01120907850620832</v>
+        <v>0.01120907850620831</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.008617067328278428</v>
+        <v>0.008617067328278421</v>
       </c>
       <c r="AA7" t="n">
         <v>0.01013244186316606</v>
@@ -1117,40 +1117,40 @@
         <v>0.01105437102106633</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01106470415405096</v>
+        <v>0.01106470415405097</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01272311496652713</v>
+        <v>0.01272311496652714</v>
       </c>
       <c r="E8" t="n">
         <v>0.0106207556663798</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01054907238210097</v>
+        <v>0.01054907238210098</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01222340404305491</v>
+        <v>0.01222340404305492</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01202476319169597</v>
+        <v>0.01202476319169599</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01271509206800214</v>
+        <v>0.01271509206800216</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01244443655465536</v>
+        <v>0.01244443655465537</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01370781100973711</v>
+        <v>0.01370781100973712</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0132417665951141</v>
+        <v>0.01324176659511412</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01711882547122138</v>
+        <v>0.01711882547122139</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01163960630112208</v>
+        <v>0.01163960630112209</v>
       </c>
       <c r="O8" t="n">
         <v>0.01120614489914618</v>
@@ -1159,10 +1159,10 @@
         <v>0.01072473437601857</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.009876509066382462</v>
+        <v>0.009876509066382468</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0117667385990196</v>
+        <v>0.01176673859901961</v>
       </c>
       <c r="S8" t="n">
         <v>0.01237067118210242</v>
@@ -1171,28 +1171,28 @@
         <v>0.01269862796247813</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01409777470249325</v>
+        <v>0.01409777470249326</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01103476605139509</v>
+        <v>0.01103476605139512</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01316165179104969</v>
+        <v>0.0131616517910497</v>
       </c>
       <c r="X8" t="n">
         <v>0.01163635780361371</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01581981632490726</v>
+        <v>0.01581981632490727</v>
       </c>
       <c r="Z8" t="n">
         <v>0.01009681270305635</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01319677863238305</v>
+        <v>0.01319677863238306</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01818303326275194</v>
+        <v>0.01818303326275196</v>
       </c>
     </row>
     <row r="9">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.011430110058535</v>
+        <v>0.01143011005853501</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01066578438976299</v>
+        <v>0.010665784389763</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01232419520223919</v>
+        <v>0.01232419520223918</v>
       </c>
       <c r="E9" t="n">
         <v>0.01086993637428816</v>
@@ -1226,7 +1226,7 @@
         <v>0.01231617230371419</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0120455167903674</v>
+        <v>0.01204551679036741</v>
       </c>
       <c r="K9" t="n">
         <v>0.01330889124544915</v>
@@ -1235,16 +1235,16 @@
         <v>0.01284284683082616</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01671990570693342</v>
+        <v>0.01671990570693341</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01244660932892144</v>
+        <v>0.01244660932892146</v>
       </c>
       <c r="O9" t="n">
         <v>0.01194058234108189</v>
       </c>
       <c r="P9" t="n">
-        <v>0.01159669734447234</v>
+        <v>0.01159669734447235</v>
       </c>
       <c r="Q9" t="n">
         <v>0.01133901110698631</v>
@@ -1253,7 +1253,7 @@
         <v>0.01136781883473165</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01197175141781446</v>
+        <v>0.01197175141781447</v>
       </c>
       <c r="T9" t="n">
         <v>0.01229970819819018</v>
@@ -1262,7 +1262,7 @@
         <v>0.01445839600001657</v>
       </c>
       <c r="V9" t="n">
-        <v>0.01196258627443316</v>
+        <v>0.01196258627443317</v>
       </c>
       <c r="W9" t="n">
         <v>0.01276242628844531</v>
@@ -1271,13 +1271,13 @@
         <v>0.01295627851510444</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.01387449551113735</v>
+        <v>0.01387449551113736</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.01081158938121151</v>
+        <v>0.0108115893812115</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.01279785886809509</v>
+        <v>0.0127978588680951</v>
       </c>
       <c r="AB9" t="n">
         <v>0.01615906146152753</v>
@@ -1446,25 +1446,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003717247939742315</v>
+        <v>0.003717247939742327</v>
       </c>
       <c r="C2" t="n">
         <v>0.003301666177617807</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003723482485583252</v>
+        <v>0.003723482485583251</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003723224211454135</v>
+        <v>0.003723224211454144</v>
       </c>
       <c r="F2" t="n">
         <v>0.003727235216085839</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003729891012457081</v>
+        <v>0.003729891012457088</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003725445329840645</v>
+        <v>0.003725445329840643</v>
       </c>
       <c r="I2" t="n">
         <v>0.003725847890252427</v>
@@ -1473,58 +1473,58 @@
         <v>0.003738359047546819</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00373475146011861</v>
+        <v>0.003734751460118601</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00373918792240103</v>
+        <v>0.003739187922401028</v>
       </c>
       <c r="M2" t="n">
         <v>0.003730346125362584</v>
       </c>
       <c r="N2" t="n">
-        <v>0.00372821666825625</v>
+        <v>0.003728216668256248</v>
       </c>
       <c r="O2" t="n">
-        <v>0.005408643836908493</v>
+        <v>0.005408643836908492</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003731572538517064</v>
+        <v>0.003731572538517062</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003722587183373334</v>
+        <v>0.003722587183373332</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003740910297822764</v>
+        <v>0.003740910297822763</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003735196952684489</v>
+        <v>0.003735196952684498</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003725708753697612</v>
+        <v>0.003725708753697622</v>
       </c>
       <c r="U2" t="n">
-        <v>0.003591228345904864</v>
+        <v>0.003591228345904871</v>
       </c>
       <c r="V2" t="n">
         <v>0.003734804886553679</v>
       </c>
       <c r="W2" t="n">
-        <v>0.003563434871944602</v>
+        <v>0.003563434871944607</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00413891388722991</v>
+        <v>0.004138913887229922</v>
       </c>
       <c r="Y2" t="n">
         <v>0.00396524879995471</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.004726362540806549</v>
+        <v>0.004726362540806561</v>
       </c>
       <c r="AA2" t="n">
         <v>0.003767642324405839</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.003721364190061453</v>
+        <v>0.00372136419006146</v>
       </c>
     </row>
     <row r="3">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003507055611520336</v>
+        <v>0.003510039736838385</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002838131895679362</v>
+        <v>0.002841942129493017</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003551948685550313</v>
+        <v>0.0035565433703774</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003548280213151346</v>
+        <v>0.003552529144311488</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003578838291707366</v>
+        <v>0.003584407100952873</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003596834409113499</v>
+        <v>0.00360298238149926</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003566355657542615</v>
+        <v>0.003571475018956312</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003568954307223814</v>
+        <v>0.003574157087111623</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00365751404215615</v>
+        <v>0.003665833427109531</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003631891701122576</v>
+        <v>0.003639339212780295</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003663091267044756</v>
+        <v>0.003671606666209637</v>
       </c>
       <c r="M3" t="n">
-        <v>0.003605565194302968</v>
+        <v>0.00361210790942856</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003585661329083995</v>
+        <v>0.003591438992075218</v>
       </c>
       <c r="O3" t="n">
-        <v>0.006375757136138493</v>
+        <v>0.006382259244272732</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003608672850478436</v>
+        <v>0.003615227987180578</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003545318972446641</v>
+        <v>0.003549678311227084</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003676971138463329</v>
+        <v>0.003686022219620511</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003634490914768565</v>
+        <v>0.003641982092221387</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003567931434635721</v>
+        <v>0.003573093951655155</v>
       </c>
       <c r="U3" t="n">
-        <v>0.003462484691911708</v>
+        <v>0.003473013217918353</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003631759515160563</v>
+        <v>0.003639144031513398</v>
       </c>
       <c r="W3" t="n">
-        <v>0.003390696500477267</v>
+        <v>0.003400007452373237</v>
       </c>
       <c r="X3" t="n">
-        <v>0.006512621505500075</v>
+        <v>0.006622605623715419</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.005278837841429932</v>
+        <v>0.005344442655491936</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.005263515824931566</v>
+        <v>0.005270682610764184</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003867096510318164</v>
+        <v>0.003882807112041415</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.003541279457071391</v>
+        <v>0.003545508687907806</v>
       </c>
     </row>
     <row r="4">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.006720761407852213</v>
+        <v>0.006720761407852218</v>
       </c>
       <c r="C4" t="n">
-        <v>0.006756422684424841</v>
+        <v>0.006756422684424846</v>
       </c>
       <c r="D4" t="n">
-        <v>0.006791183471158331</v>
+        <v>0.006791183471158336</v>
       </c>
       <c r="E4" t="n">
-        <v>0.006788266146057997</v>
+        <v>0.006788266146058</v>
       </c>
       <c r="F4" t="n">
-        <v>0.006833572288526401</v>
+        <v>0.006833572288526405</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006863570730266257</v>
+        <v>0.006863570730266258</v>
       </c>
       <c r="H4" t="n">
-        <v>0.006813354699998595</v>
+        <v>0.0068133546999986</v>
       </c>
       <c r="I4" t="n">
-        <v>0.006817901805036628</v>
+        <v>0.006817901805036632</v>
       </c>
       <c r="J4" t="n">
         <v>0.006956217689766861</v>
       </c>
       <c r="K4" t="n">
-        <v>0.006918471722519558</v>
+        <v>0.006918471722519561</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006968583604873082</v>
+        <v>0.006968583604873087</v>
       </c>
       <c r="M4" t="n">
-        <v>0.006876937997629257</v>
+        <v>0.006876937997629259</v>
       </c>
       <c r="N4" t="n">
-        <v>0.006844658242281478</v>
+        <v>0.006844658242281486</v>
       </c>
       <c r="O4" t="n">
-        <v>0.006879952603735668</v>
+        <v>0.006879952603735674</v>
       </c>
       <c r="P4" t="n">
-        <v>0.006882564340653986</v>
+        <v>0.006882564340653991</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.006781070620837966</v>
+        <v>0.006781070620837971</v>
       </c>
       <c r="R4" t="n">
-        <v>0.006988038627593398</v>
+        <v>0.006988038627593404</v>
       </c>
       <c r="S4" t="n">
-        <v>0.006923503765987918</v>
+        <v>0.006923503765987926</v>
       </c>
       <c r="T4" t="n">
-        <v>0.006816330193644016</v>
+        <v>0.00681633019364402</v>
       </c>
       <c r="U4" t="n">
-        <v>0.007047280071466721</v>
+        <v>0.007047280071466718</v>
       </c>
       <c r="V4" t="n">
-        <v>0.006898753329366184</v>
+        <v>0.006898753329366188</v>
       </c>
       <c r="W4" t="n">
-        <v>0.007003694047621373</v>
+        <v>0.007003694047621379</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01148367226064383</v>
+        <v>0.01148367226064384</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.009509949016722138</v>
+        <v>0.009509949016722136</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.006909424252434897</v>
+        <v>0.006909424252434901</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.007289989165188989</v>
+        <v>0.007289989165188995</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.006774899742606196</v>
+        <v>0.006774899742606201</v>
       </c>
     </row>
     <row r="5">
@@ -1713,31 +1713,31 @@
         <v>0.008771946170555107</v>
       </c>
       <c r="C5" t="n">
-        <v>0.009599830696085642</v>
+        <v>0.009599830696085656</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01022311307159407</v>
+        <v>0.01022311307159408</v>
       </c>
       <c r="E5" t="n">
-        <v>0.009225673931602372</v>
+        <v>0.009225673931602379</v>
       </c>
       <c r="F5" t="n">
         <v>0.01102785511664598</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01106174306879824</v>
+        <v>0.01106174306879834</v>
       </c>
       <c r="H5" t="n">
         <v>0.01082152959512993</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01075972897363942</v>
+        <v>0.01075972897363943</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01287632197568863</v>
+        <v>0.01287632197568866</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01222348239828817</v>
+        <v>0.01222348239828816</v>
       </c>
       <c r="L5" t="n">
         <v>0.01286949991384129</v>
@@ -1746,7 +1746,7 @@
         <v>0.01182311025185924</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01112980040466693</v>
+        <v>0.01112980040466694</v>
       </c>
       <c r="O5" t="n">
         <v>0.01128771614184683</v>
@@ -1755,7 +1755,7 @@
         <v>0.01131336438929064</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.009919930288438478</v>
+        <v>0.00991993028843848</v>
       </c>
       <c r="R5" t="n">
         <v>0.01403611624499386</v>
@@ -1767,28 +1767,28 @@
         <v>0.01071646443143492</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0142085370355556</v>
+        <v>0.01420853703555561</v>
       </c>
       <c r="V5" t="n">
         <v>0.01194772920983328</v>
       </c>
       <c r="W5" t="n">
-        <v>0.01383467697048949</v>
+        <v>0.01383467697048947</v>
       </c>
       <c r="X5" t="n">
-        <v>0.09099858420489511</v>
+        <v>0.09099858420489523</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.05924371707141116</v>
+        <v>0.05924371707141125</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01164006652825548</v>
+        <v>0.01164006652825549</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01903331984838084</v>
+        <v>0.01903331984838088</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0100886808101014</v>
+        <v>0.01008868081010142</v>
       </c>
     </row>
     <row r="6">
@@ -1798,46 +1798,46 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.006956659512021165</v>
+        <v>0.006956659512021166</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007643409808263068</v>
+        <v>0.007643409808263071</v>
       </c>
       <c r="D6" t="n">
-        <v>0.007027081575327289</v>
+        <v>0.007027081575327288</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007675253269896222</v>
+        <v>0.007675253269896223</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00772055941236463</v>
+        <v>0.007720559412364631</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007099468834435216</v>
+        <v>0.007099468834435212</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007049252804167549</v>
+        <v>0.00704925280416755</v>
       </c>
       <c r="I6" t="n">
         <v>0.007053799909205584</v>
       </c>
       <c r="J6" t="n">
-        <v>0.007843204813605086</v>
+        <v>0.007843204813605087</v>
       </c>
       <c r="K6" t="n">
-        <v>0.007154369826688511</v>
+        <v>0.007154369826688512</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007855570728711308</v>
+        <v>0.007855570728711313</v>
       </c>
       <c r="M6" t="n">
-        <v>0.007112836101798209</v>
+        <v>0.007112836101798208</v>
       </c>
       <c r="N6" t="n">
-        <v>0.00708329909134215</v>
+        <v>0.007083299091342149</v>
       </c>
       <c r="O6" t="n">
-        <v>0.007776561365518453</v>
+        <v>0.007776561365518458</v>
       </c>
       <c r="P6" t="n">
         <v>0.007103621417586276</v>
@@ -1846,34 +1846,34 @@
         <v>0.007016968725006922</v>
       </c>
       <c r="R6" t="n">
-        <v>0.007223936731762354</v>
+        <v>0.007223936731762351</v>
       </c>
       <c r="S6" t="n">
-        <v>0.007810490889826147</v>
+        <v>0.007810490889826144</v>
       </c>
       <c r="T6" t="n">
-        <v>0.007052228297812973</v>
+        <v>0.007052228297812971</v>
       </c>
       <c r="U6" t="n">
-        <v>0.007946363388566195</v>
+        <v>0.007946363388566196</v>
       </c>
       <c r="V6" t="n">
-        <v>0.007134651433535141</v>
+        <v>0.007134651433535139</v>
       </c>
       <c r="W6" t="n">
-        <v>0.007260395334884658</v>
+        <v>0.007260395334884644</v>
       </c>
       <c r="X6" t="n">
         <v>0.01237065938448207</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.009779908915675361</v>
+        <v>0.009779908915675355</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.007145322356603855</v>
+        <v>0.007145322356603851</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.008176976289027214</v>
+        <v>0.008176976289027216</v>
       </c>
       <c r="AB6" t="n">
         <v>0.007010891590922452</v>
@@ -1886,70 +1886,70 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007261919501797367</v>
+        <v>0.007261919501797369</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007297580778369999</v>
+        <v>0.00729758077837</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00733234156510349</v>
+        <v>0.007332341565103491</v>
       </c>
       <c r="E7" t="n">
-        <v>0.007329424240003154</v>
+        <v>0.007329424240003156</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007374730382471557</v>
+        <v>0.007374730382471558</v>
       </c>
       <c r="G7" t="n">
         <v>0.007404728824211415</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00735451279394375</v>
+        <v>0.007354512793943752</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007359059898981784</v>
+        <v>0.007359059898981785</v>
       </c>
       <c r="J7" t="n">
         <v>0.007497375783712013</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007459629816464715</v>
+        <v>0.007459629816464713</v>
       </c>
       <c r="L7" t="n">
         <v>0.007509741698818238</v>
       </c>
       <c r="M7" t="n">
-        <v>0.007418096091574411</v>
+        <v>0.007418096091574413</v>
       </c>
       <c r="N7" t="n">
-        <v>0.007385816336226631</v>
+        <v>0.007385816336226636</v>
       </c>
       <c r="O7" t="n">
         <v>0.007421089037760756</v>
       </c>
       <c r="P7" t="n">
-        <v>0.007423700774679075</v>
+        <v>0.00742370077467908</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.007322228714783122</v>
+        <v>0.007322228714783123</v>
       </c>
       <c r="R7" t="n">
-        <v>0.007529196721538553</v>
+        <v>0.007529196721538555</v>
       </c>
       <c r="S7" t="n">
-        <v>0.007464661859933076</v>
+        <v>0.007464661859933075</v>
       </c>
       <c r="T7" t="n">
-        <v>0.007357488287589172</v>
+        <v>0.007357488287589174</v>
       </c>
       <c r="U7" t="n">
-        <v>0.007599634322190687</v>
+        <v>0.007599634322190686</v>
       </c>
       <c r="V7" t="n">
-        <v>0.00743991142331134</v>
+        <v>0.007439911423311341</v>
       </c>
       <c r="W7" t="n">
-        <v>0.007544852141566528</v>
+        <v>0.007544852141566525</v>
       </c>
       <c r="X7" t="n">
         <v>0.012024830354589</v>
@@ -1958,13 +1958,13 @@
         <v>0.01006320330392854</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.00745058234638005</v>
+        <v>0.007450582346380052</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.007831147259134145</v>
+        <v>0.007831147259134147</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.007316057836551349</v>
+        <v>0.007316057836551351</v>
       </c>
     </row>
     <row r="8">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00845525284785319</v>
+        <v>0.008455252847853199</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009674398646237042</v>
+        <v>0.009674398646237049</v>
       </c>
       <c r="D8" t="n">
-        <v>0.009709159432970538</v>
+        <v>0.009709159432970547</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009076071510610321</v>
+        <v>0.009076071510610339</v>
       </c>
       <c r="F8" t="n">
-        <v>0.008752436785352846</v>
+        <v>0.008752436785352855</v>
       </c>
       <c r="G8" t="n">
-        <v>0.010026949917362</v>
+        <v>0.01002694991736201</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00973133066181079</v>
+        <v>0.009731330661810807</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009735877766848831</v>
+        <v>0.009735877766848845</v>
       </c>
       <c r="J8" t="n">
-        <v>0.009874193651579054</v>
+        <v>0.009874193651579065</v>
       </c>
       <c r="K8" t="n">
-        <v>0.00983644768433176</v>
+        <v>0.009836447684331775</v>
       </c>
       <c r="L8" t="n">
-        <v>0.009886559566685283</v>
+        <v>0.009886559566685296</v>
       </c>
       <c r="M8" t="n">
-        <v>0.009794913959441503</v>
+        <v>0.009794913959441511</v>
       </c>
       <c r="N8" t="n">
-        <v>0.008845235707048888</v>
+        <v>0.008845235707048898</v>
       </c>
       <c r="O8" t="n">
-        <v>0.00913263914114304</v>
+        <v>0.009132639141143048</v>
       </c>
       <c r="P8" t="n">
-        <v>0.009073452852546203</v>
+        <v>0.009073452852546215</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.008282980340581161</v>
+        <v>0.008282980340581165</v>
       </c>
       <c r="R8" t="n">
-        <v>0.009906014589405595</v>
+        <v>0.009906014589405612</v>
       </c>
       <c r="S8" t="n">
-        <v>0.009841479727800114</v>
+        <v>0.009841479727800136</v>
       </c>
       <c r="T8" t="n">
-        <v>0.009734306155456212</v>
+        <v>0.009734306155456221</v>
       </c>
       <c r="U8" t="n">
-        <v>0.009399028506976983</v>
+        <v>0.009399028506976994</v>
       </c>
       <c r="V8" t="n">
-        <v>0.009492514312056064</v>
+        <v>0.009492514312056078</v>
       </c>
       <c r="W8" t="n">
-        <v>0.009921902598078064</v>
+        <v>0.009921902598078075</v>
       </c>
       <c r="X8" t="n">
         <v>0.01309405068844637</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01361556837965633</v>
+        <v>0.01361556837965635</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.008621931859839524</v>
+        <v>0.008621931859839534</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01020796512700119</v>
+        <v>0.01020796512700121</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01092912424883933</v>
+        <v>0.01092912424883935</v>
       </c>
     </row>
     <row r="9">
@@ -2062,85 +2062,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00823950588626654</v>
+        <v>0.008239505886266544</v>
       </c>
       <c r="C9" t="n">
         <v>0.008730616920703749</v>
       </c>
       <c r="D9" t="n">
-        <v>0.008765377707437228</v>
+        <v>0.008765377707437232</v>
       </c>
       <c r="E9" t="n">
-        <v>0.008657344568826298</v>
+        <v>0.008657344568826296</v>
       </c>
       <c r="F9" t="n">
-        <v>0.007757830303445165</v>
+        <v>0.007757830303445168</v>
       </c>
       <c r="G9" t="n">
         <v>0.008837765139267633</v>
       </c>
       <c r="H9" t="n">
-        <v>0.008787548936277494</v>
+        <v>0.008787548936277497</v>
       </c>
       <c r="I9" t="n">
-        <v>0.008792096041315528</v>
+        <v>0.008792096041315535</v>
       </c>
       <c r="J9" t="n">
         <v>0.00893041192604576</v>
       </c>
       <c r="K9" t="n">
-        <v>0.008892665958798462</v>
+        <v>0.008892665958798465</v>
       </c>
       <c r="L9" t="n">
-        <v>0.008942777841151982</v>
+        <v>0.008942777841151986</v>
       </c>
       <c r="M9" t="n">
-        <v>0.008851132233908158</v>
+        <v>0.008851132233908163</v>
       </c>
       <c r="N9" t="n">
-        <v>0.008818852478560379</v>
+        <v>0.008818852478560381</v>
       </c>
       <c r="O9" t="n">
-        <v>0.009005082523372791</v>
+        <v>0.009005082523372792</v>
       </c>
       <c r="P9" t="n">
-        <v>0.009040520144237131</v>
+        <v>0.009040520144237129</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.008755265029839341</v>
+        <v>0.008755265029839338</v>
       </c>
       <c r="R9" t="n">
         <v>0.008962232863872295</v>
       </c>
       <c r="S9" t="n">
-        <v>0.008897698002266821</v>
+        <v>0.008897698002266823</v>
       </c>
       <c r="T9" t="n">
-        <v>0.008790524429922916</v>
+        <v>0.008790524429922921</v>
       </c>
       <c r="U9" t="n">
-        <v>0.009033570501006866</v>
+        <v>0.009033570501006869</v>
       </c>
       <c r="V9" t="n">
         <v>0.009398526929042693</v>
       </c>
       <c r="W9" t="n">
-        <v>0.008977888283900271</v>
+        <v>0.008977888283900273</v>
       </c>
       <c r="X9" t="n">
         <v>0.01345786649692274</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.01149623944626228</v>
+        <v>0.01149623944626229</v>
       </c>
       <c r="Z9" t="n">
         <v>0.008609022853480299</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.009264183401467889</v>
+        <v>0.009264183401467892</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.008749093978885094</v>
+        <v>0.008749093978885099</v>
       </c>
     </row>
   </sheetData>
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004030101591630132</v>
+        <v>0.004030101591630134</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003536640084176887</v>
+        <v>0.00353664008417689</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004080081305916832</v>
+        <v>0.004080081305916828</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003954381409662939</v>
+        <v>0.003954381409662932</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003957394232347484</v>
+        <v>0.00395739423234748</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003996479054770221</v>
+        <v>0.003996479054770218</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003930987158074366</v>
+        <v>0.003930987158074361</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003989931425760231</v>
+        <v>0.003989931425760227</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004042576494121009</v>
+        <v>0.004042576494121002</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00412622170809474</v>
+        <v>0.004126221708094746</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004103562886015232</v>
+        <v>0.004103562886015244</v>
       </c>
       <c r="M2" t="n">
-        <v>0.004424063108518169</v>
+        <v>0.004424063108518173</v>
       </c>
       <c r="N2" t="n">
-        <v>0.004008756684681558</v>
+        <v>0.004008756684681553</v>
       </c>
       <c r="O2" t="n">
-        <v>0.005778985719242469</v>
+        <v>0.005778985719242475</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003992302289559042</v>
+        <v>0.003992302289559043</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003958546185443015</v>
+        <v>0.003958546185443019</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003935228912832179</v>
+        <v>0.003935228912832173</v>
       </c>
       <c r="S2" t="n">
-        <v>0.004040778098060326</v>
+        <v>0.004040778098060327</v>
       </c>
       <c r="T2" t="n">
-        <v>0.004024088293147614</v>
+        <v>0.004024088293147607</v>
       </c>
       <c r="U2" t="n">
-        <v>0.004230037164575437</v>
+        <v>0.004230037164575442</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003937965094514304</v>
+        <v>0.003937965094514303</v>
       </c>
       <c r="W2" t="n">
         <v>0.004059958688690392</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00417802910132303</v>
+        <v>0.004178029101323024</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.004172533685842775</v>
+        <v>0.00417253368584277</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.004984199988882528</v>
+        <v>0.004984199988882534</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.004061564946437663</v>
+        <v>0.004061564946437657</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.004399050820594807</v>
+        <v>0.004399050820594847</v>
       </c>
     </row>
     <row r="3">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004581911803785269</v>
+        <v>0.004617467024578803</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003195259441614894</v>
+        <v>0.003204657577515574</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004946817130724048</v>
+        <v>0.004995600618399815</v>
       </c>
       <c r="E3" t="n">
-        <v>0.004043958200591122</v>
+        <v>0.004060422707333291</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00406871754367577</v>
+        <v>0.004086426303327155</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004343890507666041</v>
+        <v>0.004371053594102001</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003880225472710428</v>
+        <v>0.00389121381423514</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004301951873161259</v>
+        <v>0.004327889010368868</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004675298009786908</v>
+        <v>0.004714334473552064</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005270210689887381</v>
+        <v>0.005330627151558113</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005110010298095322</v>
+        <v>0.005164265364335554</v>
       </c>
       <c r="M3" t="n">
-        <v>0.007386659766836711</v>
+        <v>0.007522308253907418</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004434778985057482</v>
+        <v>0.004465326514214214</v>
       </c>
       <c r="O3" t="n">
-        <v>0.007246079039143967</v>
+        <v>0.007271438369908388</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004313931306411436</v>
+        <v>0.004339986642594973</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.004076075634315151</v>
+        <v>0.004093954173690718</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003910337027434164</v>
+        <v>0.003922379371263084</v>
       </c>
       <c r="S3" t="n">
-        <v>0.004659284363280456</v>
+        <v>0.004697623464467332</v>
       </c>
       <c r="T3" t="n">
-        <v>0.004545928796002902</v>
+        <v>0.00458051465495124</v>
       </c>
       <c r="U3" t="n">
-        <v>0.006007840665973714</v>
+        <v>0.006093747576341952</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003927073895623419</v>
+        <v>0.00393961136810434</v>
       </c>
       <c r="W3" t="n">
-        <v>0.004990602606389177</v>
+        <v>0.005042735564021772</v>
       </c>
       <c r="X3" t="n">
-        <v>0.005645818790167156</v>
+        <v>0.005719405410198508</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.005601998640190402</v>
+        <v>0.00567383869355069</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.00580970822039728</v>
+        <v>0.005829345452433092</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.004810834121720739</v>
+        <v>0.004854627736450972</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.007207948533944435</v>
+        <v>0.007336453384125201</v>
       </c>
     </row>
     <row r="4">
@@ -2482,58 +2482,58 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.008327100462443067</v>
+        <v>0.008327100462443058</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007140161114559737</v>
+        <v>0.007140161114559736</v>
       </c>
       <c r="D4" t="n">
-        <v>0.008891644327115806</v>
+        <v>0.008891644327115807</v>
       </c>
       <c r="E4" t="n">
-        <v>0.007471806174118981</v>
+        <v>0.007471806174118979</v>
       </c>
       <c r="F4" t="n">
         <v>0.007505837392307777</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00794731844147924</v>
+        <v>0.007947318441479237</v>
       </c>
       <c r="H4" t="n">
-        <v>0.007207557340538578</v>
+        <v>0.007207557340538575</v>
       </c>
       <c r="I4" t="n">
         <v>0.007873359959753251</v>
       </c>
       <c r="J4" t="n">
-        <v>0.008464284802526438</v>
+        <v>0.008464284802526444</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009412821395348974</v>
+        <v>0.009412821395348969</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009156879576387828</v>
+        <v>0.009156879576387859</v>
       </c>
       <c r="M4" t="n">
         <v>0.01273280759936471</v>
       </c>
       <c r="N4" t="n">
-        <v>0.008085999919316593</v>
+        <v>0.008085999919316588</v>
       </c>
       <c r="O4" t="n">
-        <v>0.007867666557285892</v>
+        <v>0.00786766655728589</v>
       </c>
       <c r="P4" t="n">
         <v>0.007900139957012038</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.007518849232446407</v>
+        <v>0.007518849232446412</v>
       </c>
       <c r="R4" t="n">
         <v>0.007255469911831645</v>
       </c>
       <c r="S4" t="n">
-        <v>0.00844769651400773</v>
+        <v>0.008447696514007725</v>
       </c>
       <c r="T4" t="n">
         <v>0.00825917748982904</v>
@@ -2542,22 +2542,22 @@
         <v>0.01055700288846654</v>
       </c>
       <c r="V4" t="n">
-        <v>0.007261220632305535</v>
+        <v>0.007261220632305534</v>
       </c>
       <c r="W4" t="n">
-        <v>0.009057800709497554</v>
+        <v>0.009057800709497549</v>
       </c>
       <c r="X4" t="n">
-        <v>0.009998009734440738</v>
+        <v>0.009998009734440755</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.009911305334629188</v>
+        <v>0.009911305334629181</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.007607054131472678</v>
+        <v>0.007607054131472679</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.008682493528852394</v>
+        <v>0.008682493528852395</v>
       </c>
       <c r="AB4" t="n">
         <v>0.01243644431847349</v>
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0346343975626832</v>
+        <v>0.03463439756268393</v>
       </c>
       <c r="C5" t="n">
         <v>0.01470043602726599</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0498678608026947</v>
+        <v>0.04986786080269466</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01983355148087462</v>
+        <v>0.01983355148087478</v>
       </c>
       <c r="F5" t="n">
         <v>0.02228821896844209</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02853491205235853</v>
+        <v>0.02853491205235847</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0166353178794774</v>
+        <v>0.01663531787947737</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02980166055562299</v>
+        <v>0.02980166055562306</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03971546909689697</v>
+        <v>0.03971546909689706</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05643381480529251</v>
+        <v>0.05643381480529248</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05243803580378189</v>
+        <v>0.05243803580378294</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1274347467007054</v>
+        <v>0.1274347467007053</v>
       </c>
       <c r="N5" t="n">
         <v>0.03297149078316958</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02620743592045998</v>
+        <v>0.02620743592045997</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0275597656581545</v>
+        <v>0.02755976565815461</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.02205403258352862</v>
+        <v>0.02205403258352864</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0174511139221184</v>
+        <v>0.01745111392211838</v>
       </c>
       <c r="S5" t="n">
-        <v>0.03756742817998295</v>
+        <v>0.03756742817998275</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0372065892412899</v>
+        <v>0.03720658924128988</v>
       </c>
       <c r="U5" t="n">
-        <v>0.07770746089314551</v>
+        <v>0.07770746089314533</v>
       </c>
       <c r="V5" t="n">
-        <v>0.01645789239764522</v>
+        <v>0.01645789239764523</v>
       </c>
       <c r="W5" t="n">
-        <v>0.05095009998457876</v>
+        <v>0.05095009998457877</v>
       </c>
       <c r="X5" t="n">
-        <v>0.07075541222193875</v>
+        <v>0.07075541222193892</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.06702393976634555</v>
+        <v>0.06702393976634542</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.02247648503297251</v>
+        <v>0.02247648503297277</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.04378273368313318</v>
+        <v>0.04378273368313326</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1259028211815217</v>
+        <v>0.1259028211815215</v>
       </c>
     </row>
     <row r="6">
@@ -2658,34 +2658,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.008627301539816692</v>
+        <v>0.008627301539816697</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008251261336513636</v>
+        <v>0.008251261336513634</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009191845404489432</v>
+        <v>0.009191845404489429</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008582906396072882</v>
+        <v>0.008582906396072888</v>
       </c>
       <c r="F6" t="n">
-        <v>0.007806038469681407</v>
+        <v>0.007806038469681405</v>
       </c>
       <c r="G6" t="n">
         <v>0.00905841866343314</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008318657562492475</v>
+        <v>0.008318657562492482</v>
       </c>
       <c r="I6" t="n">
         <v>0.008984460181707147</v>
       </c>
       <c r="J6" t="n">
-        <v>0.009575385024480333</v>
+        <v>0.009575385024480344</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00971302247272259</v>
+        <v>0.009713022472722594</v>
       </c>
       <c r="L6" t="n">
         <v>0.01026797979834172</v>
@@ -2694,46 +2694,46 @@
         <v>0.01384390782131861</v>
       </c>
       <c r="N6" t="n">
-        <v>0.008391291106145806</v>
+        <v>0.00839129110614574</v>
       </c>
       <c r="O6" t="n">
-        <v>0.00817256947364145</v>
+        <v>0.008172569473641152</v>
       </c>
       <c r="P6" t="n">
-        <v>0.009013880938011301</v>
+        <v>0.009013880938011299</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.007819050309820039</v>
+        <v>0.007819050309820044</v>
       </c>
       <c r="R6" t="n">
-        <v>0.008366570133785545</v>
+        <v>0.008366570133785549</v>
       </c>
       <c r="S6" t="n">
-        <v>0.00874789759138136</v>
+        <v>0.008747897591381353</v>
       </c>
       <c r="T6" t="n">
-        <v>0.008559378567202664</v>
+        <v>0.008559378567202666</v>
       </c>
       <c r="U6" t="n">
         <v>0.01088183511978626</v>
       </c>
       <c r="V6" t="n">
-        <v>0.007561421709679167</v>
+        <v>0.007561421709679166</v>
       </c>
       <c r="W6" t="n">
-        <v>0.009391385754882336</v>
+        <v>0.009391385754882334</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01110910995639464</v>
+        <v>0.01110910995639465</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0102594948737745</v>
+        <v>0.01025949487377433</v>
       </c>
       <c r="Z6" t="n">
         <v>0.007907255208846319</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.009793593750806295</v>
+        <v>0.009793593750806302</v>
       </c>
       <c r="AB6" t="n">
         <v>0.0127781139540409</v>
@@ -2746,82 +2746,82 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.009004151041548307</v>
+        <v>0.009004151041548303</v>
       </c>
       <c r="C7" t="n">
         <v>0.007817211693664977</v>
       </c>
       <c r="D7" t="n">
-        <v>0.009568694906221047</v>
+        <v>0.009568694906221045</v>
       </c>
       <c r="E7" t="n">
-        <v>0.008148856753224222</v>
+        <v>0.008148856753224229</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008182887971413021</v>
+        <v>0.008182887971413018</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008624369020584482</v>
+        <v>0.008624369020584484</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00788460791964382</v>
+        <v>0.007884607919643818</v>
       </c>
       <c r="I7" t="n">
         <v>0.008550410538858487</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00914133538163168</v>
+        <v>0.009141335381631683</v>
       </c>
       <c r="K7" t="n">
         <v>0.01008987197445421</v>
       </c>
       <c r="L7" t="n">
-        <v>0.009833930155493078</v>
+        <v>0.009833930155493038</v>
       </c>
       <c r="M7" t="n">
         <v>0.01340985817846996</v>
       </c>
       <c r="N7" t="n">
-        <v>0.008763050498421833</v>
+        <v>0.008763050498421828</v>
       </c>
       <c r="O7" t="n">
-        <v>0.008544692991916807</v>
+        <v>0.008544692991916805</v>
       </c>
       <c r="P7" t="n">
-        <v>0.00857716639164295</v>
+        <v>0.008577166391642951</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.008195899811551647</v>
+        <v>0.00819589981155164</v>
       </c>
       <c r="R7" t="n">
         <v>0.007932520490936887</v>
       </c>
       <c r="S7" t="n">
-        <v>0.009124747093112969</v>
+        <v>0.009124747093112982</v>
       </c>
       <c r="T7" t="n">
-        <v>0.008936228068934279</v>
+        <v>0.008936228068934276</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01125830477185539</v>
+        <v>0.01125830477185538</v>
       </c>
       <c r="V7" t="n">
-        <v>0.007938271211410778</v>
+        <v>0.007938271211410781</v>
       </c>
       <c r="W7" t="n">
-        <v>0.009734851288602788</v>
+        <v>0.009734851288602787</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01067506031354599</v>
+        <v>0.010675060313546</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01061298706768052</v>
+        <v>0.01061298706768051</v>
       </c>
       <c r="Z7" t="n">
         <v>0.008284104710577923</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.009359544107957625</v>
+        <v>0.009359544107957626</v>
       </c>
       <c r="AB7" t="n">
         <v>0.01311349489757873</v>
@@ -2834,85 +2834,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01038005001348973</v>
+        <v>0.01038005001348974</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01060401614530916</v>
+        <v>0.01060401614530917</v>
       </c>
       <c r="D8" t="n">
         <v>0.01235549935786523</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01018439565604281</v>
+        <v>0.01018439565604282</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009778589527487338</v>
+        <v>0.009778589527487341</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01170373391463624</v>
+        <v>0.01170373391463625</v>
       </c>
       <c r="H8" t="n">
-        <v>0.010671412371288</v>
+        <v>0.01067141237128801</v>
       </c>
       <c r="I8" t="n">
         <v>0.01133721499050267</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01192813983327586</v>
+        <v>0.01192813983327588</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01287667642609838</v>
+        <v>0.01287667642609839</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01262073460713725</v>
+        <v>0.01262073460713727</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01619666263011435</v>
+        <v>0.01619666263011437</v>
       </c>
       <c r="N8" t="n">
         <v>0.01045616716394199</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01053838870185203</v>
+        <v>0.01053838870185204</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01049718883317992</v>
+        <v>0.01049718883317993</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.009294523654397131</v>
+        <v>0.009294523654397143</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01071932494258107</v>
+        <v>0.01071932494258108</v>
       </c>
       <c r="S8" t="n">
         <v>0.01191155154475716</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01172303252057846</v>
+        <v>0.01172303252057847</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01335656927685271</v>
+        <v>0.01335656927685272</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0103391498735619</v>
+        <v>0.01033914987356191</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01252193302356309</v>
+        <v>0.0125219330235631</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0119029964470947</v>
+        <v>0.01190299644709471</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01480215114466819</v>
+        <v>0.0148021511446682</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.009633795388877882</v>
+        <v>0.009633795388877891</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01214634855960181</v>
+        <v>0.01214634855960182</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01737410810073392</v>
+        <v>0.01737410810073393</v>
       </c>
     </row>
     <row r="9">
@@ -2922,16 +2922,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01050473586472888</v>
+        <v>0.01050473586472889</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00996638160292064</v>
+        <v>0.009966381602920644</v>
       </c>
       <c r="D9" t="n">
         <v>0.01171786481547671</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01014833513793589</v>
+        <v>0.0101483351379359</v>
       </c>
       <c r="F9" t="n">
         <v>0.008836893484095321</v>
@@ -2943,13 +2943,13 @@
         <v>0.01003377782889948</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01069958044811414</v>
+        <v>0.01069958044811415</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01129050529088735</v>
+        <v>0.01129050529088736</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01223904188370986</v>
+        <v>0.01223904188370987</v>
       </c>
       <c r="L9" t="n">
         <v>0.01198310006474873</v>
@@ -2958,13 +2958,13 @@
         <v>0.0155590280877256</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01091222040767749</v>
+        <v>0.0109122204076775</v>
       </c>
       <c r="O9" t="n">
         <v>0.010908826026559</v>
       </c>
       <c r="P9" t="n">
-        <v>0.01098804517392441</v>
+        <v>0.01098804517392443</v>
       </c>
       <c r="Q9" t="n">
         <v>0.01034506876890358</v>
@@ -2973,7 +2973,7 @@
         <v>0.01008169040019255</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01127391700236863</v>
+        <v>0.01127391700236865</v>
       </c>
       <c r="T9" t="n">
         <v>0.01108539797818994</v>
@@ -2988,19 +2988,19 @@
         <v>0.01188402119785846</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01282423022280165</v>
+        <v>0.01282423022280166</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.01276215697693618</v>
+        <v>0.01276215697693617</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.01004223510937602</v>
+        <v>0.01004223510937603</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.01150871401721329</v>
+        <v>0.0115087140172133</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.01526266480683436</v>
+        <v>0.01526266480683437</v>
       </c>
     </row>
   </sheetData>
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003994566075216616</v>
+        <v>0.003994566075216604</v>
       </c>
       <c r="C2" t="n">
         <v>0.003521763962937453</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004104246026388356</v>
+        <v>0.004104246026388344</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003948763468802644</v>
+        <v>0.003948763468802636</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003950727475349819</v>
+        <v>0.003950727475349806</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003983737821440288</v>
+        <v>0.003983737821440281</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003901777856795481</v>
+        <v>0.00390177785679547</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0040207170681268</v>
+        <v>0.004020717068126789</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004035382589679574</v>
+        <v>0.004035382589679563</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004073223503473236</v>
+        <v>0.004073223503473223</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004064533138609721</v>
+        <v>0.004064533138609717</v>
       </c>
       <c r="M2" t="n">
-        <v>0.004346266327354474</v>
+        <v>0.004346266327354472</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003964842312573338</v>
+        <v>0.003964842312573326</v>
       </c>
       <c r="O2" t="n">
-        <v>0.005726995297872796</v>
+        <v>0.005726995297872794</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003977921493915357</v>
+        <v>0.003977921493915346</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003942433930689938</v>
+        <v>0.003942433930689923</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003908058047717617</v>
+        <v>0.003908058047717602</v>
       </c>
       <c r="S2" t="n">
-        <v>0.004022092996012962</v>
+        <v>0.004022092996012947</v>
       </c>
       <c r="T2" t="n">
-        <v>0.004005576383600731</v>
+        <v>0.004005576383600719</v>
       </c>
       <c r="U2" t="n">
-        <v>0.004177369872237376</v>
+        <v>0.004177369872237365</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003943784428996087</v>
+        <v>0.003943784428996074</v>
       </c>
       <c r="W2" t="n">
-        <v>0.004028736351977562</v>
+        <v>0.004028736351977557</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004443119376221692</v>
+        <v>0.004443119376221679</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.004443832545178135</v>
+        <v>0.004443832545178123</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.004974036989107623</v>
+        <v>0.004974036989107617</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.004058914240346227</v>
+        <v>0.004058914240346218</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.00436170197465403</v>
+        <v>0.004361701974654028</v>
       </c>
     </row>
     <row r="3">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004366661107652958</v>
+        <v>0.004394742372985794</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003132414567038808</v>
+        <v>0.003139775399763256</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005155940732555356</v>
+        <v>0.005212292912879808</v>
       </c>
       <c r="E3" t="n">
-        <v>0.004040778793970111</v>
+        <v>0.004057250901363889</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004057612810175433</v>
+        <v>0.004075059488451835</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004289467390136524</v>
+        <v>0.00431485469626389</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00370771278861456</v>
+        <v>0.003712675195379298</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004559265476039721</v>
+        <v>0.004594469887443064</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004660718088716797</v>
+        <v>0.004699392094782802</v>
       </c>
       <c r="K3" t="n">
-        <v>0.004926225239602007</v>
+        <v>0.00497463282880858</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004868016261145678</v>
+        <v>0.004913870754684894</v>
       </c>
       <c r="M3" t="n">
-        <v>0.006871618056570643</v>
+        <v>0.006989071190783039</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004157904655258583</v>
+        <v>0.004178774078111297</v>
       </c>
       <c r="O3" t="n">
-        <v>0.007037997472512392</v>
+        <v>0.007057488872421602</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004247991143788182</v>
+        <v>0.004271866165190192</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003997421687418656</v>
+        <v>0.004012647922737766</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003752564866536732</v>
+        <v>0.003759118031222245</v>
       </c>
       <c r="S3" t="n">
-        <v>0.004562632950367265</v>
+        <v>0.004597700932134041</v>
       </c>
       <c r="T3" t="n">
-        <v>0.004450481357447487</v>
+        <v>0.004481796562983229</v>
       </c>
       <c r="U3" t="n">
-        <v>0.005693975684289502</v>
+        <v>0.005769256156189591</v>
       </c>
       <c r="V3" t="n">
-        <v>0.004004784462544813</v>
+        <v>0.004020192591806075</v>
       </c>
       <c r="W3" t="n">
-        <v>0.004833854261760797</v>
+        <v>0.004880884148247189</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00757728267854087</v>
+        <v>0.007719552249383743</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.007575037038004708</v>
+        <v>0.007716786238150828</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.005793366436081759</v>
+        <v>0.005812817680797891</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.004828936955748124</v>
+        <v>0.004873484951365491</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.006980201644754008</v>
+        <v>0.007100756317897356</v>
       </c>
     </row>
     <row r="4">
@@ -3342,61 +3342,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.007975770326985274</v>
+        <v>0.007975770326985276</v>
       </c>
       <c r="C4" t="n">
         <v>0.007035780572255175</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009214655830740383</v>
+        <v>0.009214655830740385</v>
       </c>
       <c r="E4" t="n">
-        <v>0.007458408817299548</v>
+        <v>0.007458408817299545</v>
       </c>
       <c r="F4" t="n">
-        <v>0.007480593174737513</v>
+        <v>0.007480593174737511</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007853460219338802</v>
+        <v>0.007853460219338804</v>
       </c>
       <c r="H4" t="n">
-        <v>0.006927684715229261</v>
+        <v>0.006927684715229263</v>
       </c>
       <c r="I4" t="n">
-        <v>0.008271157821956927</v>
+        <v>0.008271157821956931</v>
       </c>
       <c r="J4" t="n">
-        <v>0.008433344915236844</v>
+        <v>0.00843334491523684</v>
       </c>
       <c r="K4" t="n">
         <v>0.008864242163348504</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008766080494449786</v>
+        <v>0.008766080494449808</v>
       </c>
       <c r="M4" t="n">
         <v>0.01191288500804202</v>
       </c>
       <c r="N4" t="n">
-        <v>0.00764002675432309</v>
+        <v>0.007640026754323086</v>
       </c>
       <c r="O4" t="n">
         <v>0.007588601155589946</v>
       </c>
       <c r="P4" t="n">
-        <v>0.007787762124301894</v>
+        <v>0.007787762124301892</v>
       </c>
       <c r="Q4" t="n">
         <v>0.007386913772585118</v>
       </c>
       <c r="R4" t="n">
-        <v>0.006998622360725297</v>
+        <v>0.006998622360725301</v>
       </c>
       <c r="S4" t="n">
-        <v>0.008286699560389216</v>
+        <v>0.008286699560389221</v>
       </c>
       <c r="T4" t="n">
-        <v>0.008100136825175977</v>
+        <v>0.008100136825175975</v>
       </c>
       <c r="U4" t="n">
         <v>0.01007105754889803</v>
@@ -3411,16 +3411,16 @@
         <v>0.01304238620655057</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.01303106922579694</v>
+        <v>0.01303106922579695</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.007584983642889454</v>
+        <v>0.00758498364288946</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.008702612453742655</v>
+        <v>0.008702612453742658</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.01206924119309312</v>
+        <v>0.01206924119309313</v>
       </c>
     </row>
     <row r="5">
@@ -3430,82 +3430,82 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02761209780596929</v>
+        <v>0.02761209780596945</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01245326177926405</v>
+        <v>0.01245326177926406</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05288625308678493</v>
+        <v>0.05288625308678496</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01898675634158539</v>
+        <v>0.01898675634158537</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0208388604320262</v>
+        <v>0.02083886043202618</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02549448151019955</v>
+        <v>0.02549448151019936</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0107777680762934</v>
+        <v>0.01077776807629339</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03592690879694004</v>
+        <v>0.03592690879694007</v>
       </c>
       <c r="J5" t="n">
         <v>0.03718672065028877</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04238413113682186</v>
+        <v>0.04238413113682189</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04262479409825114</v>
+        <v>0.04262479409825129</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1045759108827799</v>
+        <v>0.10457591088278</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0234273440156764</v>
+        <v>0.02342734401567639</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02060807100604825</v>
+        <v>0.02060807100604821</v>
       </c>
       <c r="P5" t="n">
-        <v>0.02435072988459291</v>
+        <v>0.0243507298845929</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0186639262213148</v>
+        <v>0.01866392622131478</v>
       </c>
       <c r="R5" t="n">
         <v>0.0120479860188144</v>
       </c>
       <c r="S5" t="n">
-        <v>0.03285789788928769</v>
+        <v>0.03285789788928767</v>
       </c>
       <c r="T5" t="n">
-        <v>0.03252677098952756</v>
+        <v>0.0325267709895276</v>
       </c>
       <c r="U5" t="n">
-        <v>0.06418549885485614</v>
+        <v>0.0641854988548559</v>
       </c>
       <c r="V5" t="n">
-        <v>0.01773092587376966</v>
+        <v>0.01773092587376961</v>
       </c>
       <c r="W5" t="n">
-        <v>0.04399537881621735</v>
+        <v>0.04399537881621739</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1220297315282964</v>
+        <v>0.1220297315282963</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1183707378645815</v>
+        <v>0.1183707378645817</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.02055526951575408</v>
+        <v>0.02055526951575415</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.04203242766514147</v>
+        <v>0.0420324276651415</v>
       </c>
       <c r="AB5" t="n">
         <v>0.1115889521024308</v>
@@ -3521,7 +3521,7 @@
         <v>0.009025720763750507</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007327718798030919</v>
+        <v>0.007327718798030918</v>
       </c>
       <c r="D6" t="n">
         <v>0.01026460626750562</v>
@@ -3530,7 +3530,7 @@
         <v>0.008508359254064781</v>
       </c>
       <c r="F6" t="n">
-        <v>0.007772531400513261</v>
+        <v>0.00777253140051326</v>
       </c>
       <c r="G6" t="n">
         <v>0.008145398445114544</v>
@@ -3539,40 +3539,40 @@
         <v>0.007219622941005008</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008563096047732676</v>
+        <v>0.008563096047732678</v>
       </c>
       <c r="J6" t="n">
-        <v>0.009483295352002083</v>
+        <v>0.009483295352002079</v>
       </c>
       <c r="K6" t="n">
         <v>0.009914192600113737</v>
       </c>
       <c r="L6" t="n">
-        <v>0.009816030931215041</v>
+        <v>0.009816030931215044</v>
       </c>
       <c r="M6" t="n">
         <v>0.01220482323381776</v>
       </c>
       <c r="N6" t="n">
-        <v>0.007937797790489578</v>
+        <v>0.00793779779048957</v>
       </c>
       <c r="O6" t="n">
-        <v>0.008639860251791431</v>
+        <v>0.008639860251791432</v>
       </c>
       <c r="P6" t="n">
-        <v>0.008839292396593861</v>
+        <v>0.008839292396593862</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.008436864209350347</v>
+        <v>0.00843686420935035</v>
       </c>
       <c r="R6" t="n">
-        <v>0.007290560586501044</v>
+        <v>0.007290560586501045</v>
       </c>
       <c r="S6" t="n">
-        <v>0.009336649997154453</v>
+        <v>0.009336649997154459</v>
       </c>
       <c r="T6" t="n">
-        <v>0.008392075050951721</v>
+        <v>0.008392075050951723</v>
       </c>
       <c r="U6" t="n">
         <v>0.01038236832686444</v>
@@ -3581,22 +3581,22 @@
         <v>0.008428692361907745</v>
       </c>
       <c r="W6" t="n">
-        <v>0.009866672309704084</v>
+        <v>0.00986667230970408</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01333432443232632</v>
+        <v>0.01333432443232633</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01336600011451572</v>
+        <v>0.01336600011451571</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.008634934079654688</v>
+        <v>0.008634934079654689</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.009752562890507896</v>
+        <v>0.009752562890507901</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01242645231025853</v>
+        <v>0.01242645231025854</v>
       </c>
     </row>
     <row r="7">
@@ -3606,43 +3606,43 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.008598824332920196</v>
+        <v>0.008598824332920202</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007658834578190095</v>
+        <v>0.007658834578190096</v>
       </c>
       <c r="D7" t="n">
         <v>0.009837709836675309</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00808146282323447</v>
+        <v>0.008081462823234468</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008103647180672434</v>
+        <v>0.008103647180672437</v>
       </c>
       <c r="G7" t="n">
         <v>0.008476514225273724</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007550738721164183</v>
+        <v>0.007550738721164184</v>
       </c>
       <c r="I7" t="n">
-        <v>0.008894211827891851</v>
+        <v>0.008894211827891855</v>
       </c>
       <c r="J7" t="n">
-        <v>0.009056398921171766</v>
+        <v>0.009056398921171771</v>
       </c>
       <c r="K7" t="n">
         <v>0.00948729616928343</v>
       </c>
       <c r="L7" t="n">
-        <v>0.009389134500384718</v>
+        <v>0.009389134500384727</v>
       </c>
       <c r="M7" t="n">
         <v>0.01253593901397694</v>
       </c>
       <c r="N7" t="n">
-        <v>0.008263080760258012</v>
+        <v>0.008263080760258014</v>
       </c>
       <c r="O7" t="n">
         <v>0.00821163277228025</v>
@@ -3651,40 +3651,40 @@
         <v>0.008410793740992196</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.008009967778520042</v>
+        <v>0.008009967778520043</v>
       </c>
       <c r="R7" t="n">
-        <v>0.00762167636666022</v>
+        <v>0.007621676366660225</v>
       </c>
       <c r="S7" t="n">
-        <v>0.008909753566324138</v>
+        <v>0.008909753566324142</v>
       </c>
       <c r="T7" t="n">
-        <v>0.008723190831110896</v>
+        <v>0.008723190831110898</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01071268844020144</v>
+        <v>0.01071268844020142</v>
       </c>
       <c r="V7" t="n">
         <v>0.00800179593107744</v>
       </c>
       <c r="W7" t="n">
-        <v>0.009438477104760689</v>
+        <v>0.009438477104760696</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01366544021248547</v>
+        <v>0.01366544021248548</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01367349578392253</v>
+        <v>0.01367349578392254</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.008208037648824374</v>
+        <v>0.008208037648824384</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.009325666459677581</v>
+        <v>0.009325666459677582</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01269229519902804</v>
+        <v>0.01269229519902805</v>
       </c>
     </row>
     <row r="8">
@@ -3694,25 +3694,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0098694463234402</v>
+        <v>0.009869446323440202</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01022962112352967</v>
+        <v>0.01022962112352968</v>
       </c>
       <c r="D8" t="n">
         <v>0.01240849638201489</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009959950095593301</v>
+        <v>0.009959950095593298</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009576819613486571</v>
+        <v>0.009576819613486573</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01131689836083737</v>
+        <v>0.01131689836083736</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01012152526650376</v>
+        <v>0.01012152526650377</v>
       </c>
       <c r="I8" t="n">
         <v>0.01146499837323143</v>
@@ -3724,19 +3724,19 @@
         <v>0.012058082714623</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01195992104572429</v>
+        <v>0.0119599210457243</v>
       </c>
       <c r="M8" t="n">
         <v>0.01510672555931704</v>
       </c>
       <c r="N8" t="n">
-        <v>0.009826022262814347</v>
+        <v>0.009826022262814349</v>
       </c>
       <c r="O8" t="n">
         <v>0.01005156123279826</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01018283149331645</v>
+        <v>0.01018283149331646</v>
       </c>
       <c r="Q8" t="n">
         <v>0.009025077759218325</v>
@@ -3763,16 +3763,16 @@
         <v>0.01479971285808417</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0175359811738891</v>
+        <v>0.01753598117388911</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.009454508415236002</v>
+        <v>0.009454508415236006</v>
       </c>
       <c r="AA8" t="n">
         <v>0.01189645300501717</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01662121233984538</v>
+        <v>0.01662121233984539</v>
       </c>
     </row>
     <row r="9">
@@ -3791,13 +3791,13 @@
         <v>0.01168507654457681</v>
       </c>
       <c r="E9" t="n">
-        <v>0.009797678977897876</v>
+        <v>0.009797678977897883</v>
       </c>
       <c r="F9" t="n">
         <v>0.008641041278719605</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01032388021756239</v>
+        <v>0.01032388021756238</v>
       </c>
       <c r="H9" t="n">
         <v>0.009398105429065688</v>
@@ -3812,10 +3812,10 @@
         <v>0.01133466287718493</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01123650120828622</v>
+        <v>0.01123650120828624</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01438330572187845</v>
+        <v>0.01438330572187846</v>
       </c>
       <c r="N9" t="n">
         <v>0.01011044746815952</v>
@@ -3824,13 +3824,13 @@
         <v>0.01024733853940966</v>
       </c>
       <c r="P9" t="n">
-        <v>0.01048745530850653</v>
+        <v>0.01048745530850654</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.00985733377080871</v>
+        <v>0.009857333770808708</v>
       </c>
       <c r="R9" t="n">
-        <v>0.009469043074561721</v>
+        <v>0.009469043074561726</v>
       </c>
       <c r="S9" t="n">
         <v>0.01075712027422565</v>
@@ -3839,7 +3839,7 @@
         <v>0.0105705575390124</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01256085081492514</v>
+        <v>0.01256085081492512</v>
       </c>
       <c r="V9" t="n">
         <v>0.01050490987070329</v>
@@ -3854,13 +3854,13 @@
         <v>0.01552086249182403</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.009712799276957125</v>
+        <v>0.009712799276957134</v>
       </c>
       <c r="AA9" t="n">
         <v>0.01117303316757909</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.01453966190692954</v>
+        <v>0.01453966190692955</v>
       </c>
     </row>
   </sheetData>
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003974342344336124</v>
+        <v>0.003974342344336123</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003480025254382845</v>
+        <v>0.003480025254382842</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004035819590429873</v>
+        <v>0.004035819590429867</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003926842479771572</v>
+        <v>0.003926842479771567</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003955734916750235</v>
+        <v>0.003955734916750229</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003968648396365589</v>
+        <v>0.003968648396365584</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003897944013643523</v>
+        <v>0.003897944013643516</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004016300752072321</v>
+        <v>0.004016300752072315</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004026582628959283</v>
+        <v>0.00402658262895928</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00410248986632704</v>
+        <v>0.004102489866327035</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004031728522204714</v>
+        <v>0.00403172852220471</v>
       </c>
       <c r="M2" t="n">
-        <v>0.004262399105687042</v>
+        <v>0.004262399105687041</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003935238995352395</v>
+        <v>0.003935238995352391</v>
       </c>
       <c r="O2" t="n">
-        <v>0.005687728720697318</v>
+        <v>0.00568772872069731</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003960764707794989</v>
+        <v>0.003960764707794984</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003939220700154207</v>
+        <v>0.003939220700154202</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003924533547495628</v>
+        <v>0.003924533547495627</v>
       </c>
       <c r="S2" t="n">
-        <v>0.00401078602256405</v>
+        <v>0.004010786022564047</v>
       </c>
       <c r="T2" t="n">
-        <v>0.004001622626480112</v>
+        <v>0.004001622626480108</v>
       </c>
       <c r="U2" t="n">
-        <v>0.004086888749550313</v>
+        <v>0.004086888749550308</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003970234574966038</v>
+        <v>0.003970234574966034</v>
       </c>
       <c r="W2" t="n">
-        <v>0.003901051632388439</v>
+        <v>0.003901051632388431</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004550956177447637</v>
+        <v>0.004550956177447634</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.004741848481448843</v>
+        <v>0.004741848481448842</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.004955867350207294</v>
+        <v>0.004955867350207291</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.004066742485299928</v>
+        <v>0.004066742485299923</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.004302847102272584</v>
+        <v>0.004302847102272581</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004252657145798201</v>
+        <v>0.004276697165050103</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003071644579769125</v>
+        <v>0.0030789905450038</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004694941953013611</v>
+        <v>0.004734948642078193</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003914500343359146</v>
+        <v>0.003926478011571801</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004124129203694275</v>
+        <v>0.00414388922326878</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004212078431478547</v>
+        <v>0.00423470665493325</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003711217665844779</v>
+        <v>0.003716237309318117</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004557684488400045</v>
+        <v>0.004592797820663365</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004627481261757199</v>
+        <v>0.004664980781562185</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005165158207490578</v>
+        <v>0.005222016343434607</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004662816368262747</v>
+        <v>0.004701438471583811</v>
       </c>
       <c r="M3" t="n">
-        <v>0.006300052859725805</v>
+        <v>0.006397348751105134</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003977285082549359</v>
+        <v>0.003991695163477673</v>
       </c>
       <c r="O3" t="n">
-        <v>0.006879242905834499</v>
+        <v>0.006894027998872485</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004155964590499594</v>
+        <v>0.004176571711327428</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.00400488079783344</v>
+        <v>0.004020321225711753</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003901670646472604</v>
+        <v>0.003913458703311865</v>
       </c>
       <c r="S3" t="n">
-        <v>0.00451238355549877</v>
+        <v>0.004545634012113151</v>
       </c>
       <c r="T3" t="n">
-        <v>0.004453181459585459</v>
+        <v>0.004484523273764147</v>
       </c>
       <c r="U3" t="n">
-        <v>0.005672729110890631</v>
+        <v>0.005753687338826457</v>
       </c>
       <c r="V3" t="n">
-        <v>0.004222818354617458</v>
+        <v>0.004245867697758266</v>
       </c>
       <c r="W3" t="n">
-        <v>0.004471958408658458</v>
+        <v>0.004511649646923114</v>
       </c>
       <c r="X3" t="n">
-        <v>0.008370924285599919</v>
+        <v>0.008541581125897122</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.009739148290660773</v>
+        <v>0.009957151555836985</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.005721245459328412</v>
+        <v>0.005738410269152653</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.004916087463002084</v>
+        <v>0.004963633892960435</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.006589882115844945</v>
+        <v>0.006696670204470995</v>
       </c>
     </row>
     <row r="4">
@@ -4202,67 +4202,67 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.007809545180607822</v>
+        <v>0.007809545180607818</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007051484841024359</v>
+        <v>0.007051484841024355</v>
       </c>
       <c r="D4" t="n">
-        <v>0.008503958956167158</v>
+        <v>0.008503958956167151</v>
       </c>
       <c r="E4" t="n">
-        <v>0.007273012359333963</v>
+        <v>0.00727301235933396</v>
       </c>
       <c r="F4" t="n">
-        <v>0.007599365726185611</v>
+        <v>0.007599365726185605</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007745229418935152</v>
+        <v>0.007745229418935145</v>
       </c>
       <c r="H4" t="n">
-        <v>0.006946590890466399</v>
+        <v>0.006946590890466397</v>
       </c>
       <c r="I4" t="n">
-        <v>0.008283484697809294</v>
+        <v>0.008283484697809288</v>
       </c>
       <c r="J4" t="n">
-        <v>0.008396606771908817</v>
+        <v>0.008396606771908814</v>
       </c>
       <c r="K4" t="n">
         <v>0.00925703039226781</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008457748458579585</v>
+        <v>0.008457748458579582</v>
       </c>
       <c r="M4" t="n">
         <v>0.01103604525879262</v>
       </c>
       <c r="N4" t="n">
-        <v>0.007367854865407341</v>
+        <v>0.007367854865407342</v>
       </c>
       <c r="O4" t="n">
-        <v>0.007392097510920872</v>
+        <v>0.007392097510920865</v>
       </c>
       <c r="P4" t="n">
-        <v>0.007656179529854278</v>
+        <v>0.007656179529854272</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.007412830052818475</v>
+        <v>0.007412830052818472</v>
       </c>
       <c r="R4" t="n">
-        <v>0.007246931907115833</v>
+        <v>0.007246931907115832</v>
       </c>
       <c r="S4" t="n">
-        <v>0.008221193291112495</v>
+        <v>0.00822119329111249</v>
       </c>
       <c r="T4" t="n">
-        <v>0.008117688516973916</v>
+        <v>0.008117688516973915</v>
       </c>
       <c r="U4" t="n">
         <v>0.01034837072050078</v>
       </c>
       <c r="V4" t="n">
-        <v>0.007742754709384793</v>
+        <v>0.007742754709384789</v>
       </c>
       <c r="W4" t="n">
         <v>0.008502872825463312</v>
@@ -4271,13 +4271,13 @@
         <v>0.01432266368107065</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.01646531844414828</v>
+        <v>0.01646531844414827</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.007498151554938345</v>
+        <v>0.007498151554938342</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.008853247278958865</v>
+        <v>0.008853247278958861</v>
       </c>
       <c r="AB4" t="n">
         <v>0.01147339711442709</v>
@@ -4293,82 +4293,82 @@
         <v>0.02410140197170524</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01241377558846663</v>
+        <v>0.01241377558846662</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0382067000350749</v>
+        <v>0.03820670003507486</v>
       </c>
       <c r="E5" t="n">
         <v>0.01505351236627351</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02259902544226453</v>
+        <v>0.02259902544226456</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02299458998702825</v>
+        <v>0.02299458998702822</v>
       </c>
       <c r="H5" t="n">
         <v>0.01081784272595765</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03536932857122993</v>
+        <v>0.03536932857122992</v>
       </c>
       <c r="J5" t="n">
         <v>0.03556232188918416</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04861730493940952</v>
+        <v>0.0486173049394094</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03587232627982847</v>
+        <v>0.03587232627982848</v>
       </c>
       <c r="M5" t="n">
-        <v>0.08444089321485711</v>
+        <v>0.08444089321485712</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01821224625945391</v>
+        <v>0.01821224625945388</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01728207843246073</v>
+        <v>0.01728207843246071</v>
       </c>
       <c r="P5" t="n">
-        <v>0.02149859255996994</v>
+        <v>0.02149859255997005</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01858177242066292</v>
+        <v>0.01858177242066295</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01648337720003966</v>
+        <v>0.01648337720003965</v>
       </c>
       <c r="S5" t="n">
-        <v>0.03118829386816925</v>
+        <v>0.03118829386816922</v>
       </c>
       <c r="T5" t="n">
-        <v>0.03256934829970643</v>
+        <v>0.03256934829970638</v>
       </c>
       <c r="U5" t="n">
-        <v>0.06640566400721362</v>
+        <v>0.06640566400721358</v>
       </c>
       <c r="V5" t="n">
-        <v>0.02299014399485125</v>
+        <v>0.02299014399485121</v>
       </c>
       <c r="W5" t="n">
-        <v>0.03818914399193572</v>
+        <v>0.03818914399193573</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1408230641245802</v>
+        <v>0.1408230641245803</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1819733633418559</v>
+        <v>0.1819733633418558</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01841248699824172</v>
+        <v>0.01841248699824171</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.04461622557243105</v>
+        <v>0.04461622557243109</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.09827010538445477</v>
+        <v>0.09827010538445487</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.008112367246076054</v>
+        <v>0.008112367246076049</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007354306906492594</v>
+        <v>0.007354306906492586</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009540329555873075</v>
+        <v>0.009540329555873065</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008309382959039879</v>
+        <v>0.008309382959039871</v>
       </c>
       <c r="F6" t="n">
-        <v>0.007902187791653843</v>
+        <v>0.007902187791653841</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008048051484403386</v>
+        <v>0.008048051484403374</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00798296149017232</v>
+        <v>0.007982961490172313</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00858630676327753</v>
+        <v>0.008586306763277523</v>
       </c>
       <c r="J6" t="n">
-        <v>0.009432977371614738</v>
+        <v>0.009432977371614731</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01029340099197374</v>
+        <v>0.01029340099197373</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008760570524047821</v>
+        <v>0.008760570524047818</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01133886732426086</v>
+        <v>0.01133886732426085</v>
       </c>
       <c r="N6" t="n">
-        <v>0.007680201604957484</v>
+        <v>0.007680201604957516</v>
       </c>
       <c r="O6" t="n">
-        <v>0.00773738699805751</v>
+        <v>0.007737386998057522</v>
       </c>
       <c r="P6" t="n">
-        <v>0.008695712688338221</v>
+        <v>0.008695712688338216</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.008449200652524393</v>
+        <v>0.008449200652524387</v>
       </c>
       <c r="R6" t="n">
-        <v>0.008283302506821761</v>
+        <v>0.008283302506821749</v>
       </c>
       <c r="S6" t="n">
-        <v>0.008524015356580728</v>
+        <v>0.008524015356580723</v>
       </c>
       <c r="T6" t="n">
         <v>0.009154059116679828</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01139830294562106</v>
+        <v>0.01139830294562105</v>
       </c>
       <c r="V6" t="n">
         <v>0.008045576774853019</v>
       </c>
       <c r="W6" t="n">
-        <v>0.008836390526106599</v>
+        <v>0.008836390526106592</v>
       </c>
       <c r="X6" t="n">
         <v>0.01462548574653887</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01681419219972048</v>
+        <v>0.01681419219972049</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.00780097362040658</v>
+        <v>0.007800973620406574</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.009889617878664774</v>
+        <v>0.009889617878664773</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0117995527092367</v>
+        <v>0.01179955270923668</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.008430049220740954</v>
+        <v>0.00843004922074095</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007671988881157494</v>
+        <v>0.007671988881157487</v>
       </c>
       <c r="D7" t="n">
-        <v>0.009124462996300292</v>
+        <v>0.009124462996300282</v>
       </c>
       <c r="E7" t="n">
-        <v>0.007893516399467098</v>
+        <v>0.007893516399467093</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008219869766318749</v>
+        <v>0.008219869766318744</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008365733459068291</v>
+        <v>0.008365733459068287</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007567094930599534</v>
+        <v>0.00756709493059953</v>
       </c>
       <c r="I7" t="n">
-        <v>0.008903988737942426</v>
+        <v>0.008903988737942417</v>
       </c>
       <c r="J7" t="n">
-        <v>0.009017110812041951</v>
+        <v>0.009017110812041949</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00987753443240095</v>
+        <v>0.009877534432400945</v>
       </c>
       <c r="L7" t="n">
-        <v>0.009078252498712719</v>
+        <v>0.009078252498712714</v>
       </c>
       <c r="M7" t="n">
         <v>0.01165654929892577</v>
       </c>
       <c r="N7" t="n">
-        <v>0.007988358905540484</v>
+        <v>0.007988358905540479</v>
       </c>
       <c r="O7" t="n">
-        <v>0.008012578918186708</v>
+        <v>0.008012578918186694</v>
       </c>
       <c r="P7" t="n">
-        <v>0.008276660937120104</v>
+        <v>0.008276660937120098</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.00803333409295161</v>
+        <v>0.008033334092951608</v>
       </c>
       <c r="R7" t="n">
         <v>0.007867435947248971</v>
       </c>
       <c r="S7" t="n">
-        <v>0.008841697331245631</v>
+        <v>0.008841697331245625</v>
       </c>
       <c r="T7" t="n">
-        <v>0.008738192557107055</v>
+        <v>0.00873819255710705</v>
       </c>
       <c r="U7" t="n">
         <v>0.01098142567599258</v>
       </c>
       <c r="V7" t="n">
-        <v>0.008363258749517927</v>
+        <v>0.008363258749517922</v>
       </c>
       <c r="W7" t="n">
-        <v>0.009123376865596463</v>
+        <v>0.009123376865596456</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01494316772120376</v>
+        <v>0.01494316772120377</v>
       </c>
       <c r="Y7" t="n">
         <v>0.01709938410969577</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.008118655595071481</v>
+        <v>0.008118655595071475</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.009473751319091993</v>
+        <v>0.00947375131909199</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01209390115456024</v>
+        <v>0.01209390115456023</v>
       </c>
     </row>
     <row r="8">
@@ -4554,19 +4554,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.009694356854384948</v>
+        <v>0.009694356854384944</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01022936809857665</v>
+        <v>0.01022936809857664</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01168184221371946</v>
+        <v>0.01168184221371944</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009762373141755511</v>
+        <v>0.009762373141755506</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009685622840266231</v>
+        <v>0.009685622840266228</v>
       </c>
       <c r="G8" t="n">
         <v>0.01119123949295944</v>
@@ -4575,64 +4575,64 @@
         <v>0.01012447414801869</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01146136795536159</v>
+        <v>0.01146136795536158</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01157449002946112</v>
+        <v>0.01157449002946111</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0124349136498201</v>
+        <v>0.01243491364982009</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01163563171613188</v>
+        <v>0.01163563171613187</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01421392851634566</v>
+        <v>0.01421392851634565</v>
       </c>
       <c r="N8" t="n">
-        <v>0.009543391319365794</v>
+        <v>0.009543391319365789</v>
       </c>
       <c r="O8" t="n">
-        <v>0.009843087569730374</v>
+        <v>0.009843087569730371</v>
       </c>
       <c r="P8" t="n">
         <v>0.01003964925422312</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.009043523647471186</v>
+        <v>0.009043523647471179</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01042481516466814</v>
+        <v>0.01042481516466813</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01139907654866478</v>
+        <v>0.01139907654866477</v>
       </c>
       <c r="T8" t="n">
         <v>0.01129557177452621</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01290791888628441</v>
+        <v>0.0129079188862844</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01056637742200253</v>
+        <v>0.01056637742200252</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01168101020861469</v>
+        <v>0.01168101020861468</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01607186985573822</v>
+        <v>0.01607186985573823</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.02094112501988351</v>
+        <v>0.0209411250198835</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.009358943760185028</v>
+        <v>0.009358943760185022</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01203113053651115</v>
+        <v>0.01203113053651114</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01600200176610372</v>
+        <v>0.01600200176610371</v>
       </c>
     </row>
     <row r="9">
@@ -4642,85 +4642,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.009614233376381382</v>
+        <v>0.009614233376381386</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00939682908126066</v>
+        <v>0.009396829081260657</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01084930319640347</v>
+        <v>0.01084930319640345</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00949357493411114</v>
+        <v>0.009493574934111133</v>
       </c>
       <c r="F9" t="n">
-        <v>0.008698350998172616</v>
+        <v>0.008698350998172609</v>
       </c>
       <c r="G9" t="n">
         <v>0.01009057306675006</v>
       </c>
       <c r="H9" t="n">
-        <v>0.009291935130702702</v>
+        <v>0.009291935130702696</v>
       </c>
       <c r="I9" t="n">
         <v>0.01062882893804559</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01074195101214513</v>
+        <v>0.01074195101214512</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01160237463250412</v>
+        <v>0.01160237463250411</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01080309269881589</v>
+        <v>0.01080309269881588</v>
       </c>
       <c r="M9" t="n">
         <v>0.01338138949902892</v>
       </c>
       <c r="N9" t="n">
-        <v>0.009713199105643645</v>
+        <v>0.009713199105643635</v>
       </c>
       <c r="O9" t="n">
-        <v>0.009916613667614394</v>
+        <v>0.00991661366761438</v>
       </c>
       <c r="P9" t="n">
-        <v>0.01021966263314634</v>
+        <v>0.01021966263314633</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.009758173700633378</v>
+        <v>0.009758173700633367</v>
       </c>
       <c r="R9" t="n">
-        <v>0.009592276147352139</v>
+        <v>0.009592276147352138</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0105665375313488</v>
+        <v>0.01056653753134879</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01046303275721023</v>
+        <v>0.01046303275721022</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01270727658615145</v>
+        <v>0.01270727658615143</v>
       </c>
       <c r="V9" t="n">
-        <v>0.01071200266889507</v>
+        <v>0.01071200266889506</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01084821706569963</v>
+        <v>0.01084821706569962</v>
       </c>
       <c r="X9" t="n">
         <v>0.01666800792130696</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.01882422430979896</v>
+        <v>0.01882422430979894</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.009517528042130944</v>
+        <v>0.009517528042130937</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.01119859151919517</v>
+        <v>0.01119859151919516</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.01381874135466341</v>
+        <v>0.01381874135466339</v>
       </c>
     </row>
   </sheetData>
@@ -4889,82 +4889,82 @@
         <v>0.00378061197692846</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003375213241705778</v>
+        <v>0.003375213241705777</v>
       </c>
       <c r="D2" t="n">
         <v>0.003832814918836051</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003787387430864775</v>
+        <v>0.003787387430864776</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003772874465822173</v>
+        <v>0.003772874465822172</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003791082764287807</v>
+        <v>0.003791082764287808</v>
       </c>
       <c r="H2" t="n">
         <v>0.003786910752904397</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003800536325240289</v>
+        <v>0.003800536325240291</v>
       </c>
       <c r="J2" t="n">
         <v>0.003812497952738607</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00385658518638563</v>
+        <v>0.003856585186385629</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003830353303445491</v>
+        <v>0.003830353303445492</v>
       </c>
       <c r="M2" t="n">
-        <v>0.00392699509481379</v>
+        <v>0.003926995094813792</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003826848654270893</v>
+        <v>0.003826848654270895</v>
       </c>
       <c r="O2" t="n">
         <v>0.005476357971210832</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003805660662198954</v>
+        <v>0.003805660662198955</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003792616016020762</v>
+        <v>0.003792616016020763</v>
       </c>
       <c r="R2" t="n">
         <v>0.003784127299252832</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003796310080381286</v>
+        <v>0.003796310080381288</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003787309446181521</v>
+        <v>0.003787309446181524</v>
       </c>
       <c r="U2" t="n">
-        <v>0.003854892520862564</v>
+        <v>0.003854892520862563</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003775281727414695</v>
+        <v>0.003775281727414694</v>
       </c>
       <c r="W2" t="n">
-        <v>0.003781105499413416</v>
+        <v>0.003781105499413417</v>
       </c>
       <c r="X2" t="n">
         <v>0.003847810371179243</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003805542531905559</v>
+        <v>0.00380554253190556</v>
       </c>
       <c r="Z2" t="n">
         <v>0.004798238158758235</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003842033580521241</v>
+        <v>0.003842033580521243</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.00426122480116084</v>
+        <v>0.004261224801160839</v>
       </c>
     </row>
     <row r="3">
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003672906620782665</v>
+        <v>0.00368033846288847</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00289407730239628</v>
+        <v>0.002896504172734349</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004047483381044248</v>
+        <v>0.004068269723499131</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003720434683062388</v>
+        <v>0.003729359051553024</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00361888138516939</v>
+        <v>0.003624468156633817</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003746902392248686</v>
+        <v>0.003756957166291553</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00371987977212596</v>
+        <v>0.00372906343630107</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003816904799883917</v>
+        <v>0.00382951580008133</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003900218628238038</v>
+        <v>0.003915751546547741</v>
       </c>
       <c r="K3" t="n">
-        <v>0.004214122743857769</v>
+        <v>0.004240908947653085</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004025681899397462</v>
+        <v>0.004045668571276317</v>
       </c>
       <c r="M3" t="n">
-        <v>0.004712021017556963</v>
+        <v>0.004756718397492718</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004003499114387314</v>
+        <v>0.004022694088068405</v>
       </c>
       <c r="O3" t="n">
-        <v>0.006474061740413803</v>
+        <v>0.006481584541877295</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003851067548979774</v>
+        <v>0.003864737485632436</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.00375918460072457</v>
+        <v>0.003769738857816882</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003699703620182201</v>
+        <v>0.003708155038236833</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003783418531269063</v>
+        <v>0.003794806907693288</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003721761860561874</v>
+        <v>0.00373099773810503</v>
       </c>
       <c r="U3" t="n">
-        <v>0.004400946011186751</v>
+        <v>0.004436232979153786</v>
       </c>
       <c r="V3" t="n">
-        <v>0.00363514255466479</v>
+        <v>0.003641250212395048</v>
       </c>
       <c r="W3" t="n">
-        <v>0.00408902333807779</v>
+        <v>0.004115541706769732</v>
       </c>
       <c r="X3" t="n">
-        <v>0.004154223644559809</v>
+        <v>0.004178795372754475</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.003851521771148456</v>
+        <v>0.003865307328321255</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.005436852796716112</v>
+        <v>0.005448168940383966</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.004112109360131067</v>
+        <v>0.00413508898330205</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.007078566736363708</v>
+        <v>0.007206642280779576</v>
       </c>
     </row>
     <row r="4">
@@ -5071,67 +5071,67 @@
         <v>0.007550145682984583</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00703702130867212</v>
+        <v>0.007037021308672122</v>
       </c>
       <c r="F4" t="n">
         <v>0.006873090692222151</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007078761799622613</v>
+        <v>0.007078761799622618</v>
       </c>
       <c r="H4" t="n">
         <v>0.007031637011826975</v>
       </c>
       <c r="I4" t="n">
-        <v>0.007185544119433815</v>
+        <v>0.007185544119433816</v>
       </c>
       <c r="J4" t="n">
-        <v>0.007317174150773715</v>
+        <v>0.007317174150773722</v>
       </c>
       <c r="K4" t="n">
         <v>0.007818641789820361</v>
       </c>
       <c r="L4" t="n">
-        <v>0.007522340604749145</v>
+        <v>0.007522340604749152</v>
       </c>
       <c r="M4" t="n">
-        <v>0.008606384543527074</v>
+        <v>0.00860638454352707</v>
       </c>
       <c r="N4" t="n">
         <v>0.007482753980103798</v>
       </c>
       <c r="O4" t="n">
-        <v>0.006964912079475916</v>
+        <v>0.006964912079475915</v>
       </c>
       <c r="P4" t="n">
         <v>0.007243425862693375</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.007096080583276957</v>
+        <v>0.007096080583276953</v>
       </c>
       <c r="R4" t="n">
         <v>0.007000196622380585</v>
       </c>
       <c r="S4" t="n">
-        <v>0.007137806739582677</v>
+        <v>0.007137806739582679</v>
       </c>
       <c r="T4" t="n">
-        <v>0.007036140435800028</v>
+        <v>0.00703614043580003</v>
       </c>
       <c r="U4" t="n">
         <v>0.008189579486083981</v>
       </c>
       <c r="V4" t="n">
-        <v>0.006876762330011944</v>
+        <v>0.006876762330011962</v>
       </c>
       <c r="W4" t="n">
         <v>0.007813671751055538</v>
       </c>
       <c r="X4" t="n">
-        <v>0.007719526215449814</v>
+        <v>0.007719526215449812</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.007220917568941509</v>
+        <v>0.007220917568941511</v>
       </c>
       <c r="Z4" t="n">
         <v>0.007135461819935755</v>
@@ -5140,7 +5140,7 @@
         <v>0.00765427470751273</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.01232119574813673</v>
+        <v>0.01232119574813672</v>
       </c>
     </row>
     <row r="5">
@@ -5150,13 +5150,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01248517759395807</v>
+        <v>0.01248517759395809</v>
       </c>
       <c r="C5" t="n">
-        <v>0.008744379639181437</v>
+        <v>0.008744379639181435</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02474762567275827</v>
+        <v>0.02474762567275823</v>
       </c>
       <c r="E5" t="n">
         <v>0.01347135692677173</v>
@@ -5165,58 +5165,58 @@
         <v>0.01149879117329755</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0143128217063392</v>
+        <v>0.01431282170633925</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0149530075090698</v>
+        <v>0.01495300750906978</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01773995783676943</v>
+        <v>0.01773995783676941</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01914721072358979</v>
+        <v>0.0191472107235898</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02815018285431676</v>
+        <v>0.02815018285431678</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02186780315804469</v>
+        <v>0.02186780315804472</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04276218700882042</v>
+        <v>0.04276218700882041</v>
       </c>
       <c r="N5" t="n">
-        <v>0.02269325332246965</v>
+        <v>0.02269325332246969</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01249526392420807</v>
+        <v>0.01249526392420806</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01749410942411542</v>
+        <v>0.01749410942411544</v>
       </c>
       <c r="Q5" t="n">
         <v>0.01538514634561782</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0141858478665126</v>
+        <v>0.01418584786651264</v>
       </c>
       <c r="S5" t="n">
         <v>0.01498905633790462</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01450235775996206</v>
+        <v>0.01450235775996207</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03507554077883553</v>
+        <v>0.03507554077883548</v>
       </c>
       <c r="V5" t="n">
         <v>0.01147797438139023</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02911715628005977</v>
+        <v>0.02911715628005983</v>
       </c>
       <c r="X5" t="n">
-        <v>0.02779285027428459</v>
+        <v>0.02779285027428462</v>
       </c>
       <c r="Y5" t="n">
         <v>0.01819038956892514</v>
@@ -5225,10 +5225,10 @@
         <v>0.01533820219871398</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.02606686315995941</v>
+        <v>0.0260668631599594</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.120779060570038</v>
+        <v>0.1207790605700381</v>
       </c>
     </row>
     <row r="6">
@@ -5241,82 +5241,82 @@
         <v>0.007216128274225465</v>
       </c>
       <c r="C6" t="n">
-        <v>0.006989200689533215</v>
+        <v>0.006989200689533214</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008557172105818097</v>
+        <v>0.008557172105818103</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008044047731505639</v>
+        <v>0.008044047731505643</v>
       </c>
       <c r="F6" t="n">
         <v>0.007128729526849008</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00733440063424947</v>
+        <v>0.007334400634249473</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008038663434660486</v>
+        <v>0.008038663434660497</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00819257054226733</v>
+        <v>0.008192570542267338</v>
       </c>
       <c r="J6" t="n">
-        <v>0.007572812985400574</v>
+        <v>0.00757281298540058</v>
       </c>
       <c r="K6" t="n">
-        <v>0.008825668212653889</v>
+        <v>0.008825668212653882</v>
       </c>
       <c r="L6" t="n">
         <v>0.007777979439376009</v>
       </c>
       <c r="M6" t="n">
-        <v>0.009613410966360578</v>
+        <v>0.009613410966360593</v>
       </c>
       <c r="N6" t="n">
-        <v>0.00773984539495814</v>
+        <v>0.007739845394958151</v>
       </c>
       <c r="O6" t="n">
-        <v>0.007975578185592578</v>
+        <v>0.007975578185592592</v>
       </c>
       <c r="P6" t="n">
-        <v>0.008254460242835765</v>
+        <v>0.008254460242835771</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.008103107006110468</v>
+        <v>0.008103107006110482</v>
       </c>
       <c r="R6" t="n">
-        <v>0.008007223045214102</v>
+        <v>0.008007223045214106</v>
       </c>
       <c r="S6" t="n">
-        <v>0.007393445574209533</v>
+        <v>0.007393445574209536</v>
       </c>
       <c r="T6" t="n">
         <v>0.007291779270426887</v>
       </c>
       <c r="U6" t="n">
-        <v>0.008466392278456147</v>
+        <v>0.008466392278456148</v>
       </c>
       <c r="V6" t="n">
-        <v>0.00788378875284545</v>
+        <v>0.007883788752845483</v>
       </c>
       <c r="W6" t="n">
-        <v>0.008824471060430921</v>
+        <v>0.008824471060430918</v>
       </c>
       <c r="X6" t="n">
-        <v>0.007975165050076673</v>
+        <v>0.007975165050076671</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.007515774108421357</v>
+        <v>0.007515774108421355</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.007391100654562612</v>
+        <v>0.007391100654562611</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.008661301130346242</v>
+        <v>0.008661301130346251</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01262024539215192</v>
+        <v>0.01262024539215191</v>
       </c>
     </row>
     <row r="7">
@@ -5332,37 +5332,37 @@
         <v>0.007337266489512701</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00815385031759093</v>
+        <v>0.008153850317590926</v>
       </c>
       <c r="E7" t="n">
         <v>0.007640725943278464</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0074767953268285</v>
+        <v>0.007476795326828497</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007682466434228959</v>
+        <v>0.007682466434228961</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007635341646433324</v>
+        <v>0.007635341646433321</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007789248754040161</v>
+        <v>0.00778924875404016</v>
       </c>
       <c r="J7" t="n">
-        <v>0.007920878785380062</v>
+        <v>0.007920878785380066</v>
       </c>
       <c r="K7" t="n">
         <v>0.00842234642442671</v>
       </c>
       <c r="L7" t="n">
-        <v>0.008126045239355497</v>
+        <v>0.008126045239355501</v>
       </c>
       <c r="M7" t="n">
-        <v>0.009210089178133412</v>
+        <v>0.00921008917813341</v>
       </c>
       <c r="N7" t="n">
-        <v>0.008086458614710145</v>
+        <v>0.008086458614710143</v>
       </c>
       <c r="O7" t="n">
         <v>0.00756859382205576</v>
@@ -5380,28 +5380,28 @@
         <v>0.007741511374189025</v>
       </c>
       <c r="T7" t="n">
-        <v>0.007639845070406373</v>
+        <v>0.007639845070406374</v>
       </c>
       <c r="U7" t="n">
-        <v>0.008813576800441182</v>
+        <v>0.008813576800441179</v>
       </c>
       <c r="V7" t="n">
-        <v>0.007480466964618307</v>
+        <v>0.007480466964618309</v>
       </c>
       <c r="W7" t="n">
-        <v>0.008417376385661885</v>
+        <v>0.008417376385661883</v>
       </c>
       <c r="X7" t="n">
-        <v>0.008323230850056164</v>
+        <v>0.008323230850056162</v>
       </c>
       <c r="Y7" t="n">
         <v>0.007845796161293167</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0077391664545421</v>
+        <v>0.007739166454542099</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.00825797934211908</v>
+        <v>0.008257979342119078</v>
       </c>
       <c r="AB7" t="n">
         <v>0.01292490038274309</v>
@@ -5414,85 +5414,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.008876212825899888</v>
+        <v>0.008876212825899895</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009959018322108902</v>
+        <v>0.009959018322108907</v>
       </c>
       <c r="D8" t="n">
         <v>0.01077560215018713</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009565083545004148</v>
+        <v>0.009565083545004151</v>
       </c>
       <c r="F8" t="n">
-        <v>0.008992855185353602</v>
+        <v>0.008992855185353607</v>
       </c>
       <c r="G8" t="n">
         <v>0.01057579995326666</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01025709347902952</v>
+        <v>0.01025709347902953</v>
       </c>
       <c r="I8" t="n">
         <v>0.01041100058663636</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01054263061797626</v>
+        <v>0.01054263061797628</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01104409825702291</v>
+        <v>0.01104409825702292</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0107477970719517</v>
+        <v>0.01074779707195171</v>
       </c>
       <c r="M8" t="n">
         <v>0.0118318410107297</v>
       </c>
       <c r="N8" t="n">
-        <v>0.009692948196035641</v>
+        <v>0.009692948196035649</v>
       </c>
       <c r="O8" t="n">
-        <v>0.009454109177431665</v>
+        <v>0.009454109177431671</v>
       </c>
       <c r="P8" t="n">
-        <v>0.009664232612610114</v>
+        <v>0.009664232612610117</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.008754411525983628</v>
+        <v>0.008754411525983632</v>
       </c>
       <c r="R8" t="n">
         <v>0.01022565308958313</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01036326320678522</v>
+        <v>0.01036326320678523</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01026159690300257</v>
+        <v>0.01026159690300258</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01079628144700099</v>
+        <v>0.010796281447001</v>
       </c>
       <c r="V8" t="n">
-        <v>0.009743515270743883</v>
+        <v>0.009743515270743904</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01103938561833424</v>
+        <v>0.01103938561833425</v>
       </c>
       <c r="X8" t="n">
-        <v>0.009497896797498753</v>
+        <v>0.009497896797498758</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01176864777312273</v>
+        <v>0.01176864777312274</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.009026856241841632</v>
+        <v>0.00902685624184163</v>
       </c>
       <c r="AA8" t="n">
         <v>0.01087973117471528</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01691477793643793</v>
+        <v>0.01691477793643794</v>
       </c>
     </row>
     <row r="9">
@@ -5502,67 +5502,67 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008825897599052756</v>
+        <v>0.008825897599052761</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00915512129845786</v>
+        <v>0.009155121298457861</v>
       </c>
       <c r="D9" t="n">
-        <v>0.009971705126536085</v>
+        <v>0.009971705126536086</v>
       </c>
       <c r="E9" t="n">
-        <v>0.009330223125148389</v>
+        <v>0.00933022312514839</v>
       </c>
       <c r="F9" t="n">
         <v>0.008012569941938818</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009500321010199122</v>
+        <v>0.009500321010199125</v>
       </c>
       <c r="H9" t="n">
-        <v>0.009453196455378475</v>
+        <v>0.009453196455378478</v>
       </c>
       <c r="I9" t="n">
         <v>0.009607103562985313</v>
       </c>
       <c r="J9" t="n">
-        <v>0.00973873359432522</v>
+        <v>0.009738733594325224</v>
       </c>
       <c r="K9" t="n">
         <v>0.01024020123337187</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009943900048300647</v>
+        <v>0.009943900048300655</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01102794398707858</v>
+        <v>0.01102794398707857</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0099043134236553</v>
+        <v>0.009904313423655301</v>
       </c>
       <c r="O9" t="n">
         <v>0.009570779020176702</v>
       </c>
       <c r="P9" t="n">
-        <v>0.009889376572508083</v>
+        <v>0.009889376572508081</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.009517639793853462</v>
+        <v>0.009517639793853463</v>
       </c>
       <c r="R9" t="n">
-        <v>0.009421756065932086</v>
+        <v>0.009421756065932088</v>
       </c>
       <c r="S9" t="n">
-        <v>0.009559366183134176</v>
+        <v>0.009559366183134178</v>
       </c>
       <c r="T9" t="n">
-        <v>0.009457699879351531</v>
+        <v>0.009457699879351529</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0106323128873808</v>
+        <v>0.01063231288738079</v>
       </c>
       <c r="V9" t="n">
-        <v>0.009940107493510876</v>
+        <v>0.00994010749351089</v>
       </c>
       <c r="W9" t="n">
         <v>0.01023523119460704</v>
@@ -5571,10 +5571,10 @@
         <v>0.01014108565900131</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.009663650970238327</v>
+        <v>0.009663650970238325</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.009221711401566529</v>
+        <v>0.009221711401566527</v>
       </c>
       <c r="AA9" t="n">
         <v>0.01007583415106423</v>
@@ -5749,13 +5749,13 @@
         <v>0.003719927467596873</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003341101735902524</v>
+        <v>0.003341101735902525</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003733224359631671</v>
+        <v>0.00373322435963167</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003729856158419683</v>
+        <v>0.003729856158419684</v>
       </c>
       <c r="F2" t="n">
         <v>0.003727662134037216</v>
@@ -5767,22 +5767,22 @@
         <v>0.003728723122056</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003729129558657142</v>
+        <v>0.003729129558657141</v>
       </c>
       <c r="J2" t="n">
         <v>0.003732338521982052</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003726989195418299</v>
+        <v>0.003726989195418298</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003730002255728383</v>
+        <v>0.003730002255728382</v>
       </c>
       <c r="M2" t="n">
         <v>0.003721272251973345</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003729735304660732</v>
+        <v>0.00372973530466073</v>
       </c>
       <c r="O2" t="n">
         <v>0.005407198355078673</v>
@@ -5797,10 +5797,10 @@
         <v>0.003740162220649536</v>
       </c>
       <c r="S2" t="n">
-        <v>0.00373252233088747</v>
+        <v>0.003732522330887471</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003720054528455498</v>
+        <v>0.003720054528455499</v>
       </c>
       <c r="U2" t="n">
         <v>0.003668769052198066</v>
@@ -5818,10 +5818,10 @@
         <v>0.003830559961541156</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.004730173209076681</v>
+        <v>0.004730173209076683</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003751597417601561</v>
+        <v>0.003751597417601562</v>
       </c>
       <c r="AB2" t="n">
         <v>0.003713868074792603</v>
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003535991623550937</v>
+        <v>0.003540057667313679</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002926606696150605</v>
+        <v>0.002931457474416357</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003631310189688488</v>
+        <v>0.003638797884522082</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003605576999368655</v>
+        <v>0.00361191003755691</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003591802490588049</v>
+        <v>0.003597901708782698</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003582443284834408</v>
+        <v>0.003588150401289666</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003599864409313305</v>
+        <v>0.003606244128577013</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003602369163486553</v>
+        <v>0.003608826898076529</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00362439995497361</v>
+        <v>0.00363160590610723</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003586689501014548</v>
+        <v>0.003592587174076125</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003607375180322506</v>
+        <v>0.003613994285487901</v>
       </c>
       <c r="M3" t="n">
-        <v>0.003551493790162968</v>
+        <v>0.003556178265790778</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003606174503085794</v>
+        <v>0.003612753382624856</v>
       </c>
       <c r="O3" t="n">
-        <v>0.006384064912024427</v>
+        <v>0.006391016713376892</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003605828674254957</v>
+        <v>0.003612343799712898</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.00353001344485114</v>
+        <v>0.003533895924299737</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003681478192708846</v>
+        <v>0.003690759579630838</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003625041626453038</v>
+        <v>0.003632275396554362</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003537484215345515</v>
+        <v>0.003541629463256864</v>
       </c>
       <c r="U3" t="n">
-        <v>0.003457669427350699</v>
+        <v>0.003462021395598502</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003612012109658214</v>
+        <v>0.003618765522676919</v>
       </c>
       <c r="W3" t="n">
-        <v>0.003592821230227748</v>
+        <v>0.003604305336505199</v>
       </c>
       <c r="X3" t="n">
-        <v>0.004746869043147054</v>
+        <v>0.00479408870158618</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.004326062013210531</v>
+        <v>0.004358083181366491</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.005291397862664414</v>
+        <v>0.00529951111327416</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003762346858415931</v>
+        <v>0.003774426457499694</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.00349841173113694</v>
+        <v>0.003501189919070415</v>
       </c>
     </row>
     <row r="4">
@@ -5922,85 +5922,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.006767706609872022</v>
+        <v>0.006767706609872024</v>
       </c>
       <c r="C4" t="n">
-        <v>0.006800796887416283</v>
+        <v>0.006800796887416285</v>
       </c>
       <c r="D4" t="n">
-        <v>0.006917901122277629</v>
+        <v>0.006917901122277628</v>
       </c>
       <c r="E4" t="n">
-        <v>0.006879855740139129</v>
+        <v>0.00687985574013913</v>
       </c>
       <c r="F4" t="n">
-        <v>0.006855073225438102</v>
+        <v>0.006855073225438103</v>
       </c>
       <c r="G4" t="n">
         <v>0.006841731438105928</v>
       </c>
       <c r="H4" t="n">
-        <v>0.006867057573188861</v>
+        <v>0.006867057573188862</v>
       </c>
       <c r="I4" t="n">
-        <v>0.006871648461568814</v>
+        <v>0.006871648461568813</v>
       </c>
       <c r="J4" t="n">
-        <v>0.006904699744820885</v>
+        <v>0.006904699744820886</v>
       </c>
       <c r="K4" t="n">
         <v>0.006847472074170339</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006881505976449</v>
+        <v>0.006881505976448999</v>
       </c>
       <c r="M4" t="n">
-        <v>0.006792620463227715</v>
+        <v>0.006792620463227718</v>
       </c>
       <c r="N4" t="n">
-        <v>0.00687849064133627</v>
+        <v>0.006878490641336269</v>
       </c>
       <c r="O4" t="n">
-        <v>0.006898360300326566</v>
+        <v>0.006898360300326568</v>
       </c>
       <c r="P4" t="n">
-        <v>0.006878824930634396</v>
+        <v>0.006878824930634398</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.006757844202028604</v>
+        <v>0.006757844202028606</v>
       </c>
       <c r="R4" t="n">
-        <v>0.006996267454048162</v>
+        <v>0.006996267454048163</v>
       </c>
       <c r="S4" t="n">
-        <v>0.006909971384662744</v>
+        <v>0.006909971384662747</v>
       </c>
       <c r="T4" t="n">
         <v>0.006769141820721108</v>
       </c>
       <c r="U4" t="n">
-        <v>0.006766089931418573</v>
+        <v>0.006766089931418575</v>
       </c>
       <c r="V4" t="n">
-        <v>0.006867070330967959</v>
+        <v>0.006867070330967958</v>
       </c>
       <c r="W4" t="n">
-        <v>0.007099141632800633</v>
+        <v>0.007099141632800634</v>
       </c>
       <c r="X4" t="n">
-        <v>0.008687191741422854</v>
+        <v>0.008687191741422852</v>
       </c>
       <c r="Y4" t="n">
         <v>0.00800357333651568</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.006950200263581199</v>
+        <v>0.0069502002635812</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.007125433264071764</v>
+        <v>0.007125433264071766</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.00670840355168542</v>
+        <v>0.006708403551685422</v>
       </c>
     </row>
     <row r="5">
@@ -6010,31 +6010,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.009595302870047534</v>
+        <v>0.009595302870047539</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01043379532978912</v>
+        <v>0.01043379532978913</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01246835070556787</v>
+        <v>0.01246835070556786</v>
       </c>
       <c r="E5" t="n">
         <v>0.01091749445426233</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01145569281356494</v>
+        <v>0.01145569281356495</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01073819647581603</v>
+        <v>0.01073819647581606</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01192137564991776</v>
+        <v>0.01192137564991778</v>
       </c>
       <c r="I5" t="n">
         <v>0.01179735398373816</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01198348450725685</v>
+        <v>0.01198348450725686</v>
       </c>
       <c r="K5" t="n">
         <v>0.01116050418963264</v>
@@ -6046,19 +6046,19 @@
         <v>0.01035785954807074</v>
       </c>
       <c r="N5" t="n">
-        <v>0.011649980752903</v>
+        <v>0.01164998075290302</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0116280653947963</v>
+        <v>0.01162806539479631</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01136721619460428</v>
+        <v>0.01136721619460429</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.009552185677115766</v>
+        <v>0.009552185677115767</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01419234522996689</v>
+        <v>0.0141923452299669</v>
       </c>
       <c r="S5" t="n">
         <v>0.01167609630350436</v>
@@ -6070,7 +6070,7 @@
         <v>0.009900634304549729</v>
       </c>
       <c r="V5" t="n">
-        <v>0.01149794969007611</v>
+        <v>0.01149794969007612</v>
       </c>
       <c r="W5" t="n">
         <v>0.01527653657629606</v>
@@ -6079,16 +6079,16 @@
         <v>0.0425332265039628</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03194647958218209</v>
+        <v>0.03194647958218211</v>
       </c>
       <c r="Z5" t="n">
         <v>0.01239335176335405</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01609082756365026</v>
+        <v>0.01609082756365025</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.008909208770902566</v>
+        <v>0.008909208770902568</v>
       </c>
     </row>
     <row r="6">
@@ -6098,70 +6098,70 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.007665502683299183</v>
+        <v>0.007665502683299184</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007034083781072778</v>
+        <v>0.007034083781072779</v>
       </c>
       <c r="D6" t="n">
         <v>0.007151188015934123</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007113142633795623</v>
+        <v>0.007113142633795625</v>
       </c>
       <c r="F6" t="n">
-        <v>0.007752869298865262</v>
+        <v>0.007752869298865265</v>
       </c>
       <c r="G6" t="n">
         <v>0.007739527511533085</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007764853646616018</v>
+        <v>0.007764853646616019</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007769444534995972</v>
+        <v>0.007769444534995973</v>
       </c>
       <c r="J6" t="n">
-        <v>0.007802495818248044</v>
+        <v>0.007802495818248047</v>
       </c>
       <c r="K6" t="n">
-        <v>0.007745268147597498</v>
+        <v>0.007745268147597501</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007114792870105494</v>
+        <v>0.007114792870105495</v>
       </c>
       <c r="M6" t="n">
-        <v>0.007690416536654874</v>
+        <v>0.007690416536654876</v>
       </c>
       <c r="N6" t="n">
-        <v>0.007112810370367884</v>
+        <v>0.007112810370367885</v>
       </c>
       <c r="O6" t="n">
-        <v>0.007797318576701464</v>
+        <v>0.007797318576701461</v>
       </c>
       <c r="P6" t="n">
         <v>0.007094497391715026</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.007655640275455765</v>
+        <v>0.007655640275455766</v>
       </c>
       <c r="R6" t="n">
         <v>0.007229554347704658</v>
       </c>
       <c r="S6" t="n">
-        <v>0.007807767458089903</v>
+        <v>0.007807767458089906</v>
       </c>
       <c r="T6" t="n">
-        <v>0.007002428714377603</v>
+        <v>0.007002428714377605</v>
       </c>
       <c r="U6" t="n">
-        <v>0.007013155010993768</v>
+        <v>0.00701315501099377</v>
       </c>
       <c r="V6" t="n">
-        <v>0.007100357224624454</v>
+        <v>0.007100357224624453</v>
       </c>
       <c r="W6" t="n">
-        <v>0.007353118158635772</v>
+        <v>0.007353118158635771</v>
       </c>
       <c r="X6" t="n">
         <v>0.009584987814850019</v>
@@ -6173,7 +6173,7 @@
         <v>0.007183487157237694</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.008023229337498924</v>
+        <v>0.008023229337498928</v>
       </c>
       <c r="AB6" t="n">
         <v>0.006980589881187864</v>
@@ -6186,85 +6186,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007304850906796989</v>
+        <v>0.007304850906796992</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007337941184341249</v>
+        <v>0.007337941184341251</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007455045419202595</v>
+        <v>0.007455045419202598</v>
       </c>
       <c r="E7" t="n">
         <v>0.007417000037064097</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007392217522363072</v>
+        <v>0.007392217522363074</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007378875735030893</v>
+        <v>0.007378875735030895</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007404201870113827</v>
+        <v>0.007404201870113828</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007408792758493777</v>
+        <v>0.007408792758493782</v>
       </c>
       <c r="J7" t="n">
-        <v>0.007441844041745853</v>
+        <v>0.007441844041745856</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007384616371095305</v>
+        <v>0.007384616371095306</v>
       </c>
       <c r="L7" t="n">
         <v>0.007418650273373967</v>
       </c>
       <c r="M7" t="n">
-        <v>0.007329764760152684</v>
+        <v>0.007329764760152685</v>
       </c>
       <c r="N7" t="n">
-        <v>0.007415634938261235</v>
+        <v>0.007415634938261238</v>
       </c>
       <c r="O7" t="n">
-        <v>0.007435483032827185</v>
+        <v>0.007435483032827187</v>
       </c>
       <c r="P7" t="n">
-        <v>0.007415947663135015</v>
+        <v>0.007415947663135017</v>
       </c>
       <c r="Q7" t="n">
         <v>0.007294988498953573</v>
       </c>
       <c r="R7" t="n">
-        <v>0.00753341175097313</v>
+        <v>0.007533411750973133</v>
       </c>
       <c r="S7" t="n">
-        <v>0.007447115681587714</v>
+        <v>0.007447115681587717</v>
       </c>
       <c r="T7" t="n">
-        <v>0.007306286117646075</v>
+        <v>0.007306286117646076</v>
       </c>
       <c r="U7" t="n">
-        <v>0.00731623303777594</v>
+        <v>0.007316233037775941</v>
       </c>
       <c r="V7" t="n">
-        <v>0.007404214627892928</v>
+        <v>0.00740421462789293</v>
       </c>
       <c r="W7" t="n">
-        <v>0.007636285929725599</v>
+        <v>0.007636285929725602</v>
       </c>
       <c r="X7" t="n">
-        <v>0.009224336038347819</v>
+        <v>0.009224336038347823</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.008554495819359346</v>
+        <v>0.008554495819359348</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.007487344560506164</v>
+        <v>0.007487344560506167</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.007662577560996734</v>
+        <v>0.007662577560996735</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.007245547848610389</v>
+        <v>0.007245547848610391</v>
       </c>
     </row>
     <row r="8">
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.008494659864557217</v>
+        <v>0.008494659864557219</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009705667649268007</v>
+        <v>0.009705667649268009</v>
       </c>
       <c r="D8" t="n">
         <v>0.009822771884129356</v>
@@ -6286,46 +6286,46 @@
         <v>0.009157520175812089</v>
       </c>
       <c r="F8" t="n">
-        <v>0.008765532261130377</v>
+        <v>0.008765532261130381</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00999085106848911</v>
+        <v>0.009990851068489112</v>
       </c>
       <c r="H8" t="n">
         <v>0.009771928335040588</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009776519223420528</v>
+        <v>0.009776519223420529</v>
       </c>
       <c r="J8" t="n">
-        <v>0.009809570506672605</v>
+        <v>0.009809570506672614</v>
       </c>
       <c r="K8" t="n">
-        <v>0.00975234283602206</v>
+        <v>0.009752342836022065</v>
       </c>
       <c r="L8" t="n">
-        <v>0.009786376738300727</v>
+        <v>0.009786376738300724</v>
       </c>
       <c r="M8" t="n">
-        <v>0.009697491225079315</v>
+        <v>0.009697491225079317</v>
       </c>
       <c r="N8" t="n">
-        <v>0.00887027827383464</v>
+        <v>0.008870278273834643</v>
       </c>
       <c r="O8" t="n">
-        <v>0.009141071104954863</v>
+        <v>0.009141071104954865</v>
       </c>
       <c r="P8" t="n">
-        <v>0.009060028402617945</v>
+        <v>0.009060028402617947</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.008253309781893875</v>
+        <v>0.008253309781893878</v>
       </c>
       <c r="R8" t="n">
         <v>0.009901138215899885</v>
       </c>
       <c r="S8" t="n">
-        <v>0.00981484214651447</v>
+        <v>0.009814842146514473</v>
       </c>
       <c r="T8" t="n">
         <v>0.009674012582572835</v>
@@ -6349,10 +6349,10 @@
         <v>0.008655273095824841</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01003030402592348</v>
+        <v>0.01003030402592349</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01084370764565787</v>
+        <v>0.01084370764565788</v>
       </c>
     </row>
     <row r="9">
@@ -6362,70 +6362,70 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008346500582280321</v>
+        <v>0.008346500582280326</v>
       </c>
       <c r="C9" t="n">
-        <v>0.008851309232352151</v>
+        <v>0.00885130923235215</v>
       </c>
       <c r="D9" t="n">
-        <v>0.008968413467213497</v>
+        <v>0.008968413467213499</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00882149757107817</v>
+        <v>0.008821497571078168</v>
       </c>
       <c r="F9" t="n">
-        <v>0.007818145702167042</v>
+        <v>0.007818145702167044</v>
       </c>
       <c r="G9" t="n">
-        <v>0.008892243994010972</v>
+        <v>0.008892243994010974</v>
       </c>
       <c r="H9" t="n">
-        <v>0.008917569918124727</v>
+        <v>0.008917569918124731</v>
       </c>
       <c r="I9" t="n">
-        <v>0.008922160806504681</v>
+        <v>0.008922160806504684</v>
       </c>
       <c r="J9" t="n">
         <v>0.008955212089756756</v>
       </c>
       <c r="K9" t="n">
-        <v>0.008897984419106213</v>
+        <v>0.008897984419106214</v>
       </c>
       <c r="L9" t="n">
-        <v>0.008932018321384872</v>
+        <v>0.008932018321384875</v>
       </c>
       <c r="M9" t="n">
-        <v>0.008843132808163583</v>
+        <v>0.008843132808163586</v>
       </c>
       <c r="N9" t="n">
-        <v>0.00892900298627214</v>
+        <v>0.008929002986272142</v>
       </c>
       <c r="O9" t="n">
-        <v>0.009105199777139656</v>
+        <v>0.00910519977713966</v>
       </c>
       <c r="P9" t="n">
-        <v>0.009119662830626707</v>
+        <v>0.00911966283062671</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.008808356757933655</v>
+        <v>0.008808356757933658</v>
       </c>
       <c r="R9" t="n">
-        <v>0.009046779798984033</v>
+        <v>0.009046779798984037</v>
       </c>
       <c r="S9" t="n">
-        <v>0.008960483729598619</v>
+        <v>0.008960483729598621</v>
       </c>
       <c r="T9" t="n">
-        <v>0.008819654165656977</v>
+        <v>0.008819654165656984</v>
       </c>
       <c r="U9" t="n">
-        <v>0.008830380462273146</v>
+        <v>0.008830380462273147</v>
       </c>
       <c r="V9" t="n">
-        <v>0.009461935731238243</v>
+        <v>0.009461935731238245</v>
       </c>
       <c r="W9" t="n">
-        <v>0.009149653977736502</v>
+        <v>0.009149653977736507</v>
       </c>
       <c r="X9" t="n">
         <v>0.01073770408635872</v>
@@ -6434,13 +6434,13 @@
         <v>0.01006786386737025</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.008716308460490789</v>
+        <v>0.008716308460490792</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.009175945609007636</v>
+        <v>0.009175945609007639</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.008758915896621294</v>
+        <v>0.008758915896621297</v>
       </c>
     </row>
   </sheetData>
@@ -6606,43 +6606,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003719496730968309</v>
+        <v>0.003719496730968306</v>
       </c>
       <c r="C2" t="n">
         <v>0.003298500630514835</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003724327767735262</v>
+        <v>0.003724327767735264</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003730237526854597</v>
+        <v>0.003730237526854596</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00372045489888539</v>
+        <v>0.003720454898885391</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0037173698561408</v>
+        <v>0.003717369856140798</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003718643691939121</v>
+        <v>0.003718643691939119</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003718547481274779</v>
+        <v>0.00371854748127478</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003725099386233088</v>
+        <v>0.003725099386233089</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003717827245376119</v>
+        <v>0.003717827245376118</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003725245303639581</v>
+        <v>0.00372524530363958</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003715184722843513</v>
+        <v>0.003715184722843514</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003718496344346919</v>
+        <v>0.003718496344346915</v>
       </c>
       <c r="O2" t="n">
         <v>0.005412080652775575</v>
@@ -6654,37 +6654,37 @@
         <v>0.003713488456775702</v>
       </c>
       <c r="R2" t="n">
-        <v>0.00373461110208357</v>
+        <v>0.003734611102083571</v>
       </c>
       <c r="S2" t="n">
-        <v>0.00372431391500053</v>
+        <v>0.003724313915000531</v>
       </c>
       <c r="T2" t="n">
         <v>0.00371358790737681</v>
       </c>
       <c r="U2" t="n">
-        <v>0.003555198986957071</v>
+        <v>0.00355519898695707</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003729300854951447</v>
+        <v>0.003729300854951445</v>
       </c>
       <c r="W2" t="n">
-        <v>0.003550080817832747</v>
+        <v>0.003550080817832745</v>
       </c>
       <c r="X2" t="n">
-        <v>0.003937204529351535</v>
+        <v>0.003937204529351536</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003811960490298973</v>
+        <v>0.00381196049029897</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.004715445247181514</v>
+        <v>0.004715445247181517</v>
       </c>
       <c r="AA2" t="n">
         <v>0.003747152431731161</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.003712990538847193</v>
+        <v>0.003712990538847192</v>
       </c>
     </row>
     <row r="3">
@@ -6694,85 +6694,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003570942570768011</v>
+        <v>0.003576401021909704</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002861016786853695</v>
+        <v>0.002865842232290634</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003606138634766626</v>
+        <v>0.003612890214485003</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003646094616950283</v>
+        <v>0.003654033413127381</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003578684139332817</v>
+        <v>0.003584474572809302</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003555864682284358</v>
+        <v>0.003560793427663775</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003565993744737874</v>
+        <v>0.00357132972686829</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003565033950374654</v>
+        <v>0.00357032531691117</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003611089030562455</v>
+        <v>0.003617989376450731</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003559660381634589</v>
+        <v>0.003564755737629858</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003611763459141447</v>
+        <v>0.003618695062199887</v>
       </c>
       <c r="M3" t="n">
-        <v>0.003545984048841107</v>
+        <v>0.003550631988261917</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003564315985633932</v>
+        <v>0.003569569673746069</v>
       </c>
       <c r="O3" t="n">
-        <v>0.006441993463920184</v>
+        <v>0.006450990779401077</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003623488569183115</v>
+        <v>0.003630790598774087</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003528562794587471</v>
+        <v>0.003532554756811801</v>
       </c>
       <c r="R3" t="n">
-        <v>0.00368018105461583</v>
+        <v>0.003689576193757028</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003605091100451479</v>
+        <v>0.003611770839715275</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003529529584566156</v>
+        <v>0.003533555684879711</v>
       </c>
       <c r="U3" t="n">
-        <v>0.003284388453076776</v>
+        <v>0.003289151683622639</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003640575258491967</v>
+        <v>0.003648496573128514</v>
       </c>
       <c r="W3" t="n">
-        <v>0.003372624515463502</v>
+        <v>0.003381844900550919</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00512095054233769</v>
+        <v>0.005181702461869727</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.004232028573353571</v>
+        <v>0.004260868840108811</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.005244863822000686</v>
+        <v>0.005251715081464386</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003768887609563164</v>
+        <v>0.003781359091737357</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.003529675265595672</v>
+        <v>0.003533721746312799</v>
       </c>
     </row>
     <row r="4">
@@ -6785,19 +6785,19 @@
         <v>0.006829353273362562</v>
       </c>
       <c r="C4" t="n">
-        <v>0.006798431220921704</v>
+        <v>0.006798431220921705</v>
       </c>
       <c r="D4" t="n">
-        <v>0.006883922056032101</v>
+        <v>0.006883922056032102</v>
       </c>
       <c r="E4" t="n">
-        <v>0.006950675503908413</v>
+        <v>0.006950675503908411</v>
       </c>
       <c r="F4" t="n">
-        <v>0.006840176220765057</v>
+        <v>0.006840176220765058</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006805329243775088</v>
+        <v>0.006805329243775087</v>
       </c>
       <c r="H4" t="n">
         <v>0.006819717805110566</v>
@@ -6806,25 +6806,25 @@
         <v>0.006818631061397759</v>
       </c>
       <c r="J4" t="n">
-        <v>0.006889663568913678</v>
+        <v>0.006889663568913679</v>
       </c>
       <c r="K4" t="n">
         <v>0.006810495665597456</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006894286046158676</v>
+        <v>0.006894286046158678</v>
       </c>
       <c r="M4" t="n">
-        <v>0.00678977096611211</v>
+        <v>0.006789770966112112</v>
       </c>
       <c r="N4" t="n">
         <v>0.006818053446273393</v>
       </c>
       <c r="O4" t="n">
-        <v>0.006989611407279073</v>
+        <v>0.006989611407279072</v>
       </c>
       <c r="P4" t="n">
-        <v>0.006913184262246362</v>
+        <v>0.006913184262246361</v>
       </c>
       <c r="Q4" t="n">
         <v>0.006761487052414442</v>
@@ -6833,19 +6833,19 @@
         <v>0.007000077048063692</v>
       </c>
       <c r="S4" t="n">
-        <v>0.006883765583020702</v>
+        <v>0.006883765583020703</v>
       </c>
       <c r="T4" t="n">
         <v>0.006762610392703462</v>
       </c>
       <c r="U4" t="n">
-        <v>0.006786197647307926</v>
+        <v>0.006786197647307927</v>
       </c>
       <c r="V4" t="n">
-        <v>0.006919970805342427</v>
+        <v>0.006919970805342428</v>
       </c>
       <c r="W4" t="n">
-        <v>0.006996438252296981</v>
+        <v>0.006996438252296979</v>
       </c>
       <c r="X4" t="n">
         <v>0.009288463006636395</v>
@@ -6854,13 +6854,13 @@
         <v>0.007862872552232227</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.006891993980099088</v>
+        <v>0.006891993980099089</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.007141737135729923</v>
+        <v>0.007141737135729925</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.006763570110933379</v>
+        <v>0.006763570110933378</v>
       </c>
     </row>
     <row r="5">
@@ -6879,7 +6879,7 @@
         <v>0.01192175746188536</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01195077067524544</v>
+        <v>0.01195077067524543</v>
       </c>
       <c r="F5" t="n">
         <v>0.01124461788645133</v>
@@ -6894,16 +6894,16 @@
         <v>0.01084445734009098</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01178444891510784</v>
+        <v>0.01178444891510785</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01057971466480015</v>
+        <v>0.01057971466480016</v>
       </c>
       <c r="L5" t="n">
         <v>0.011626390490136</v>
       </c>
       <c r="M5" t="n">
-        <v>0.010330456229376</v>
+        <v>0.01033045622937601</v>
       </c>
       <c r="N5" t="n">
         <v>0.0106513090211263</v>
@@ -6912,19 +6912,19 @@
         <v>0.01305251733017672</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01184882950999558</v>
+        <v>0.0118488295099956</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.009644802827571027</v>
+        <v>0.009644802827571023</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01431286663114705</v>
+        <v>0.01431286663114706</v>
       </c>
       <c r="S5" t="n">
         <v>0.01142736750583091</v>
       </c>
       <c r="T5" t="n">
-        <v>0.009797857847677871</v>
+        <v>0.009797857847677881</v>
       </c>
       <c r="U5" t="n">
         <v>0.01015579178643567</v>
@@ -6936,16 +6936,16 @@
         <v>0.01363280174537473</v>
       </c>
       <c r="X5" t="n">
-        <v>0.05211794194808415</v>
+        <v>0.05211794194808411</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.02966255265963691</v>
+        <v>0.02966255265963686</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01143420315152144</v>
+        <v>0.01143420315152145</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01640298125293267</v>
+        <v>0.01640298125293274</v>
       </c>
       <c r="AB5" t="n">
         <v>0.009929678621106039</v>
@@ -6958,40 +6958,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.007717569352188174</v>
+        <v>0.007717569352188176</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007686647299747314</v>
+        <v>0.007686647299747315</v>
       </c>
       <c r="D6" t="n">
-        <v>0.007772138134857711</v>
+        <v>0.007772138134857716</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007186958795620007</v>
+        <v>0.007186958795620008</v>
       </c>
       <c r="F6" t="n">
-        <v>0.007728392299590668</v>
+        <v>0.007728392299590667</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007693545322600699</v>
+        <v>0.007693545322600701</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007707933883936176</v>
+        <v>0.007707933883936179</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007706847140223366</v>
+        <v>0.00770684714022337</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00712594686062527</v>
+        <v>0.007125946860625272</v>
       </c>
       <c r="K6" t="n">
         <v>0.007046778957309052</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007782502124984287</v>
+        <v>0.007782502124984288</v>
       </c>
       <c r="M6" t="n">
-        <v>0.007677987044937719</v>
+        <v>0.007677987044937721</v>
       </c>
       <c r="N6" t="n">
         <v>0.007055388772528804</v>
@@ -7000,40 +7000,40 @@
         <v>0.007259945487928248</v>
       </c>
       <c r="P6" t="n">
-        <v>0.007800781414891187</v>
+        <v>0.007800781414891195</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.00764970313124005</v>
+        <v>0.007649703131240052</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0078882931268893</v>
+        <v>0.007888293126889304</v>
       </c>
       <c r="S6" t="n">
-        <v>0.007771981661846312</v>
+        <v>0.007771981661846314</v>
       </c>
       <c r="T6" t="n">
-        <v>0.006998893684415056</v>
+        <v>0.006998893684415057</v>
       </c>
       <c r="U6" t="n">
-        <v>0.007685315144334512</v>
+        <v>0.007685315144334511</v>
       </c>
       <c r="V6" t="n">
-        <v>0.007156254097054021</v>
+        <v>0.007156254097054024</v>
       </c>
       <c r="W6" t="n">
-        <v>0.007883393522117822</v>
+        <v>0.007883393522117825</v>
       </c>
       <c r="X6" t="n">
-        <v>0.009524746298347986</v>
+        <v>0.009524746298347982</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.008130352293658352</v>
+        <v>0.008130352293658315</v>
       </c>
       <c r="Z6" t="n">
         <v>0.007128277271810682</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.008029953214555534</v>
+        <v>0.008029953214555539</v>
       </c>
       <c r="AB6" t="n">
         <v>0.00699900501137975</v>
@@ -7049,28 +7049,28 @@
         <v>0.007364569340780264</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007333647288339404</v>
+        <v>0.007333647288339405</v>
       </c>
       <c r="D7" t="n">
         <v>0.007419138123449802</v>
       </c>
       <c r="E7" t="n">
-        <v>0.007485891571326111</v>
+        <v>0.007485891571326113</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007375392288182757</v>
+        <v>0.007375392288182756</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007340545311192787</v>
+        <v>0.007340545311192789</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007354933872528267</v>
+        <v>0.007354933872528268</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007353847128815461</v>
+        <v>0.007353847128815459</v>
       </c>
       <c r="J7" t="n">
-        <v>0.007424879636331376</v>
+        <v>0.007424879636331377</v>
       </c>
       <c r="K7" t="n">
         <v>0.007345711733015158</v>
@@ -7079,49 +7079,49 @@
         <v>0.007429502113576375</v>
       </c>
       <c r="M7" t="n">
-        <v>0.007324987033529811</v>
+        <v>0.007324987033529812</v>
       </c>
       <c r="N7" t="n">
-        <v>0.007353269513691091</v>
+        <v>0.007353269513691092</v>
       </c>
       <c r="O7" t="n">
-        <v>0.007524805736446928</v>
+        <v>0.00752480573644693</v>
       </c>
       <c r="P7" t="n">
-        <v>0.007448378591414219</v>
+        <v>0.007448378591414218</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.007296703119832141</v>
+        <v>0.007296703119832142</v>
       </c>
       <c r="R7" t="n">
         <v>0.007535293115481393</v>
       </c>
       <c r="S7" t="n">
-        <v>0.007418981650438402</v>
+        <v>0.007418981650438401</v>
       </c>
       <c r="T7" t="n">
-        <v>0.00729782646012116</v>
+        <v>0.007297826460121161</v>
       </c>
       <c r="U7" t="n">
-        <v>0.007331571348616354</v>
+        <v>0.007331571348616357</v>
       </c>
       <c r="V7" t="n">
-        <v>0.007455186872760129</v>
+        <v>0.00745518687276013</v>
       </c>
       <c r="W7" t="n">
-        <v>0.007531654319714681</v>
+        <v>0.00753165431971468</v>
       </c>
       <c r="X7" t="n">
         <v>0.009823679074054095</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.008408990037850903</v>
+        <v>0.008408990037850901</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.007427210047516788</v>
+        <v>0.007427210047516787</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.007676953203147624</v>
+        <v>0.007676953203147627</v>
       </c>
       <c r="AB7" t="n">
         <v>0.007298786178351079</v>
@@ -7134,79 +7134,79 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00855170510430402</v>
+        <v>0.008551705104304022</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009694890537301328</v>
+        <v>0.009694890537301333</v>
       </c>
       <c r="D8" t="n">
-        <v>0.009780381372411729</v>
+        <v>0.009780381372411733</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009221957218288432</v>
+        <v>0.009221957218288434</v>
       </c>
       <c r="F8" t="n">
         <v>0.008745440275858352</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009945247395861825</v>
+        <v>0.00994524739586183</v>
       </c>
       <c r="H8" t="n">
-        <v>0.009716177121490189</v>
+        <v>0.009716177121490196</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009715090377777381</v>
+        <v>0.00971509037777739</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0097861228852933</v>
+        <v>0.009786122885293302</v>
       </c>
       <c r="K8" t="n">
-        <v>0.009706954981977078</v>
+        <v>0.009706954981977082</v>
       </c>
       <c r="L8" t="n">
-        <v>0.009790745362538301</v>
+        <v>0.009790745362538303</v>
       </c>
       <c r="M8" t="n">
         <v>0.009686230282491541</v>
       </c>
       <c r="N8" t="n">
-        <v>0.008804383037545112</v>
+        <v>0.008804383037545114</v>
       </c>
       <c r="O8" t="n">
-        <v>0.009226052549556722</v>
+        <v>0.009226052549556725</v>
       </c>
       <c r="P8" t="n">
-        <v>0.009088317019827536</v>
+        <v>0.009088317019827537</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.008253099964761515</v>
+        <v>0.008253099964761514</v>
       </c>
       <c r="R8" t="n">
-        <v>0.009896536364443313</v>
+        <v>0.009896536364443315</v>
       </c>
       <c r="S8" t="n">
         <v>0.009780224899400329</v>
       </c>
       <c r="T8" t="n">
-        <v>0.009659069709083085</v>
+        <v>0.009659069709083088</v>
       </c>
       <c r="U8" t="n">
-        <v>0.009119932620935417</v>
+        <v>0.009119932620935415</v>
       </c>
       <c r="V8" t="n">
-        <v>0.009494911655480767</v>
+        <v>0.00949491165548077</v>
       </c>
       <c r="W8" t="n">
-        <v>0.009893128314479922</v>
+        <v>0.009893128314479928</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01088768520303574</v>
+        <v>0.01088768520303575</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01193666437718584</v>
+        <v>0.01193666437718585</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.008592536161707447</v>
+        <v>0.008592536161707451</v>
       </c>
       <c r="AA8" t="n">
         <v>0.01003819645210955</v>
@@ -7225,13 +7225,13 @@
         <v>0.008338173049968299</v>
       </c>
       <c r="C9" t="n">
-        <v>0.008759231899379185</v>
+        <v>0.008759231899379188</v>
       </c>
       <c r="D9" t="n">
-        <v>0.008844722734489583</v>
+        <v>0.008844722734489581</v>
       </c>
       <c r="E9" t="n">
-        <v>0.008807160975458994</v>
+        <v>0.008807160975458998</v>
       </c>
       <c r="F9" t="n">
         <v>0.007759037322804957</v>
@@ -7240,67 +7240,67 @@
         <v>0.008766130106376132</v>
       </c>
       <c r="H9" t="n">
-        <v>0.008780518483568048</v>
+        <v>0.008780518483568049</v>
       </c>
       <c r="I9" t="n">
-        <v>0.008779431739855244</v>
+        <v>0.008779431739855246</v>
       </c>
       <c r="J9" t="n">
         <v>0.008850464247371159</v>
       </c>
       <c r="K9" t="n">
-        <v>0.008771296344054939</v>
+        <v>0.008771296344054942</v>
       </c>
       <c r="L9" t="n">
-        <v>0.008855086724616159</v>
+        <v>0.00885508672461616</v>
       </c>
       <c r="M9" t="n">
         <v>0.008750571644569596</v>
       </c>
       <c r="N9" t="n">
-        <v>0.008778854124730874</v>
+        <v>0.008778854124730878</v>
       </c>
       <c r="O9" t="n">
         <v>0.009100198209960228</v>
       </c>
       <c r="P9" t="n">
-        <v>0.009056346937000997</v>
+        <v>0.009056346937000999</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.008722287915015484</v>
+        <v>0.008722287915015487</v>
       </c>
       <c r="R9" t="n">
-        <v>0.008960877726521174</v>
+        <v>0.008960877726521177</v>
       </c>
       <c r="S9" t="n">
-        <v>0.008844566261478186</v>
+        <v>0.008844566261478188</v>
       </c>
       <c r="T9" t="n">
-        <v>0.008723411071160942</v>
+        <v>0.008723411071160946</v>
       </c>
       <c r="U9" t="n">
-        <v>0.008757899743966383</v>
+        <v>0.008757899743966385</v>
       </c>
       <c r="V9" t="n">
-        <v>0.009402347898072585</v>
+        <v>0.009402347898072589</v>
       </c>
       <c r="W9" t="n">
-        <v>0.008957238930754464</v>
+        <v>0.008957238930754468</v>
       </c>
       <c r="X9" t="n">
         <v>0.01124926368509388</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.009834574648890688</v>
+        <v>0.009834574648890686</v>
       </c>
       <c r="Z9" t="n">
         <v>0.008580290439571281</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.009102537814187406</v>
+        <v>0.009102537814187411</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.00872437078939086</v>
+        <v>0.008724370789390862</v>
       </c>
     </row>
   </sheetData>
@@ -7469,82 +7469,82 @@
         <v>0.003940103912448254</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003485709937841947</v>
+        <v>0.003485709937841948</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003982328326586782</v>
+        <v>0.00398232832658678</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003903412905599441</v>
+        <v>0.003903412905599437</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00389956813609461</v>
+        <v>0.003899568136094609</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003957144900433602</v>
+        <v>0.003957144900433599</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00389446420277477</v>
+        <v>0.003894464202774767</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003954329989250814</v>
+        <v>0.003954329989250811</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003988788839830577</v>
+        <v>0.003988788839830571</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004011411537652975</v>
+        <v>0.004011411537652974</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004042089945954244</v>
+        <v>0.004042089945954228</v>
       </c>
       <c r="M2" t="n">
-        <v>0.004371396573337336</v>
+        <v>0.004371396573337337</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003989458396433537</v>
+        <v>0.003989458396433535</v>
       </c>
       <c r="O2" t="n">
-        <v>0.005674057880671554</v>
+        <v>0.005674057880671553</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003943305520990648</v>
+        <v>0.003943305520990646</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003904606044791308</v>
+        <v>0.003904606044791305</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003905999017053341</v>
+        <v>0.003905999017053339</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003950073149472851</v>
+        <v>0.003950073149472848</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003945427817881905</v>
+        <v>0.003945427817881903</v>
       </c>
       <c r="U2" t="n">
-        <v>0.004123534850679608</v>
+        <v>0.004123534850679603</v>
       </c>
       <c r="V2" t="n">
-        <v>0.00389439880146457</v>
+        <v>0.003894398801464568</v>
       </c>
       <c r="W2" t="n">
-        <v>0.003938995894990627</v>
+        <v>0.00393899589499062</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004230711542886612</v>
+        <v>0.004230711542886606</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.004136074459375198</v>
+        <v>0.004136074459375197</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.004931264977233492</v>
+        <v>0.00493126497723349</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.004006463866294023</v>
+        <v>0.004006463866294022</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.004295968400456064</v>
+        <v>0.004295968400456065</v>
       </c>
     </row>
     <row r="3">
@@ -7554,85 +7554,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004163061264062324</v>
+        <v>0.004184844175947661</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003055525485893288</v>
+        <v>0.003060952413316557</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004469734341168704</v>
+        <v>0.004502561238502488</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003902176581999764</v>
+        <v>0.003914602513336998</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003877275093840604</v>
+        <v>0.003889137888103664</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004283827130749745</v>
+        <v>0.004309884558213718</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003841427440584802</v>
+        <v>0.003852005331996664</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004269366560104719</v>
+        <v>0.004295129524609686</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0045113045676298</v>
+        <v>0.004545576247680881</v>
       </c>
       <c r="K3" t="n">
-        <v>0.004671537733508794</v>
+        <v>0.004711694797467509</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004890840331938086</v>
+        <v>0.004938413332131732</v>
       </c>
       <c r="M3" t="n">
-        <v>0.00721534401019071</v>
+        <v>0.007346447817881728</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004519079627109622</v>
+        <v>0.004553576382778467</v>
       </c>
       <c r="O3" t="n">
-        <v>0.006921801452181111</v>
+        <v>0.006938844743510649</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004186468276589812</v>
+        <v>0.00420900951613092</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003912470415321796</v>
+        <v>0.003925530365904196</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003923849781106837</v>
+        <v>0.003937342045389342</v>
       </c>
       <c r="S3" t="n">
-        <v>0.004233066939390458</v>
+        <v>0.004257413805213178</v>
       </c>
       <c r="T3" t="n">
-        <v>0.00420552029227207</v>
+        <v>0.004228990850337033</v>
       </c>
       <c r="U3" t="n">
-        <v>0.005578311340238709</v>
+        <v>0.005651211403590657</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003838372515830815</v>
+        <v>0.003848743298155117</v>
       </c>
       <c r="W3" t="n">
-        <v>0.004479741177440371</v>
+        <v>0.004516189606883367</v>
       </c>
       <c r="X3" t="n">
-        <v>0.006244825324917035</v>
+        <v>0.006340635301356031</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.005563389354881701</v>
+        <v>0.005634839778431849</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.005694889174587645</v>
+        <v>0.005711900423478264</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.004639415637617134</v>
+        <v>0.004678117846234494</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.006694950440311221</v>
+        <v>0.00680631483169383</v>
       </c>
     </row>
     <row r="4">
@@ -7642,37 +7642,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0076797930137208</v>
+        <v>0.007679793013720765</v>
       </c>
       <c r="C4" t="n">
-        <v>0.006938173510755482</v>
+        <v>0.006938173510755484</v>
       </c>
       <c r="D4" t="n">
-        <v>0.008156737195605569</v>
+        <v>0.008156737195605565</v>
       </c>
       <c r="E4" t="n">
-        <v>0.007265351212666311</v>
+        <v>0.007265351212666305</v>
       </c>
       <c r="F4" t="n">
-        <v>0.007221922772427953</v>
+        <v>0.007221922772427954</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007872278812257045</v>
+        <v>0.00787227881225705</v>
       </c>
       <c r="H4" t="n">
-        <v>0.007164271497655005</v>
+        <v>0.007164271497655</v>
       </c>
       <c r="I4" t="n">
-        <v>0.007840483095524263</v>
+        <v>0.007840483095524264</v>
       </c>
       <c r="J4" t="n">
-        <v>0.008226004658085685</v>
+        <v>0.00822600465808568</v>
       </c>
       <c r="K4" t="n">
         <v>0.008485245443536321</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008831772178064169</v>
+        <v>0.008831772178064093</v>
       </c>
       <c r="M4" t="n">
         <v>0.01250627554421347</v>
@@ -7681,25 +7681,25 @@
         <v>0.008237274614518874</v>
       </c>
       <c r="O4" t="n">
-        <v>0.007466449528530761</v>
+        <v>0.007466449528530763</v>
       </c>
       <c r="P4" t="n">
-        <v>0.007715956655019788</v>
+        <v>0.007715956655019785</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.007278828268709693</v>
+        <v>0.007278828268709689</v>
       </c>
       <c r="R4" t="n">
-        <v>0.00729456253120818</v>
+        <v>0.007294562531208183</v>
       </c>
       <c r="S4" t="n">
-        <v>0.00779240013198918</v>
+        <v>0.007792400131989174</v>
       </c>
       <c r="T4" t="n">
-        <v>0.007739928974711332</v>
+        <v>0.007739928974711329</v>
       </c>
       <c r="U4" t="n">
-        <v>0.009946809162058168</v>
+        <v>0.009946809162058166</v>
       </c>
       <c r="V4" t="n">
         <v>0.007138497001192967</v>
@@ -7708,16 +7708,16 @@
         <v>0.008329713755712755</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01096233988563686</v>
+        <v>0.01096233988563684</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.009868175702997257</v>
+        <v>0.009868175702997254</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.007463433611166882</v>
+        <v>0.007463433611166871</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.008429359219495725</v>
+        <v>0.008429359219495721</v>
       </c>
       <c r="AB4" t="n">
         <v>0.01164905134855173</v>
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02372237155207518</v>
+        <v>0.02372237155207485</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0113165212164278</v>
+        <v>0.01131652121642781</v>
       </c>
       <c r="D5" t="n">
         <v>0.03569651847363715</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0164316546846572</v>
+        <v>0.01643165468465711</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01702248627131342</v>
+        <v>0.01702248627131341</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02688552240953428</v>
+        <v>0.02688552240953427</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01625464123250715</v>
+        <v>0.01625464123250719</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02941524163138069</v>
+        <v>0.0294152416313807</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03454835380473047</v>
+        <v>0.03454835380473042</v>
       </c>
       <c r="K5" t="n">
         <v>0.03870173953227148</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04544808068110114</v>
+        <v>0.04544808068109991</v>
       </c>
       <c r="M5" t="n">
         <v>0.1142387892132546</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0363615153000075</v>
+        <v>0.03636151530000752</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01977509526856564</v>
+        <v>0.01977509526856566</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0247159118797009</v>
+        <v>0.02471591187970088</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01767550505141343</v>
+        <v>0.01767550505141331</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01877256110908236</v>
+        <v>0.01877256110908242</v>
       </c>
       <c r="S5" t="n">
-        <v>0.02521459375811649</v>
+        <v>0.02521459375811633</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02734099556081708</v>
+        <v>0.02734099556081702</v>
       </c>
       <c r="U5" t="n">
-        <v>0.06654249493075891</v>
+        <v>0.06654249493075887</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0147762307389829</v>
+        <v>0.01477623073898292</v>
       </c>
       <c r="W5" t="n">
-        <v>0.03758663589692036</v>
+        <v>0.03758663589692026</v>
       </c>
       <c r="X5" t="n">
-        <v>0.09006132485469065</v>
+        <v>0.09006132485469055</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.06650888789221933</v>
+        <v>0.06650888789221931</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.02008972873897236</v>
+        <v>0.02008972873897208</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.03941899655359857</v>
+        <v>0.03941899655359851</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1095882607136975</v>
+        <v>0.1095882607136973</v>
       </c>
     </row>
     <row r="6">
@@ -7818,85 +7818,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.007960435459393031</v>
+        <v>0.007960435459393012</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00721881595642771</v>
+        <v>0.007218815956427713</v>
       </c>
       <c r="D6" t="n">
         <v>0.008437379641277798</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008342839428449041</v>
+        <v>0.008342839428449031</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00750256521810018</v>
+        <v>0.007502565218100184</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008949767028039766</v>
+        <v>0.008949767028039771</v>
       </c>
       <c r="H6" t="n">
         <v>0.007444913943327233</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00812112554119649</v>
+        <v>0.008121125541196494</v>
       </c>
       <c r="J6" t="n">
-        <v>0.008506647103757915</v>
+        <v>0.008506647103757913</v>
       </c>
       <c r="K6" t="n">
-        <v>0.009562733659319046</v>
+        <v>0.009562733659319042</v>
       </c>
       <c r="L6" t="n">
-        <v>0.009909260393846894</v>
+        <v>0.009909260393846771</v>
       </c>
       <c r="M6" t="n">
         <v>0.0127869179898857</v>
       </c>
       <c r="N6" t="n">
-        <v>0.00852268119522415</v>
+        <v>0.008522681195224131</v>
       </c>
       <c r="O6" t="n">
-        <v>0.008549301707330642</v>
+        <v>0.008549301707330637</v>
       </c>
       <c r="P6" t="n">
-        <v>0.008799181560775672</v>
+        <v>0.008799181560775667</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.00755947071438192</v>
+        <v>0.007559470714381913</v>
       </c>
       <c r="R6" t="n">
-        <v>0.008372050746990904</v>
+        <v>0.008372050746990907</v>
       </c>
       <c r="S6" t="n">
-        <v>0.008073042577661406</v>
+        <v>0.008073042577661399</v>
       </c>
       <c r="T6" t="n">
-        <v>0.00802057142038356</v>
+        <v>0.008020571420383564</v>
       </c>
       <c r="U6" t="n">
         <v>0.0110494921670097</v>
       </c>
       <c r="V6" t="n">
-        <v>0.007419139446865197</v>
+        <v>0.007419139446865198</v>
       </c>
       <c r="W6" t="n">
-        <v>0.008639475521895085</v>
+        <v>0.00863947552189508</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01203982810141958</v>
+        <v>0.01203982810141956</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0101960416254818</v>
+        <v>0.01019604162548182</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.008540921826949608</v>
+        <v>0.008540921826949594</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.009506847435278448</v>
+        <v>0.009506847435278439</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01196772328096821</v>
+        <v>0.0119677232809682</v>
       </c>
     </row>
     <row r="7">
@@ -7906,82 +7906,82 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.008336386940575131</v>
+        <v>0.008336386940575105</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007594767437609814</v>
+        <v>0.007594767437609816</v>
       </c>
       <c r="D7" t="n">
-        <v>0.008813331122459902</v>
+        <v>0.008813331122459904</v>
       </c>
       <c r="E7" t="n">
-        <v>0.007921945139520646</v>
+        <v>0.00792194513952064</v>
       </c>
       <c r="F7" t="n">
         <v>0.007878516699282285</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008528872739111383</v>
+        <v>0.008528872739111385</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007820865424509339</v>
+        <v>0.007820865424509334</v>
       </c>
       <c r="I7" t="n">
-        <v>0.008497077022378598</v>
+        <v>0.008497077022378599</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00888259858494002</v>
+        <v>0.008882598584940012</v>
       </c>
       <c r="K7" t="n">
-        <v>0.009141839370390661</v>
+        <v>0.009141839370390658</v>
       </c>
       <c r="L7" t="n">
-        <v>0.009488366104918509</v>
+        <v>0.00948836610491839</v>
       </c>
       <c r="M7" t="n">
         <v>0.01316286947106779</v>
       </c>
       <c r="N7" t="n">
-        <v>0.008893868541373209</v>
+        <v>0.008893868541373208</v>
       </c>
       <c r="O7" t="n">
-        <v>0.008123019797841484</v>
+        <v>0.008123019797841486</v>
       </c>
       <c r="P7" t="n">
-        <v>0.008372526924330511</v>
+        <v>0.008372526924330504</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.007935422195564024</v>
+        <v>0.007935422195564016</v>
       </c>
       <c r="R7" t="n">
-        <v>0.007951156458062514</v>
+        <v>0.007951156458062518</v>
       </c>
       <c r="S7" t="n">
-        <v>0.00844899405884351</v>
+        <v>0.008448994058843504</v>
       </c>
       <c r="T7" t="n">
-        <v>0.008396522901565664</v>
+        <v>0.008396522901565662</v>
       </c>
       <c r="U7" t="n">
         <v>0.01062797048933927</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0077950909280473</v>
+        <v>0.007795090928047298</v>
       </c>
       <c r="W7" t="n">
-        <v>0.008986307682567085</v>
+        <v>0.008986307682567083</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0116189338124912</v>
+        <v>0.01161893381249118</v>
       </c>
       <c r="Y7" t="n">
         <v>0.01054996441902041</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.008120027538021213</v>
+        <v>0.008120027538021208</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.009085953146350063</v>
+        <v>0.009085953146350058</v>
       </c>
       <c r="AB7" t="n">
         <v>0.01230564527540605</v>
@@ -7994,25 +7994,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.009695147033321536</v>
+        <v>0.009695147033321506</v>
       </c>
       <c r="C8" t="n">
         <v>0.01033701715943071</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01155558084428078</v>
+        <v>0.01155558084428079</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009927527444257013</v>
+        <v>0.009927527444257008</v>
       </c>
       <c r="F8" t="n">
         <v>0.009452808307050208</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01155799804811474</v>
+        <v>0.01155799804811475</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01056311514633023</v>
+        <v>0.01056311514633022</v>
       </c>
       <c r="I8" t="n">
         <v>0.01123932674419949</v>
@@ -8024,7 +8024,7 @@
         <v>0.01188408909221155</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01223061582673939</v>
+        <v>0.01223061582673932</v>
       </c>
       <c r="M8" t="n">
         <v>0.01590511919288897</v>
@@ -8039,10 +8039,10 @@
         <v>0.0102648373951024</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.009022294999597443</v>
+        <v>0.009022294999597445</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01069340617988341</v>
+        <v>0.01069340617988342</v>
       </c>
       <c r="S8" t="n">
         <v>0.0111912437806644</v>
@@ -8060,13 +8060,13 @@
         <v>0.01172882929971009</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01283260619004557</v>
+        <v>0.01283260619004556</v>
       </c>
       <c r="Y8" t="n">
         <v>0.0146669859875833</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.009453088600626295</v>
+        <v>0.009453088600626283</v>
       </c>
       <c r="AA8" t="n">
         <v>0.01182820286817095</v>
@@ -8082,58 +8082,58 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.009788775162097096</v>
+        <v>0.009788775162097058</v>
       </c>
       <c r="C9" t="n">
-        <v>0.009675218750141977</v>
+        <v>0.009675218750141974</v>
       </c>
       <c r="D9" t="n">
         <v>0.01089378243499206</v>
       </c>
       <c r="E9" t="n">
-        <v>0.009857441303135893</v>
+        <v>0.009857441303135879</v>
       </c>
       <c r="F9" t="n">
-        <v>0.008511112443911218</v>
+        <v>0.008511112443911216</v>
       </c>
       <c r="G9" t="n">
         <v>0.01060932307747497</v>
       </c>
       <c r="H9" t="n">
-        <v>0.009901316737041496</v>
+        <v>0.009901316737041499</v>
       </c>
       <c r="I9" t="n">
         <v>0.01057752833491076</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01096304989747217</v>
+        <v>0.01096304989747216</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01122229068292283</v>
+        <v>0.01122229068292282</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01156881741745067</v>
+        <v>0.01156881741745054</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01524332078359997</v>
+        <v>0.01524332078359996</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01097431985390537</v>
+        <v>0.01097431985390536</v>
       </c>
       <c r="O9" t="n">
         <v>0.01041163275689283</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0107064065368025</v>
+        <v>0.01070640653680249</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.01001587253392761</v>
+        <v>0.0100158725339276</v>
       </c>
       <c r="R9" t="n">
-        <v>0.01003160777059468</v>
+        <v>0.01003160777059467</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01052944537137568</v>
+        <v>0.01052944537137566</v>
       </c>
       <c r="T9" t="n">
         <v>0.01047697421409782</v>
@@ -8145,16 +8145,16 @@
         <v>0.01060031084032843</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01106675899509925</v>
+        <v>0.01106675899509924</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01369938512502336</v>
+        <v>0.01369938512502333</v>
       </c>
       <c r="Y9" t="n">
         <v>0.01263041573155256</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.009821812269391819</v>
+        <v>0.009821812269391801</v>
       </c>
       <c r="AA9" t="n">
         <v>0.01116640445888222</v>
@@ -8326,85 +8326,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003815093471769076</v>
+        <v>0.003815093471769073</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003431928902596505</v>
+        <v>0.003431928902596502</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003835532269870233</v>
+        <v>0.003835532269870229</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003829158159508395</v>
+        <v>0.003829158159508391</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003821953545793705</v>
+        <v>0.003821953545793704</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00389076489197997</v>
+        <v>0.003890764891979963</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003822140946515484</v>
+        <v>0.003822140946515482</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003828162268963356</v>
+        <v>0.003828162268963351</v>
       </c>
       <c r="J2" t="n">
         <v>0.003882634942977412</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003841905463573692</v>
+        <v>0.00384190546357369</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003885974276522062</v>
+        <v>0.003885974276522055</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003858605717063106</v>
+        <v>0.003858605717063108</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003832626041732633</v>
+        <v>0.003832626041732631</v>
       </c>
       <c r="O2" t="n">
-        <v>0.005523270456218045</v>
+        <v>0.00552327045621805</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003869121239336907</v>
+        <v>0.003869121239336904</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003829902864543988</v>
+        <v>0.00382990286454398</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003839887786001725</v>
+        <v>0.003839887786001729</v>
       </c>
       <c r="S2" t="n">
-        <v>0.00383979326981827</v>
+        <v>0.003839793269818268</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003823504117119589</v>
+        <v>0.003823504117119587</v>
       </c>
       <c r="U2" t="n">
-        <v>0.003812664794298036</v>
+        <v>0.003812664794298043</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003825135941918613</v>
+        <v>0.003825135941918609</v>
       </c>
       <c r="W2" t="n">
-        <v>0.003781652881277615</v>
+        <v>0.003781652881277622</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004203549079402723</v>
+        <v>0.004203549079402721</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.004308466012889062</v>
+        <v>0.004308466012889057</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.004816786108156994</v>
+        <v>0.004816786108156992</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003852466330550858</v>
+        <v>0.003852466330550862</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.006556942306285844</v>
+        <v>0.006556942306285843</v>
       </c>
     </row>
     <row r="3">
@@ -8414,85 +8414,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00360023638862956</v>
+        <v>0.003603480478470446</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002985264786844034</v>
+        <v>0.002989350710248541</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003746683969843337</v>
+        <v>0.003755149715723422</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003699226718408315</v>
+        <v>0.003705769877901678</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003649748175828233</v>
+        <v>0.003654784328051928</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004136566645137616</v>
+        <v>0.004158742275829453</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003651395161625393</v>
+        <v>0.00365648638785907</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003694226257382684</v>
+        <v>0.003700830528893937</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004081626248357599</v>
+        <v>0.004101919822500521</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003791304587179731</v>
+        <v>0.003801376209901855</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004103734397202945</v>
+        <v>0.004124825209639163</v>
       </c>
       <c r="M3" t="n">
-        <v>0.003914375760472228</v>
+        <v>0.003928900524217046</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003725775668716057</v>
+        <v>0.003733476057294596</v>
       </c>
       <c r="O3" t="n">
-        <v>0.006484499319071784</v>
+        <v>0.006490702250066102</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003984022942304846</v>
+        <v>0.004000744789467299</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003705830005548319</v>
+        <v>0.00371285142335137</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003778407767458979</v>
+        <v>0.003788012535919544</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003775472186145962</v>
+        <v>0.003784917242757318</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003660805454807614</v>
+        <v>0.003666219445509362</v>
       </c>
       <c r="U3" t="n">
-        <v>0.003834432418560748</v>
+        <v>0.003848654800751729</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003671678614355892</v>
+        <v>0.003677441445768425</v>
       </c>
       <c r="W3" t="n">
-        <v>0.003822991537147354</v>
+        <v>0.003839008509362545</v>
       </c>
       <c r="X3" t="n">
-        <v>0.006373085441259971</v>
+        <v>0.006474908075537397</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.007120328273726126</v>
+        <v>0.007248135728986141</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.005339628400137531</v>
+        <v>0.005346825879602351</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003867225369838267</v>
+        <v>0.003879913802833261</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.02301322547414383</v>
+        <v>0.02370326720306572</v>
       </c>
     </row>
     <row r="4">
@@ -8508,31 +8508,31 @@
         <v>0.006824716205596319</v>
       </c>
       <c r="D4" t="n">
-        <v>0.007019388655684181</v>
+        <v>0.007019388655684179</v>
       </c>
       <c r="E4" t="n">
-        <v>0.006947390146911661</v>
+        <v>0.006947390146911662</v>
       </c>
       <c r="F4" t="n">
-        <v>0.006866010720718154</v>
+        <v>0.006866010720718155</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007643266530675112</v>
+        <v>0.007643266530675108</v>
       </c>
       <c r="H4" t="n">
-        <v>0.006868127498079253</v>
+        <v>0.006868127498079251</v>
       </c>
       <c r="I4" t="n">
         <v>0.006936141105073125</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00754792799469015</v>
+        <v>0.007547927994690149</v>
       </c>
       <c r="K4" t="n">
         <v>0.007091376810378722</v>
       </c>
       <c r="L4" t="n">
-        <v>0.007589154325286119</v>
+        <v>0.007589154325286118</v>
       </c>
       <c r="M4" t="n">
         <v>0.007286656666863549</v>
@@ -8547,28 +8547,28 @@
         <v>0.007398791517499655</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0069558019328699</v>
+        <v>0.006955801932869902</v>
       </c>
       <c r="R4" t="n">
-        <v>0.007068586214025822</v>
+        <v>0.007068586214025823</v>
       </c>
       <c r="S4" t="n">
         <v>0.0070675186102541</v>
       </c>
       <c r="T4" t="n">
-        <v>0.00688352513714208</v>
+        <v>0.006883525137142081</v>
       </c>
       <c r="U4" t="n">
-        <v>0.00726098210443831</v>
+        <v>0.007260982104438312</v>
       </c>
       <c r="V4" t="n">
         <v>0.006878254031158316</v>
       </c>
       <c r="W4" t="n">
-        <v>0.00736026495952224</v>
+        <v>0.007360264959522239</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01117630781545025</v>
+        <v>0.01117630781545026</v>
       </c>
       <c r="Y4" t="n">
         <v>0.01234098623399455</v>
@@ -8580,7 +8580,7 @@
         <v>0.007210666661124662</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.03732961331750825</v>
+        <v>0.03732961331750827</v>
       </c>
     </row>
     <row r="5">
@@ -8590,13 +8590,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.009024389465172707</v>
+        <v>0.0090243894651727</v>
       </c>
       <c r="C5" t="n">
-        <v>0.009905021365644253</v>
+        <v>0.009905021365644251</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01340553580351304</v>
+        <v>0.01340553580351303</v>
       </c>
       <c r="E5" t="n">
         <v>0.01111385954274931</v>
@@ -8605,34 +8605,34 @@
         <v>0.01068047917303075</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02220354943221063</v>
+        <v>0.02220354943221052</v>
       </c>
       <c r="H5" t="n">
-        <v>0.010878307117697</v>
+        <v>0.01087830711769699</v>
       </c>
       <c r="I5" t="n">
         <v>0.01200693552074958</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02217377279052188</v>
+        <v>0.02217377279052183</v>
       </c>
       <c r="K5" t="n">
         <v>0.01423040549160956</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02195055278447079</v>
+        <v>0.02195055278447081</v>
       </c>
       <c r="M5" t="n">
         <v>0.01782492890899358</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01273869717951994</v>
+        <v>0.01273869717951992</v>
       </c>
       <c r="O5" t="n">
         <v>0.01116442084435913</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01887880739625658</v>
+        <v>0.01887880739625657</v>
       </c>
       <c r="Q5" t="n">
         <v>0.01193025961947198</v>
@@ -8641,34 +8641,34 @@
         <v>0.01460643884897797</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01341584295181784</v>
+        <v>0.01341584295181783</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0109854694537689</v>
+        <v>0.01098546945376893</v>
       </c>
       <c r="U5" t="n">
-        <v>0.01710454133796101</v>
+        <v>0.01710454133796103</v>
       </c>
       <c r="V5" t="n">
-        <v>0.01088705019356411</v>
+        <v>0.0108870501935641</v>
       </c>
       <c r="W5" t="n">
-        <v>0.01926703494571608</v>
+        <v>0.01926703494571607</v>
       </c>
       <c r="X5" t="n">
-        <v>0.08684830277292042</v>
+        <v>0.08684830277292038</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1070028797542557</v>
+        <v>0.1070028797542556</v>
       </c>
       <c r="Z5" t="n">
         <v>0.01182060455924125</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01662389287844776</v>
+        <v>0.01662389287844773</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.5893842039663295</v>
+        <v>0.5893842039663304</v>
       </c>
     </row>
     <row r="6">
@@ -8678,7 +8678,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.007911020078096093</v>
+        <v>0.007911020078096099</v>
       </c>
       <c r="C6" t="n">
         <v>0.00794721325487243</v>
@@ -8687,16 +8687,16 @@
         <v>0.008141885704960293</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007184268367155759</v>
+        <v>0.007184268367155756</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00710288894096225</v>
+        <v>0.007102888940962251</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007880144750919211</v>
+        <v>0.007880144750919204</v>
       </c>
       <c r="H6" t="n">
-        <v>0.007105005718323348</v>
+        <v>0.007105005718323349</v>
       </c>
       <c r="I6" t="n">
         <v>0.008058638154349236</v>
@@ -8705,43 +8705,43 @@
         <v>0.008670425043966258</v>
       </c>
       <c r="K6" t="n">
-        <v>0.007328255030622817</v>
+        <v>0.007328255030622818</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008711651374562224</v>
+        <v>0.008711651374562226</v>
       </c>
       <c r="M6" t="n">
-        <v>0.007523534887107643</v>
+        <v>0.007523534887107644</v>
       </c>
       <c r="N6" t="n">
-        <v>0.007226406434760077</v>
+        <v>0.007226406434760078</v>
       </c>
       <c r="O6" t="n">
-        <v>0.008039528252794415</v>
+        <v>0.008039528252794416</v>
       </c>
       <c r="P6" t="n">
-        <v>0.007619028944206316</v>
+        <v>0.007619028944206319</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.007192680153113998</v>
+        <v>0.007192680153113997</v>
       </c>
       <c r="R6" t="n">
-        <v>0.008191083263301932</v>
+        <v>0.008191083263301934</v>
       </c>
       <c r="S6" t="n">
-        <v>0.007304396830498194</v>
+        <v>0.007304396830498197</v>
       </c>
       <c r="T6" t="n">
         <v>0.007120403357386176</v>
       </c>
       <c r="U6" t="n">
-        <v>0.008403885763072249</v>
+        <v>0.008403885763072251</v>
       </c>
       <c r="V6" t="n">
         <v>0.007115132251402414</v>
       </c>
       <c r="W6" t="n">
-        <v>0.007619663783241389</v>
+        <v>0.007619663783241369</v>
       </c>
       <c r="X6" t="n">
         <v>0.01229880486472637</v>
@@ -8750,13 +8750,13 @@
         <v>0.01261611026696002</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.008089323550259193</v>
+        <v>0.008089323550259195</v>
       </c>
       <c r="AA6" t="n">
         <v>0.007447544881368757</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0377743193769623</v>
+        <v>0.03777431937696226</v>
       </c>
     </row>
     <row r="7">
@@ -8766,7 +8766,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.007357189148434479</v>
+        <v>0.007357189148434481</v>
       </c>
       <c r="C7" t="n">
         <v>0.007393382325210811</v>
@@ -8775,13 +8775,13 @@
         <v>0.007588054775298675</v>
       </c>
       <c r="E7" t="n">
-        <v>0.007516056266526154</v>
+        <v>0.007516056266526157</v>
       </c>
       <c r="F7" t="n">
         <v>0.007434676840332648</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008211932650289603</v>
+        <v>0.008211932650289596</v>
       </c>
       <c r="H7" t="n">
         <v>0.007436793617693747</v>
@@ -8793,46 +8793,46 @@
         <v>0.008116594114304642</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007660042929993215</v>
+        <v>0.007660042929993218</v>
       </c>
       <c r="L7" t="n">
-        <v>0.008157820444900611</v>
+        <v>0.008157820444900613</v>
       </c>
       <c r="M7" t="n">
-        <v>0.007855322786478039</v>
+        <v>0.00785532278647804</v>
       </c>
       <c r="N7" t="n">
         <v>0.007555227591553552</v>
       </c>
       <c r="O7" t="n">
-        <v>0.007491083791190553</v>
+        <v>0.007491083791190555</v>
       </c>
       <c r="P7" t="n">
         <v>0.007967436061582667</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.007524468052484392</v>
+        <v>0.007524468052484394</v>
       </c>
       <c r="R7" t="n">
-        <v>0.007637252333640314</v>
+        <v>0.007637252333640315</v>
       </c>
       <c r="S7" t="n">
-        <v>0.00763618472986859</v>
+        <v>0.007636184729868592</v>
       </c>
       <c r="T7" t="n">
-        <v>0.007452191256756574</v>
+        <v>0.007452191256756576</v>
       </c>
       <c r="U7" t="n">
         <v>0.007849129453692746</v>
       </c>
       <c r="V7" t="n">
-        <v>0.007446920150772811</v>
+        <v>0.007446920150772812</v>
       </c>
       <c r="W7" t="n">
         <v>0.007928931079136734</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01174497393506476</v>
+        <v>0.01174497393506477</v>
       </c>
       <c r="Y7" t="n">
         <v>0.01293005896296687</v>
@@ -8844,7 +8844,7 @@
         <v>0.007779332780739155</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.03789827943712268</v>
+        <v>0.03789827943712269</v>
       </c>
     </row>
     <row r="8">
@@ -8857,28 +8857,28 @@
         <v>0.008597663809960193</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009871983102791361</v>
+        <v>0.009871983102791351</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01006665555287923</v>
+        <v>0.01006665555287922</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009335391409744154</v>
+        <v>0.009335391409744149</v>
       </c>
       <c r="F8" t="n">
-        <v>0.008868037080454022</v>
+        <v>0.008868037080454017</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01094726694367517</v>
+        <v>0.01094726694367515</v>
       </c>
       <c r="H8" t="n">
-        <v>0.009915394395274299</v>
+        <v>0.009915394395274292</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009983408002268176</v>
+        <v>0.009983408002268166</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0105951948918852</v>
+        <v>0.01059519489188519</v>
       </c>
       <c r="K8" t="n">
         <v>0.01013864370757377</v>
@@ -8887,31 +8887,31 @@
         <v>0.01063642122248116</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01033392356405863</v>
+        <v>0.01033392356405862</v>
       </c>
       <c r="N8" t="n">
-        <v>0.009074073495203739</v>
+        <v>0.009074073495203736</v>
       </c>
       <c r="O8" t="n">
-        <v>0.009273700243139867</v>
+        <v>0.009273700243139863</v>
       </c>
       <c r="P8" t="n">
-        <v>0.009685401267237837</v>
+        <v>0.009685401267237834</v>
       </c>
       <c r="Q8" t="n">
         <v>0.008521622673357841</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01011585311122087</v>
+        <v>0.01011585311122086</v>
       </c>
       <c r="S8" t="n">
         <v>0.01011478550744914</v>
       </c>
       <c r="T8" t="n">
-        <v>0.009930792034337131</v>
+        <v>0.009930792034337121</v>
       </c>
       <c r="U8" t="n">
-        <v>0.009723642352769547</v>
+        <v>0.00972364235276954</v>
       </c>
       <c r="V8" t="n">
         <v>0.009586349842708583</v>
@@ -8926,13 +8926,13 @@
         <v>0.0166385021309697</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0087529684538635</v>
+        <v>0.008752968453863499</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01025793355831971</v>
+        <v>0.0102579335583197</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.04167020647335135</v>
+        <v>0.04167020647335131</v>
       </c>
     </row>
     <row r="9">
@@ -8942,67 +8942,67 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008516374226646761</v>
+        <v>0.008516374226646764</v>
       </c>
       <c r="C9" t="n">
-        <v>0.009068985620523476</v>
+        <v>0.009068985620523478</v>
       </c>
       <c r="D9" t="n">
-        <v>0.009263658070611341</v>
+        <v>0.009263658070611342</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00907247198402034</v>
+        <v>0.009072471984020338</v>
       </c>
       <c r="F9" t="n">
-        <v>0.007919795811778589</v>
+        <v>0.007919795811778591</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009887535477919839</v>
+        <v>0.009887535477919826</v>
       </c>
       <c r="H9" t="n">
         <v>0.009112396913006408</v>
       </c>
       <c r="I9" t="n">
-        <v>0.009180410520000288</v>
+        <v>0.009180410520000286</v>
       </c>
       <c r="J9" t="n">
-        <v>0.009792197409617306</v>
+        <v>0.009792197409617308</v>
       </c>
       <c r="K9" t="n">
-        <v>0.009335646225305881</v>
+        <v>0.009335646225305879</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009833423740213273</v>
+        <v>0.009833423740213282</v>
       </c>
       <c r="M9" t="n">
-        <v>0.009530926081790705</v>
+        <v>0.009530926081790706</v>
       </c>
       <c r="N9" t="n">
-        <v>0.009230830886866213</v>
+        <v>0.00923083088686622</v>
       </c>
       <c r="O9" t="n">
-        <v>0.009337848360318014</v>
+        <v>0.009337848360318023</v>
       </c>
       <c r="P9" t="n">
-        <v>0.009851420680536925</v>
+        <v>0.00985142068053693</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.00920007088011462</v>
+        <v>0.009200070880114621</v>
       </c>
       <c r="R9" t="n">
         <v>0.00931285562895298</v>
       </c>
       <c r="S9" t="n">
-        <v>0.00931178802518126</v>
+        <v>0.009311788025181258</v>
       </c>
       <c r="T9" t="n">
-        <v>0.009127794552069237</v>
+        <v>0.009127794552069239</v>
       </c>
       <c r="U9" t="n">
         <v>0.009525658128723297</v>
       </c>
       <c r="V9" t="n">
-        <v>0.009718457604168897</v>
+        <v>0.009718457604168902</v>
       </c>
       <c r="W9" t="n">
         <v>0.009604534374449391</v>
@@ -9014,13 +9014,13 @@
         <v>0.01460566225827954</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.008899741466986784</v>
+        <v>0.008899741466986785</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.00945493607605182</v>
+        <v>0.009454936076051816</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.03957388273243544</v>
+        <v>0.03957388273243546</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia acidification results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia acidification results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004116316214163047</v>
+        <v>0.004116316214163049</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003592553314559209</v>
+        <v>0.003592553314559208</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00412632469171674</v>
+        <v>0.004126324691716738</v>
       </c>
       <c r="E2" t="n">
         <v>0.004013536159650488</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00405012523862136</v>
+        <v>0.004050125238621363</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00405352605212567</v>
+        <v>0.004053526052125672</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004064498810041621</v>
+        <v>0.004064498810041623</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004125614415330575</v>
+        <v>0.004125614415330573</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004101922240287679</v>
+        <v>0.004101922240287677</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004213500959104581</v>
+        <v>0.004213500959104579</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004172241513833184</v>
+        <v>0.004172241513833185</v>
       </c>
       <c r="M2" t="n">
-        <v>0.004519596152194602</v>
+        <v>0.004519596152194601</v>
       </c>
       <c r="N2" t="n">
-        <v>0.004137162154417323</v>
+        <v>0.004137162154417319</v>
       </c>
       <c r="O2" t="n">
-        <v>0.005896372691256778</v>
+        <v>0.005896372691256777</v>
       </c>
       <c r="P2" t="n">
         <v>0.004034020157004442</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.00403910531207905</v>
+        <v>0.004039105312079048</v>
       </c>
       <c r="R2" t="n">
-        <v>0.004041655597622014</v>
+        <v>0.004041655597622021</v>
       </c>
       <c r="S2" t="n">
-        <v>0.004095122440217856</v>
+        <v>0.004095122440217849</v>
       </c>
       <c r="T2" t="n">
-        <v>0.004124156829230423</v>
+        <v>0.004124156829230418</v>
       </c>
       <c r="U2" t="n">
-        <v>0.004359513622554978</v>
+        <v>0.004359513622554977</v>
       </c>
       <c r="V2" t="n">
-        <v>0.004016337980127827</v>
+        <v>0.004016337980127831</v>
       </c>
       <c r="W2" t="n">
-        <v>0.004169487840825711</v>
+        <v>0.004169487840825707</v>
       </c>
       <c r="X2" t="n">
         <v>0.004182283750630094</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.004263574551906477</v>
+        <v>0.00426357455190648</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.005068054346676956</v>
+        <v>0.00506805434667695</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.004168258678017679</v>
+        <v>0.004168258678017681</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.004470950558842215</v>
+        <v>0.004470950558842214</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.008594192593173115</v>
+        <v>0.00515152929541813</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005067615446859746</v>
+        <v>0.00371279020737122</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00888339855252197</v>
+        <v>0.00529962234951566</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007256339340167855</v>
+        <v>0.005393043648383875</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007114620065286725</v>
+        <v>0.004686189517275222</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007150606670213436</v>
+        <v>0.004671486934643645</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007456589891590963</v>
+        <v>0.004812127672878742</v>
       </c>
       <c r="I3" t="n">
-        <v>0.008873745102350679</v>
+        <v>0.00530084461095746</v>
       </c>
       <c r="J3" t="n">
-        <v>0.008291284345652674</v>
+        <v>0.005075472660864938</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01091107240371009</v>
+        <v>0.006004012370278936</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009913027355347213</v>
+        <v>0.00563315734334752</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01801489554664811</v>
+        <v>0.008503558120233914</v>
       </c>
       <c r="N3" t="n">
-        <v>0.009119638784926777</v>
+        <v>0.005369554879105863</v>
       </c>
       <c r="O3" t="n">
-        <v>0.009338667672653634</v>
+        <v>0.006606646813028761</v>
       </c>
       <c r="P3" t="n">
-        <v>0.00669672331436594</v>
+        <v>0.004514997433798235</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.006841899753829385</v>
+        <v>0.00458107283352896</v>
       </c>
       <c r="R3" t="n">
-        <v>0.006914450867470232</v>
+        <v>0.004616608801662004</v>
       </c>
       <c r="S3" t="n">
-        <v>0.008116087492202556</v>
+        <v>0.005000041560708876</v>
       </c>
       <c r="T3" t="n">
-        <v>0.008835114072954123</v>
+        <v>0.005284292984731221</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01326071676649973</v>
+        <v>0.006797798874289068</v>
       </c>
       <c r="V3" t="n">
-        <v>0.006294648161808454</v>
+        <v>0.004376589936776094</v>
       </c>
       <c r="W3" t="n">
-        <v>0.009759706908587525</v>
+        <v>0.005586451612618704</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01018451831880765</v>
+        <v>0.005746144178270253</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01204804647145436</v>
+        <v>0.00637137918360827</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.007737781302447152</v>
+        <v>0.005552858742182467</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.00983192283164952</v>
+        <v>0.005611997600082292</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01682689122345592</v>
+        <v>0.008149614160138607</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04404090123646597</v>
+        <v>0.04404090123646594</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0161482592416798</v>
+        <v>0.01614825924167981</v>
       </c>
       <c r="D4" t="n">
-        <v>0.05153583717977606</v>
+        <v>0.05153583717977607</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02255448260692944</v>
+        <v>0.02255448260692948</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03387757666265365</v>
+        <v>0.03387757666265361</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03145337423595934</v>
+        <v>0.03145337423595932</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03799280319889014</v>
+        <v>0.03799280319889015</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05190147953311985</v>
+        <v>0.05190147953311983</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04375861302327586</v>
+        <v>0.0437586130232759</v>
       </c>
       <c r="K4" t="n">
-        <v>0.07193298227979573</v>
+        <v>0.0719329822797956</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05941866425918457</v>
+        <v>0.05941866425918404</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1467848251833351</v>
+        <v>0.1467848251833353</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05272152432887291</v>
+        <v>0.05272152432887292</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0335997018411005</v>
+        <v>0.03359970184110048</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0269772649563173</v>
+        <v>0.02697726495631725</v>
       </c>
       <c r="Q4" t="n">
         <v>0.03007205254476871</v>
       </c>
       <c r="R4" t="n">
-        <v>0.03181196975579498</v>
+        <v>0.031811969755795</v>
       </c>
       <c r="S4" t="n">
-        <v>0.04059981683046312</v>
+        <v>0.04059981683046313</v>
       </c>
       <c r="T4" t="n">
-        <v>0.05119573235399744</v>
+        <v>0.05119573235399739</v>
       </c>
       <c r="U4" t="n">
-        <v>0.09016878285551398</v>
+        <v>0.09016878285551387</v>
       </c>
       <c r="V4" t="n">
         <v>0.02315219962089005</v>
       </c>
       <c r="W4" t="n">
-        <v>0.05824332354439237</v>
+        <v>0.0582433235443924</v>
       </c>
       <c r="X4" t="n">
-        <v>0.06418972519984315</v>
+        <v>0.06418972519984303</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.08078873585539734</v>
+        <v>0.08078873585539735</v>
       </c>
       <c r="Z4" t="n">
         <v>0.0272413358120987</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.05932765302177016</v>
+        <v>0.05932765302177007</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.138840759695284</v>
+        <v>0.1388407596952839</v>
       </c>
     </row>
     <row r="5">
@@ -850,19 +850,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01105437102106633</v>
+        <v>0.0110543710210663</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01106470415405096</v>
+        <v>0.01106470415405095</v>
       </c>
       <c r="D5" t="n">
         <v>0.01272311496652713</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0106207556663798</v>
+        <v>0.01062075566637979</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01054907238210097</v>
+        <v>0.01054907238210095</v>
       </c>
       <c r="G5" t="n">
         <v>0.0122234040430549</v>
@@ -877,25 +877,25 @@
         <v>0.01244443655465536</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01370781100973711</v>
+        <v>0.01370781100973712</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01324176659511411</v>
+        <v>0.0132417665951141</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01711882547122136</v>
+        <v>0.01711882547122138</v>
       </c>
       <c r="N5" t="n">
-        <v>0.05272152432887291</v>
+        <v>0.01163960630112207</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01120614489914618</v>
+        <v>0.01120614489914616</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01072473437601857</v>
+        <v>0.01072473437601855</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.009876509066382468</v>
+        <v>0.009876509066382461</v>
       </c>
       <c r="R5" t="n">
         <v>0.0117667385990196</v>
@@ -904,7 +904,7 @@
         <v>0.01237067118210241</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01269862796247813</v>
+        <v>0.01269862796247814</v>
       </c>
       <c r="U5" t="n">
         <v>0.01409777470249325</v>
@@ -913,19 +913,19 @@
         <v>0.0110347660513951</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0131616517910497</v>
+        <v>0.01316165179104968</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01163635780361371</v>
+        <v>0.01163635780361369</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.01581981632490725</v>
+        <v>0.01581981632490726</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01009681270305635</v>
+        <v>0.01009681270305634</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01319677863238305</v>
+        <v>0.01319677863238306</v>
       </c>
       <c r="AB5" t="n">
         <v>0.01818303326275194</v>
@@ -941,61 +941,61 @@
         <v>0.01143011005853501</v>
       </c>
       <c r="C6" t="n">
-        <v>0.010665784389763</v>
+        <v>0.01066578438976299</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01232419520223919</v>
+        <v>0.01232419520223917</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01086993637428816</v>
+        <v>0.01086993637428817</v>
       </c>
       <c r="F6" t="n">
-        <v>0.009662990389446855</v>
+        <v>0.009662990389446853</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01150189999968109</v>
+        <v>0.01150189999968108</v>
       </c>
       <c r="H6" t="n">
         <v>0.01162584342740802</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01231617230371419</v>
+        <v>0.0123161723037142</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01204551679036741</v>
+        <v>0.01204551679036739</v>
       </c>
       <c r="K6" t="n">
         <v>0.01330889124544915</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01284284683082617</v>
+        <v>0.01284284683082614</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01671990570693342</v>
+        <v>0.01671990570693341</v>
       </c>
       <c r="N6" t="n">
-        <v>0.05272152432887291</v>
+        <v>0.01244660932892144</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01194058234108189</v>
+        <v>0.01194058234108188</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01159669734447235</v>
+        <v>0.01159669734447234</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01133901110698632</v>
+        <v>0.01133901110698629</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01136781883473165</v>
+        <v>0.01136781883473163</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01197175141781447</v>
+        <v>0.01197175141781446</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01229970819819018</v>
+        <v>0.01229970819819017</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01445839600001657</v>
+        <v>0.01445839600001658</v>
       </c>
       <c r="V6" t="n">
         <v>0.01196258627443316</v>
@@ -1004,19 +1004,19 @@
         <v>0.01276242628844531</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01295627851510444</v>
+        <v>0.01295627851510443</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01387449551113735</v>
+        <v>0.01387449551113733</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0108115893812115</v>
+        <v>0.01081158938121148</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0127978588680951</v>
+        <v>0.01279785886809509</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01615906146152753</v>
+        <v>0.01615906146152751</v>
       </c>
     </row>
   </sheetData>
@@ -1182,82 +1182,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003717247939742316</v>
+        <v>0.003717247939742312</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003301666177617805</v>
+        <v>0.003301666177617806</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003723482485583252</v>
+        <v>0.003723482485583248</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003723224211454137</v>
+        <v>0.003723224211454134</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00372723521608584</v>
+        <v>0.003727235216085837</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003729891012457082</v>
+        <v>0.003729891012457079</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003725445329840645</v>
+        <v>0.003725445329840642</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003725847890252428</v>
+        <v>0.003725847890252431</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003738359047546829</v>
+        <v>0.003738359047546818</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003734751460118602</v>
+        <v>0.003734751460118604</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003739187922401031</v>
+        <v>0.00373918792240103</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003730346125362581</v>
+        <v>0.003730346125362582</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003728216668256252</v>
+        <v>0.003728216668256246</v>
       </c>
       <c r="O2" t="n">
-        <v>0.005408643836908493</v>
+        <v>0.005408643836908492</v>
       </c>
       <c r="P2" t="n">
-        <v>0.00373157253851708</v>
+        <v>0.003731572538517065</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003722587183373335</v>
+        <v>0.003722587183373332</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003740910297822766</v>
+        <v>0.003740910297822764</v>
       </c>
       <c r="S2" t="n">
-        <v>0.00373519695268449</v>
+        <v>0.003735196952684488</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003725708753697611</v>
+        <v>0.003725708753697609</v>
       </c>
       <c r="U2" t="n">
-        <v>0.00359122834590487</v>
+        <v>0.00359122834590486</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003734804886553681</v>
+        <v>0.003734804886553678</v>
       </c>
       <c r="W2" t="n">
-        <v>0.003563434871944607</v>
+        <v>0.003563434871944597</v>
       </c>
       <c r="X2" t="n">
         <v>0.004138913887229911</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003965248799954712</v>
+        <v>0.003965248799954709</v>
       </c>
       <c r="Z2" t="n">
         <v>0.004726362540806553</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003767642324405841</v>
+        <v>0.003767642324405837</v>
       </c>
       <c r="AB2" t="n">
         <v>0.003721364190061458</v>
@@ -1270,85 +1270,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004568614379909142</v>
+        <v>0.003645437931717802</v>
       </c>
       <c r="C3" t="n">
-        <v>0.004225579379591434</v>
+        <v>0.003254891475071838</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004716348885218291</v>
+        <v>0.003698373836111406</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005765082038581433</v>
+        <v>0.004758084806269655</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004805468629352889</v>
+        <v>0.003729232529432313</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0048598078814057</v>
+        <v>0.003743012258851792</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004764363790226785</v>
+        <v>0.003717151294123178</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004772166484006694</v>
+        <v>0.003718247686800112</v>
       </c>
       <c r="J3" t="n">
-        <v>0.005059047862984505</v>
+        <v>0.003812627613354594</v>
       </c>
       <c r="K3" t="n">
-        <v>0.004978110449640204</v>
+        <v>0.003784797951092578</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005077033572058963</v>
+        <v>0.003816651944818877</v>
       </c>
       <c r="M3" t="n">
-        <v>0.004894268628897011</v>
+        <v>0.00375962569811083</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004825361653484233</v>
+        <v>0.00373563313424038</v>
       </c>
       <c r="O3" t="n">
-        <v>0.006569831135912802</v>
+        <v>0.005430953645662738</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004897485376824836</v>
+        <v>0.003755189077419045</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.004694667056242835</v>
+        <v>0.003689370185468795</v>
       </c>
       <c r="R3" t="n">
-        <v>0.005125659862841531</v>
+        <v>0.003842691660254049</v>
       </c>
       <c r="S3" t="n">
-        <v>0.00498307235408726</v>
+        <v>0.003783824627555818</v>
       </c>
       <c r="T3" t="n">
-        <v>0.004768546905157513</v>
+        <v>0.003716899357767079</v>
       </c>
       <c r="U3" t="n">
-        <v>0.00510605857132985</v>
+        <v>0.003720972595476393</v>
       </c>
       <c r="V3" t="n">
-        <v>0.004973461770308819</v>
+        <v>0.0037811871979622</v>
       </c>
       <c r="W3" t="n">
-        <v>0.004971776250223184</v>
+        <v>0.003667728913219776</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01439511849324644</v>
+        <v>0.006988269134142067</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01033039758164508</v>
+        <v>0.005642090019997978</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.005945613744766558</v>
+        <v>0.004764448675527013</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.005739558844562689</v>
+        <v>0.004051244664849631</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.004682368474600931</v>
+        <v>0.003688428570678786</v>
       </c>
     </row>
     <row r="4">
@@ -1358,28 +1358,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.008771946170555111</v>
+        <v>0.008771946170555104</v>
       </c>
       <c r="C4" t="n">
         <v>0.009599830696085644</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01022311307159407</v>
+        <v>0.01022311307159408</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009225673931602379</v>
+        <v>0.009225673931602372</v>
       </c>
       <c r="F4" t="n">
         <v>0.01102785511664598</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01106174306879824</v>
+        <v>0.01106174306879823</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01082152959512992</v>
+        <v>0.01082152959512993</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01075972897363943</v>
+        <v>0.01075972897363941</v>
       </c>
       <c r="J4" t="n">
         <v>0.01287632197568863</v>
@@ -1391,40 +1391,40 @@
         <v>0.01286949991384129</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01182311025185925</v>
+        <v>0.01182311025185924</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01112980040466694</v>
+        <v>0.01112980040466693</v>
       </c>
       <c r="O4" t="n">
         <v>0.01128771614184683</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01131336438929065</v>
+        <v>0.01131336438929064</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.009919930288438484</v>
+        <v>0.009919930288438477</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01403611624499386</v>
+        <v>0.01403611624499385</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01201176230763607</v>
+        <v>0.01201176230763606</v>
       </c>
       <c r="T4" t="n">
         <v>0.01071646443143492</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01420853703555562</v>
+        <v>0.0142085370355556</v>
       </c>
       <c r="V4" t="n">
-        <v>0.01194772920983328</v>
+        <v>0.01194772920983327</v>
       </c>
       <c r="W4" t="n">
         <v>0.01383467697048948</v>
       </c>
       <c r="X4" t="n">
-        <v>0.09099858420489512</v>
+        <v>0.09099858420489521</v>
       </c>
       <c r="Y4" t="n">
         <v>0.05924371707141118</v>
@@ -1433,7 +1433,7 @@
         <v>0.01164006652825548</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01903331984838085</v>
+        <v>0.01903331984838084</v>
       </c>
       <c r="AB4" t="n">
         <v>0.01008868081010141</v>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.008455252847853196</v>
+        <v>0.00845525284785319</v>
       </c>
       <c r="C5" t="n">
-        <v>0.009674398646237032</v>
+        <v>0.009674398646237035</v>
       </c>
       <c r="D5" t="n">
-        <v>0.009709159432970526</v>
+        <v>0.009709159432970529</v>
       </c>
       <c r="E5" t="n">
-        <v>0.009076071510610323</v>
+        <v>0.009076071510610321</v>
       </c>
       <c r="F5" t="n">
-        <v>0.008752436785352846</v>
+        <v>0.008752436785352844</v>
       </c>
       <c r="G5" t="n">
         <v>0.01002694991736199</v>
       </c>
       <c r="H5" t="n">
-        <v>0.009731330661810792</v>
+        <v>0.009731330661810794</v>
       </c>
       <c r="I5" t="n">
-        <v>0.009735877766848837</v>
+        <v>0.009735877766848828</v>
       </c>
       <c r="J5" t="n">
-        <v>0.009874193651579049</v>
+        <v>0.009874193651579044</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00983644768433176</v>
+        <v>0.009836447684331758</v>
       </c>
       <c r="L5" t="n">
-        <v>0.009886559566685273</v>
+        <v>0.009886559566685278</v>
       </c>
       <c r="M5" t="n">
-        <v>0.009794913959441496</v>
+        <v>0.009794913959441499</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01112980040466694</v>
+        <v>0.008845235707048885</v>
       </c>
       <c r="O5" t="n">
-        <v>0.00913263914114304</v>
+        <v>0.009132639141143036</v>
       </c>
       <c r="P5" t="n">
-        <v>0.009073452852546205</v>
+        <v>0.009073452852546201</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.008282980340581158</v>
+        <v>0.008282980340581156</v>
       </c>
       <c r="R5" t="n">
-        <v>0.009906014589405595</v>
+        <v>0.009906014589405593</v>
       </c>
       <c r="S5" t="n">
         <v>0.009841479727800114</v>
       </c>
       <c r="T5" t="n">
-        <v>0.009734306155456205</v>
+        <v>0.00973430615545621</v>
       </c>
       <c r="U5" t="n">
-        <v>0.009399028506976983</v>
+        <v>0.00939902850697698</v>
       </c>
       <c r="V5" t="n">
-        <v>0.009492514312056062</v>
+        <v>0.009492514312056046</v>
       </c>
       <c r="W5" t="n">
         <v>0.009921902598078064</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01309405068844637</v>
+        <v>0.01309405068844636</v>
       </c>
       <c r="Y5" t="n">
         <v>0.01361556837965633</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.008621931859839531</v>
+        <v>0.008621931859839524</v>
       </c>
       <c r="AA5" t="n">
         <v>0.01020796512700119</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.01092912424883933</v>
+        <v>0.01092912424883932</v>
       </c>
     </row>
     <row r="6">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.008239505886266544</v>
+        <v>0.00823950588626654</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008730616920703751</v>
+        <v>0.008730616920703746</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008765377707437233</v>
+        <v>0.008765377707437228</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008657344568826296</v>
+        <v>0.008657344568826294</v>
       </c>
       <c r="F6" t="n">
-        <v>0.007757830303445169</v>
+        <v>0.007757830303445165</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008837765139267638</v>
+        <v>0.008837765139267633</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008787548936277499</v>
+        <v>0.008787548936277496</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008792096041315537</v>
+        <v>0.00879209604131553</v>
       </c>
       <c r="J6" t="n">
-        <v>0.008930411926045758</v>
+        <v>0.008930411926045757</v>
       </c>
       <c r="K6" t="n">
-        <v>0.008892665958798467</v>
+        <v>0.00889266595879846</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008942777841151986</v>
+        <v>0.00894277784115198</v>
       </c>
       <c r="M6" t="n">
-        <v>0.008851132233908163</v>
+        <v>0.008851132233908154</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01112980040466694</v>
+        <v>0.008818852478560379</v>
       </c>
       <c r="O6" t="n">
-        <v>0.009005082523372796</v>
+        <v>0.009005082523372792</v>
       </c>
       <c r="P6" t="n">
-        <v>0.009040520144237134</v>
+        <v>0.009040520144237131</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.008755265029839344</v>
+        <v>0.008755265029839341</v>
       </c>
       <c r="R6" t="n">
-        <v>0.008962232863872299</v>
+        <v>0.008962232863872295</v>
       </c>
       <c r="S6" t="n">
-        <v>0.008897698002266823</v>
+        <v>0.008897698002266819</v>
       </c>
       <c r="T6" t="n">
-        <v>0.008790524429922923</v>
+        <v>0.008790524429922916</v>
       </c>
       <c r="U6" t="n">
-        <v>0.009033570501006873</v>
+        <v>0.009033570501006866</v>
       </c>
       <c r="V6" t="n">
-        <v>0.009398526929042693</v>
+        <v>0.009398526929042684</v>
       </c>
       <c r="W6" t="n">
-        <v>0.008977888283900273</v>
+        <v>0.008977888283900269</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01345786649692275</v>
+        <v>0.01345786649692274</v>
       </c>
       <c r="Y6" t="n">
         <v>0.01149623944626228</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.008609022853480306</v>
+        <v>0.008609022853480299</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.009264183401467896</v>
+        <v>0.009264183401467887</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.008749093978885099</v>
+        <v>0.008749093978885096</v>
       </c>
     </row>
   </sheetData>
@@ -1778,85 +1778,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004030101591630135</v>
+        <v>0.004030101591630129</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003536640084176891</v>
+        <v>0.003536640084176894</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004080081305916835</v>
+        <v>0.00408008130591683</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003954381409662943</v>
+        <v>0.003954381409662935</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003957394232347487</v>
+        <v>0.00395739423234748</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003996479054770226</v>
+        <v>0.003996479054770217</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003930987158074368</v>
+        <v>0.003930987158074372</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003989931425760236</v>
+        <v>0.00398993142576023</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004042576494121009</v>
+        <v>0.004042576494121001</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004126221708094745</v>
+        <v>0.004126221708094738</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004103562886015239</v>
+        <v>0.004103562886015241</v>
       </c>
       <c r="M2" t="n">
-        <v>0.004424063108518172</v>
+        <v>0.004424063108518173</v>
       </c>
       <c r="N2" t="n">
-        <v>0.004008756684681562</v>
+        <v>0.004008756684681556</v>
       </c>
       <c r="O2" t="n">
-        <v>0.005778985719242472</v>
+        <v>0.00577898571924247</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003992302289559046</v>
+        <v>0.003992302289559033</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003958546185443017</v>
+        <v>0.003958546185443011</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003935228912832181</v>
+        <v>0.003935228912832176</v>
       </c>
       <c r="S2" t="n">
-        <v>0.004040778098060328</v>
+        <v>0.004040778098060331</v>
       </c>
       <c r="T2" t="n">
-        <v>0.004024088293147616</v>
+        <v>0.00402408829314761</v>
       </c>
       <c r="U2" t="n">
-        <v>0.00423003716457544</v>
+        <v>0.004230037164575437</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003937965094514309</v>
+        <v>0.003937965094514301</v>
       </c>
       <c r="W2" t="n">
-        <v>0.004059958688690394</v>
+        <v>0.004059958688690389</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004178029101323031</v>
+        <v>0.00417802910132303</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.004172533685842778</v>
+        <v>0.004172533685842771</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.004984199988882529</v>
+        <v>0.004984199988882525</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.004061564946437665</v>
+        <v>0.004061564946437659</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.004399050820594847</v>
+        <v>0.004399050820594849</v>
       </c>
     </row>
     <row r="3">
@@ -1866,85 +1866,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.007739713425310471</v>
+        <v>0.004826218337655414</v>
       </c>
       <c r="C3" t="n">
-        <v>0.004941497880080433</v>
+        <v>0.003632614309333131</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00895119229151786</v>
+        <v>0.005289354453230694</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0070339838791011</v>
+        <v>0.005288063476289751</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006092519678662039</v>
+        <v>0.00428930979062243</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006967563437292515</v>
+        <v>0.004572360779198234</v>
       </c>
       <c r="H3" t="n">
-        <v>0.005475502326297333</v>
+        <v>0.004077897180576674</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006850118617126833</v>
+        <v>0.00455723867279136</v>
       </c>
       <c r="J3" t="n">
-        <v>0.008056933664297971</v>
+        <v>0.004959692875032621</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01001569670092336</v>
+        <v>0.005613155585371078</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009460228432503237</v>
+        <v>0.005442854479073752</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01693190021002076</v>
+        <v>0.008081729711380502</v>
       </c>
       <c r="N3" t="n">
-        <v>0.007275834057249482</v>
+        <v>0.004695869810626372</v>
       </c>
       <c r="O3" t="n">
-        <v>0.00859024778046079</v>
+        <v>0.006294229364562831</v>
       </c>
       <c r="P3" t="n">
-        <v>0.006866700354912762</v>
+        <v>0.004537739820173939</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.006109957410793605</v>
+        <v>0.004291742694354504</v>
       </c>
       <c r="R3" t="n">
-        <v>0.005572667785925344</v>
+        <v>0.004110550995234503</v>
       </c>
       <c r="S3" t="n">
-        <v>0.00799500316228946</v>
+        <v>0.004920681346826813</v>
       </c>
       <c r="T3" t="n">
-        <v>0.007645312545839257</v>
+        <v>0.004831902584980189</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01237335381693935</v>
+        <v>0.006428553925066605</v>
       </c>
       <c r="V3" t="n">
-        <v>0.005619716026597379</v>
+        <v>0.00411082525408201</v>
       </c>
       <c r="W3" t="n">
-        <v>0.009228836702983391</v>
+        <v>0.005343317813979133</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01123100817872937</v>
+        <v>0.006072224272774983</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01107371371628439</v>
+        <v>0.005992630551992458</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.007292049678478016</v>
+        <v>0.005354608948576971</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.008495352628121263</v>
+        <v>0.005111576656976551</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0162948575609561</v>
+        <v>0.007928198472500618</v>
       </c>
     </row>
     <row r="4">
@@ -1954,85 +1954,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03463439756268316</v>
+        <v>0.0346343975626837</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01470043602726598</v>
+        <v>0.01470043602726599</v>
       </c>
       <c r="D4" t="n">
-        <v>0.04986786080269486</v>
+        <v>0.04986786080269461</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0198335514808747</v>
+        <v>0.01983355148087516</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02228821896844205</v>
+        <v>0.0222882189684421</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02853491205235847</v>
+        <v>0.02853491205235845</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01663531787947741</v>
+        <v>0.01663531787947742</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02980166055562298</v>
+        <v>0.029801660555623</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03971546909689702</v>
+        <v>0.03971546909689704</v>
       </c>
       <c r="K4" t="n">
-        <v>0.05643381480529253</v>
+        <v>0.0564338148052926</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0524380358037819</v>
+        <v>0.05243803580378591</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1274347467007052</v>
+        <v>0.1274347467007053</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03297149078316956</v>
+        <v>0.0329714907831696</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02620743592045995</v>
+        <v>0.02620743592046002</v>
       </c>
       <c r="P4" t="n">
-        <v>0.02755976565815451</v>
+        <v>0.02755976565815453</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.02205403258352862</v>
+        <v>0.02205403258352871</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01745111392211842</v>
+        <v>0.01745111392211841</v>
       </c>
       <c r="S4" t="n">
-        <v>0.03756742817998288</v>
+        <v>0.03756742817998296</v>
       </c>
       <c r="T4" t="n">
-        <v>0.03720658924128988</v>
+        <v>0.03720658924128994</v>
       </c>
       <c r="U4" t="n">
-        <v>0.07770746089314545</v>
+        <v>0.07770746089314542</v>
       </c>
       <c r="V4" t="n">
-        <v>0.01645789239764524</v>
+        <v>0.01645789239764523</v>
       </c>
       <c r="W4" t="n">
-        <v>0.05095009998457872</v>
+        <v>0.05095009998457874</v>
       </c>
       <c r="X4" t="n">
-        <v>0.07075541222193868</v>
+        <v>0.0707554122219389</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.06702393976634548</v>
+        <v>0.06702393976634557</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.02247648503297247</v>
+        <v>0.02247648503297305</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.04378273368313326</v>
+        <v>0.04378273368313336</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.125902821181521</v>
+        <v>0.1259028211815216</v>
       </c>
     </row>
     <row r="5">
@@ -2048,10 +2048,10 @@
         <v>0.01060401614530917</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01235549935786525</v>
+        <v>0.01235549935786523</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01018439565604282</v>
+        <v>0.01018439565604285</v>
       </c>
       <c r="F5" t="n">
         <v>0.009778589527487346</v>
@@ -2060,46 +2060,46 @@
         <v>0.01170373391463625</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01067141237128802</v>
+        <v>0.01067141237128801</v>
       </c>
       <c r="I5" t="n">
         <v>0.01133721499050268</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01192813983327588</v>
+        <v>0.01192813983327587</v>
       </c>
       <c r="K5" t="n">
         <v>0.01287667642609839</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01262073460713726</v>
+        <v>0.01262073460713741</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01619666263011436</v>
+        <v>0.01619666263011435</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03297149078316956</v>
+        <v>0.010456167163942</v>
       </c>
       <c r="O5" t="n">
         <v>0.01053838870185203</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01049718883317992</v>
+        <v>0.01049718883317994</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.009294523654397134</v>
+        <v>0.009294523654397145</v>
       </c>
       <c r="R5" t="n">
         <v>0.01071932494258108</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01191155154475716</v>
+        <v>0.01191155154475717</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01172303252057846</v>
+        <v>0.01172303252057847</v>
       </c>
       <c r="U5" t="n">
-        <v>0.01335656927685271</v>
+        <v>0.01335656927685272</v>
       </c>
       <c r="V5" t="n">
         <v>0.01033914987356191</v>
@@ -2108,16 +2108,16 @@
         <v>0.0125219330235631</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01190299644709471</v>
+        <v>0.01190299644709472</v>
       </c>
       <c r="Y5" t="n">
         <v>0.01480215114466819</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.009633795388877896</v>
+        <v>0.009633795388877901</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01214634855960182</v>
+        <v>0.01214634855960183</v>
       </c>
       <c r="AB5" t="n">
         <v>0.01737410810073394</v>
@@ -2130,43 +2130,43 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01050473586472888</v>
+        <v>0.01050473586472891</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00996638160292064</v>
+        <v>0.009966381602920647</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0117178648154767</v>
+        <v>0.01171786481547672</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0101483351379359</v>
+        <v>0.01014833513793592</v>
       </c>
       <c r="F6" t="n">
-        <v>0.008836893484095321</v>
+        <v>0.008836893484095325</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01077353797793641</v>
+        <v>0.01077353797793642</v>
       </c>
       <c r="H6" t="n">
         <v>0.01003377782889948</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01069958044811415</v>
+        <v>0.01069958044811416</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01129050529088735</v>
+        <v>0.01129050529088736</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01223904188370987</v>
+        <v>0.01223904188370988</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01198310006474873</v>
+        <v>0.01198310006474872</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01555902808772561</v>
+        <v>0.0155590280877256</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03297149078316956</v>
+        <v>0.0109122204076775</v>
       </c>
       <c r="O6" t="n">
         <v>0.010908826026559</v>
@@ -2178,13 +2178,13 @@
         <v>0.01034506876890358</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01008169040019255</v>
+        <v>0.01008169040019256</v>
       </c>
       <c r="S6" t="n">
         <v>0.01127391700236863</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01108539797818994</v>
+        <v>0.01108539797818995</v>
       </c>
       <c r="U6" t="n">
         <v>0.01340785453077353</v>
@@ -2196,7 +2196,7 @@
         <v>0.01188402119785847</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01282423022280165</v>
+        <v>0.01282423022280171</v>
       </c>
       <c r="Y6" t="n">
         <v>0.01276215697693618</v>
@@ -2205,7 +2205,7 @@
         <v>0.01004223510937603</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0115087140172133</v>
+        <v>0.01150871401721331</v>
       </c>
       <c r="AB6" t="n">
         <v>0.01526266480683438</v>
@@ -2374,82 +2374,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003994566075216612</v>
+        <v>0.003994566075216621</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003521763962937453</v>
+        <v>0.003521763962937455</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004104246026388351</v>
+        <v>0.004104246026388358</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003948763468802639</v>
+        <v>0.003948763468802648</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003950727475349815</v>
+        <v>0.003950727475349822</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003983737821440286</v>
+        <v>0.003983737821440293</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003901777856795478</v>
+        <v>0.003901777856795486</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004020717068126798</v>
+        <v>0.004020717068126804</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004035382589679572</v>
+        <v>0.004035382589679573</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00407322350347323</v>
+        <v>0.00407322350347324</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004064533138609721</v>
+        <v>0.004064533138609729</v>
       </c>
       <c r="M2" t="n">
-        <v>0.004346266327354471</v>
+        <v>0.004346266327354473</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003964842312573335</v>
+        <v>0.003964842312573343</v>
       </c>
       <c r="O2" t="n">
-        <v>0.005726995297872794</v>
+        <v>0.005726995297872801</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003977921493915355</v>
+        <v>0.003977921493915361</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003942433930689933</v>
+        <v>0.00394243393068994</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003908058047717611</v>
+        <v>0.003908058047717617</v>
       </c>
       <c r="S2" t="n">
-        <v>0.004022092996012957</v>
+        <v>0.004022092996012964</v>
       </c>
       <c r="T2" t="n">
-        <v>0.004005576383600728</v>
+        <v>0.004005576383600736</v>
       </c>
       <c r="U2" t="n">
-        <v>0.00417736987223737</v>
+        <v>0.004177369872237376</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003943784428996084</v>
+        <v>0.003943784428996091</v>
       </c>
       <c r="W2" t="n">
-        <v>0.00402873635197756</v>
+        <v>0.004028736351977568</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004443119376221686</v>
+        <v>0.004443119376221696</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.004443832545178132</v>
+        <v>0.004443832545178138</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.004974036989107624</v>
+        <v>0.004974036989107629</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.004058914240346224</v>
+        <v>0.00405891424034623</v>
       </c>
       <c r="AB2" t="n">
         <v>0.004361701974654028</v>
@@ -2462,85 +2462,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.007046362714794215</v>
+        <v>0.004593885585338243</v>
       </c>
       <c r="C3" t="n">
-        <v>0.004747192318086453</v>
+        <v>0.003560937073967522</v>
       </c>
       <c r="D3" t="n">
-        <v>0.009640494227115342</v>
+        <v>0.005521294104028363</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007029877050633813</v>
+        <v>0.00528467353917726</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006062361019008889</v>
+        <v>0.004273256431274553</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006797760902247956</v>
+        <v>0.004508038126905547</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004916242576345563</v>
+        <v>0.00387750829083961</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007696002332378147</v>
+        <v>0.004849303387680275</v>
       </c>
       <c r="J3" t="n">
-        <v>0.008017103670658108</v>
+        <v>0.004941666236826317</v>
       </c>
       <c r="K3" t="n">
-        <v>0.008903894608986371</v>
+        <v>0.005209693653382017</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008680822958942848</v>
+        <v>0.005168742703521662</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01525411932717171</v>
+        <v>0.00749413432278364</v>
       </c>
       <c r="N3" t="n">
-        <v>0.006379878518514139</v>
+        <v>0.004382490069911134</v>
       </c>
       <c r="O3" t="n">
-        <v>0.00802120970620325</v>
+        <v>0.006084317799633349</v>
       </c>
       <c r="P3" t="n">
-        <v>0.006659662538057793</v>
+        <v>0.004461730417740986</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.005859919972825295</v>
+        <v>0.004199115701805316</v>
       </c>
       <c r="R3" t="n">
-        <v>0.00506248340790077</v>
+        <v>0.003927961722490402</v>
       </c>
       <c r="S3" t="n">
-        <v>0.007687727185362749</v>
+        <v>0.004810315634136852</v>
       </c>
       <c r="T3" t="n">
-        <v>0.007339006475225964</v>
+        <v>0.004722608626364471</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01138345488644422</v>
+        <v>0.006074130587293463</v>
       </c>
       <c r="V3" t="n">
-        <v>0.005877855604903538</v>
+        <v>0.004192301335598606</v>
       </c>
       <c r="W3" t="n">
-        <v>0.008748129442813682</v>
+        <v>0.005170950507847711</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01753837373959054</v>
+        <v>0.008252730694837587</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01749870148911124</v>
+        <v>0.008201366154294731</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.007263987583964825</v>
+        <v>0.00532934763307405</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.008559182080381153</v>
+        <v>0.005131795847795091</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01555792259348745</v>
+        <v>0.007668323588068038</v>
       </c>
     </row>
     <row r="4">
@@ -2550,85 +2550,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02761209780596943</v>
+        <v>0.0276120978059695</v>
       </c>
       <c r="C4" t="n">
         <v>0.01245326177926405</v>
       </c>
       <c r="D4" t="n">
-        <v>0.05288625308678482</v>
+        <v>0.05288625308678495</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01898675634158538</v>
+        <v>0.01898675634158537</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02083886043202619</v>
+        <v>0.02083886043202621</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02549448151019953</v>
+        <v>0.02549448151019957</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01077776807629335</v>
+        <v>0.0107777680762934</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03592690879694005</v>
+        <v>0.03592690879694006</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03718672065028879</v>
+        <v>0.0371867206502888</v>
       </c>
       <c r="K4" t="n">
-        <v>0.04238413113682187</v>
+        <v>0.04238413113682194</v>
       </c>
       <c r="L4" t="n">
         <v>0.0426247940982513</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1045759108827802</v>
+        <v>0.10457591088278</v>
       </c>
       <c r="N4" t="n">
         <v>0.0234273440156764</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02060807100604815</v>
+        <v>0.02060807100604821</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0243507298845928</v>
+        <v>0.0243507298845929</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01866392622131472</v>
+        <v>0.01866392622131476</v>
       </c>
       <c r="R4" t="n">
         <v>0.01204798601881439</v>
       </c>
       <c r="S4" t="n">
-        <v>0.03285789788928758</v>
+        <v>0.03285789788928765</v>
       </c>
       <c r="T4" t="n">
-        <v>0.03252677098952755</v>
+        <v>0.03252677098952763</v>
       </c>
       <c r="U4" t="n">
-        <v>0.06418549885485579</v>
+        <v>0.06418549885485575</v>
       </c>
       <c r="V4" t="n">
-        <v>0.01773092587376958</v>
+        <v>0.01773092587376959</v>
       </c>
       <c r="W4" t="n">
-        <v>0.04399537881621737</v>
+        <v>0.04399537881621731</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1220297315282961</v>
+        <v>0.1220297315282962</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1183707378645814</v>
+        <v>0.1183707378645815</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.02055526951575415</v>
+        <v>0.02055526951575413</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.04203242766514147</v>
+        <v>0.04203242766514154</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.111588952102431</v>
+        <v>0.1115889521024312</v>
       </c>
     </row>
     <row r="5">
@@ -2638,19 +2638,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.009869446323440192</v>
+        <v>0.009869446323440204</v>
       </c>
       <c r="C5" t="n">
         <v>0.01022962112352967</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01240849638201487</v>
+        <v>0.01240849638201489</v>
       </c>
       <c r="E5" t="n">
-        <v>0.009959950095593289</v>
+        <v>0.009959950095593301</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00957681961348656</v>
+        <v>0.009576819613486569</v>
       </c>
       <c r="G5" t="n">
         <v>0.01131689836083737</v>
@@ -2659,61 +2659,61 @@
         <v>0.01012152526650376</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01146499837323142</v>
+        <v>0.01146499837323143</v>
       </c>
       <c r="J5" t="n">
         <v>0.01162718546651134</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01205808271462299</v>
+        <v>0.012058082714623</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01195992104572428</v>
+        <v>0.01195992104572429</v>
       </c>
       <c r="M5" t="n">
         <v>0.01510672555931703</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0234273440156764</v>
+        <v>0.009826022262814343</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01005156123279825</v>
+        <v>0.01005156123279826</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01018283149331644</v>
+        <v>0.01018283149331645</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.00902507775921832</v>
+        <v>0.009025077759218325</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01019246291199979</v>
+        <v>0.0101924629119998</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0114805401116637</v>
+        <v>0.01148054011166371</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01129397737645046</v>
+        <v>0.01129397737645047</v>
       </c>
       <c r="U5" t="n">
         <v>0.01264907841510328</v>
       </c>
       <c r="V5" t="n">
-        <v>0.01021656692093232</v>
+        <v>0.01021656692093233</v>
       </c>
       <c r="W5" t="n">
-        <v>0.01200951916966427</v>
+        <v>0.01200951916966428</v>
       </c>
       <c r="X5" t="n">
         <v>0.01479971285808417</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.01753598117388909</v>
+        <v>0.01753598117388911</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.009454508415235999</v>
+        <v>0.009454508415236002</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01189645300501716</v>
+        <v>0.01189645300501717</v>
       </c>
       <c r="AB5" t="n">
         <v>0.01662121233984538</v>
@@ -2726,7 +2726,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.009877940084845905</v>
+        <v>0.009877940084845917</v>
       </c>
       <c r="C6" t="n">
         <v>0.009506201286091597</v>
@@ -2735,49 +2735,49 @@
         <v>0.01168507654457681</v>
       </c>
       <c r="E6" t="n">
-        <v>0.009797678977897878</v>
+        <v>0.009797678977897881</v>
       </c>
       <c r="F6" t="n">
         <v>0.008641041278719607</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01032388021756238</v>
+        <v>0.01032388021756239</v>
       </c>
       <c r="H6" t="n">
-        <v>0.009398105429065684</v>
+        <v>0.009398105429065688</v>
       </c>
       <c r="I6" t="n">
         <v>0.01074157853579336</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01090376562907327</v>
+        <v>0.01090376562907328</v>
       </c>
       <c r="K6" t="n">
         <v>0.01133466287718493</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01123650120828623</v>
+        <v>0.01123650120828624</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01438330572187845</v>
+        <v>0.01438330572187846</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0234273440156764</v>
+        <v>0.01011044746815952</v>
       </c>
       <c r="O6" t="n">
         <v>0.01024733853940966</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01048745530850653</v>
+        <v>0.01048745530850654</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.009857333770808706</v>
+        <v>0.009857333770808711</v>
       </c>
       <c r="R6" t="n">
-        <v>0.009469043074561723</v>
+        <v>0.009469043074561726</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01075712027422564</v>
+        <v>0.01075712027422565</v>
       </c>
       <c r="T6" t="n">
         <v>0.0105705575390124</v>
@@ -2786,25 +2786,25 @@
         <v>0.01256085081492512</v>
       </c>
       <c r="V6" t="n">
-        <v>0.01050490987070328</v>
+        <v>0.0105049098707033</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0112858438126622</v>
+        <v>0.01128584381266221</v>
       </c>
       <c r="X6" t="n">
-        <v>0.015512806920387</v>
+        <v>0.01551280692038699</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01552086249182402</v>
+        <v>0.01552086249182404</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.009712799276957128</v>
+        <v>0.009712799276957134</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.01117303316757908</v>
+        <v>0.01117303316757909</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01453966190692954</v>
+        <v>0.01453966190692955</v>
       </c>
     </row>
   </sheetData>
@@ -2970,85 +2970,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003974342344336127</v>
+        <v>0.003974342344336123</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003480025254382845</v>
+        <v>0.003480025254382844</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004035819590429873</v>
+        <v>0.004035819590429869</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003926842479771575</v>
+        <v>0.003926842479771569</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003955734916750239</v>
+        <v>0.003955734916750232</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003968648396365591</v>
+        <v>0.003968648396365586</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003897944013643524</v>
+        <v>0.003897944013643518</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004016300752072322</v>
+        <v>0.004016300752072316</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004026582628959287</v>
+        <v>0.004026582628959281</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004102489866327042</v>
+        <v>0.004102489866327036</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004031728522204716</v>
+        <v>0.004031728522204711</v>
       </c>
       <c r="M2" t="n">
-        <v>0.004262399105687044</v>
+        <v>0.004262399105687046</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003935238995352398</v>
+        <v>0.003935238995352392</v>
       </c>
       <c r="O2" t="n">
-        <v>0.005687728720697322</v>
+        <v>0.005687728720697314</v>
       </c>
       <c r="P2" t="n">
-        <v>0.00396076470779499</v>
+        <v>0.003960764707794985</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003939220700154206</v>
+        <v>0.003939220700154202</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003924533547495634</v>
+        <v>0.003924533547495628</v>
       </c>
       <c r="S2" t="n">
-        <v>0.004010786022564052</v>
+        <v>0.004010786022564047</v>
       </c>
       <c r="T2" t="n">
-        <v>0.004001622626480114</v>
+        <v>0.00400162262648011</v>
       </c>
       <c r="U2" t="n">
-        <v>0.004086888749550318</v>
+        <v>0.004086888749550312</v>
       </c>
       <c r="V2" t="n">
-        <v>0.00397023457496604</v>
+        <v>0.003970234574966036</v>
       </c>
       <c r="W2" t="n">
-        <v>0.003901051632388438</v>
+        <v>0.003901051632388434</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00455095617744764</v>
+        <v>0.004550956177447635</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.004741848481448847</v>
+        <v>0.004741848481448842</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.004955867350207299</v>
+        <v>0.004955867350207294</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.004066742485299929</v>
+        <v>0.004066742485299923</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.004302847102272587</v>
+        <v>0.004302847102272584</v>
       </c>
     </row>
     <row r="3">
@@ -3058,85 +3058,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006658913432493713</v>
+        <v>0.004450570645492194</v>
       </c>
       <c r="C3" t="n">
-        <v>0.004693863284536788</v>
+        <v>0.003512455522391808</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008121250189569751</v>
+        <v>0.004969684925660234</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006608573967295151</v>
+        <v>0.005133966648388601</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006260227625766096</v>
+        <v>0.004335053091260115</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006528535511229203</v>
+        <v>0.004405534942492722</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004907201242784986</v>
+        <v>0.003869253145486795</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007672417334972497</v>
+        <v>0.004829303445796172</v>
       </c>
       <c r="J3" t="n">
-        <v>0.007892974497669221</v>
+        <v>0.004883832316917314</v>
       </c>
       <c r="K3" t="n">
-        <v>0.009665293791594986</v>
+        <v>0.005459985802546397</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00799875961718771</v>
+        <v>0.004914085387597835</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01338083735455686</v>
+        <v>0.006786973806797626</v>
       </c>
       <c r="N3" t="n">
-        <v>0.005771436682771461</v>
+        <v>0.00416659216982911</v>
       </c>
       <c r="O3" t="n">
-        <v>0.007557352695199491</v>
+        <v>0.005913828180256223</v>
       </c>
       <c r="P3" t="n">
-        <v>0.00634345941628347</v>
+        <v>0.004343612030657672</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.005864835148734101</v>
+        <v>0.00419219867985301</v>
       </c>
       <c r="R3" t="n">
-        <v>0.005529249344788007</v>
+        <v>0.004087152947867665</v>
       </c>
       <c r="S3" t="n">
-        <v>0.007505551905215141</v>
+        <v>0.004739134355799631</v>
       </c>
       <c r="T3" t="n">
-        <v>0.007327206707787175</v>
+        <v>0.004713783619791819</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01177855617591537</v>
+        <v>0.006101960115896491</v>
       </c>
       <c r="V3" t="n">
-        <v>0.006566197035159165</v>
+        <v>0.004413820121079091</v>
       </c>
       <c r="W3" t="n">
-        <v>0.007964020657908955</v>
+        <v>0.004833810123964053</v>
       </c>
       <c r="X3" t="n">
-        <v>0.02012538388247927</v>
+        <v>0.009085249745800428</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.02450517117857857</v>
+        <v>0.01065465025162291</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.007033347314993721</v>
+        <v>0.005236694335935138</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.008821169250067398</v>
+        <v>0.005219933915103116</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0142737432574116</v>
+        <v>0.007187566437449341</v>
       </c>
     </row>
     <row r="4">
@@ -3149,25 +3149,25 @@
         <v>0.02410140197170523</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01241377558846661</v>
+        <v>0.01241377558846662</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03820670003507488</v>
+        <v>0.03820670003507499</v>
       </c>
       <c r="E4" t="n">
         <v>0.0150535123662735</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02259902544226456</v>
+        <v>0.02259902544226457</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02299458998702842</v>
+        <v>0.02299458998702821</v>
       </c>
       <c r="H4" t="n">
         <v>0.01081784272595766</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03536932857122992</v>
+        <v>0.03536932857122996</v>
       </c>
       <c r="J4" t="n">
         <v>0.03556232188918419</v>
@@ -3176,22 +3176,22 @@
         <v>0.04861730493940951</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03587232627982846</v>
+        <v>0.03587232627982847</v>
       </c>
       <c r="M4" t="n">
-        <v>0.08444089321485714</v>
+        <v>0.08444089321485711</v>
       </c>
       <c r="N4" t="n">
         <v>0.01821224625945393</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01728207843246079</v>
+        <v>0.0172820784324608</v>
       </c>
       <c r="P4" t="n">
-        <v>0.02149859255997006</v>
+        <v>0.02149859255997008</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01858177242066292</v>
+        <v>0.01858177242066291</v>
       </c>
       <c r="R4" t="n">
         <v>0.01648337720003967</v>
@@ -3200,31 +3200,31 @@
         <v>0.03118829386816925</v>
       </c>
       <c r="T4" t="n">
-        <v>0.03256934829970639</v>
+        <v>0.03256934829970644</v>
       </c>
       <c r="U4" t="n">
-        <v>0.06640566400721375</v>
+        <v>0.06640566400721358</v>
       </c>
       <c r="V4" t="n">
-        <v>0.02299014399485133</v>
+        <v>0.02299014399485129</v>
       </c>
       <c r="W4" t="n">
         <v>0.03818914399193575</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1408230641245803</v>
+        <v>0.1408230641245804</v>
       </c>
       <c r="Y4" t="n">
         <v>0.1819733633418559</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.01841248699824172</v>
+        <v>0.01841248699824174</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.04461622557243102</v>
+        <v>0.0446162255724311</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.09827010538445491</v>
+        <v>0.09827010538445492</v>
       </c>
     </row>
     <row r="5">
@@ -3234,19 +3234,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.009694356854384937</v>
+        <v>0.009694356854384953</v>
       </c>
       <c r="C5" t="n">
         <v>0.01022936809857666</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01168184221371945</v>
+        <v>0.01168184221371946</v>
       </c>
       <c r="E5" t="n">
-        <v>0.009762373141755518</v>
+        <v>0.00976237314175552</v>
       </c>
       <c r="F5" t="n">
-        <v>0.009685622840266226</v>
+        <v>0.009685622840266238</v>
       </c>
       <c r="G5" t="n">
         <v>0.01119123949295945</v>
@@ -3258,7 +3258,7 @@
         <v>0.0114613679553616</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01157449002946112</v>
+        <v>0.01157449002946113</v>
       </c>
       <c r="K5" t="n">
         <v>0.01243491364982011</v>
@@ -3267,19 +3267,19 @@
         <v>0.01163563171613189</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01421392851634566</v>
+        <v>0.01421392851634567</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01821224625945393</v>
+        <v>0.009543391319365799</v>
       </c>
       <c r="O5" t="n">
-        <v>0.009843087569730393</v>
+        <v>0.009843087569730385</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01003964925422314</v>
+        <v>0.01003964925422312</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.009043523647471196</v>
+        <v>0.009043523647471187</v>
       </c>
       <c r="R5" t="n">
         <v>0.01042481516466814</v>
@@ -3291,28 +3291,28 @@
         <v>0.01129557177452621</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0129079188862844</v>
+        <v>0.01290791888628441</v>
       </c>
       <c r="V5" t="n">
         <v>0.01056637742200255</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0116810102086147</v>
+        <v>0.01168101020861469</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01607186985573823</v>
+        <v>0.01607186985573824</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.02094112501988351</v>
+        <v>0.02094112501988353</v>
       </c>
       <c r="Z5" t="n">
         <v>0.009358943760185034</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01203113053651114</v>
+        <v>0.01203113053651116</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.01600200176610373</v>
+        <v>0.01600200176610372</v>
       </c>
     </row>
     <row r="6">
@@ -3322,64 +3322,64 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.009614233376381398</v>
+        <v>0.009614233376381388</v>
       </c>
       <c r="C6" t="n">
-        <v>0.009396829081260666</v>
+        <v>0.009396829081260662</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01084930319640347</v>
+        <v>0.01084930319640346</v>
       </c>
       <c r="E6" t="n">
-        <v>0.009493574934111137</v>
+        <v>0.00949357493411114</v>
       </c>
       <c r="F6" t="n">
-        <v>0.008698350998172623</v>
+        <v>0.008698350998172615</v>
       </c>
       <c r="G6" t="n">
         <v>0.01009057306675006</v>
       </c>
       <c r="H6" t="n">
-        <v>0.009291935130702698</v>
+        <v>0.009291935130702703</v>
       </c>
       <c r="I6" t="n">
         <v>0.01062882893804559</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01074195101214512</v>
+        <v>0.01074195101214513</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01160237463250411</v>
+        <v>0.01160237463250412</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01080309269881588</v>
+        <v>0.01080309269881589</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01338138949902892</v>
+        <v>0.01338138949902893</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01821224625945393</v>
+        <v>0.009713199105643644</v>
       </c>
       <c r="O6" t="n">
-        <v>0.009916613667614402</v>
+        <v>0.009916613667614394</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01021966263314635</v>
+        <v>0.01021966263314634</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.009758173700633374</v>
+        <v>0.00975817370063338</v>
       </c>
       <c r="R6" t="n">
-        <v>0.009592276147352138</v>
+        <v>0.009592276147352143</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01056653753134879</v>
+        <v>0.0105665375313488</v>
       </c>
       <c r="T6" t="n">
         <v>0.01046303275721022</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01270727658615145</v>
+        <v>0.01270727658615144</v>
       </c>
       <c r="V6" t="n">
         <v>0.01071200266889507</v>
@@ -3394,13 +3394,13 @@
         <v>0.01882422430979895</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.009517528042130952</v>
+        <v>0.009517528042130949</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.01119859151919516</v>
+        <v>0.01119859151919517</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01381874135466341</v>
+        <v>0.0138187413546634</v>
       </c>
     </row>
   </sheetData>
@@ -3566,25 +3566,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003780611976928462</v>
+        <v>0.003780611976928461</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003375213241705781</v>
+        <v>0.003375213241705777</v>
       </c>
       <c r="D2" t="n">
         <v>0.003832814918836051</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003787387430864777</v>
+        <v>0.003787387430864776</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003772874465822173</v>
+        <v>0.003772874465822175</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00379108276428781</v>
+        <v>0.003791082764287808</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003786910752904399</v>
+        <v>0.003786910752904398</v>
       </c>
       <c r="I2" t="n">
         <v>0.003800536325240292</v>
@@ -3593,31 +3593,31 @@
         <v>0.00381249795273861</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003856585186385631</v>
+        <v>0.00385658518638563</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003830353303445493</v>
+        <v>0.003830353303445491</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003926995094813795</v>
+        <v>0.003926995094813791</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003826848654270895</v>
+        <v>0.003826848654270893</v>
       </c>
       <c r="O2" t="n">
-        <v>0.005476357971210834</v>
+        <v>0.005476357971210831</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003805660662198956</v>
+        <v>0.003805660662198955</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003792616016020764</v>
+        <v>0.003792616016020763</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003784127299252834</v>
+        <v>0.003784127299252833</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003796310080381289</v>
+        <v>0.003796310080381288</v>
       </c>
       <c r="T2" t="n">
         <v>0.003787309446181524</v>
@@ -3626,25 +3626,25 @@
         <v>0.003854892520862565</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003775281727414698</v>
+        <v>0.003775281727414695</v>
       </c>
       <c r="W2" t="n">
-        <v>0.003781105499413418</v>
+        <v>0.003781105499413417</v>
       </c>
       <c r="X2" t="n">
-        <v>0.003847810371179244</v>
+        <v>0.003847810371179242</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.00380554253190556</v>
+        <v>0.003805542531905559</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.004798238158758237</v>
+        <v>0.004798238158758236</v>
       </c>
       <c r="AA2" t="n">
         <v>0.003842033580521244</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.004261224801160843</v>
+        <v>0.004261224801160841</v>
       </c>
     </row>
     <row r="3">
@@ -3654,85 +3654,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005037697514958343</v>
+        <v>0.003836692141960599</v>
       </c>
       <c r="C3" t="n">
-        <v>0.004191486023292067</v>
+        <v>0.003298393350814779</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006264238295248691</v>
+        <v>0.004269650916335821</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006241582431609016</v>
+        <v>0.004946791051540302</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004866772418375163</v>
+        <v>0.003784132102011661</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005278688161242502</v>
+        <v>0.003914777889891237</v>
       </c>
       <c r="H3" t="n">
-        <v>0.005197275233237257</v>
+        <v>0.003902710439646436</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005512599602878025</v>
+        <v>0.004009950927415004</v>
       </c>
       <c r="J3" t="n">
-        <v>0.005781489245284332</v>
+        <v>0.00408974863422168</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006813157415746935</v>
+        <v>0.004436748965008457</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006190398415598265</v>
+        <v>0.004217394669128313</v>
       </c>
       <c r="M3" t="n">
-        <v>0.008454137345901509</v>
+        <v>0.004991656881840892</v>
       </c>
       <c r="N3" t="n">
-        <v>0.006118339390919996</v>
+        <v>0.004211109353164469</v>
       </c>
       <c r="O3" t="n">
-        <v>0.006741461654603399</v>
+        <v>0.005534156154405423</v>
       </c>
       <c r="P3" t="n">
-        <v>0.005612802135134947</v>
+        <v>0.004032169627851554</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.00532348337444243</v>
+        <v>0.003937432472392199</v>
       </c>
       <c r="R3" t="n">
-        <v>0.00513026322541772</v>
+        <v>0.003878038754470794</v>
       </c>
       <c r="S3" t="n">
-        <v>0.005400263530859927</v>
+        <v>0.003950558747834509</v>
       </c>
       <c r="T3" t="n">
-        <v>0.005202188786729677</v>
+        <v>0.003898472124101652</v>
       </c>
       <c r="U3" t="n">
-        <v>0.007563658081586725</v>
+        <v>0.004670796013773106</v>
       </c>
       <c r="V3" t="n">
-        <v>0.004915653836105712</v>
+        <v>0.003796228048443792</v>
       </c>
       <c r="W3" t="n">
-        <v>0.006718863918727209</v>
+        <v>0.004372498003539699</v>
       </c>
       <c r="X3" t="n">
-        <v>0.006612165831382352</v>
+        <v>0.004387393630896066</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.005621510051264763</v>
+        <v>0.004041351561861444</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006396897483569633</v>
+        <v>0.004956400970005292</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.006467793845097136</v>
+        <v>0.004334240197894781</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01613534803982847</v>
+        <v>0.007733924500992843</v>
       </c>
     </row>
     <row r="4">
@@ -3745,82 +3745,82 @@
         <v>0.01248517759395808</v>
       </c>
       <c r="C4" t="n">
-        <v>0.008744379639181435</v>
+        <v>0.008744379639181437</v>
       </c>
       <c r="D4" t="n">
         <v>0.02474762567275825</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01347135692677172</v>
+        <v>0.01347135692677171</v>
       </c>
       <c r="F4" t="n">
         <v>0.01149879117329755</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01431282170633921</v>
+        <v>0.01431282170633919</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01495300750906979</v>
+        <v>0.01495300750906977</v>
       </c>
       <c r="I4" t="n">
         <v>0.01773995783676941</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01914721072358979</v>
+        <v>0.01914721072358978</v>
       </c>
       <c r="K4" t="n">
         <v>0.02815018285431673</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02186780315804472</v>
+        <v>0.0218678031580447</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0427621870088204</v>
+        <v>0.04276218700882039</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02269325332246966</v>
+        <v>0.0226932533224696</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01249526392420806</v>
+        <v>0.01249526392420803</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01749410942411543</v>
+        <v>0.01749410942411542</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01538514634561782</v>
+        <v>0.0153851463456178</v>
       </c>
       <c r="R4" t="n">
         <v>0.0141858478665126</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01498905633790462</v>
+        <v>0.01498905633790464</v>
       </c>
       <c r="T4" t="n">
-        <v>0.01450235775996206</v>
+        <v>0.01450235775996205</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03507554077883551</v>
+        <v>0.03507554077883559</v>
       </c>
       <c r="V4" t="n">
-        <v>0.01147797438139023</v>
+        <v>0.01147797438139019</v>
       </c>
       <c r="W4" t="n">
-        <v>0.02911715628005978</v>
+        <v>0.0291171562800598</v>
       </c>
       <c r="X4" t="n">
-        <v>0.02779285027428459</v>
+        <v>0.02779285027428461</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.01819038956892514</v>
+        <v>0.01819038956892515</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.01533820219871405</v>
+        <v>0.01533820219871398</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.02606686315995941</v>
+        <v>0.02606686315995937</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1207790605700382</v>
+        <v>0.1207790605700381</v>
       </c>
     </row>
     <row r="5">
@@ -3830,28 +3830,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.008876212825899895</v>
+        <v>0.00887621282589989</v>
       </c>
       <c r="C5" t="n">
-        <v>0.009959018322108904</v>
+        <v>0.009959018322108893</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01077560215018713</v>
+        <v>0.01077560215018712</v>
       </c>
       <c r="E5" t="n">
-        <v>0.009565083545004151</v>
+        <v>0.009565083545004148</v>
       </c>
       <c r="F5" t="n">
-        <v>0.008992855185353605</v>
+        <v>0.008992855185353603</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01057579995326666</v>
+        <v>0.01057579995326665</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01025709347902953</v>
+        <v>0.01025709347902951</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01041100058663637</v>
+        <v>0.01041100058663635</v>
       </c>
       <c r="J5" t="n">
         <v>0.01054263061797627</v>
@@ -3860,55 +3860,55 @@
         <v>0.01104409825702291</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0107477970719517</v>
+        <v>0.01074779707195169</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0118318410107297</v>
+        <v>0.01183184101072969</v>
       </c>
       <c r="N5" t="n">
-        <v>0.02269325332246966</v>
+        <v>0.009692948196035641</v>
       </c>
       <c r="O5" t="n">
-        <v>0.009454109177431671</v>
+        <v>0.009454109177431665</v>
       </c>
       <c r="P5" t="n">
-        <v>0.009664232612610114</v>
+        <v>0.009664232612610107</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.008754411525983632</v>
+        <v>0.008754411525983625</v>
       </c>
       <c r="R5" t="n">
         <v>0.01022565308958313</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01036326320678522</v>
+        <v>0.01036326320678521</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01026159690300258</v>
+        <v>0.01026159690300257</v>
       </c>
       <c r="U5" t="n">
-        <v>0.010796281447001</v>
+        <v>0.01079628144700098</v>
       </c>
       <c r="V5" t="n">
-        <v>0.009743515270743901</v>
+        <v>0.009743515270743897</v>
       </c>
       <c r="W5" t="n">
-        <v>0.01103938561833424</v>
+        <v>0.01103938561833423</v>
       </c>
       <c r="X5" t="n">
-        <v>0.009497896797498757</v>
+        <v>0.009497896797498752</v>
       </c>
       <c r="Y5" t="n">
         <v>0.01176864777312273</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.009026856241841635</v>
+        <v>0.009026856241841626</v>
       </c>
       <c r="AA5" t="n">
         <v>0.01087973117471528</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.01691477793643794</v>
+        <v>0.01691477793643793</v>
       </c>
     </row>
     <row r="6">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.008825897599052765</v>
+        <v>0.008825897599052761</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00915512129845786</v>
+        <v>0.009155121298457858</v>
       </c>
       <c r="D6" t="n">
         <v>0.009971705126536086</v>
@@ -3930,19 +3930,19 @@
         <v>0.00933022312514839</v>
       </c>
       <c r="F6" t="n">
-        <v>0.008012569941938821</v>
+        <v>0.008012569941938818</v>
       </c>
       <c r="G6" t="n">
-        <v>0.009500321010199118</v>
+        <v>0.00950032101019912</v>
       </c>
       <c r="H6" t="n">
-        <v>0.009453196455378477</v>
+        <v>0.009453196455378478</v>
       </c>
       <c r="I6" t="n">
-        <v>0.009607103562985312</v>
+        <v>0.009607103562985313</v>
       </c>
       <c r="J6" t="n">
-        <v>0.009738733594325226</v>
+        <v>0.009738733594325224</v>
       </c>
       <c r="K6" t="n">
         <v>0.01024020123337187</v>
@@ -3954,22 +3954,22 @@
         <v>0.01102794398707857</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02269325332246966</v>
+        <v>0.009904313423655303</v>
       </c>
       <c r="O6" t="n">
         <v>0.009570779020176702</v>
       </c>
       <c r="P6" t="n">
-        <v>0.009889376572508079</v>
+        <v>0.009889376572508077</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.00951763979385346</v>
+        <v>0.009517639793853465</v>
       </c>
       <c r="R6" t="n">
-        <v>0.009421756065932088</v>
+        <v>0.009421756065932086</v>
       </c>
       <c r="S6" t="n">
-        <v>0.009559366183134174</v>
+        <v>0.009559366183134176</v>
       </c>
       <c r="T6" t="n">
         <v>0.009457699879351531</v>
@@ -3978,7 +3978,7 @@
         <v>0.01063231288738079</v>
       </c>
       <c r="V6" t="n">
-        <v>0.009940107493510892</v>
+        <v>0.009940107493510894</v>
       </c>
       <c r="W6" t="n">
         <v>0.01023523119460704</v>
@@ -3987,10 +3987,10 @@
         <v>0.01014108565900131</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.009663650970238328</v>
+        <v>0.009663650970238327</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.009221711401566529</v>
+        <v>0.009221711401566531</v>
       </c>
       <c r="AA6" t="n">
         <v>0.01007583415106423</v>
@@ -4162,85 +4162,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003719927467596874</v>
+        <v>0.003719927467596868</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003341101735902525</v>
+        <v>0.003341101735902524</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003733224359631672</v>
+        <v>0.003733224359631669</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003729856158419685</v>
+        <v>0.003729856158419681</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003727662134037217</v>
+        <v>0.003727662134037218</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003726480970339123</v>
+        <v>0.003726480970339118</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003728723122056001</v>
+        <v>0.003728723122055997</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003729129558657144</v>
+        <v>0.003729129558657143</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003732338521982054</v>
+        <v>0.003732338521982053</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0037269891954183</v>
+        <v>0.003726989195418296</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003730002255728383</v>
+        <v>0.003730002255728379</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003721272251973346</v>
+        <v>0.003721272251973344</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003729735304660732</v>
+        <v>0.003729735304660728</v>
       </c>
       <c r="O2" t="n">
-        <v>0.005407198355078673</v>
+        <v>0.005407198355078674</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003729764899674783</v>
+        <v>0.003729764899674784</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003719054337345993</v>
+        <v>0.003719054337345991</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003740162220649537</v>
+        <v>0.003740162220649534</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003732522330887471</v>
+        <v>0.003732522330887466</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003720054528455499</v>
+        <v>0.003720054528455496</v>
       </c>
       <c r="U2" t="n">
-        <v>0.003668769052198068</v>
+        <v>0.003668769052198064</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003730637213934809</v>
+        <v>0.003730637213934806</v>
       </c>
       <c r="W2" t="n">
-        <v>0.003657041766419437</v>
+        <v>0.003657041766419431</v>
       </c>
       <c r="X2" t="n">
-        <v>0.003889861682554796</v>
+        <v>0.003889861682554792</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003830559961541156</v>
+        <v>0.003830559961541152</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.004730173209076684</v>
+        <v>0.00473017320907668</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003751597417601562</v>
+        <v>0.003751597417601557</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.003713868074792605</v>
+        <v>0.003713868074792604</v>
       </c>
     </row>
     <row r="3">
@@ -4250,85 +4250,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004682029624019595</v>
+        <v>0.003688331776833909</v>
       </c>
       <c r="C3" t="n">
-        <v>0.004371927977003355</v>
+        <v>0.00333379991498539</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004995756596391857</v>
+        <v>0.00379794353484149</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005961810235759441</v>
+        <v>0.004824819817265937</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004867876879897431</v>
+        <v>0.003754944131536926</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004832959658862503</v>
+        <v>0.003738262903569554</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004893888290000408</v>
+        <v>0.003767182812172331</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004901213909855397</v>
+        <v>0.003767372750022266</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004970540502724329</v>
+        <v>0.003786283258487505</v>
       </c>
       <c r="K3" t="n">
-        <v>0.004849729235802966</v>
+        <v>0.003747147009332521</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004916142366689774</v>
+        <v>0.003764931575999231</v>
       </c>
       <c r="M3" t="n">
-        <v>0.004737303829933326</v>
+        <v>0.003709943250083105</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004912544332752778</v>
+        <v>0.003768215072500601</v>
       </c>
       <c r="O3" t="n">
-        <v>0.006623409625756631</v>
+        <v>0.005452376224093745</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004907702063553595</v>
+        <v>0.003764089742400878</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.004664580253682464</v>
+        <v>0.003683341532107047</v>
       </c>
       <c r="R3" t="n">
-        <v>0.005160468484069546</v>
+        <v>0.003858459849945844</v>
       </c>
       <c r="S3" t="n">
-        <v>0.004972841364733083</v>
+        <v>0.003782610799517542</v>
       </c>
       <c r="T3" t="n">
-        <v>0.004688856130458371</v>
+        <v>0.003693890742039435</v>
       </c>
       <c r="U3" t="n">
-        <v>0.004655956897762359</v>
+        <v>0.003646056310483159</v>
       </c>
       <c r="V3" t="n">
-        <v>0.004929141775588651</v>
+        <v>0.003770770319384059</v>
       </c>
       <c r="W3" t="n">
-        <v>0.005271582257606049</v>
+        <v>0.0038280782256825</v>
       </c>
       <c r="X3" t="n">
-        <v>0.008644017915666385</v>
+        <v>0.005032621653378986</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.007253439228874455</v>
+        <v>0.00457664812339397</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006048269150459996</v>
+        <v>0.004805231302770513</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.00541908699533835</v>
+        <v>0.003944072168050651</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.004562609536154003</v>
+        <v>0.003650942514343768</v>
       </c>
     </row>
     <row r="4">
@@ -4338,13 +4338,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009595302870047534</v>
+        <v>0.009595302870047537</v>
       </c>
       <c r="C4" t="n">
         <v>0.01043379532978913</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01246835070556787</v>
+        <v>0.01246835070556786</v>
       </c>
       <c r="E4" t="n">
         <v>0.01091749445426233</v>
@@ -4359,16 +4359,16 @@
         <v>0.01192137564991777</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01179735398373816</v>
+        <v>0.01179735398373815</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01198348450725686</v>
+        <v>0.01198348450725685</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01116050418963265</v>
+        <v>0.01116050418963264</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01133818852395688</v>
+        <v>0.01133818852395687</v>
       </c>
       <c r="M4" t="n">
         <v>0.01035785954807074</v>
@@ -4383,7 +4383,7 @@
         <v>0.01136721619460429</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.009552185677115767</v>
+        <v>0.009552185677115769</v>
       </c>
       <c r="R4" t="n">
         <v>0.0141923452299669</v>
@@ -4395,22 +4395,22 @@
         <v>0.009924238141939101</v>
       </c>
       <c r="U4" t="n">
-        <v>0.009900634304549735</v>
+        <v>0.009900634304549729</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0114979496900761</v>
+        <v>0.01149794969007609</v>
       </c>
       <c r="W4" t="n">
-        <v>0.01527653657629606</v>
+        <v>0.01527653657629605</v>
       </c>
       <c r="X4" t="n">
-        <v>0.04253322650396277</v>
+        <v>0.04253322650396283</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.03194647958218211</v>
+        <v>0.03194647958218206</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.01239335176335405</v>
+        <v>0.01239335176335404</v>
       </c>
       <c r="AA4" t="n">
         <v>0.01609082756365024</v>
@@ -4426,85 +4426,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.008494659864557226</v>
+        <v>0.008494659864557219</v>
       </c>
       <c r="C5" t="n">
-        <v>0.009705667649268024</v>
+        <v>0.009705667649268009</v>
       </c>
       <c r="D5" t="n">
-        <v>0.009822771884129371</v>
+        <v>0.009822771884129358</v>
       </c>
       <c r="E5" t="n">
-        <v>0.009157520175812102</v>
+        <v>0.009157520175812089</v>
       </c>
       <c r="F5" t="n">
-        <v>0.008765532261130388</v>
+        <v>0.008765532261130377</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00999085106848913</v>
+        <v>0.00999085106848911</v>
       </c>
       <c r="H5" t="n">
-        <v>0.009771928335040606</v>
+        <v>0.009771928335040586</v>
       </c>
       <c r="I5" t="n">
-        <v>0.009776519223420543</v>
+        <v>0.009776519223420529</v>
       </c>
       <c r="J5" t="n">
-        <v>0.009809570506672624</v>
+        <v>0.00980957050667261</v>
       </c>
       <c r="K5" t="n">
-        <v>0.009752342836022082</v>
+        <v>0.009752342836022063</v>
       </c>
       <c r="L5" t="n">
-        <v>0.009786376738300743</v>
+        <v>0.009786376738300729</v>
       </c>
       <c r="M5" t="n">
-        <v>0.009697491225079331</v>
+        <v>0.009697491225079315</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01164998075290301</v>
+        <v>0.008870278273834643</v>
       </c>
       <c r="O5" t="n">
-        <v>0.009141071104954875</v>
+        <v>0.009141071104954863</v>
       </c>
       <c r="P5" t="n">
-        <v>0.009060028402617956</v>
+        <v>0.009060028402617947</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.008253309781893885</v>
+        <v>0.008253309781893876</v>
       </c>
       <c r="R5" t="n">
-        <v>0.009901138215899904</v>
+        <v>0.009901138215899885</v>
       </c>
       <c r="S5" t="n">
-        <v>0.009814842146514485</v>
+        <v>0.009814842146514473</v>
       </c>
       <c r="T5" t="n">
-        <v>0.00967401258257285</v>
+        <v>0.009674012582572833</v>
       </c>
       <c r="U5" t="n">
-        <v>0.00910922577970133</v>
+        <v>0.009109225779701319</v>
       </c>
       <c r="V5" t="n">
-        <v>0.009449350718291701</v>
+        <v>0.009449350718291692</v>
       </c>
       <c r="W5" t="n">
-        <v>0.01000424388922133</v>
+        <v>0.01000424388922132</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01029061580139451</v>
+        <v>0.0102906158013945</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.01209239417549246</v>
+        <v>0.01209239417549244</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.008655273095824851</v>
+        <v>0.008655273095824839</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0100303040259235</v>
+        <v>0.01003030402592349</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0108437076456579</v>
+        <v>0.01084370764565788</v>
       </c>
     </row>
     <row r="6">
@@ -4514,85 +4514,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.008346500582280326</v>
+        <v>0.008346500582280321</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008851309232352153</v>
+        <v>0.00885130923235215</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008968413467213502</v>
+        <v>0.008968413467213495</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00882149757107817</v>
+        <v>0.008821497571078165</v>
       </c>
       <c r="F6" t="n">
-        <v>0.007818145702167042</v>
+        <v>0.00781814570216704</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008892243994010986</v>
+        <v>0.00889224399401097</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008917569918124733</v>
+        <v>0.008917569918124729</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008922160806504684</v>
+        <v>0.008922160806504681</v>
       </c>
       <c r="J6" t="n">
-        <v>0.008955212089756755</v>
+        <v>0.008955212089756753</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00889798441910622</v>
+        <v>0.008897984419106213</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008932018321384877</v>
+        <v>0.008932018321384868</v>
       </c>
       <c r="M6" t="n">
-        <v>0.008843132808163583</v>
+        <v>0.008843132808163581</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01164998075290301</v>
+        <v>0.008929002986272139</v>
       </c>
       <c r="O6" t="n">
-        <v>0.00910519977713966</v>
+        <v>0.009105199777139651</v>
       </c>
       <c r="P6" t="n">
-        <v>0.00911966283062671</v>
+        <v>0.009119662830626705</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.008808356757933657</v>
+        <v>0.008808356757933655</v>
       </c>
       <c r="R6" t="n">
-        <v>0.009046779798984037</v>
+        <v>0.009046779798984031</v>
       </c>
       <c r="S6" t="n">
-        <v>0.008960483729598625</v>
+        <v>0.008960483729598616</v>
       </c>
       <c r="T6" t="n">
-        <v>0.008819654165656977</v>
+        <v>0.008819654165656976</v>
       </c>
       <c r="U6" t="n">
-        <v>0.008830380462273146</v>
+        <v>0.008830380462273144</v>
       </c>
       <c r="V6" t="n">
-        <v>0.009461935731238246</v>
+        <v>0.00946193573123824</v>
       </c>
       <c r="W6" t="n">
-        <v>0.009149653977736504</v>
+        <v>0.0091496539777365</v>
       </c>
       <c r="X6" t="n">
         <v>0.01073770408635872</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01006786386737026</v>
+        <v>0.01006786386737025</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.008716308460490794</v>
+        <v>0.008716308460490789</v>
       </c>
       <c r="AA6" t="n">
         <v>0.009175945609007636</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.008758915896621297</v>
+        <v>0.008758915896621292</v>
       </c>
     </row>
   </sheetData>
@@ -4758,85 +4758,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003719496730968312</v>
+        <v>0.003719496730968307</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003298500630514835</v>
+        <v>0.003298500630514836</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00372432776773527</v>
+        <v>0.003724327767735266</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003730237526854601</v>
+        <v>0.003730237526854597</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003720454898885396</v>
+        <v>0.003720454898885392</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003717369856140802</v>
+        <v>0.003717369856140797</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003718643691939124</v>
+        <v>0.003718643691939121</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003718547481274782</v>
+        <v>0.00371854748127478</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003725099386233091</v>
+        <v>0.003725099386233087</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003717827245376123</v>
+        <v>0.003717827245376117</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003725245303639584</v>
+        <v>0.00372524530363958</v>
       </c>
       <c r="M2" t="n">
         <v>0.003715184722843516</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003718496344346917</v>
+        <v>0.003718496344346916</v>
       </c>
       <c r="O2" t="n">
-        <v>0.005412080652775582</v>
+        <v>0.005412080652775574</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003726918384333028</v>
+        <v>0.003726918384333031</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003713488456775708</v>
+        <v>0.003713488456775702</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003734611102083576</v>
+        <v>0.003734611102083574</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003724313915000537</v>
+        <v>0.003724313915000532</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003713587907376817</v>
+        <v>0.003713587907376812</v>
       </c>
       <c r="U2" t="n">
-        <v>0.003555198986957069</v>
+        <v>0.003555198986957071</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003729300854951443</v>
+        <v>0.003729300854951446</v>
       </c>
       <c r="W2" t="n">
-        <v>0.003550080817832746</v>
+        <v>0.003550080817832744</v>
       </c>
       <c r="X2" t="n">
-        <v>0.003937204529351541</v>
+        <v>0.003937204529351536</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003811960490298976</v>
+        <v>0.003811960490298973</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.004715445247181521</v>
+        <v>0.004715445247181516</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003747152431731166</v>
+        <v>0.003747152431731162</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.003712990538847195</v>
+        <v>0.003712990538847161</v>
       </c>
     </row>
     <row r="3">
@@ -4846,85 +4846,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004790370631916904</v>
+        <v>0.003714962694258035</v>
       </c>
       <c r="C3" t="n">
-        <v>0.004313258352481454</v>
+        <v>0.003280097497038697</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004908407694911689</v>
+        <v>0.003759174940272168</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00610257955804326</v>
+        <v>0.004869424561428064</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004819814044380298</v>
+        <v>0.003729655685804558</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004741584305519613</v>
+        <v>0.003698743826912532</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004778184952650796</v>
+        <v>0.003716980437430296</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004774258496433586</v>
+        <v>0.003714095357623563</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004922556169346001</v>
+        <v>0.003761025231701316</v>
       </c>
       <c r="K3" t="n">
-        <v>0.004756309467808509</v>
+        <v>0.003706534888088017</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004925188148536593</v>
+        <v>0.00375938335803751</v>
       </c>
       <c r="M3" t="n">
-        <v>0.004714215144242418</v>
+        <v>0.00369280797388931</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004770988792974758</v>
+        <v>0.003710954396058455</v>
       </c>
       <c r="O3" t="n">
-        <v>0.006794537597479645</v>
+        <v>0.005501331471752174</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004960198527842376</v>
+        <v>0.003771033382801671</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.004654859161641853</v>
+        <v>0.003670826867055884</v>
       </c>
       <c r="R3" t="n">
-        <v>0.005151176244501831</v>
+        <v>0.003846431456956085</v>
       </c>
       <c r="S3" t="n">
-        <v>0.004902366064414338</v>
+        <v>0.003751719041709387</v>
       </c>
       <c r="T3" t="n">
-        <v>0.004658056156798645</v>
+        <v>0.003673597024412481</v>
       </c>
       <c r="U3" t="n">
-        <v>0.004564680655830312</v>
+        <v>0.00353280515800499</v>
       </c>
       <c r="V3" t="n">
-        <v>0.005016818144971458</v>
+        <v>0.003790743770065946</v>
       </c>
       <c r="W3" t="n">
-        <v>0.004951776554488783</v>
+        <v>0.003650436098252763</v>
       </c>
       <c r="X3" t="n">
-        <v>0.009865473262862745</v>
+        <v>0.00542739517561293</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.006941485808455059</v>
+        <v>0.004463264052520089</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.005908545932750271</v>
+        <v>0.004745885327155073</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.005435347172165915</v>
+        <v>0.003940454486508737</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.004659480532896243</v>
+        <v>0.003675283116742241</v>
       </c>
     </row>
     <row r="4">
@@ -4940,31 +4940,31 @@
         <v>0.01039091389008361</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01192175746188537</v>
+        <v>0.01192175746188536</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01195077067524545</v>
+        <v>0.01195077067524544</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01124461788645133</v>
+        <v>0.01124461788645134</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01021301060019881</v>
+        <v>0.01021301060019889</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01100522300388006</v>
+        <v>0.01100522300388007</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01084445734009098</v>
+        <v>0.01084445734009099</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01178444891510786</v>
+        <v>0.01178444891510785</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01057971466480015</v>
+        <v>0.01057971466480016</v>
       </c>
       <c r="L4" t="n">
-        <v>0.011626390490136</v>
+        <v>0.01162639049013601</v>
       </c>
       <c r="M4" t="n">
         <v>0.01033045622937601</v>
@@ -4976,19 +4976,19 @@
         <v>0.01305251733017672</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01184882950999559</v>
+        <v>0.01184882950999557</v>
       </c>
       <c r="Q4" t="n">
         <v>0.009644802827571027</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01431286663114708</v>
+        <v>0.01431286663114706</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01142736750583091</v>
+        <v>0.01142736750583092</v>
       </c>
       <c r="T4" t="n">
-        <v>0.009797857847677878</v>
+        <v>0.009797857847677874</v>
       </c>
       <c r="U4" t="n">
         <v>0.01015579178643567</v>
@@ -4997,19 +4997,19 @@
         <v>0.01234762147926137</v>
       </c>
       <c r="W4" t="n">
-        <v>0.01363280174537472</v>
+        <v>0.01363280174537473</v>
       </c>
       <c r="X4" t="n">
-        <v>0.05211794194808411</v>
+        <v>0.0521179419480841</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.02966255265963686</v>
+        <v>0.02966255265963691</v>
       </c>
       <c r="Z4" t="n">
         <v>0.01143420315152144</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01640298125293266</v>
+        <v>0.01640298125293267</v>
       </c>
       <c r="AB4" t="n">
         <v>0.009929678621106046</v>
@@ -5022,43 +5022,43 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.008551705104304022</v>
+        <v>0.008551705104304023</v>
       </c>
       <c r="C5" t="n">
-        <v>0.009694890537301333</v>
+        <v>0.009694890537301335</v>
       </c>
       <c r="D5" t="n">
         <v>0.009780381372411733</v>
       </c>
       <c r="E5" t="n">
-        <v>0.009221957218288435</v>
+        <v>0.009221957218288434</v>
       </c>
       <c r="F5" t="n">
-        <v>0.008745440275858354</v>
+        <v>0.008745440275858352</v>
       </c>
       <c r="G5" t="n">
-        <v>0.009945247395861827</v>
+        <v>0.00994524739586183</v>
       </c>
       <c r="H5" t="n">
         <v>0.009716177121490196</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00971509037777739</v>
+        <v>0.009715090377777392</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0097861228852933</v>
+        <v>0.009786122885293303</v>
       </c>
       <c r="K5" t="n">
-        <v>0.009706954981977082</v>
+        <v>0.009706954981977085</v>
       </c>
       <c r="L5" t="n">
-        <v>0.009790745362538305</v>
+        <v>0.009790745362538307</v>
       </c>
       <c r="M5" t="n">
-        <v>0.009686230282491545</v>
+        <v>0.009686230282491548</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0106513090211263</v>
+        <v>0.008804383037545117</v>
       </c>
       <c r="O5" t="n">
         <v>0.009226052549556723</v>
@@ -5067,34 +5067,34 @@
         <v>0.009088317019827537</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.008253099964761515</v>
+        <v>0.008253099964761519</v>
       </c>
       <c r="R5" t="n">
         <v>0.009896536364443317</v>
       </c>
       <c r="S5" t="n">
-        <v>0.009780224899400329</v>
+        <v>0.009780224899400333</v>
       </c>
       <c r="T5" t="n">
         <v>0.009659069709083085</v>
       </c>
       <c r="U5" t="n">
-        <v>0.009119932620935417</v>
+        <v>0.009119932620935415</v>
       </c>
       <c r="V5" t="n">
-        <v>0.00949491165548077</v>
+        <v>0.009494911655480776</v>
       </c>
       <c r="W5" t="n">
-        <v>0.009893128314479928</v>
+        <v>0.009893128314479924</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01088768520303574</v>
+        <v>0.01088768520303575</v>
       </c>
       <c r="Y5" t="n">
         <v>0.01193666437718585</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.008592536161707451</v>
+        <v>0.008592536161707453</v>
       </c>
       <c r="AA5" t="n">
         <v>0.01003819645210955</v>
@@ -5110,13 +5110,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.008338173049968299</v>
+        <v>0.008338173049968296</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008759231899379192</v>
+        <v>0.008759231899379188</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008844722734489585</v>
+        <v>0.008844722734489581</v>
       </c>
       <c r="E6" t="n">
         <v>0.008807160975459</v>
@@ -5125,70 +5125,70 @@
         <v>0.007759037322804958</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008766130106376127</v>
+        <v>0.008766130106376132</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008780518483568056</v>
+        <v>0.008780518483568053</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008779431739855247</v>
+        <v>0.008779431739855244</v>
       </c>
       <c r="J6" t="n">
         <v>0.008850464247371162</v>
       </c>
       <c r="K6" t="n">
-        <v>0.008771296344054944</v>
+        <v>0.008771296344054942</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008855086724616162</v>
+        <v>0.00885508672461616</v>
       </c>
       <c r="M6" t="n">
-        <v>0.008750571644569599</v>
+        <v>0.008750571644569598</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0106513090211263</v>
+        <v>0.008778854124730879</v>
       </c>
       <c r="O6" t="n">
         <v>0.009100198209960228</v>
       </c>
       <c r="P6" t="n">
-        <v>0.009056346937001001</v>
+        <v>0.009056346937000999</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.008722287915015486</v>
+        <v>0.008722287915015484</v>
       </c>
       <c r="R6" t="n">
-        <v>0.008960877726521181</v>
+        <v>0.008960877726521176</v>
       </c>
       <c r="S6" t="n">
-        <v>0.00884456626147819</v>
+        <v>0.008844566261478188</v>
       </c>
       <c r="T6" t="n">
-        <v>0.008723411071160947</v>
+        <v>0.008723411071160942</v>
       </c>
       <c r="U6" t="n">
         <v>0.008757899743966386</v>
       </c>
       <c r="V6" t="n">
-        <v>0.009402347898072587</v>
+        <v>0.009402347898072589</v>
       </c>
       <c r="W6" t="n">
-        <v>0.008957238930754469</v>
+        <v>0.008957238930754464</v>
       </c>
       <c r="X6" t="n">
         <v>0.01124926368509388</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.00983457464889069</v>
+        <v>0.009834574648890693</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.008580290439571285</v>
+        <v>0.008580290439571281</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.009102537814187413</v>
+        <v>0.009102537814187409</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.008724370789390864</v>
+        <v>0.00872437078939086</v>
       </c>
     </row>
   </sheetData>
@@ -5354,85 +5354,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003940103912448257</v>
+        <v>0.003940103912448252</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003485709937841928</v>
+        <v>0.00348570993784195</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003982328326586774</v>
+        <v>0.003982328326586779</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003903412905599446</v>
+        <v>0.003903412905599438</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003899568136094604</v>
+        <v>0.003899568136094605</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003957144900433587</v>
+        <v>0.003957144900433601</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003894464202774764</v>
+        <v>0.003894464202774779</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003954329989250813</v>
+        <v>0.00395432998925082</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00398878883983058</v>
+        <v>0.003988788839830572</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004011411537652989</v>
+        <v>0.004011411537652978</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004042089945954246</v>
+        <v>0.004042089945954255</v>
       </c>
       <c r="M2" t="n">
-        <v>0.004371396573337351</v>
+        <v>0.004371396573337338</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003989458396433511</v>
+        <v>0.003989458396433539</v>
       </c>
       <c r="O2" t="n">
-        <v>0.005674057880671558</v>
+        <v>0.005674057880671564</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003943305520990644</v>
+        <v>0.003943305520990642</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003904606044791291</v>
+        <v>0.003904606044791314</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003905999017053352</v>
+        <v>0.003905999017053351</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003950073149472865</v>
+        <v>0.003950073149472853</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003945427817881899</v>
+        <v>0.003945427817881918</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0041235348506796</v>
+        <v>0.004123534850679624</v>
       </c>
       <c r="V2" t="n">
-        <v>0.003894398801464564</v>
+        <v>0.003894398801464565</v>
       </c>
       <c r="W2" t="n">
-        <v>0.00393899589499064</v>
+        <v>0.003938995894990633</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004230711542886597</v>
+        <v>0.004230711542886618</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.004136074459375212</v>
+        <v>0.004136074459375192</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.004931264977233477</v>
+        <v>0.004931264977233488</v>
       </c>
       <c r="AA2" t="n">
         <v>0.004006463866294026</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.004295968400456055</v>
+        <v>0.004295968400456064</v>
       </c>
     </row>
     <row r="3">
@@ -5442,85 +5442,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006441679685091722</v>
+        <v>0.004366280067102815</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00454643700544628</v>
+        <v>0.003475080729496193</v>
       </c>
       <c r="D3" t="n">
-        <v>0.007454372394297197</v>
+        <v>0.004745059517807395</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006636174718404335</v>
+        <v>0.005132378343152526</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005525735437962172</v>
+        <v>0.004069504862276682</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006834629460731929</v>
+        <v>0.00449596055614856</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00540804113054622</v>
+        <v>0.004033120031995493</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006803946921749834</v>
+        <v>0.004517057053468339</v>
       </c>
       <c r="J3" t="n">
-        <v>0.007586862784921298</v>
+        <v>0.004761797043130367</v>
       </c>
       <c r="K3" t="n">
-        <v>0.008123150155740404</v>
+        <v>0.004933606040232864</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008812959438323626</v>
+        <v>0.005181054731163411</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01646826995235963</v>
+        <v>0.007778985960529346</v>
       </c>
       <c r="N3" t="n">
-        <v>0.007609320446096863</v>
+        <v>0.004790098994630254</v>
       </c>
       <c r="O3" t="n">
-        <v>0.007758061247976728</v>
+        <v>0.005969331374650358</v>
       </c>
       <c r="P3" t="n">
-        <v>0.006513099710732008</v>
+        <v>0.004396050471660818</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.005636753171558801</v>
+        <v>0.004103868123043151</v>
       </c>
       <c r="R3" t="n">
-        <v>0.005676169536053154</v>
+        <v>0.004126101281968868</v>
       </c>
       <c r="S3" t="n">
-        <v>0.006675337468957278</v>
+        <v>0.004437330153289265</v>
       </c>
       <c r="T3" t="n">
-        <v>0.006593763602716626</v>
+        <v>0.004443432264404476</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01112585534788377</v>
+        <v>0.005962083805573721</v>
       </c>
       <c r="V3" t="n">
-        <v>0.005390583268530213</v>
+        <v>0.004012551570844941</v>
       </c>
       <c r="W3" t="n">
-        <v>0.007731797392667947</v>
+        <v>0.00478953884382588</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01324417544715267</v>
+        <v>0.006749611360083238</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0110077967015489</v>
+        <v>0.005946340391841541</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.007012466808092858</v>
+        <v>0.005229824534133452</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.007997075919375204</v>
+        <v>0.004918055367050049</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01468662308710867</v>
+        <v>0.007330262971706303</v>
       </c>
     </row>
     <row r="4">
@@ -5530,85 +5530,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02372237155207511</v>
+        <v>0.02372237155207521</v>
       </c>
       <c r="C4" t="n">
         <v>0.01131652121642781</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03569651847363715</v>
+        <v>0.03569651847363717</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01643165468465712</v>
+        <v>0.0164316546846572</v>
       </c>
       <c r="F4" t="n">
         <v>0.01702248627131342</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0268855224095343</v>
+        <v>0.02688552240953429</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01625464123250717</v>
+        <v>0.01625464123250716</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02941524163138067</v>
+        <v>0.02941524163138068</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03454835380473043</v>
+        <v>0.03454835380473046</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03870173953227149</v>
+        <v>0.03870173953227151</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04544808068110077</v>
+        <v>0.04544808068110109</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1142387892132545</v>
+        <v>0.1142387892132546</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03636151530000755</v>
+        <v>0.03636151530000754</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01977509526856564</v>
+        <v>0.01977509526856563</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0247159118797009</v>
+        <v>0.02471591187970091</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01767550505141346</v>
+        <v>0.01767550505141345</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01877256110908238</v>
+        <v>0.01877256110908234</v>
       </c>
       <c r="S4" t="n">
-        <v>0.02521459375811647</v>
+        <v>0.02521459375811649</v>
       </c>
       <c r="T4" t="n">
-        <v>0.02734099556081705</v>
+        <v>0.02734099556081707</v>
       </c>
       <c r="U4" t="n">
-        <v>0.06654249493075891</v>
+        <v>0.06654249493075907</v>
       </c>
       <c r="V4" t="n">
-        <v>0.01477623073898293</v>
+        <v>0.01477623073898292</v>
       </c>
       <c r="W4" t="n">
-        <v>0.03758663589692035</v>
+        <v>0.03758663589692039</v>
       </c>
       <c r="X4" t="n">
-        <v>0.09006132485469065</v>
+        <v>0.09006132485469071</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.06650888789221937</v>
+        <v>0.06650888789221936</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.02008972873897237</v>
+        <v>0.02008972873897234</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0394189965535986</v>
+        <v>0.03941899655359865</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1095882607136976</v>
+        <v>0.1095882607136973</v>
       </c>
     </row>
     <row r="5">
@@ -5618,25 +5618,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.009695147033321538</v>
+        <v>0.009695147033321539</v>
       </c>
       <c r="C5" t="n">
         <v>0.01033701715943071</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01155558084428079</v>
+        <v>0.0115555808442808</v>
       </c>
       <c r="E5" t="n">
-        <v>0.009927527444257015</v>
+        <v>0.009927527444257022</v>
       </c>
       <c r="F5" t="n">
-        <v>0.009452808307050208</v>
+        <v>0.009452808307050215</v>
       </c>
       <c r="G5" t="n">
         <v>0.01155799804811475</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01056311514633022</v>
+        <v>0.01056311514633023</v>
       </c>
       <c r="I5" t="n">
         <v>0.0112393267441995</v>
@@ -5645,16 +5645,16 @@
         <v>0.0116248483067609</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01188408909221155</v>
+        <v>0.01188408909221156</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01223061582673939</v>
+        <v>0.0122306158267394</v>
       </c>
       <c r="M5" t="n">
         <v>0.01590511919288897</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03636151530000755</v>
+        <v>0.01056368234788048</v>
       </c>
       <c r="O5" t="n">
         <v>0.01008757196321063</v>
@@ -5663,7 +5663,7 @@
         <v>0.01026483739510241</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.009022294999597445</v>
+        <v>0.009022294999597448</v>
       </c>
       <c r="R5" t="n">
         <v>0.01069340617988341</v>
@@ -5672,10 +5672,10 @@
         <v>0.0111912437806644</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01113877262338656</v>
+        <v>0.01113877262338655</v>
       </c>
       <c r="U5" t="n">
-        <v>0.01269511690030358</v>
+        <v>0.01269511690030359</v>
       </c>
       <c r="V5" t="n">
         <v>0.01015869601924325</v>
@@ -5684,19 +5684,19 @@
         <v>0.01172882929971009</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01283260619004557</v>
+        <v>0.01283260619004558</v>
       </c>
       <c r="Y5" t="n">
         <v>0.0146669859875833</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.00945308860062629</v>
+        <v>0.009453088600626301</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01182820286817095</v>
+        <v>0.01182820286817096</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.01649306560028645</v>
+        <v>0.01649306560028646</v>
       </c>
     </row>
     <row r="6">
@@ -5706,7 +5706,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.009788775162097101</v>
+        <v>0.009788775162097106</v>
       </c>
       <c r="C6" t="n">
         <v>0.009675218750141976</v>
@@ -5715,22 +5715,22 @@
         <v>0.01089378243499206</v>
       </c>
       <c r="E6" t="n">
-        <v>0.009857441303135895</v>
+        <v>0.009857441303135893</v>
       </c>
       <c r="F6" t="n">
-        <v>0.008511112443911222</v>
+        <v>0.008511112443911223</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01060932307747496</v>
+        <v>0.01060932307747497</v>
       </c>
       <c r="H6" t="n">
-        <v>0.009901316737041494</v>
+        <v>0.009901316737041506</v>
       </c>
       <c r="I6" t="n">
         <v>0.01057752833491076</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01096304989747217</v>
+        <v>0.01096304989747218</v>
       </c>
       <c r="K6" t="n">
         <v>0.01122229068292283</v>
@@ -5739,22 +5739,22 @@
         <v>0.01156881741745067</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01524332078359997</v>
+        <v>0.01524332078359998</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03636151530000755</v>
+        <v>0.01097431985390537</v>
       </c>
       <c r="O6" t="n">
         <v>0.01041163275689284</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01070640653680251</v>
+        <v>0.0107064065368025</v>
       </c>
       <c r="Q6" t="n">
         <v>0.01001587253392761</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01003160777059468</v>
+        <v>0.01003160777059467</v>
       </c>
       <c r="S6" t="n">
         <v>0.01052944537137569</v>
@@ -5763,10 +5763,10 @@
         <v>0.01047697421409783</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01270904919061347</v>
+        <v>0.01270904919061348</v>
       </c>
       <c r="V6" t="n">
-        <v>0.01060031084032844</v>
+        <v>0.01060031084032842</v>
       </c>
       <c r="W6" t="n">
         <v>0.01106675899509925</v>
@@ -5775,13 +5775,13 @@
         <v>0.01369938512502336</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01263041573155256</v>
+        <v>0.01263041573155257</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.009821812269391822</v>
+        <v>0.009821812269391817</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.01116640445888222</v>
+        <v>0.01116640445888223</v>
       </c>
       <c r="AB6" t="n">
         <v>0.01438609658793824</v>
@@ -5950,28 +5950,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003815093471769073</v>
+        <v>0.003815093471769075</v>
       </c>
       <c r="C2" t="n">
         <v>0.003431928902596503</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003835532269870232</v>
+        <v>0.00383553226987023</v>
       </c>
       <c r="E2" t="n">
         <v>0.003829158159508394</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003821953545793704</v>
+        <v>0.003821953545793703</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00389076489197997</v>
+        <v>0.003890764891979968</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003822140946515482</v>
+        <v>0.003822140946515483</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003828162268963355</v>
+        <v>0.003828162268963354</v>
       </c>
       <c r="J2" t="n">
         <v>0.003882634942977411</v>
@@ -5980,10 +5980,10 @@
         <v>0.00384190546357369</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003885974276522062</v>
+        <v>0.00388597427652206</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003858605717063106</v>
+        <v>0.003858605717063104</v>
       </c>
       <c r="N2" t="n">
         <v>0.003832626041732632</v>
@@ -5992,16 +5992,16 @@
         <v>0.005523270456218043</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003869121239336907</v>
+        <v>0.003869121239336905</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003829902864543988</v>
+        <v>0.003829902864543986</v>
       </c>
       <c r="R2" t="n">
         <v>0.003839887786001724</v>
       </c>
       <c r="S2" t="n">
-        <v>0.00383979326981827</v>
+        <v>0.003839793269818268</v>
       </c>
       <c r="T2" t="n">
         <v>0.003823504117119588</v>
@@ -6013,22 +6013,22 @@
         <v>0.003825135941918611</v>
       </c>
       <c r="W2" t="n">
-        <v>0.003781652881277615</v>
+        <v>0.003781652881277614</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004203549079402722</v>
+        <v>0.004203549079402723</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.004308466012889062</v>
+        <v>0.004308466012889061</v>
       </c>
       <c r="Z2" t="n">
         <v>0.00481678610815699</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003852466330550857</v>
+        <v>0.003852466330550856</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.006556942306285837</v>
+        <v>0.006556942306285838</v>
       </c>
     </row>
     <row r="3">
@@ -6038,85 +6038,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004691950877700864</v>
+        <v>0.003749143810371152</v>
       </c>
       <c r="C3" t="n">
-        <v>0.004382732636459308</v>
+        <v>0.003391988060686475</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005171477378843212</v>
+        <v>0.003917053769417108</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006059919782674539</v>
+        <v>0.004910912699133498</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004856012514782982</v>
+        <v>0.003808295606431562</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006433469035022408</v>
+        <v>0.004325399043310616</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004861215926916006</v>
+        <v>0.003812167474860497</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005000408884898917</v>
+        <v>0.003859208467980952</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006259652670801854</v>
+        <v>0.004284185055739237</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005318399089213869</v>
+        <v>0.003961407867361467</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006332278308159851</v>
+        <v>0.004297654922614762</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0057257384947631</v>
+        <v>0.004101266552910119</v>
       </c>
       <c r="N3" t="n">
-        <v>0.005101610611835602</v>
+        <v>0.003892496405601215</v>
       </c>
       <c r="O3" t="n">
-        <v>0.006660762809264209</v>
+        <v>0.005536844974986127</v>
       </c>
       <c r="P3" t="n">
-        <v>0.005933497407992303</v>
+        <v>0.004167064252371622</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.005038455635402885</v>
+        <v>0.003866843016439511</v>
       </c>
       <c r="R3" t="n">
-        <v>0.005276015511539361</v>
+        <v>0.003956811640431382</v>
       </c>
       <c r="S3" t="n">
-        <v>0.005262075408995775</v>
+        <v>0.00393859236772727</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0048910610986718</v>
+        <v>0.003820602032382518</v>
       </c>
       <c r="U3" t="n">
-        <v>0.00565534043608935</v>
+        <v>0.004042538473818948</v>
       </c>
       <c r="V3" t="n">
-        <v>0.004923727986340189</v>
+        <v>0.003827651299753103</v>
       </c>
       <c r="W3" t="n">
-        <v>0.005783201546693152</v>
+        <v>0.004071726983975052</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01374893082007536</v>
+        <v>0.006859227838507739</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01614875762928574</v>
+        <v>0.007685484861071555</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.006041520708046456</v>
+        <v>0.004855958784954804</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.005560751338648338</v>
+        <v>0.004049949832617023</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.06789052675122108</v>
+        <v>0.02600510603217809</v>
       </c>
     </row>
     <row r="4">
@@ -6126,16 +6126,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009024389465172701</v>
+        <v>0.009024389465172703</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009905021365644249</v>
+        <v>0.009905021365644253</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01340553580351302</v>
+        <v>0.01340553580351303</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0111138595427493</v>
+        <v>0.01111385954274931</v>
       </c>
       <c r="F4" t="n">
         <v>0.01068047917303074</v>
@@ -6144,19 +6144,19 @@
         <v>0.02220354943221051</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01087830711769699</v>
+        <v>0.010878307117697</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01200693552074957</v>
+        <v>0.01200693552074958</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02217377279052184</v>
+        <v>0.02217377279052183</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01423040549160956</v>
+        <v>0.01423040549160955</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02195055278447081</v>
+        <v>0.02195055278447082</v>
       </c>
       <c r="M4" t="n">
         <v>0.01782492890899357</v>
@@ -6165,7 +6165,7 @@
         <v>0.01273869717951992</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01116442084435912</v>
+        <v>0.01116442084435915</v>
       </c>
       <c r="P4" t="n">
         <v>0.01887880739625657</v>
@@ -6174,7 +6174,7 @@
         <v>0.01193025961947197</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01460643884897797</v>
+        <v>0.01460643884897798</v>
       </c>
       <c r="S4" t="n">
         <v>0.01341584295181783</v>
@@ -6186,16 +6186,16 @@
         <v>0.01710454133796101</v>
       </c>
       <c r="V4" t="n">
-        <v>0.01088705019356411</v>
+        <v>0.0108870501935641</v>
       </c>
       <c r="W4" t="n">
-        <v>0.01926703494571607</v>
+        <v>0.01926703494571606</v>
       </c>
       <c r="X4" t="n">
-        <v>0.08684830277292042</v>
+        <v>0.08684830277292044</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1070028797542556</v>
+        <v>0.1070028797542555</v>
       </c>
       <c r="Z4" t="n">
         <v>0.01182060455924124</v>
@@ -6214,31 +6214,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.008597663809960188</v>
+        <v>0.008597663809960191</v>
       </c>
       <c r="C5" t="n">
-        <v>0.009871983102791353</v>
+        <v>0.009871983102791354</v>
       </c>
       <c r="D5" t="n">
         <v>0.01006665555287922</v>
       </c>
       <c r="E5" t="n">
-        <v>0.009335391409744145</v>
+        <v>0.009335391409744149</v>
       </c>
       <c r="F5" t="n">
-        <v>0.008868037080454014</v>
+        <v>0.008868037080454015</v>
       </c>
       <c r="G5" t="n">
         <v>0.01094726694367515</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00991539439527429</v>
+        <v>0.009915394395274292</v>
       </c>
       <c r="I5" t="n">
-        <v>0.009983408002268164</v>
+        <v>0.009983408002268169</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01059519489188518</v>
+        <v>0.01059519489188519</v>
       </c>
       <c r="K5" t="n">
         <v>0.01013864370757376</v>
@@ -6250,16 +6250,16 @@
         <v>0.01033392356405862</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01273869717951992</v>
+        <v>0.009074073495203734</v>
       </c>
       <c r="O5" t="n">
-        <v>0.00927370024313986</v>
+        <v>0.009273700243139863</v>
       </c>
       <c r="P5" t="n">
-        <v>0.009685401267237832</v>
+        <v>0.009685401267237831</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.008521622673357836</v>
+        <v>0.00852162267335784</v>
       </c>
       <c r="R5" t="n">
         <v>0.01011585311122086</v>
@@ -6268,13 +6268,13 @@
         <v>0.01011478550744914</v>
       </c>
       <c r="T5" t="n">
-        <v>0.009930792034337119</v>
+        <v>0.009930792034337124</v>
       </c>
       <c r="U5" t="n">
-        <v>0.009723642352769544</v>
+        <v>0.00972364235276954</v>
       </c>
       <c r="V5" t="n">
-        <v>0.009586349842708574</v>
+        <v>0.009586349842708579</v>
       </c>
       <c r="W5" t="n">
         <v>0.01040777518397225</v>
@@ -6283,16 +6283,16 @@
         <v>0.01285560527466684</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.01663850213096968</v>
+        <v>0.01663850213096969</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.008752968453863494</v>
+        <v>0.008752968453863497</v>
       </c>
       <c r="AA5" t="n">
         <v>0.0102579335583197</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.04167020647335134</v>
+        <v>0.04167020647335133</v>
       </c>
     </row>
     <row r="6">
@@ -6302,49 +6302,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.008516374226646759</v>
+        <v>0.008516374226646755</v>
       </c>
       <c r="C6" t="n">
-        <v>0.009068985620523469</v>
+        <v>0.009068985620523468</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009263658070611337</v>
+        <v>0.009263658070611332</v>
       </c>
       <c r="E6" t="n">
-        <v>0.009072471984020334</v>
+        <v>0.009072471984020333</v>
       </c>
       <c r="F6" t="n">
-        <v>0.007919795811778582</v>
+        <v>0.007919795811778587</v>
       </c>
       <c r="G6" t="n">
         <v>0.009887535477919821</v>
       </c>
       <c r="H6" t="n">
-        <v>0.009112396913006396</v>
+        <v>0.0091123969130064</v>
       </c>
       <c r="I6" t="n">
-        <v>0.009180410520000279</v>
+        <v>0.009180410520000275</v>
       </c>
       <c r="J6" t="n">
-        <v>0.009792197409617301</v>
+        <v>0.009792197409617299</v>
       </c>
       <c r="K6" t="n">
-        <v>0.009335646225305876</v>
+        <v>0.009335646225305872</v>
       </c>
       <c r="L6" t="n">
-        <v>0.009833423740213272</v>
+        <v>0.00983342374021327</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0095309260817907</v>
+        <v>0.009530926081790698</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01273869717951992</v>
+        <v>0.009230830886866211</v>
       </c>
       <c r="O6" t="n">
-        <v>0.009337848360318016</v>
+        <v>0.009337848360318014</v>
       </c>
       <c r="P6" t="n">
-        <v>0.009851420680536923</v>
+        <v>0.009851420680536922</v>
       </c>
       <c r="Q6" t="n">
         <v>0.009200070880114614</v>
@@ -6353,16 +6353,16 @@
         <v>0.009312855628952973</v>
       </c>
       <c r="S6" t="n">
-        <v>0.009311788025181253</v>
+        <v>0.009311788025181249</v>
       </c>
       <c r="T6" t="n">
-        <v>0.009127794552069234</v>
+        <v>0.009127794552069232</v>
       </c>
       <c r="U6" t="n">
-        <v>0.009525658128723292</v>
+        <v>0.00952565812872329</v>
       </c>
       <c r="V6" t="n">
-        <v>0.009718457604168894</v>
+        <v>0.009718457604168895</v>
       </c>
       <c r="W6" t="n">
         <v>0.009604534374449386</v>
@@ -6371,16 +6371,16 @@
         <v>0.0134205772303774</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01460566225827953</v>
+        <v>0.01460566225827952</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.00889974146698678</v>
+        <v>0.008899741466986778</v>
       </c>
       <c r="AA6" t="n">
         <v>0.009454936076051811</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.03957388273243543</v>
+        <v>0.03957388273243544</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia acidification results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia acidification results.xlsx
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00515152929541813</v>
+        <v>0.00475630154616578</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00371279020737122</v>
+        <v>0.003611429915116802</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00529962234951566</v>
+        <v>0.004822059884195935</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005393043648383875</v>
+        <v>0.005224518390542061</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004686189517275222</v>
+        <v>0.004395980501335413</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004671486934643645</v>
+        <v>0.004408744993558373</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004812127672878742</v>
+        <v>0.004477829858602846</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00530084461095746</v>
+        <v>0.004819114426961836</v>
       </c>
       <c r="J3" t="n">
-        <v>0.005075472660864938</v>
+        <v>0.004681546094215711</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006004012370278936</v>
+        <v>0.005309930905468578</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00563315734334752</v>
+        <v>0.005073457693996074</v>
       </c>
       <c r="M3" t="n">
-        <v>0.008503558120233914</v>
+        <v>0.007012653098963048</v>
       </c>
       <c r="N3" t="n">
-        <v>0.005369554879105863</v>
+        <v>0.004880133074950263</v>
       </c>
       <c r="O3" t="n">
-        <v>0.006606646813028761</v>
+        <v>0.006321971522704535</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004514997433798235</v>
+        <v>0.004299722841595393</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.00458107283352896</v>
+        <v>0.004331920823817347</v>
       </c>
       <c r="R3" t="n">
-        <v>0.004616608801662004</v>
+        <v>0.00434837172205766</v>
       </c>
       <c r="S3" t="n">
-        <v>0.005000041560708876</v>
+        <v>0.004640524242714765</v>
       </c>
       <c r="T3" t="n">
-        <v>0.005284292984731221</v>
+        <v>0.004810250799350538</v>
       </c>
       <c r="U3" t="n">
-        <v>0.006797798874289068</v>
+        <v>0.005913143429587232</v>
       </c>
       <c r="V3" t="n">
-        <v>0.004376589936776094</v>
+        <v>0.004201521724515688</v>
       </c>
       <c r="W3" t="n">
-        <v>0.005586451612618704</v>
+        <v>0.005038964282256941</v>
       </c>
       <c r="X3" t="n">
-        <v>0.005746144178270253</v>
+        <v>0.005134495121420642</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.00637137918360827</v>
+        <v>0.005584832578054595</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.005552858742182467</v>
+        <v>0.005334648969529088</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.005611997600082292</v>
+        <v>0.005052811276656849</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.008149614160138607</v>
+        <v>0.006741058752345005</v>
       </c>
     </row>
     <row r="4">
@@ -1270,85 +1270,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003645437931717802</v>
+        <v>0.003617560132961736</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003254891475071838</v>
+        <v>0.003216879528596969</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003698373836111406</v>
+        <v>0.003652833500733288</v>
       </c>
       <c r="E3" t="n">
-        <v>0.004758084806269655</v>
+        <v>0.004725266428994807</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003729232529432313</v>
+        <v>0.003673940144700154</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003743012258851792</v>
+        <v>0.00368767011936538</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003717151294123178</v>
+        <v>0.003664239608628296</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003718247686800112</v>
+        <v>0.003666184723761092</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003812627613354594</v>
+        <v>0.003735258459715881</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003784797951092578</v>
+        <v>0.003715297096590988</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003816651944818877</v>
+        <v>0.00373952824445754</v>
       </c>
       <c r="M3" t="n">
-        <v>0.00375962569811083</v>
+        <v>0.00369471511734311</v>
       </c>
       <c r="N3" t="n">
-        <v>0.00373563313424038</v>
+        <v>0.003679178473702394</v>
       </c>
       <c r="O3" t="n">
-        <v>0.005430953645662738</v>
+        <v>0.005372930408165264</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003755189077419045</v>
+        <v>0.003696871156067111</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003689370185468795</v>
+        <v>0.003647578810999362</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003842691660254049</v>
+        <v>0.003750893432009013</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003783824627555818</v>
+        <v>0.003717096473992295</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003716899357767079</v>
+        <v>0.003665369732168272</v>
       </c>
       <c r="U3" t="n">
-        <v>0.003720972595476393</v>
+        <v>0.003627881307970526</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0037811871979622</v>
+        <v>0.00371496154958483</v>
       </c>
       <c r="W3" t="n">
-        <v>0.003667728913219776</v>
+        <v>0.003578707767957667</v>
       </c>
       <c r="X3" t="n">
-        <v>0.006988269134142067</v>
+        <v>0.005969472607439716</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.005642090019997978</v>
+        <v>0.005004409670355869</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.004764448675527013</v>
+        <v>0.004702295161838431</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.004051244664849631</v>
+        <v>0.003899384593925172</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.003688428570678786</v>
+        <v>0.003644399595497629</v>
       </c>
     </row>
     <row r="4">
@@ -1866,85 +1866,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004826218337655414</v>
+        <v>0.004510646555299536</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003632614309333131</v>
+        <v>0.003540500744855535</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005289354453230694</v>
+        <v>0.004798934070973262</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005288063476289751</v>
+        <v>0.005138717994832641</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00428930979062243</v>
+        <v>0.004111111136566731</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004572360779198234</v>
+        <v>0.004324965944399106</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004077897180576674</v>
+        <v>0.003963523813674098</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00455723867279136</v>
+        <v>0.004293863060321729</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004959692875032621</v>
+        <v>0.004585191615198104</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005613155585371078</v>
+        <v>0.005050683489102076</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005442854479073752</v>
+        <v>0.0049249599879095</v>
       </c>
       <c r="M3" t="n">
-        <v>0.008081729711380502</v>
+        <v>0.006712523438492563</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004695869810626372</v>
+        <v>0.004397245481821942</v>
       </c>
       <c r="O3" t="n">
-        <v>0.006294229364562831</v>
+        <v>0.006073627841014481</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004537739820173939</v>
+        <v>0.004301406051675558</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.004291742694354504</v>
+        <v>0.004116490560246356</v>
       </c>
       <c r="R3" t="n">
-        <v>0.004110550995234503</v>
+        <v>0.003987024714854306</v>
       </c>
       <c r="S3" t="n">
-        <v>0.004920681346826813</v>
+        <v>0.004571586287564775</v>
       </c>
       <c r="T3" t="n">
-        <v>0.004831902584980189</v>
+        <v>0.004484861521313669</v>
       </c>
       <c r="U3" t="n">
-        <v>0.006428553925066605</v>
+        <v>0.005626438956106801</v>
       </c>
       <c r="V3" t="n">
-        <v>0.00411082525408201</v>
+        <v>0.003999206387867785</v>
       </c>
       <c r="W3" t="n">
-        <v>0.005343317813979133</v>
+        <v>0.004841978031949404</v>
       </c>
       <c r="X3" t="n">
-        <v>0.006072224272774983</v>
+        <v>0.005346018786647459</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.005992630551992458</v>
+        <v>0.005310163073954306</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.005354608948576971</v>
+        <v>0.005175372695753898</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.005111576656976551</v>
+        <v>0.004691195942028261</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.007928198472500618</v>
+        <v>0.006573719687161633</v>
       </c>
     </row>
     <row r="4">
@@ -2462,85 +2462,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004593885585338243</v>
+        <v>0.004340745240698558</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003560937073967522</v>
+        <v>0.003489684711914426</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005521294104028363</v>
+        <v>0.004960693741391984</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00528467353917726</v>
+        <v>0.005135250759845194</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004273256431274553</v>
+        <v>0.004100425254231116</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004508038126905547</v>
+        <v>0.00428042180933939</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00387750829083961</v>
+        <v>0.003826306137267302</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004849303387680275</v>
+        <v>0.0044935782950734</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004941666236826317</v>
+        <v>0.004571900289608097</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005209693653382017</v>
+        <v>0.004778954300844869</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005168742703521662</v>
+        <v>0.004733669094373102</v>
       </c>
       <c r="M3" t="n">
-        <v>0.00749413432278364</v>
+        <v>0.006306833878787491</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004382490069911134</v>
+        <v>0.004178586399615412</v>
       </c>
       <c r="O3" t="n">
-        <v>0.006084317799633349</v>
+        <v>0.005915820530957377</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004461730417740986</v>
+        <v>0.004247904598928745</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.004199115701805316</v>
+        <v>0.004052908009616871</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003927961722490402</v>
+        <v>0.003861418333095633</v>
       </c>
       <c r="S3" t="n">
-        <v>0.004810315634136852</v>
+        <v>0.004494048247679068</v>
       </c>
       <c r="T3" t="n">
-        <v>0.004722608626364471</v>
+        <v>0.004408190509794036</v>
       </c>
       <c r="U3" t="n">
-        <v>0.006074130587293463</v>
+        <v>0.005380192809932625</v>
       </c>
       <c r="V3" t="n">
-        <v>0.004192301335598606</v>
+        <v>0.004057924082174647</v>
       </c>
       <c r="W3" t="n">
-        <v>0.005170950507847711</v>
+        <v>0.004718975523021216</v>
       </c>
       <c r="X3" t="n">
-        <v>0.008252730694837587</v>
+        <v>0.006856608981202488</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.008201366154294731</v>
+        <v>0.006852153463703358</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.00532934763307405</v>
+        <v>0.005161479527572714</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.005131795847795091</v>
+        <v>0.004703487925520639</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.007668323588068038</v>
+        <v>0.006393312187478102</v>
       </c>
     </row>
     <row r="4">
@@ -3058,85 +3058,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004450570645492194</v>
+        <v>0.004240242295129216</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003512455522391808</v>
+        <v>0.003441938566019737</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004969684925660234</v>
+        <v>0.004587804070884886</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005133966648388601</v>
+        <v>0.005032515873950779</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004335053091260115</v>
+        <v>0.004141254571418103</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004405534942492722</v>
+        <v>0.004208542240552228</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003869253145486795</v>
+        <v>0.003817809611420968</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004829303445796172</v>
+        <v>0.004480898032293482</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004883832316917314</v>
+        <v>0.004534405187648553</v>
       </c>
       <c r="K3" t="n">
-        <v>0.005459985802546397</v>
+        <v>0.004954565439311659</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004914085387597835</v>
+        <v>0.004561474797849866</v>
       </c>
       <c r="M3" t="n">
-        <v>0.006786973806797626</v>
+        <v>0.005846054060777188</v>
       </c>
       <c r="N3" t="n">
-        <v>0.00416659216982911</v>
+        <v>0.004025947988795171</v>
       </c>
       <c r="O3" t="n">
-        <v>0.005913828180256223</v>
+        <v>0.005785392851620231</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004343612030657672</v>
+        <v>0.004164617051204141</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.00419219867985301</v>
+        <v>0.004047402831324989</v>
       </c>
       <c r="R3" t="n">
-        <v>0.004087152947867665</v>
+        <v>0.003967077670023685</v>
       </c>
       <c r="S3" t="n">
-        <v>0.004739134355799631</v>
+        <v>0.004443416051689507</v>
       </c>
       <c r="T3" t="n">
-        <v>0.004713783619791819</v>
+        <v>0.004399074782006483</v>
       </c>
       <c r="U3" t="n">
-        <v>0.006101960115896491</v>
+        <v>0.005383124381328509</v>
       </c>
       <c r="V3" t="n">
-        <v>0.004413820121079091</v>
+        <v>0.00421685263585543</v>
       </c>
       <c r="W3" t="n">
-        <v>0.004833810123964053</v>
+        <v>0.004452139952888987</v>
       </c>
       <c r="X3" t="n">
-        <v>0.009085249745800428</v>
+        <v>0.007465129821260874</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01065465025162291</v>
+        <v>0.00853571664537694</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.005236694335935138</v>
+        <v>0.005095155428158253</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.005219933915103116</v>
+        <v>0.004760530292314878</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.007187566437449341</v>
+        <v>0.006075337542360375</v>
       </c>
     </row>
     <row r="4">
@@ -3654,85 +3654,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003836692141960599</v>
+        <v>0.003769104357956635</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003298393350814779</v>
+        <v>0.003272689723286423</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004269650916335821</v>
+        <v>0.004062927367989487</v>
       </c>
       <c r="E3" t="n">
-        <v>0.004946791051540302</v>
+        <v>0.004868360574808307</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003784132102011661</v>
+        <v>0.003727259949608121</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003914777889891237</v>
+        <v>0.003826814967817229</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003902710439646436</v>
+        <v>0.00380655500581501</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004009950927415004</v>
+        <v>0.003882410501360673</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00408974863422168</v>
+        <v>0.0039470032114954</v>
       </c>
       <c r="K3" t="n">
-        <v>0.004436748965008457</v>
+        <v>0.004192668459622574</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004217394669128313</v>
+        <v>0.004044666212233724</v>
       </c>
       <c r="M3" t="n">
-        <v>0.004991656881840892</v>
+        <v>0.004582795816363712</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004211109353164469</v>
+        <v>0.00402806994782425</v>
       </c>
       <c r="O3" t="n">
-        <v>0.005534156154405423</v>
+        <v>0.005466500861111466</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004032169627851554</v>
+        <v>0.003908249563403318</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003937432472392199</v>
+        <v>0.003836894234303158</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003878038754470794</v>
+        <v>0.003790652847421511</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003950558747834509</v>
+        <v>0.003855239131603985</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003898472124101652</v>
+        <v>0.003807741963462998</v>
       </c>
       <c r="U3" t="n">
-        <v>0.004670796013773106</v>
+        <v>0.004348841403691328</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003796228048443792</v>
+        <v>0.00373964778991033</v>
       </c>
       <c r="W3" t="n">
-        <v>0.004372498003539699</v>
+        <v>0.004116832257986879</v>
       </c>
       <c r="X3" t="n">
-        <v>0.004387393630896066</v>
+        <v>0.004146390985627578</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.004041351561861444</v>
+        <v>0.003909116166738828</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.004956400970005292</v>
+        <v>0.004856891701540103</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.004334240197894781</v>
+        <v>0.00411303296414596</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.007733924500992843</v>
+        <v>0.006439407768562327</v>
       </c>
     </row>
     <row r="4">
@@ -4250,85 +4250,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003688331776833909</v>
+        <v>0.003650537744710968</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00333379991498539</v>
+        <v>0.003285703149765216</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00379794353484149</v>
+        <v>0.003725318667055274</v>
       </c>
       <c r="E3" t="n">
-        <v>0.004824819817265937</v>
+        <v>0.004771546879429921</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003754944131536926</v>
+        <v>0.00369446952252107</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003738262903569554</v>
+        <v>0.003686795864377204</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003767182812172331</v>
+        <v>0.003700904476101842</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003767372750022266</v>
+        <v>0.003702739630282036</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003786283258487505</v>
+        <v>0.003719691943711237</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003747147009332521</v>
+        <v>0.003690351229401641</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003764931575999231</v>
+        <v>0.003706298214679351</v>
       </c>
       <c r="M3" t="n">
-        <v>0.003709943250083105</v>
+        <v>0.003662713264952313</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003768215072500601</v>
+        <v>0.003705554681727383</v>
       </c>
       <c r="O3" t="n">
-        <v>0.005452376224093745</v>
+        <v>0.005390250348731751</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003764089742400878</v>
+        <v>0.003705050762062595</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003683341532107047</v>
+        <v>0.00364597289636686</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003858459849945844</v>
+        <v>0.0037647840483272</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003782610799517542</v>
+        <v>0.003720019040478735</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003693890742039435</v>
+        <v>0.003651907317594457</v>
       </c>
       <c r="U3" t="n">
-        <v>0.003646056310483159</v>
+        <v>0.003604512038322188</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003770770319384059</v>
+        <v>0.003709908626311452</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0038280782256825</v>
+        <v>0.00372184938027437</v>
       </c>
       <c r="X3" t="n">
-        <v>0.005032621653378986</v>
+        <v>0.004598038662836747</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.00457664812339397</v>
+        <v>0.004268922552867977</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.004805231302770513</v>
+        <v>0.004733978995849864</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003944072168050651</v>
+        <v>0.003827763207110225</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.003650942514343768</v>
+        <v>0.003621166415305028</v>
       </c>
     </row>
     <row r="4">
@@ -4846,85 +4846,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003714962694258035</v>
+        <v>0.003665312296943972</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003280097497038697</v>
+        <v>0.003232536855170037</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003759174940272168</v>
+        <v>0.003693125295261187</v>
       </c>
       <c r="E3" t="n">
-        <v>0.004869424561428064</v>
+        <v>0.004803857690826978</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003729655685804558</v>
+        <v>0.003671708435838738</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003698743826912532</v>
+        <v>0.003653547169948862</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003716980437430296</v>
+        <v>0.003661833830464645</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003714095357623563</v>
+        <v>0.003660991369030648</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003761025231701316</v>
+        <v>0.003696805488094616</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003706534888088017</v>
+        <v>0.003656713428857249</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00375938335803751</v>
+        <v>0.003697244634264877</v>
       </c>
       <c r="M3" t="n">
-        <v>0.00369280797388931</v>
+        <v>0.003645909926262251</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003710954396058455</v>
+        <v>0.003660313778695303</v>
       </c>
       <c r="O3" t="n">
-        <v>0.005501331471752174</v>
+        <v>0.005422169088563432</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003771033382801671</v>
+        <v>0.003706290957894361</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003670826867055884</v>
+        <v>0.003632337913086556</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003846431456956085</v>
+        <v>0.003751280517940058</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003751719041709387</v>
+        <v>0.003691991648830393</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003673597024412481</v>
+        <v>0.003633164555040814</v>
       </c>
       <c r="U3" t="n">
-        <v>0.00353280515800499</v>
+        <v>0.003488235165392973</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003790743770065946</v>
+        <v>0.003719707594408686</v>
       </c>
       <c r="W3" t="n">
-        <v>0.003650436098252763</v>
+        <v>0.0035639380256175</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00542739517561293</v>
+        <v>0.004877913494708245</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.004463264052520089</v>
+        <v>0.004182935750721319</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.004745885327155073</v>
+        <v>0.004686175750400917</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003940454486508737</v>
+        <v>0.003820378848428258</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.003675283116742241</v>
+        <v>0.003633176668140904</v>
       </c>
     </row>
     <row r="4">
@@ -5442,85 +5442,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004366280067102815</v>
+        <v>0.004173126473484574</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003475080729496193</v>
+        <v>0.00342096085593859</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004745059517807395</v>
+        <v>0.0044148631229862</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005132378343152526</v>
+        <v>0.005021187642446015</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004069504862276682</v>
+        <v>0.003950753994741352</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00449596055614856</v>
+        <v>0.004267397631206144</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004033120031995493</v>
+        <v>0.003922834435972172</v>
       </c>
       <c r="I3" t="n">
-        <v>0.004517057053468339</v>
+        <v>0.004257961729432467</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004761797043130367</v>
+        <v>0.004446112031063508</v>
       </c>
       <c r="K3" t="n">
-        <v>0.004933606040232864</v>
+        <v>0.004571504126312763</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005181054731163411</v>
+        <v>0.004742669175528582</v>
       </c>
       <c r="M3" t="n">
-        <v>0.007778985960529346</v>
+        <v>0.00656443707528221</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004790098994630254</v>
+        <v>0.004452936039663867</v>
       </c>
       <c r="O3" t="n">
-        <v>0.005969331374650358</v>
+        <v>0.005820685007856884</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004396050471660818</v>
+        <v>0.004191485268986765</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.004103868123043151</v>
+        <v>0.003978011785064406</v>
       </c>
       <c r="R3" t="n">
-        <v>0.004126101281968868</v>
+        <v>0.003987355950800449</v>
       </c>
       <c r="S3" t="n">
-        <v>0.004437330153289265</v>
+        <v>0.00422773201046274</v>
       </c>
       <c r="T3" t="n">
-        <v>0.004443432264404476</v>
+        <v>0.004207862686554871</v>
       </c>
       <c r="U3" t="n">
-        <v>0.005962083805573721</v>
+        <v>0.005285851086223456</v>
       </c>
       <c r="V3" t="n">
-        <v>0.004012551570844941</v>
+        <v>0.003919580908781914</v>
       </c>
       <c r="W3" t="n">
-        <v>0.00478953884382588</v>
+        <v>0.004438874705738962</v>
       </c>
       <c r="X3" t="n">
-        <v>0.006749611360083238</v>
+        <v>0.005804846547047841</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.005946340391841541</v>
+        <v>0.00526957097265774</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.005229824534133452</v>
+        <v>0.005077391893157824</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.004918055367050049</v>
+        <v>0.004546737844909813</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.007330262971706303</v>
+        <v>0.006160929001720865</v>
       </c>
     </row>
     <row r="4">
@@ -6038,85 +6038,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003749143810371152</v>
+        <v>0.003718758395573584</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003391988060686475</v>
+        <v>0.003350800555977182</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003917053769417108</v>
+        <v>0.00383357781750148</v>
       </c>
       <c r="E3" t="n">
-        <v>0.004910912699133498</v>
+        <v>0.004855830943243302</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003808295606431562</v>
+        <v>0.003757716659015531</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004325399043310616</v>
+        <v>0.004137359258775102</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003812167474860497</v>
+        <v>0.003759084983295392</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003859208467980952</v>
+        <v>0.003792558554568348</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004284185055739237</v>
+        <v>0.004095306601141474</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003961407867361467</v>
+        <v>0.003868301028338838</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004297654922614762</v>
+        <v>0.004112159274874537</v>
       </c>
       <c r="M3" t="n">
-        <v>0.004101266552910119</v>
+        <v>0.003964676470466324</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003892496405601215</v>
+        <v>0.003817130750371946</v>
       </c>
       <c r="O3" t="n">
-        <v>0.005536844974986127</v>
+        <v>0.005480797264354369</v>
       </c>
       <c r="P3" t="n">
-        <v>0.004167064252371622</v>
+        <v>0.004018427352140826</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.003866843016439511</v>
+        <v>0.003801425445860153</v>
       </c>
       <c r="R3" t="n">
-        <v>0.003956811640431382</v>
+        <v>0.003858603031338092</v>
       </c>
       <c r="S3" t="n">
-        <v>0.00393859236772727</v>
+        <v>0.003855600246482266</v>
       </c>
       <c r="T3" t="n">
-        <v>0.003820602032382518</v>
+        <v>0.003766345683579464</v>
       </c>
       <c r="U3" t="n">
-        <v>0.004042538473818948</v>
+        <v>0.003915096226729143</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003827651299753103</v>
+        <v>0.003774586505421414</v>
       </c>
       <c r="W3" t="n">
-        <v>0.004071726983975052</v>
+        <v>0.003917631030163016</v>
       </c>
       <c r="X3" t="n">
-        <v>0.006859227838507739</v>
+        <v>0.00588944487976165</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.007685484861071555</v>
+        <v>0.006473043492767813</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.004855958784954804</v>
+        <v>0.004792084952434004</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.004049949832617023</v>
+        <v>0.003927751378569443</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.02600510603217809</v>
+        <v>0.01894142012151382</v>
       </c>
     </row>
     <row r="4">
